--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -37934,7 +37934,7 @@
     <row r="2150">
       <c r="A2150" t="inlineStr">
         <is>
-          <t>Son güncelleme: 07.08.2026 18:31</t>
+          <t>Son güncelleme: 08.08.2026 10:40</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -37934,7 +37934,7 @@
     <row r="2150">
       <c r="A2150" t="inlineStr">
         <is>
-          <t>Son güncelleme: 08.08.2026 10:40</t>
+          <t>Son güncelleme: 09.08.2026 11:01</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -37934,7 +37934,7 @@
     <row r="2150">
       <c r="A2150" t="inlineStr">
         <is>
-          <t>Son güncelleme: 09.08.2026 11:01</t>
+          <t>Son güncelleme: 10.08.2026 13:04</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2150"/>
+  <dimension ref="A1:I2151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B222" s="12" t="inlineStr">
         <is>
-          <t>maks: 4.99%</t>
+          <t>maks: 4.49%</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr"/>
@@ -30167,8 +30167,7 @@
       <c r="E1737" s="12" t="inlineStr"/>
       <c r="F1737" s="12" t="inlineStr">
         <is>
-          <t>83 TL / 1.6 %
-maks: 83 TL / 1.6 %</t>
+          <t>6 USD / 1.6 %</t>
         </is>
       </c>
       <c r="G1737" s="12" t="inlineStr"/>
@@ -30813,76 +30812,76 @@
       <c r="H1770" s="12" t="inlineStr"/>
       <c r="I1770" s="12" t="inlineStr"/>
     </row>
-    <row r="1771" ht="16" customHeight="1">
-      <c r="A1771" s="10" t="inlineStr">
+    <row r="1771" ht="32" customHeight="1">
+      <c r="A1771" s="11" t="inlineStr">
+        <is>
+          <t>HGS Kart</t>
+        </is>
+      </c>
+      <c r="B1771" s="12" t="inlineStr"/>
+      <c r="C1771" s="12" t="inlineStr"/>
+      <c r="D1771" s="12" t="inlineStr"/>
+      <c r="E1771" s="12" t="inlineStr"/>
+      <c r="F1771" s="12" t="inlineStr">
+        <is>
+          <t>500 TL
+maks: 500 TL</t>
+        </is>
+      </c>
+      <c r="G1771" s="12" t="inlineStr"/>
+      <c r="H1771" s="12" t="inlineStr"/>
+      <c r="I1771" s="12" t="inlineStr"/>
+    </row>
+    <row r="1772" ht="16" customHeight="1">
+      <c r="A1772" s="10" t="inlineStr">
         <is>
           <t>Kampanyalı Ürün veya Hizmetler Ücreti</t>
         </is>
       </c>
-    </row>
-    <row r="1772" ht="32" customHeight="1">
-      <c r="A1772" s="11" t="inlineStr">
-        <is>
-          <t>Şanj Bürosu Efektif Alış/Satış/Arbitraj İşlemleri</t>
-        </is>
-      </c>
-      <c r="B1772" s="12" t="inlineStr"/>
-      <c r="C1772" s="12" t="inlineStr"/>
-      <c r="D1772" s="12" t="inlineStr"/>
-      <c r="E1772" s="12" t="inlineStr"/>
-      <c r="F1772" s="12" t="inlineStr">
-        <is>
-          <t>maks: 4 %</t>
-        </is>
-      </c>
-      <c r="G1772" s="12" t="inlineStr"/>
-      <c r="H1772" s="12" t="inlineStr"/>
-      <c r="I1772" s="12" t="inlineStr"/>
     </row>
     <row r="1773" ht="32" customHeight="1">
       <c r="A1773" s="11" t="inlineStr">
         <is>
-          <t>KKB Risk Raporu Hizmet Bedeli (Gerçek kişiler için)-Şube</t>
+          <t>Şanj Bürosu Efektif Alış/Satış/Arbitraj İşlemleri</t>
         </is>
       </c>
       <c r="B1773" s="12" t="inlineStr"/>
       <c r="C1773" s="12" t="inlineStr"/>
       <c r="D1773" s="12" t="inlineStr"/>
       <c r="E1773" s="12" t="inlineStr"/>
-      <c r="F1773" s="12" t="inlineStr"/>
-      <c r="G1773" s="12" t="inlineStr">
-        <is>
-          <t>95,24 TL
-maks: 95,24 TL</t>
-        </is>
-      </c>
+      <c r="F1773" s="12" t="inlineStr">
+        <is>
+          <t>maks: 4 %</t>
+        </is>
+      </c>
+      <c r="G1773" s="12" t="inlineStr"/>
       <c r="H1773" s="12" t="inlineStr"/>
       <c r="I1773" s="12" t="inlineStr"/>
     </row>
     <row r="1774" ht="32" customHeight="1">
       <c r="A1774" s="11" t="inlineStr">
         <is>
-          <t>KKB Risk Raporu Hizmet Bedeli (Gerçek kişiler için)-Akbank Mobil</t>
+          <t>KKB Risk Raporu Hizmet Bedeli (Gerçek kişiler için)-Şube</t>
         </is>
       </c>
       <c r="B1774" s="12" t="inlineStr"/>
       <c r="C1774" s="12" t="inlineStr"/>
       <c r="D1774" s="12" t="inlineStr"/>
       <c r="E1774" s="12" t="inlineStr"/>
-      <c r="F1774" s="12" t="inlineStr">
+      <c r="F1774" s="12" t="inlineStr"/>
+      <c r="G1774" s="12" t="inlineStr">
         <is>
           <t>95,24 TL
 maks: 95,24 TL</t>
         </is>
       </c>
-      <c r="G1774" s="12" t="inlineStr"/>
       <c r="H1774" s="12" t="inlineStr"/>
       <c r="I1774" s="12" t="inlineStr"/>
     </row>
     <row r="1775" ht="32" customHeight="1">
       <c r="A1775" s="11" t="inlineStr">
         <is>
-          <t>KKB Risk Raporu Hizmet Bedeli (Gerçek kişiler için)-Akbank İnternet</t>
+          <t>KKB Risk Raporu Hizmet Bedeli (Gerçek kişiler için)-Akbank Mobil</t>
         </is>
       </c>
       <c r="B1775" s="12" t="inlineStr"/>
@@ -30902,7 +30901,7 @@
     <row r="1776" ht="32" customHeight="1">
       <c r="A1776" s="11" t="inlineStr">
         <is>
-          <t>Fiziki Altın Teslim Etme</t>
+          <t>KKB Risk Raporu Hizmet Bedeli (Gerçek kişiler için)-Akbank İnternet</t>
         </is>
       </c>
       <c r="B1776" s="12" t="inlineStr"/>
@@ -30911,7 +30910,8 @@
       <c r="E1776" s="12" t="inlineStr"/>
       <c r="F1776" s="12" t="inlineStr">
         <is>
-          <t>maks: 10 %</t>
+          <t>95,24 TL
+maks: 95,24 TL</t>
         </is>
       </c>
       <c r="G1776" s="12" t="inlineStr"/>
@@ -30921,7 +30921,7 @@
     <row r="1777" ht="32" customHeight="1">
       <c r="A1777" s="11" t="inlineStr">
         <is>
-          <t>DCC İşlemleri</t>
+          <t>Fiziki Altın Teslim Etme</t>
         </is>
       </c>
       <c r="B1777" s="12" t="inlineStr"/>
@@ -30930,8 +30930,7 @@
       <c r="E1777" s="12" t="inlineStr"/>
       <c r="F1777" s="12" t="inlineStr">
         <is>
-          <t>14.98 %
-maks: 19.98 %</t>
+          <t>maks: 10 %</t>
         </is>
       </c>
       <c r="G1777" s="12" t="inlineStr"/>
@@ -30941,7 +30940,7 @@
     <row r="1778" ht="32" customHeight="1">
       <c r="A1778" s="11" t="inlineStr">
         <is>
-          <t>Akbank Direkt Şifreci Cihazı</t>
+          <t>DCC İşlemleri</t>
         </is>
       </c>
       <c r="B1778" s="12" t="inlineStr"/>
@@ -30950,8 +30949,8 @@
       <c r="E1778" s="12" t="inlineStr"/>
       <c r="F1778" s="12" t="inlineStr">
         <is>
-          <t>35 TL
-maks: 35 TL</t>
+          <t>14.98 %
+maks: 19.98 %</t>
         </is>
       </c>
       <c r="G1778" s="12" t="inlineStr"/>
@@ -30961,7 +30960,7 @@
     <row r="1779" ht="32" customHeight="1">
       <c r="A1779" s="11" t="inlineStr">
         <is>
-          <t>Güvenli Ödeme Sistemi</t>
+          <t>Akbank Direkt Şifreci Cihazı</t>
         </is>
       </c>
       <c r="B1779" s="12" t="inlineStr"/>
@@ -30970,23 +30969,18 @@
       <c r="E1779" s="12" t="inlineStr"/>
       <c r="F1779" s="12" t="inlineStr">
         <is>
-          <t>243,84 TL
-maks: 243,84 TL</t>
+          <t>35 TL
+maks: 35 TL</t>
         </is>
       </c>
       <c r="G1779" s="12" t="inlineStr"/>
-      <c r="H1779" s="12" t="inlineStr">
-        <is>
-          <t>97,53 TL / -
-maks: 97,53 TL / -</t>
-        </is>
-      </c>
+      <c r="H1779" s="12" t="inlineStr"/>
       <c r="I1779" s="12" t="inlineStr"/>
     </row>
     <row r="1780" ht="32" customHeight="1">
       <c r="A1780" s="11" t="inlineStr">
         <is>
-          <t>Garantili Ödeme Sistemi</t>
+          <t>Güvenli Ödeme Sistemi</t>
         </is>
       </c>
       <c r="B1780" s="12" t="inlineStr"/>
@@ -30995,14 +30989,15 @@
       <c r="E1780" s="12" t="inlineStr"/>
       <c r="F1780" s="12" t="inlineStr">
         <is>
-          <t>0,002 %</t>
+          <t>243,84 TL
+maks: 243,84 TL</t>
         </is>
       </c>
       <c r="G1780" s="12" t="inlineStr"/>
       <c r="H1780" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: - / 5</t>
+          <t>97,53 TL / -
+maks: 97,53 TL / -</t>
         </is>
       </c>
       <c r="I1780" s="12" t="inlineStr"/>
@@ -31010,7 +31005,7 @@
     <row r="1781" ht="32" customHeight="1">
       <c r="A1781" s="11" t="inlineStr">
         <is>
-          <t>Bireysel Kota Havale 75</t>
+          <t>Garantili Ödeme Sistemi</t>
         </is>
       </c>
       <c r="B1781" s="12" t="inlineStr"/>
@@ -31019,18 +31014,22 @@
       <c r="E1781" s="12" t="inlineStr"/>
       <c r="F1781" s="12" t="inlineStr">
         <is>
-          <t>1.119,05 TL
-maks: 1.119,05 TL</t>
+          <t>0,002 %</t>
         </is>
       </c>
       <c r="G1781" s="12" t="inlineStr"/>
-      <c r="H1781" s="12" t="inlineStr"/>
+      <c r="H1781" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: - / 5</t>
+        </is>
+      </c>
       <c r="I1781" s="12" t="inlineStr"/>
     </row>
     <row r="1782" ht="32" customHeight="1">
       <c r="A1782" s="11" t="inlineStr">
         <is>
-          <t>Bireysel Kota EFT 75</t>
+          <t>Bireysel Kota Havale 75</t>
         </is>
       </c>
       <c r="B1782" s="12" t="inlineStr"/>
@@ -31039,49 +31038,45 @@
       <c r="E1782" s="12" t="inlineStr"/>
       <c r="F1782" s="12" t="inlineStr">
         <is>
-          <t>2.238,10 TL
-maks: 2.238,10 TL</t>
+          <t>1.119,05 TL
+maks: 1.119,05 TL</t>
         </is>
       </c>
       <c r="G1782" s="12" t="inlineStr"/>
       <c r="H1782" s="12" t="inlineStr"/>
       <c r="I1782" s="12" t="inlineStr"/>
     </row>
-    <row r="1783" ht="16" customHeight="1">
-      <c r="A1783" s="10" t="inlineStr">
+    <row r="1783" ht="32" customHeight="1">
+      <c r="A1783" s="11" t="inlineStr">
+        <is>
+          <t>Bireysel Kota EFT 75</t>
+        </is>
+      </c>
+      <c r="B1783" s="12" t="inlineStr"/>
+      <c r="C1783" s="12" t="inlineStr"/>
+      <c r="D1783" s="12" t="inlineStr"/>
+      <c r="E1783" s="12" t="inlineStr"/>
+      <c r="F1783" s="12" t="inlineStr">
+        <is>
+          <t>2.238,10 TL
+maks: 2.238,10 TL</t>
+        </is>
+      </c>
+      <c r="G1783" s="12" t="inlineStr"/>
+      <c r="H1783" s="12" t="inlineStr"/>
+      <c r="I1783" s="12" t="inlineStr"/>
+    </row>
+    <row r="1784" ht="16" customHeight="1">
+      <c r="A1784" s="10" t="inlineStr">
         <is>
           <t>Kredi Kartları</t>
         </is>
       </c>
-    </row>
-    <row r="1784" ht="32" customHeight="1">
-      <c r="A1784" s="11" t="inlineStr">
-        <is>
-          <t>Axess Business</t>
-        </is>
-      </c>
-      <c r="B1784" s="12" t="inlineStr"/>
-      <c r="C1784" s="12" t="inlineStr"/>
-      <c r="D1784" s="12" t="inlineStr"/>
-      <c r="E1784" s="12" t="inlineStr"/>
-      <c r="F1784" s="12" t="inlineStr">
-        <is>
-          <t>1.692 TL</t>
-        </is>
-      </c>
-      <c r="G1784" s="12" t="inlineStr">
-        <is>
-          <t>1 %
-maks: 1 %</t>
-        </is>
-      </c>
-      <c r="H1784" s="12" t="inlineStr"/>
-      <c r="I1784" s="12" t="inlineStr"/>
     </row>
     <row r="1785" ht="32" customHeight="1">
       <c r="A1785" s="11" t="inlineStr">
         <is>
-          <t>Wings Business</t>
+          <t>Axess Business</t>
         </is>
       </c>
       <c r="B1785" s="12" t="inlineStr"/>
@@ -31090,7 +31085,7 @@
       <c r="E1785" s="12" t="inlineStr"/>
       <c r="F1785" s="12" t="inlineStr">
         <is>
-          <t>2.444 TL</t>
+          <t>1.692 TL</t>
         </is>
       </c>
       <c r="G1785" s="12" t="inlineStr">
@@ -31105,7 +31100,7 @@
     <row r="1786" ht="32" customHeight="1">
       <c r="A1786" s="11" t="inlineStr">
         <is>
-          <t>Axess Kobi</t>
+          <t>Wings Business</t>
         </is>
       </c>
       <c r="B1786" s="12" t="inlineStr"/>
@@ -31114,7 +31109,7 @@
       <c r="E1786" s="12" t="inlineStr"/>
       <c r="F1786" s="12" t="inlineStr">
         <is>
-          <t>1.692 TL</t>
+          <t>2.444 TL</t>
         </is>
       </c>
       <c r="G1786" s="12" t="inlineStr">
@@ -31129,7 +31124,7 @@
     <row r="1787" ht="32" customHeight="1">
       <c r="A1787" s="11" t="inlineStr">
         <is>
-          <t>Vade Farklı Taksitli İşlemler Kredi Faiz Oranı</t>
+          <t>Axess Kobi</t>
         </is>
       </c>
       <c r="B1787" s="12" t="inlineStr"/>
@@ -31138,18 +31133,22 @@
       <c r="E1787" s="12" t="inlineStr"/>
       <c r="F1787" s="12" t="inlineStr">
         <is>
-          <t>4.25 %
-maks: 4.25 %</t>
-        </is>
-      </c>
-      <c r="G1787" s="12" t="inlineStr"/>
+          <t>1.692 TL</t>
+        </is>
+      </c>
+      <c r="G1787" s="12" t="inlineStr">
+        <is>
+          <t>1 %
+maks: 1 %</t>
+        </is>
+      </c>
       <c r="H1787" s="12" t="inlineStr"/>
       <c r="I1787" s="12" t="inlineStr"/>
     </row>
     <row r="1788" ht="32" customHeight="1">
       <c r="A1788" s="11" t="inlineStr">
         <is>
-          <t>Taksit İste Faizi</t>
+          <t>Vade Farklı Taksitli İşlemler Kredi Faiz Oranı</t>
         </is>
       </c>
       <c r="B1788" s="12" t="inlineStr"/>
@@ -31169,7 +31168,7 @@
     <row r="1789" ht="32" customHeight="1">
       <c r="A1789" s="11" t="inlineStr">
         <is>
-          <t>Ek Taksit Faizi</t>
+          <t>Taksit İste Faizi</t>
         </is>
       </c>
       <c r="B1789" s="12" t="inlineStr"/>
@@ -31189,7 +31188,7 @@
     <row r="1790" ht="32" customHeight="1">
       <c r="A1790" s="11" t="inlineStr">
         <is>
-          <t>Nakit Çekim veye Kullanım İşlemlerinde Uygulanan Akdi Faiz Oranı</t>
+          <t>Ek Taksit Faizi</t>
         </is>
       </c>
       <c r="B1790" s="12" t="inlineStr"/>
@@ -31209,7 +31208,7 @@
     <row r="1791" ht="32" customHeight="1">
       <c r="A1791" s="11" t="inlineStr">
         <is>
-          <t>Nakit Çekim veye Kullanım İşlemlerinde Uygulanan Gecikme Faiz Oranı</t>
+          <t>Nakit Çekim veye Kullanım İşlemlerinde Uygulanan Akdi Faiz Oranı</t>
         </is>
       </c>
       <c r="B1791" s="12" t="inlineStr"/>
@@ -31218,8 +31217,8 @@
       <c r="E1791" s="12" t="inlineStr"/>
       <c r="F1791" s="12" t="inlineStr">
         <is>
-          <t>4.55 %
-maks: 4.55 %</t>
+          <t>4.25 %
+maks: 4.25 %</t>
         </is>
       </c>
       <c r="G1791" s="12" t="inlineStr"/>
@@ -31229,7 +31228,7 @@
     <row r="1792" ht="32" customHeight="1">
       <c r="A1792" s="11" t="inlineStr">
         <is>
-          <t>Ticari Kredi Kartı ile Anlık/Otomatik Fatura Ödeme Faiz Oranı</t>
+          <t>Nakit Çekim veye Kullanım İşlemlerinde Uygulanan Gecikme Faiz Oranı</t>
         </is>
       </c>
       <c r="B1792" s="12" t="inlineStr"/>
@@ -31238,8 +31237,8 @@
       <c r="E1792" s="12" t="inlineStr"/>
       <c r="F1792" s="12" t="inlineStr">
         <is>
-          <t>4.25 %
-maks: 4.25 %</t>
+          <t>4.55 %
+maks: 4.55 %</t>
         </is>
       </c>
       <c r="G1792" s="12" t="inlineStr"/>
@@ -31249,7 +31248,7 @@
     <row r="1793" ht="32" customHeight="1">
       <c r="A1793" s="11" t="inlineStr">
         <is>
-          <t>Ticari Kredi Kartı ile Anlık/Otomatik Fatura Ödeme Gecikme Faiz Oranı</t>
+          <t>Ticari Kredi Kartı ile Anlık/Otomatik Fatura Ödeme Faiz Oranı</t>
         </is>
       </c>
       <c r="B1793" s="12" t="inlineStr"/>
@@ -31258,8 +31257,8 @@
       <c r="E1793" s="12" t="inlineStr"/>
       <c r="F1793" s="12" t="inlineStr">
         <is>
-          <t>4.55 %
-maks: 4.55 %</t>
+          <t>4.25 %
+maks: 4.25 %</t>
         </is>
       </c>
       <c r="G1793" s="12" t="inlineStr"/>
@@ -31269,7 +31268,7 @@
     <row r="1794" ht="32" customHeight="1">
       <c r="A1794" s="11" t="inlineStr">
         <is>
-          <t>Kayıp Çalıntı/ Kart Yenileme Ücreti</t>
+          <t>Ticari Kredi Kartı ile Anlık/Otomatik Fatura Ödeme Gecikme Faiz Oranı</t>
         </is>
       </c>
       <c r="B1794" s="12" t="inlineStr"/>
@@ -31278,8 +31277,8 @@
       <c r="E1794" s="12" t="inlineStr"/>
       <c r="F1794" s="12" t="inlineStr">
         <is>
-          <t>162 TL
-maks: 162 TL</t>
+          <t>4.55 %
+maks: 4.55 %</t>
         </is>
       </c>
       <c r="G1794" s="12" t="inlineStr"/>
@@ -31289,7 +31288,7 @@
     <row r="1795" ht="32" customHeight="1">
       <c r="A1795" s="11" t="inlineStr">
         <is>
-          <t>Başka banka ATM'sinden Borç Ödeme</t>
+          <t>Kayıp Çalıntı/ Kart Yenileme Ücreti</t>
         </is>
       </c>
       <c r="B1795" s="12" t="inlineStr"/>
@@ -31298,8 +31297,8 @@
       <c r="E1795" s="12" t="inlineStr"/>
       <c r="F1795" s="12" t="inlineStr">
         <is>
-          <t>1.04 TL / 1.15 %
-maks: 1.04 TL / 1.15 %</t>
+          <t>162 TL
+maks: 162 TL</t>
         </is>
       </c>
       <c r="G1795" s="12" t="inlineStr"/>
@@ -31309,7 +31308,7 @@
     <row r="1796" ht="32" customHeight="1">
       <c r="A1796" s="11" t="inlineStr">
         <is>
-          <t>Başka banka ATM'sinden Bakiye/Borç/Limit Sorgulama</t>
+          <t>Başka banka ATM'sinden Borç Ödeme</t>
         </is>
       </c>
       <c r="B1796" s="12" t="inlineStr"/>
@@ -31318,8 +31317,8 @@
       <c r="E1796" s="12" t="inlineStr"/>
       <c r="F1796" s="12" t="inlineStr">
         <is>
-          <t>0.27 TL
-maks: 0.27 TL</t>
+          <t>1.04 TL / 1.15 %
+maks: 1.04 TL / 1.15 %</t>
         </is>
       </c>
       <c r="G1796" s="12" t="inlineStr"/>
@@ -31329,7 +31328,7 @@
     <row r="1797" ht="32" customHeight="1">
       <c r="A1797" s="11" t="inlineStr">
         <is>
-          <t>Talimatlı SGK Prim Ödeme İşlem Ücreti</t>
+          <t>Başka banka ATM'sinden Bakiye/Borç/Limit Sorgulama</t>
         </is>
       </c>
       <c r="B1797" s="12" t="inlineStr"/>
@@ -31338,8 +31337,8 @@
       <c r="E1797" s="12" t="inlineStr"/>
       <c r="F1797" s="12" t="inlineStr">
         <is>
-          <t>1 TL / 3,5%
-maks: 3,5%</t>
+          <t>0.27 TL
+maks: 0.27 TL</t>
         </is>
       </c>
       <c r="G1797" s="12" t="inlineStr"/>
@@ -31349,7 +31348,7 @@
     <row r="1798" ht="32" customHeight="1">
       <c r="A1798" s="11" t="inlineStr">
         <is>
-          <t>Anlık SGK Prim Ödeme İşlem Ücreti</t>
+          <t>Talimatlı SGK Prim Ödeme İşlem Ücreti</t>
         </is>
       </c>
       <c r="B1798" s="12" t="inlineStr"/>
@@ -31369,7 +31368,7 @@
     <row r="1799" ht="32" customHeight="1">
       <c r="A1799" s="11" t="inlineStr">
         <is>
-          <t>sgk.gov.tr adresinden SGK Prim Ödeme İşlem Ücreti</t>
+          <t>Anlık SGK Prim Ödeme İşlem Ücreti</t>
         </is>
       </c>
       <c r="B1799" s="12" t="inlineStr"/>
@@ -31378,7 +31377,7 @@
       <c r="E1799" s="12" t="inlineStr"/>
       <c r="F1799" s="12" t="inlineStr">
         <is>
-          <t>2 TL / 3,5%
+          <t>1 TL / 3,5%
 maks: 3,5%</t>
         </is>
       </c>
@@ -31389,7 +31388,7 @@
     <row r="1800" ht="32" customHeight="1">
       <c r="A1800" s="11" t="inlineStr">
         <is>
-          <t>Basılı Ekstre Gönderim Ücreti</t>
+          <t>sgk.gov.tr adresinden SGK Prim Ödeme İşlem Ücreti</t>
         </is>
       </c>
       <c r="B1800" s="12" t="inlineStr"/>
@@ -31398,44 +31397,45 @@
       <c r="E1800" s="12" t="inlineStr"/>
       <c r="F1800" s="12" t="inlineStr">
         <is>
-          <t>45 TL
-maks: 45 TL</t>
+          <t>2 TL / 3,5%
+maks: 3,5%</t>
         </is>
       </c>
       <c r="G1800" s="12" t="inlineStr"/>
       <c r="H1800" s="12" t="inlineStr"/>
       <c r="I1800" s="12" t="inlineStr"/>
     </row>
-    <row r="1801" ht="16" customHeight="1">
-      <c r="A1801" s="10" t="inlineStr">
+    <row r="1801" ht="32" customHeight="1">
+      <c r="A1801" s="11" t="inlineStr">
+        <is>
+          <t>Basılı Ekstre Gönderim Ücreti</t>
+        </is>
+      </c>
+      <c r="B1801" s="12" t="inlineStr"/>
+      <c r="C1801" s="12" t="inlineStr"/>
+      <c r="D1801" s="12" t="inlineStr"/>
+      <c r="E1801" s="12" t="inlineStr"/>
+      <c r="F1801" s="12" t="inlineStr">
+        <is>
+          <t>45 TL
+maks: 45 TL</t>
+        </is>
+      </c>
+      <c r="G1801" s="12" t="inlineStr"/>
+      <c r="H1801" s="12" t="inlineStr"/>
+      <c r="I1801" s="12" t="inlineStr"/>
+    </row>
+    <row r="1802" ht="16" customHeight="1">
+      <c r="A1802" s="10" t="inlineStr">
         <is>
           <t>Ortak Ücretler</t>
         </is>
       </c>
-    </row>
-    <row r="1802" ht="32" customHeight="1">
-      <c r="A1802" s="11" t="inlineStr">
-        <is>
-          <t>Kredi Tahsis</t>
-        </is>
-      </c>
-      <c r="B1802" s="12" t="inlineStr"/>
-      <c r="C1802" s="12" t="inlineStr"/>
-      <c r="D1802" s="12" t="inlineStr"/>
-      <c r="E1802" s="12" t="inlineStr"/>
-      <c r="F1802" s="12" t="inlineStr">
-        <is>
-          <t>maks: 0.2 %</t>
-        </is>
-      </c>
-      <c r="G1802" s="12" t="inlineStr"/>
-      <c r="H1802" s="12" t="inlineStr"/>
-      <c r="I1802" s="12" t="inlineStr"/>
     </row>
     <row r="1803" ht="32" customHeight="1">
       <c r="A1803" s="11" t="inlineStr">
         <is>
-          <t>Ticari ve Taksitli Ticari Kredi Erken Kapama Komisyonu (TL)</t>
+          <t>Kredi Tahsis</t>
         </is>
       </c>
       <c r="B1803" s="12" t="inlineStr"/>
@@ -31444,7 +31444,7 @@
       <c r="E1803" s="12" t="inlineStr"/>
       <c r="F1803" s="12" t="inlineStr">
         <is>
-          <t>maks: 2 %</t>
+          <t>maks: 0.2 %</t>
         </is>
       </c>
       <c r="G1803" s="12" t="inlineStr"/>
@@ -31454,7 +31454,7 @@
     <row r="1804" ht="32" customHeight="1">
       <c r="A1804" s="11" t="inlineStr">
         <is>
-          <t>Aylık Hesap Özeti (Ticari Müşteri)</t>
+          <t>Ticari ve Taksitli Ticari Kredi Erken Kapama Komisyonu (TL)</t>
         </is>
       </c>
       <c r="B1804" s="12" t="inlineStr"/>
@@ -31463,7 +31463,7 @@
       <c r="E1804" s="12" t="inlineStr"/>
       <c r="F1804" s="12" t="inlineStr">
         <is>
-          <t>12 TL</t>
+          <t>maks: 2 %</t>
         </is>
       </c>
       <c r="G1804" s="12" t="inlineStr"/>
@@ -31473,7 +31473,7 @@
     <row r="1805" ht="32" customHeight="1">
       <c r="A1805" s="11" t="inlineStr">
         <is>
-          <t>KGF komisyonu</t>
+          <t>Aylık Hesap Özeti (Ticari Müşteri)</t>
         </is>
       </c>
       <c r="B1805" s="12" t="inlineStr"/>
@@ -31482,7 +31482,7 @@
       <c r="E1805" s="12" t="inlineStr"/>
       <c r="F1805" s="12" t="inlineStr">
         <is>
-          <t>maks: 0.35 %</t>
+          <t>12 TL</t>
         </is>
       </c>
       <c r="G1805" s="12" t="inlineStr"/>
@@ -31492,7 +31492,7 @@
     <row r="1806" ht="32" customHeight="1">
       <c r="A1806" s="11" t="inlineStr">
         <is>
-          <t>Doğrudan Borçlandırma Sistemi Dönem Ücreti</t>
+          <t>KGF komisyonu</t>
         </is>
       </c>
       <c r="B1806" s="12" t="inlineStr"/>
@@ -31501,7 +31501,7 @@
       <c r="E1806" s="12" t="inlineStr"/>
       <c r="F1806" s="12" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>maks: 0.35 %</t>
         </is>
       </c>
       <c r="G1806" s="12" t="inlineStr"/>
@@ -31511,7 +31511,7 @@
     <row r="1807" ht="32" customHeight="1">
       <c r="A1807" s="11" t="inlineStr">
         <is>
-          <t>Doğrudan Borçlandırma Sistemi Dönem Ücreti - Akaryakıt</t>
+          <t>Doğrudan Borçlandırma Sistemi Dönem Ücreti</t>
         </is>
       </c>
       <c r="B1807" s="12" t="inlineStr"/>
@@ -31520,7 +31520,7 @@
       <c r="E1807" s="12" t="inlineStr"/>
       <c r="F1807" s="12" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G1807" s="12" t="inlineStr"/>
@@ -31530,46 +31530,46 @@
     <row r="1808" ht="32" customHeight="1">
       <c r="A1808" s="11" t="inlineStr">
         <is>
-          <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti</t>
+          <t>Doğrudan Borçlandırma Sistemi Dönem Ücreti - Akaryakıt</t>
         </is>
       </c>
       <c r="B1808" s="12" t="inlineStr"/>
       <c r="C1808" s="12" t="inlineStr"/>
       <c r="D1808" s="12" t="inlineStr"/>
       <c r="E1808" s="12" t="inlineStr"/>
-      <c r="F1808" s="12" t="inlineStr"/>
+      <c r="F1808" s="12" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="G1808" s="12" t="inlineStr"/>
-      <c r="H1808" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / -</t>
-        </is>
-      </c>
+      <c r="H1808" s="12" t="inlineStr"/>
       <c r="I1808" s="12" t="inlineStr"/>
     </row>
     <row r="1809" ht="32" customHeight="1">
       <c r="A1809" s="11" t="inlineStr">
         <is>
-          <t>İtibar /Niyet/Referans Mektubu Düzenleme Ücreti</t>
+          <t>Ekspertiz, Teminat Tesis, Değişiklik ve İptal Ücreti</t>
         </is>
       </c>
       <c r="B1809" s="12" t="inlineStr"/>
       <c r="C1809" s="12" t="inlineStr"/>
       <c r="D1809" s="12" t="inlineStr"/>
       <c r="E1809" s="12" t="inlineStr"/>
-      <c r="F1809" s="12" t="inlineStr">
-        <is>
-          <t>maks: 5000 TL</t>
-        </is>
-      </c>
+      <c r="F1809" s="12" t="inlineStr"/>
       <c r="G1809" s="12" t="inlineStr"/>
-      <c r="H1809" s="12" t="inlineStr"/>
+      <c r="H1809" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: - / -</t>
+        </is>
+      </c>
       <c r="I1809" s="12" t="inlineStr"/>
     </row>
     <row r="1810" ht="32" customHeight="1">
       <c r="A1810" s="11" t="inlineStr">
         <is>
-          <t>Basılı Ekstre Gönderimi</t>
+          <t>İtibar /Niyet/Referans Mektubu Düzenleme Ücreti</t>
         </is>
       </c>
       <c r="B1810" s="12" t="inlineStr"/>
@@ -31578,44 +31578,44 @@
       <c r="E1810" s="12" t="inlineStr"/>
       <c r="F1810" s="12" t="inlineStr">
         <is>
-          <t>0 TL
-maks: 5,12</t>
+          <t>maks: 5000 TL</t>
         </is>
       </c>
       <c r="G1810" s="12" t="inlineStr"/>
       <c r="H1810" s="12" t="inlineStr"/>
       <c r="I1810" s="12" t="inlineStr"/>
     </row>
-    <row r="1811" ht="16" customHeight="1">
-      <c r="A1811" s="10" t="inlineStr">
+    <row r="1811" ht="32" customHeight="1">
+      <c r="A1811" s="11" t="inlineStr">
+        <is>
+          <t>Basılı Ekstre Gönderimi</t>
+        </is>
+      </c>
+      <c r="B1811" s="12" t="inlineStr"/>
+      <c r="C1811" s="12" t="inlineStr"/>
+      <c r="D1811" s="12" t="inlineStr"/>
+      <c r="E1811" s="12" t="inlineStr"/>
+      <c r="F1811" s="12" t="inlineStr">
+        <is>
+          <t>0 TL
+maks: 5,12</t>
+        </is>
+      </c>
+      <c r="G1811" s="12" t="inlineStr"/>
+      <c r="H1811" s="12" t="inlineStr"/>
+      <c r="I1811" s="12" t="inlineStr"/>
+    </row>
+    <row r="1812" ht="16" customHeight="1">
+      <c r="A1812" s="10" t="inlineStr">
         <is>
           <t>Gayrinakit Krediler</t>
         </is>
       </c>
-    </row>
-    <row r="1812" ht="32" customHeight="1">
-      <c r="A1812" s="11" t="inlineStr">
-        <is>
-          <t>Teminat Mektubu Teslim/Güncelleme/İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B1812" s="12" t="inlineStr"/>
-      <c r="C1812" s="12" t="inlineStr"/>
-      <c r="D1812" s="12" t="inlineStr"/>
-      <c r="E1812" s="12" t="inlineStr"/>
-      <c r="F1812" s="12" t="inlineStr">
-        <is>
-          <t>maks: 75 TL</t>
-        </is>
-      </c>
-      <c r="G1812" s="12" t="inlineStr"/>
-      <c r="H1812" s="12" t="inlineStr"/>
-      <c r="I1812" s="12" t="inlineStr"/>
     </row>
     <row r="1813" ht="32" customHeight="1">
       <c r="A1813" s="11" t="inlineStr">
         <is>
-          <t>Teminat Mektubu Komisyonu</t>
+          <t>Teminat Mektubu Teslim/Güncelleme/İade Ücreti</t>
         </is>
       </c>
       <c r="B1813" s="12" t="inlineStr"/>
@@ -31624,7 +31624,7 @@
       <c r="E1813" s="12" t="inlineStr"/>
       <c r="F1813" s="12" t="inlineStr">
         <is>
-          <t>400 TL / 4 %</t>
+          <t>maks: 75 TL</t>
         </is>
       </c>
       <c r="G1813" s="12" t="inlineStr"/>
@@ -31634,7 +31634,7 @@
     <row r="1814" ht="32" customHeight="1">
       <c r="A1814" s="11" t="inlineStr">
         <is>
-          <t>Teminat Mektubu Teyit Yazısının Hazırlanması Masrafı</t>
+          <t>Teminat Mektubu Komisyonu</t>
         </is>
       </c>
       <c r="B1814" s="12" t="inlineStr"/>
@@ -31643,7 +31643,7 @@
       <c r="E1814" s="12" t="inlineStr"/>
       <c r="F1814" s="12" t="inlineStr">
         <is>
-          <t>maks: 75 TL</t>
+          <t>400 TL / 4 %</t>
         </is>
       </c>
       <c r="G1814" s="12" t="inlineStr"/>
@@ -31653,7 +31653,7 @@
     <row r="1815" ht="32" customHeight="1">
       <c r="A1815" s="11" t="inlineStr">
         <is>
-          <t>Teminat Mektubu Uzatım Yazısının Hazırlanması Masrafı</t>
+          <t>Teminat Mektubu Teyit Yazısının Hazırlanması Masrafı</t>
         </is>
       </c>
       <c r="B1815" s="12" t="inlineStr"/>
@@ -31662,7 +31662,7 @@
       <c r="E1815" s="12" t="inlineStr"/>
       <c r="F1815" s="12" t="inlineStr">
         <is>
-          <t>100 TL</t>
+          <t>maks: 75 TL</t>
         </is>
       </c>
       <c r="G1815" s="12" t="inlineStr"/>
@@ -31672,7 +31672,7 @@
     <row r="1816" ht="32" customHeight="1">
       <c r="A1816" s="11" t="inlineStr">
         <is>
-          <t>Aval Kredileri</t>
+          <t>Teminat Mektubu Uzatım Yazısının Hazırlanması Masrafı</t>
         </is>
       </c>
       <c r="B1816" s="12" t="inlineStr"/>
@@ -31681,8 +31681,7 @@
       <c r="E1816" s="12" t="inlineStr"/>
       <c r="F1816" s="12" t="inlineStr">
         <is>
-          <t>100 Dolar
-maks: 4 %</t>
+          <t>100 TL</t>
         </is>
       </c>
       <c r="G1816" s="12" t="inlineStr"/>
@@ -31692,7 +31691,7 @@
     <row r="1817" ht="32" customHeight="1">
       <c r="A1817" s="11" t="inlineStr">
         <is>
-          <t>İthalat Akreditifleri</t>
+          <t>Aval Kredileri</t>
         </is>
       </c>
       <c r="B1817" s="12" t="inlineStr"/>
@@ -31712,7 +31711,7 @@
     <row r="1818" ht="32" customHeight="1">
       <c r="A1818" s="11" t="inlineStr">
         <is>
-          <t>Dövizi Natık Teminat Mektupları</t>
+          <t>İthalat Akreditifleri</t>
         </is>
       </c>
       <c r="B1818" s="12" t="inlineStr"/>
@@ -31729,36 +31728,37 @@
       <c r="H1818" s="12" t="inlineStr"/>
       <c r="I1818" s="12" t="inlineStr"/>
     </row>
-    <row r="1819" ht="16" customHeight="1">
-      <c r="A1819" s="10" t="inlineStr">
+    <row r="1819" ht="32" customHeight="1">
+      <c r="A1819" s="11" t="inlineStr">
+        <is>
+          <t>Dövizi Natık Teminat Mektupları</t>
+        </is>
+      </c>
+      <c r="B1819" s="12" t="inlineStr"/>
+      <c r="C1819" s="12" t="inlineStr"/>
+      <c r="D1819" s="12" t="inlineStr"/>
+      <c r="E1819" s="12" t="inlineStr"/>
+      <c r="F1819" s="12" t="inlineStr">
+        <is>
+          <t>100 Dolar
+maks: 4 %</t>
+        </is>
+      </c>
+      <c r="G1819" s="12" t="inlineStr"/>
+      <c r="H1819" s="12" t="inlineStr"/>
+      <c r="I1819" s="12" t="inlineStr"/>
+    </row>
+    <row r="1820" ht="16" customHeight="1">
+      <c r="A1820" s="10" t="inlineStr">
         <is>
           <t>Nakit Krediler</t>
         </is>
       </c>
-    </row>
-    <row r="1820" ht="32" customHeight="1">
-      <c r="A1820" s="11" t="inlineStr">
-        <is>
-          <t>İşlek Kredi (TL) Kullandırım Ücreti</t>
-        </is>
-      </c>
-      <c r="B1820" s="12" t="inlineStr"/>
-      <c r="C1820" s="12" t="inlineStr"/>
-      <c r="D1820" s="12" t="inlineStr"/>
-      <c r="E1820" s="12" t="inlineStr"/>
-      <c r="F1820" s="12" t="inlineStr">
-        <is>
-          <t>maks: 1 %</t>
-        </is>
-      </c>
-      <c r="G1820" s="12" t="inlineStr"/>
-      <c r="H1820" s="12" t="inlineStr"/>
-      <c r="I1820" s="12" t="inlineStr"/>
     </row>
     <row r="1821" ht="32" customHeight="1">
       <c r="A1821" s="11" t="inlineStr">
         <is>
-          <t>İşlek Kredi (YP/DEK) Kullandırım Ücreti</t>
+          <t>İşlek Kredi (TL) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1821" s="12" t="inlineStr"/>
@@ -31777,7 +31777,7 @@
     <row r="1822" ht="32" customHeight="1">
       <c r="A1822" s="11" t="inlineStr">
         <is>
-          <t>Spot Kredi (TL) Kullandırım Ücreti</t>
+          <t>İşlek Kredi (YP/DEK) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1822" s="12" t="inlineStr"/>
@@ -31786,7 +31786,7 @@
       <c r="E1822" s="12" t="inlineStr"/>
       <c r="F1822" s="12" t="inlineStr">
         <is>
-          <t>maks: 1.10 %</t>
+          <t>maks: 1 %</t>
         </is>
       </c>
       <c r="G1822" s="12" t="inlineStr"/>
@@ -31796,7 +31796,7 @@
     <row r="1823" ht="32" customHeight="1">
       <c r="A1823" s="11" t="inlineStr">
         <is>
-          <t>Spot Kredi (YP/DEK) Kullandırım Ücreti</t>
+          <t>Spot Kredi (TL) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1823" s="12" t="inlineStr"/>
@@ -31815,7 +31815,7 @@
     <row r="1824" ht="32" customHeight="1">
       <c r="A1824" s="11" t="inlineStr">
         <is>
-          <t>Taksitli Ticari Kredi (TL) Kullandırım Ücreti</t>
+          <t>Spot Kredi (YP/DEK) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1824" s="12" t="inlineStr"/>
@@ -31834,7 +31834,7 @@
     <row r="1825" ht="32" customHeight="1">
       <c r="A1825" s="11" t="inlineStr">
         <is>
-          <t>Taksitli Ticari Kredi (YP/DEK) Kullandırım Ücreti</t>
+          <t>Taksitli Ticari Kredi (TL) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1825" s="12" t="inlineStr"/>
@@ -31853,7 +31853,7 @@
     <row r="1826" ht="32" customHeight="1">
       <c r="A1826" s="11" t="inlineStr">
         <is>
-          <t>İşyeri Kredisi (TL) Kullandırım Ücreti</t>
+          <t>Taksitli Ticari Kredi (YP/DEK) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1826" s="12" t="inlineStr"/>
@@ -31872,7 +31872,7 @@
     <row r="1827" ht="32" customHeight="1">
       <c r="A1827" s="11" t="inlineStr">
         <is>
-          <t>İşyeri Kredisi (YP/DEK) Kullandırım Ücreti</t>
+          <t>İşyeri Kredisi (TL) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1827" s="12" t="inlineStr"/>
@@ -31891,7 +31891,7 @@
     <row r="1828" ht="32" customHeight="1">
       <c r="A1828" s="11" t="inlineStr">
         <is>
-          <t>Taşıt Kredisi (TL)  Kullandırım Ücreti</t>
+          <t>İşyeri Kredisi (YP/DEK) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1828" s="12" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
     <row r="1829" ht="32" customHeight="1">
       <c r="A1829" s="11" t="inlineStr">
         <is>
-          <t>Taşıt Kredisi (YP/DEK)  Kullandırım Ücreti</t>
+          <t>Taşıt Kredisi (TL)  Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1829" s="12" t="inlineStr"/>
@@ -31929,7 +31929,7 @@
     <row r="1830" ht="32" customHeight="1">
       <c r="A1830" s="11" t="inlineStr">
         <is>
-          <t>İskonto/İştira Kredisi (TL) Kullandırım Ücreti</t>
+          <t>Taşıt Kredisi (YP/DEK)  Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1830" s="12" t="inlineStr"/>
@@ -31948,7 +31948,7 @@
     <row r="1831" ht="32" customHeight="1">
       <c r="A1831" s="11" t="inlineStr">
         <is>
-          <t>İskonto/İştira Kredisi (YP/DEK) Kullandırım Ücreti</t>
+          <t>İskonto/İştira Kredisi (TL) Kullandırım Ücreti</t>
         </is>
       </c>
       <c r="B1831" s="12" t="inlineStr"/>
@@ -31964,63 +31964,62 @@
       <c r="H1831" s="12" t="inlineStr"/>
       <c r="I1831" s="12" t="inlineStr"/>
     </row>
-    <row r="1832" ht="16" customHeight="1">
-      <c r="A1832" s="10" t="inlineStr">
+    <row r="1832" ht="32" customHeight="1">
+      <c r="A1832" s="11" t="inlineStr">
+        <is>
+          <t>İskonto/İştira Kredisi (YP/DEK) Kullandırım Ücreti</t>
+        </is>
+      </c>
+      <c r="B1832" s="12" t="inlineStr"/>
+      <c r="C1832" s="12" t="inlineStr"/>
+      <c r="D1832" s="12" t="inlineStr"/>
+      <c r="E1832" s="12" t="inlineStr"/>
+      <c r="F1832" s="12" t="inlineStr">
+        <is>
+          <t>maks: 1.10 %</t>
+        </is>
+      </c>
+      <c r="G1832" s="12" t="inlineStr"/>
+      <c r="H1832" s="12" t="inlineStr"/>
+      <c r="I1832" s="12" t="inlineStr"/>
+    </row>
+    <row r="1833" ht="16" customHeight="1">
+      <c r="A1833" s="10" t="inlineStr">
         <is>
           <t>Tarım Kart</t>
         </is>
       </c>
     </row>
-    <row r="1833" ht="32" customHeight="1">
-      <c r="A1833" s="11" t="inlineStr">
+    <row r="1834" ht="32" customHeight="1">
+      <c r="A1834" s="11" t="inlineStr">
         <is>
           <t>Tarım Kart Üyelik Ücreti</t>
         </is>
       </c>
-      <c r="B1833" s="12" t="inlineStr"/>
-      <c r="C1833" s="12" t="inlineStr"/>
-      <c r="D1833" s="12" t="inlineStr"/>
-      <c r="E1833" s="12" t="inlineStr"/>
-      <c r="F1833" s="12" t="inlineStr">
+      <c r="B1834" s="12" t="inlineStr"/>
+      <c r="C1834" s="12" t="inlineStr"/>
+      <c r="D1834" s="12" t="inlineStr"/>
+      <c r="E1834" s="12" t="inlineStr"/>
+      <c r="F1834" s="12" t="inlineStr">
         <is>
           <t>225 TL</t>
         </is>
       </c>
-      <c r="G1833" s="12" t="inlineStr"/>
-      <c r="H1833" s="12" t="inlineStr"/>
-      <c r="I1833" s="12" t="inlineStr"/>
-    </row>
-    <row r="1834" ht="16" customHeight="1">
-      <c r="A1834" s="10" t="inlineStr">
+      <c r="G1834" s="12" t="inlineStr"/>
+      <c r="H1834" s="12" t="inlineStr"/>
+      <c r="I1834" s="12" t="inlineStr"/>
+    </row>
+    <row r="1835" ht="16" customHeight="1">
+      <c r="A1835" s="10" t="inlineStr">
         <is>
           <t>Ürün ve Hizmet Paketleri</t>
         </is>
       </c>
-    </row>
-    <row r="1835" ht="32" customHeight="1">
-      <c r="A1835" s="11" t="inlineStr">
-        <is>
-          <t>Esnaf Kota</t>
-        </is>
-      </c>
-      <c r="B1835" s="12" t="inlineStr"/>
-      <c r="C1835" s="12" t="inlineStr"/>
-      <c r="D1835" s="12" t="inlineStr"/>
-      <c r="E1835" s="12" t="inlineStr"/>
-      <c r="F1835" s="12" t="inlineStr">
-        <is>
-          <t>10.095,24 TL
-maks: 10.095,24 TL</t>
-        </is>
-      </c>
-      <c r="G1835" s="12" t="inlineStr"/>
-      <c r="H1835" s="12" t="inlineStr"/>
-      <c r="I1835" s="12" t="inlineStr"/>
     </row>
     <row r="1836" ht="32" customHeight="1">
       <c r="A1836" s="11" t="inlineStr">
         <is>
-          <t>Şirket Kota</t>
+          <t>Esnaf Kota</t>
         </is>
       </c>
       <c r="B1836" s="12" t="inlineStr"/>
@@ -32029,8 +32028,8 @@
       <c r="E1836" s="12" t="inlineStr"/>
       <c r="F1836" s="12" t="inlineStr">
         <is>
-          <t>23.809,52 TL
-maks: 23.809,52 TL</t>
+          <t>10.095,24 TL
+maks: 10.095,24 TL</t>
         </is>
       </c>
       <c r="G1836" s="12" t="inlineStr"/>
@@ -32040,7 +32039,7 @@
     <row r="1837" ht="32" customHeight="1">
       <c r="A1837" s="11" t="inlineStr">
         <is>
-          <t>Çek/senet Paketi 1</t>
+          <t>Şirket Kota</t>
         </is>
       </c>
       <c r="B1837" s="12" t="inlineStr"/>
@@ -32049,8 +32048,8 @@
       <c r="E1837" s="12" t="inlineStr"/>
       <c r="F1837" s="12" t="inlineStr">
         <is>
-          <t>5.952,39 TL
-maks: 5.952,39 TL</t>
+          <t>23.809,52 TL
+maks: 23.809,52 TL</t>
         </is>
       </c>
       <c r="G1837" s="12" t="inlineStr"/>
@@ -32060,7 +32059,7 @@
     <row r="1838" ht="32" customHeight="1">
       <c r="A1838" s="11" t="inlineStr">
         <is>
-          <t>Çek/senet Paketi 2</t>
+          <t>Çek/senet Paketi 1</t>
         </is>
       </c>
       <c r="B1838" s="12" t="inlineStr"/>
@@ -32069,8 +32068,8 @@
       <c r="E1838" s="12" t="inlineStr"/>
       <c r="F1838" s="12" t="inlineStr">
         <is>
-          <t>14.047,62 TL
-maks: 14.047,62 TL</t>
+          <t>5.952,39 TL
+maks: 5.952,39 TL</t>
         </is>
       </c>
       <c r="G1838" s="12" t="inlineStr"/>
@@ -32080,7 +32079,7 @@
     <row r="1839" ht="32" customHeight="1">
       <c r="A1839" s="11" t="inlineStr">
         <is>
-          <t>Çek/senet Paketi 3</t>
+          <t>Çek/senet Paketi 2</t>
         </is>
       </c>
       <c r="B1839" s="12" t="inlineStr"/>
@@ -32089,8 +32088,8 @@
       <c r="E1839" s="12" t="inlineStr"/>
       <c r="F1839" s="12" t="inlineStr">
         <is>
-          <t>41.904,77 TL
-maks: 41.904,77 TL</t>
+          <t>14.047,62 TL
+maks: 14.047,62 TL</t>
         </is>
       </c>
       <c r="G1839" s="12" t="inlineStr"/>
@@ -32100,7 +32099,7 @@
     <row r="1840" ht="32" customHeight="1">
       <c r="A1840" s="11" t="inlineStr">
         <is>
-          <t>KOTA Masaüstü POS</t>
+          <t>Çek/senet Paketi 3</t>
         </is>
       </c>
       <c r="B1840" s="12" t="inlineStr"/>
@@ -32109,8 +32108,8 @@
       <c r="E1840" s="12" t="inlineStr"/>
       <c r="F1840" s="12" t="inlineStr">
         <is>
-          <t>38.095,24 TL
-maks: 38.095,24 TL</t>
+          <t>41.904,77 TL
+maks: 41.904,77 TL</t>
         </is>
       </c>
       <c r="G1840" s="12" t="inlineStr"/>
@@ -32120,7 +32119,7 @@
     <row r="1841" ht="32" customHeight="1">
       <c r="A1841" s="11" t="inlineStr">
         <is>
-          <t>KOTA Mobil POS</t>
+          <t>KOTA Masaüstü POS</t>
         </is>
       </c>
       <c r="B1841" s="12" t="inlineStr"/>
@@ -32129,8 +32128,8 @@
       <c r="E1841" s="12" t="inlineStr"/>
       <c r="F1841" s="12" t="inlineStr">
         <is>
-          <t>53.571,43 TL
-maks: 53.571,43 TL</t>
+          <t>38.095,24 TL
+maks: 38.095,24 TL</t>
         </is>
       </c>
       <c r="G1841" s="12" t="inlineStr"/>
@@ -32140,7 +32139,7 @@
     <row r="1842" ht="32" customHeight="1">
       <c r="A1842" s="11" t="inlineStr">
         <is>
-          <t>KOTA ÖKC</t>
+          <t>KOTA Mobil POS</t>
         </is>
       </c>
       <c r="B1842" s="12" t="inlineStr"/>
@@ -32149,8 +32148,8 @@
       <c r="E1842" s="12" t="inlineStr"/>
       <c r="F1842" s="12" t="inlineStr">
         <is>
-          <t>48.809,52 TL
-maks: 48.809,52 TL</t>
+          <t>53.571,43 TL
+maks: 53.571,43 TL</t>
         </is>
       </c>
       <c r="G1842" s="12" t="inlineStr"/>
@@ -32160,7 +32159,7 @@
     <row r="1843" ht="32" customHeight="1">
       <c r="A1843" s="11" t="inlineStr">
         <is>
-          <t>KOTA Sanal POS</t>
+          <t>KOTA ÖKC</t>
         </is>
       </c>
       <c r="B1843" s="12" t="inlineStr"/>
@@ -32169,8 +32168,8 @@
       <c r="E1843" s="12" t="inlineStr"/>
       <c r="F1843" s="12" t="inlineStr">
         <is>
-          <t>41.666,67 TL
-maks: 41.666,67 TL</t>
+          <t>48.809,52 TL
+maks: 48.809,52 TL</t>
         </is>
       </c>
       <c r="G1843" s="12" t="inlineStr"/>
@@ -32180,7 +32179,7 @@
     <row r="1844" ht="32" customHeight="1">
       <c r="A1844" s="11" t="inlineStr">
         <is>
-          <t>KOTA Senet 300</t>
+          <t>KOTA Sanal POS</t>
         </is>
       </c>
       <c r="B1844" s="12" t="inlineStr"/>
@@ -32189,8 +32188,8 @@
       <c r="E1844" s="12" t="inlineStr"/>
       <c r="F1844" s="12" t="inlineStr">
         <is>
-          <t>55.333,33 TL
-maks: 55.333,33 TL</t>
+          <t>41.666,67 TL
+maks: 41.666,67 TL</t>
         </is>
       </c>
       <c r="G1844" s="12" t="inlineStr"/>
@@ -32200,7 +32199,7 @@
     <row r="1845" ht="32" customHeight="1">
       <c r="A1845" s="11" t="inlineStr">
         <is>
-          <t>Mikro Kota EFT 75</t>
+          <t>KOTA Senet 300</t>
         </is>
       </c>
       <c r="B1845" s="12" t="inlineStr"/>
@@ -32209,8 +32208,8 @@
       <c r="E1845" s="12" t="inlineStr"/>
       <c r="F1845" s="12" t="inlineStr">
         <is>
-          <t>2.238,10 TL
-maks: 2.238,10 TL</t>
+          <t>55.333,33 TL
+maks: 55.333,33 TL</t>
         </is>
       </c>
       <c r="G1845" s="12" t="inlineStr"/>
@@ -32220,7 +32219,7 @@
     <row r="1846" ht="32" customHeight="1">
       <c r="A1846" s="11" t="inlineStr">
         <is>
-          <t>Şİrket Kota EFT 200</t>
+          <t>Mikro Kota EFT 75</t>
         </is>
       </c>
       <c r="B1846" s="12" t="inlineStr"/>
@@ -32229,8 +32228,8 @@
       <c r="E1846" s="12" t="inlineStr"/>
       <c r="F1846" s="12" t="inlineStr">
         <is>
-          <t>5.476,19 TL
-maks: 5.476,19 TL</t>
+          <t>2.238,10 TL
+maks: 2.238,10 TL</t>
         </is>
       </c>
       <c r="G1846" s="12" t="inlineStr"/>
@@ -32240,7 +32239,7 @@
     <row r="1847" ht="32" customHeight="1">
       <c r="A1847" s="11" t="inlineStr">
         <is>
-          <t>Mikro Kota Havale 75</t>
+          <t>Şİrket Kota EFT 200</t>
         </is>
       </c>
       <c r="B1847" s="12" t="inlineStr"/>
@@ -32249,8 +32248,8 @@
       <c r="E1847" s="12" t="inlineStr"/>
       <c r="F1847" s="12" t="inlineStr">
         <is>
-          <t>1.119,05 TL
-maks: 1.119,05 TL</t>
+          <t>5.476,19 TL
+maks: 5.476,19 TL</t>
         </is>
       </c>
       <c r="G1847" s="12" t="inlineStr"/>
@@ -32260,7 +32259,7 @@
     <row r="1848" ht="32" customHeight="1">
       <c r="A1848" s="11" t="inlineStr">
         <is>
-          <t>Şirket Kota Havale 200</t>
+          <t>Mikro Kota Havale 75</t>
         </is>
       </c>
       <c r="B1848" s="12" t="inlineStr"/>
@@ -32269,8 +32268,8 @@
       <c r="E1848" s="12" t="inlineStr"/>
       <c r="F1848" s="12" t="inlineStr">
         <is>
-          <t>2.738,10 TL
-maks: 2.738,10 TL</t>
+          <t>1.119,05 TL
+maks: 1.119,05 TL</t>
         </is>
       </c>
       <c r="G1848" s="12" t="inlineStr"/>
@@ -32280,7 +32279,7 @@
     <row r="1849" ht="32" customHeight="1">
       <c r="A1849" s="11" t="inlineStr">
         <is>
-          <t>Kobi Giden Swift Paketi 500</t>
+          <t>Şirket Kota Havale 200</t>
         </is>
       </c>
       <c r="B1849" s="12" t="inlineStr"/>
@@ -32289,8 +32288,8 @@
       <c r="E1849" s="12" t="inlineStr"/>
       <c r="F1849" s="12" t="inlineStr">
         <is>
-          <t>1.390.476,20 TL
-maks: 1.390.476,20 TL</t>
+          <t>2.738,10 TL
+maks: 2.738,10 TL</t>
         </is>
       </c>
       <c r="G1849" s="12" t="inlineStr"/>
@@ -32300,7 +32299,7 @@
     <row r="1850" ht="32" customHeight="1">
       <c r="A1850" s="11" t="inlineStr">
         <is>
-          <t>Kobi Gelen Swift Paketi 500</t>
+          <t>Kobi Giden Swift Paketi 500</t>
         </is>
       </c>
       <c r="B1850" s="12" t="inlineStr"/>
@@ -32309,8 +32308,8 @@
       <c r="E1850" s="12" t="inlineStr"/>
       <c r="F1850" s="12" t="inlineStr">
         <is>
-          <t>642.857,15 TL
-maks: 642.857,15 TL</t>
+          <t>1.390.476,20 TL
+maks: 1.390.476,20 TL</t>
         </is>
       </c>
       <c r="G1850" s="12" t="inlineStr"/>
@@ -32320,7 +32319,7 @@
     <row r="1851" ht="32" customHeight="1">
       <c r="A1851" s="11" t="inlineStr">
         <is>
-          <t>Kobi Gelen Swift Paketi 250</t>
+          <t>Kobi Gelen Swift Paketi 500</t>
         </is>
       </c>
       <c r="B1851" s="12" t="inlineStr"/>
@@ -32329,8 +32328,8 @@
       <c r="E1851" s="12" t="inlineStr"/>
       <c r="F1851" s="12" t="inlineStr">
         <is>
-          <t>323.809,53 TL
-maks: 323.809,53 TL</t>
+          <t>642.857,15 TL
+maks: 642.857,15 TL</t>
         </is>
       </c>
       <c r="G1851" s="12" t="inlineStr"/>
@@ -32340,7 +32339,7 @@
     <row r="1852" ht="32" customHeight="1">
       <c r="A1852" s="11" t="inlineStr">
         <is>
-          <t>Kobi Giden Swift Paketi 250</t>
+          <t>Kobi Gelen Swift Paketi 250</t>
         </is>
       </c>
       <c r="B1852" s="12" t="inlineStr"/>
@@ -32349,8 +32348,8 @@
       <c r="E1852" s="12" t="inlineStr"/>
       <c r="F1852" s="12" t="inlineStr">
         <is>
-          <t>685.714,29 TL
-maks: 685.714,29 TL</t>
+          <t>323.809,53 TL
+maks: 323.809,53 TL</t>
         </is>
       </c>
       <c r="G1852" s="12" t="inlineStr"/>
@@ -32360,7 +32359,7 @@
     <row r="1853" ht="32" customHeight="1">
       <c r="A1853" s="11" t="inlineStr">
         <is>
-          <t>Kobi Gelen Swift Paketi 350</t>
+          <t>Kobi Giden Swift Paketi 250</t>
         </is>
       </c>
       <c r="B1853" s="12" t="inlineStr"/>
@@ -32369,8 +32368,8 @@
       <c r="E1853" s="12" t="inlineStr"/>
       <c r="F1853" s="12" t="inlineStr">
         <is>
-          <t>461.904,77 TL
-maks: 461.904,77 TL</t>
+          <t>685.714,29 TL
+maks: 685.714,29 TL</t>
         </is>
       </c>
       <c r="G1853" s="12" t="inlineStr"/>
@@ -32380,7 +32379,7 @@
     <row r="1854" ht="32" customHeight="1">
       <c r="A1854" s="11" t="inlineStr">
         <is>
-          <t>Kobi Giden Swift Paketi 350</t>
+          <t>Kobi Gelen Swift Paketi 350</t>
         </is>
       </c>
       <c r="B1854" s="12" t="inlineStr"/>
@@ -32389,8 +32388,8 @@
       <c r="E1854" s="12" t="inlineStr"/>
       <c r="F1854" s="12" t="inlineStr">
         <is>
-          <t>919.047,62 TL
-maks: 919.047,62 TL</t>
+          <t>461.904,77 TL
+maks: 461.904,77 TL</t>
         </is>
       </c>
       <c r="G1854" s="12" t="inlineStr"/>
@@ -32400,7 +32399,7 @@
     <row r="1855" ht="32" customHeight="1">
       <c r="A1855" s="11" t="inlineStr">
         <is>
-          <t>KKB-Risk Raporu Hizmet Bedeli</t>
+          <t>Kobi Giden Swift Paketi 350</t>
         </is>
       </c>
       <c r="B1855" s="12" t="inlineStr"/>
@@ -32409,7 +32408,8 @@
       <c r="E1855" s="12" t="inlineStr"/>
       <c r="F1855" s="12" t="inlineStr">
         <is>
-          <t>65 TL</t>
+          <t>919.047,62 TL
+maks: 919.047,62 TL</t>
         </is>
       </c>
       <c r="G1855" s="12" t="inlineStr"/>
@@ -32419,7 +32419,7 @@
     <row r="1856" ht="32" customHeight="1">
       <c r="A1856" s="11" t="inlineStr">
         <is>
-          <t>Ticari EFT Paketi 100 Ücreti</t>
+          <t>KKB-Risk Raporu Hizmet Bedeli</t>
         </is>
       </c>
       <c r="B1856" s="12" t="inlineStr"/>
@@ -32428,8 +32428,7 @@
       <c r="E1856" s="12" t="inlineStr"/>
       <c r="F1856" s="12" t="inlineStr">
         <is>
-          <t>61.904,77 TL
-maks: 61.904,77 TL</t>
+          <t>65 TL</t>
         </is>
       </c>
       <c r="G1856" s="12" t="inlineStr"/>
@@ -32439,7 +32438,7 @@
     <row r="1857" ht="32" customHeight="1">
       <c r="A1857" s="11" t="inlineStr">
         <is>
-          <t>Ticari EFT Paketi 500 Ücreti</t>
+          <t>Ticari EFT Paketi 100 Ücreti</t>
         </is>
       </c>
       <c r="B1857" s="12" t="inlineStr"/>
@@ -32448,8 +32447,8 @@
       <c r="E1857" s="12" t="inlineStr"/>
       <c r="F1857" s="12" t="inlineStr">
         <is>
-          <t>309.523,82 TL
-maks: 309.523,82 TL</t>
+          <t>61.904,77 TL
+maks: 61.904,77 TL</t>
         </is>
       </c>
       <c r="G1857" s="12" t="inlineStr"/>
@@ -32459,7 +32458,7 @@
     <row r="1858" ht="32" customHeight="1">
       <c r="A1858" s="11" t="inlineStr">
         <is>
-          <t>Ticari EFT Paketi 1000 Ücreti</t>
+          <t>Ticari EFT Paketi 500 Ücreti</t>
         </is>
       </c>
       <c r="B1858" s="12" t="inlineStr"/>
@@ -32468,8 +32467,8 @@
       <c r="E1858" s="12" t="inlineStr"/>
       <c r="F1858" s="12" t="inlineStr">
         <is>
-          <t>619.047,62 TL
-maks: 619.047,62 TL</t>
+          <t>309.523,82 TL
+maks: 309.523,82 TL</t>
         </is>
       </c>
       <c r="G1858" s="12" t="inlineStr"/>
@@ -32479,7 +32478,7 @@
     <row r="1859" ht="32" customHeight="1">
       <c r="A1859" s="11" t="inlineStr">
         <is>
-          <t>Ticari Havale Paketi 100 Ücreti</t>
+          <t>Ticari EFT Paketi 1000 Ücreti</t>
         </is>
       </c>
       <c r="B1859" s="12" t="inlineStr"/>
@@ -32488,8 +32487,8 @@
       <c r="E1859" s="12" t="inlineStr"/>
       <c r="F1859" s="12" t="inlineStr">
         <is>
-          <t>30.476,20 TL
-maks: 30.476,20 TL</t>
+          <t>619.047,62 TL
+maks: 619.047,62 TL</t>
         </is>
       </c>
       <c r="G1859" s="12" t="inlineStr"/>
@@ -32499,7 +32498,7 @@
     <row r="1860" ht="32" customHeight="1">
       <c r="A1860" s="11" t="inlineStr">
         <is>
-          <t>Ticari Havale Paketi 500 Ücreti</t>
+          <t>Ticari Havale Paketi 100 Ücreti</t>
         </is>
       </c>
       <c r="B1860" s="12" t="inlineStr"/>
@@ -32508,8 +32507,8 @@
       <c r="E1860" s="12" t="inlineStr"/>
       <c r="F1860" s="12" t="inlineStr">
         <is>
-          <t>152.380,96 TL
-maks: 152.380,96 TL</t>
+          <t>30.476,20 TL
+maks: 30.476,20 TL</t>
         </is>
       </c>
       <c r="G1860" s="12" t="inlineStr"/>
@@ -32519,7 +32518,7 @@
     <row r="1861" ht="32" customHeight="1">
       <c r="A1861" s="11" t="inlineStr">
         <is>
-          <t>Ticari Havale Paketi 1000 Ücreti</t>
+          <t>Ticari Havale Paketi 500 Ücreti</t>
         </is>
       </c>
       <c r="B1861" s="12" t="inlineStr"/>
@@ -32528,8 +32527,8 @@
       <c r="E1861" s="12" t="inlineStr"/>
       <c r="F1861" s="12" t="inlineStr">
         <is>
-          <t>309.523,81 TL
-maks: 309.523,81 TL</t>
+          <t>152.380,96 TL
+maks: 152.380,96 TL</t>
         </is>
       </c>
       <c r="G1861" s="12" t="inlineStr"/>
@@ -32539,27 +32538,27 @@
     <row r="1862" ht="32" customHeight="1">
       <c r="A1862" s="11" t="inlineStr">
         <is>
-          <t>KOBİ Aktif Paket</t>
+          <t>Ticari Havale Paketi 1000 Ücreti</t>
         </is>
       </c>
       <c r="B1862" s="12" t="inlineStr"/>
       <c r="C1862" s="12" t="inlineStr"/>
       <c r="D1862" s="12" t="inlineStr"/>
       <c r="E1862" s="12" t="inlineStr"/>
-      <c r="F1862" s="12" t="inlineStr"/>
+      <c r="F1862" s="12" t="inlineStr">
+        <is>
+          <t>309.523,81 TL
+maks: 309.523,81 TL</t>
+        </is>
+      </c>
       <c r="G1862" s="12" t="inlineStr"/>
-      <c r="H1862" s="12" t="inlineStr">
-        <is>
-          <t>22.500 TL / -
-maks: 22.500 TL / -</t>
-        </is>
-      </c>
+      <c r="H1862" s="12" t="inlineStr"/>
       <c r="I1862" s="12" t="inlineStr"/>
     </row>
     <row r="1863" ht="32" customHeight="1">
       <c r="A1863" s="11" t="inlineStr">
         <is>
-          <t>Maxi Swift</t>
+          <t>KOBİ Aktif Paket</t>
         </is>
       </c>
       <c r="B1863" s="12" t="inlineStr"/>
@@ -32570,8 +32569,8 @@
       <c r="G1863" s="12" t="inlineStr"/>
       <c r="H1863" s="12" t="inlineStr">
         <is>
-          <t>1.750.000 TL / -
-maks: 1.750.000 TL / -</t>
+          <t>22.500 TL / -
+maks: 22.500 TL / -</t>
         </is>
       </c>
       <c r="I1863" s="12" t="inlineStr"/>
@@ -32579,7 +32578,7 @@
     <row r="1864" ht="32" customHeight="1">
       <c r="A1864" s="11" t="inlineStr">
         <is>
-          <t>Sınırları Kaldıran Kadınlar Paketi</t>
+          <t>Maxi Swift</t>
         </is>
       </c>
       <c r="B1864" s="12" t="inlineStr"/>
@@ -32590,8 +32589,8 @@
       <c r="G1864" s="12" t="inlineStr"/>
       <c r="H1864" s="12" t="inlineStr">
         <is>
-          <t>10.000 TL / -
-maks: 10.000 TL / -</t>
+          <t>1.750.000 TL / -
+maks: 1.750.000 TL / -</t>
         </is>
       </c>
       <c r="I1864" s="12" t="inlineStr"/>
@@ -32599,7 +32598,7 @@
     <row r="1865" ht="32" customHeight="1">
       <c r="A1865" s="11" t="inlineStr">
         <is>
-          <t>Midi Swift</t>
+          <t>Sınırları Kaldıran Kadınlar Paketi</t>
         </is>
       </c>
       <c r="B1865" s="12" t="inlineStr"/>
@@ -32610,8 +32609,8 @@
       <c r="G1865" s="12" t="inlineStr"/>
       <c r="H1865" s="12" t="inlineStr">
         <is>
-          <t>950.000 TL / -
-maks: 950.000 TL / -</t>
+          <t>10.000 TL / -
+maks: 10.000 TL / -</t>
         </is>
       </c>
       <c r="I1865" s="12" t="inlineStr"/>
@@ -32619,7 +32618,7 @@
     <row r="1866" ht="32" customHeight="1">
       <c r="A1866" s="11" t="inlineStr">
         <is>
-          <t>Mini Swift</t>
+          <t>Midi Swift</t>
         </is>
       </c>
       <c r="B1866" s="12" t="inlineStr"/>
@@ -32630,8 +32629,8 @@
       <c r="G1866" s="12" t="inlineStr"/>
       <c r="H1866" s="12" t="inlineStr">
         <is>
-          <t>650.000 TL / -
-maks: 650.000 TL / -</t>
+          <t>950.000 TL / -
+maks: 950.000 TL / -</t>
         </is>
       </c>
       <c r="I1866" s="12" t="inlineStr"/>
@@ -32639,7 +32638,7 @@
     <row r="1867" ht="32" customHeight="1">
       <c r="A1867" s="11" t="inlineStr">
         <is>
-          <t>Maxi Plus Dış Ticaret Paketi</t>
+          <t>Mini Swift</t>
         </is>
       </c>
       <c r="B1867" s="12" t="inlineStr"/>
@@ -32650,8 +32649,8 @@
       <c r="G1867" s="12" t="inlineStr"/>
       <c r="H1867" s="12" t="inlineStr">
         <is>
-          <t>900.000 TL / -
-maks: 900.000 TL / -</t>
+          <t>650.000 TL / -
+maks: 650.000 TL / -</t>
         </is>
       </c>
       <c r="I1867" s="12" t="inlineStr"/>
@@ -32659,7 +32658,7 @@
     <row r="1868" ht="32" customHeight="1">
       <c r="A1868" s="11" t="inlineStr">
         <is>
-          <t>Kobi Hoş Geldin Paketi</t>
+          <t>Maxi Plus Dış Ticaret Paketi</t>
         </is>
       </c>
       <c r="B1868" s="12" t="inlineStr"/>
@@ -32670,8 +32669,8 @@
       <c r="G1868" s="12" t="inlineStr"/>
       <c r="H1868" s="12" t="inlineStr">
         <is>
-          <t>20.000 TL / -
-maks: 20.000 TL / -</t>
+          <t>900.000 TL / -
+maks: 900.000 TL / -</t>
         </is>
       </c>
       <c r="I1868" s="12" t="inlineStr"/>
@@ -32679,7 +32678,7 @@
     <row r="1869" ht="32" customHeight="1">
       <c r="A1869" s="11" t="inlineStr">
         <is>
-          <t>Maxi Karma Paket</t>
+          <t>Kobi Hoş Geldin Paketi</t>
         </is>
       </c>
       <c r="B1869" s="12" t="inlineStr"/>
@@ -32690,8 +32689,8 @@
       <c r="G1869" s="12" t="inlineStr"/>
       <c r="H1869" s="12" t="inlineStr">
         <is>
-          <t>250.000 TL / -
-maks: 250.000 TL / -</t>
+          <t>20.000 TL / -
+maks: 20.000 TL / -</t>
         </is>
       </c>
       <c r="I1869" s="12" t="inlineStr"/>
@@ -32699,7 +32698,7 @@
     <row r="1870" ht="32" customHeight="1">
       <c r="A1870" s="11" t="inlineStr">
         <is>
-          <t>Karma Paket</t>
+          <t>Maxi Karma Paket</t>
         </is>
       </c>
       <c r="B1870" s="12" t="inlineStr"/>
@@ -32710,8 +32709,8 @@
       <c r="G1870" s="12" t="inlineStr"/>
       <c r="H1870" s="12" t="inlineStr">
         <is>
-          <t>70.000 TL / -
-maks: 70.000 TL / -</t>
+          <t>250.000 TL / -
+maks: 250.000 TL / -</t>
         </is>
       </c>
       <c r="I1870" s="12" t="inlineStr"/>
@@ -32719,7 +32718,7 @@
     <row r="1871" ht="32" customHeight="1">
       <c r="A1871" s="11" t="inlineStr">
         <is>
-          <t>Mini Karma Paket</t>
+          <t>Karma Paket</t>
         </is>
       </c>
       <c r="B1871" s="12" t="inlineStr"/>
@@ -32730,8 +32729,8 @@
       <c r="G1871" s="12" t="inlineStr"/>
       <c r="H1871" s="12" t="inlineStr">
         <is>
-          <t>25.000 TL / -
-maks: 25.000 TL / -</t>
+          <t>70.000 TL / -
+maks: 70.000 TL / -</t>
         </is>
       </c>
       <c r="I1871" s="12" t="inlineStr"/>
@@ -32739,7 +32738,7 @@
     <row r="1872" ht="32" customHeight="1">
       <c r="A1872" s="11" t="inlineStr">
         <is>
-          <t>Maxi Dış Ticaret Paketi (Yıllık)</t>
+          <t>Mini Karma Paket</t>
         </is>
       </c>
       <c r="B1872" s="12" t="inlineStr"/>
@@ -32750,8 +32749,8 @@
       <c r="G1872" s="12" t="inlineStr"/>
       <c r="H1872" s="12" t="inlineStr">
         <is>
-          <t>450.000 TL / -
-maks: 450.000 TL / -</t>
+          <t>25.000 TL / -
+maks: 25.000 TL / -</t>
         </is>
       </c>
       <c r="I1872" s="12" t="inlineStr"/>
@@ -32759,7 +32758,7 @@
     <row r="1873" ht="32" customHeight="1">
       <c r="A1873" s="11" t="inlineStr">
         <is>
-          <t>Dış Ticaret Paketi (Yıllık)</t>
+          <t>Maxi Dış Ticaret Paketi (Yıllık)</t>
         </is>
       </c>
       <c r="B1873" s="12" t="inlineStr"/>
@@ -32770,8 +32769,8 @@
       <c r="G1873" s="12" t="inlineStr"/>
       <c r="H1873" s="12" t="inlineStr">
         <is>
-          <t>225.000 TL / -
-maks: 225.000 TL / -</t>
+          <t>450.000 TL / -
+maks: 450.000 TL / -</t>
         </is>
       </c>
       <c r="I1873" s="12" t="inlineStr"/>
@@ -32779,7 +32778,7 @@
     <row r="1874" ht="32" customHeight="1">
       <c r="A1874" s="11" t="inlineStr">
         <is>
-          <t>İşlem Paketi (Yıllık)</t>
+          <t>Dış Ticaret Paketi (Yıllık)</t>
         </is>
       </c>
       <c r="B1874" s="12" t="inlineStr"/>
@@ -32790,8 +32789,8 @@
       <c r="G1874" s="12" t="inlineStr"/>
       <c r="H1874" s="12" t="inlineStr">
         <is>
-          <t>70.000 TL / -
-maks: 70.000 TL / -</t>
+          <t>225.000 TL / -
+maks: 225.000 TL / -</t>
         </is>
       </c>
       <c r="I1874" s="12" t="inlineStr"/>
@@ -32799,7 +32798,7 @@
     <row r="1875" ht="32" customHeight="1">
       <c r="A1875" s="11" t="inlineStr">
         <is>
-          <t>Çek ve Senet Paketi (Yıllık)</t>
+          <t>İşlem Paketi (Yıllık)</t>
         </is>
       </c>
       <c r="B1875" s="12" t="inlineStr"/>
@@ -32810,8 +32809,8 @@
       <c r="G1875" s="12" t="inlineStr"/>
       <c r="H1875" s="12" t="inlineStr">
         <is>
-          <t>40.000 TL / -
-maks: 40.000 TL / -</t>
+          <t>70.000 TL / -
+maks: 70.000 TL / -</t>
         </is>
       </c>
       <c r="I1875" s="12" t="inlineStr"/>
@@ -32819,7 +32818,7 @@
     <row r="1876" ht="32" customHeight="1">
       <c r="A1876" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Mini Çek Paketi</t>
+          <t>Çek ve Senet Paketi (Yıllık)</t>
         </is>
       </c>
       <c r="B1876" s="12" t="inlineStr"/>
@@ -32830,8 +32829,8 @@
       <c r="G1876" s="12" t="inlineStr"/>
       <c r="H1876" s="12" t="inlineStr">
         <is>
-          <t>20.000 TL / -
-maks: 20.000 TL / -</t>
+          <t>40.000 TL / -
+maks: 40.000 TL / -</t>
         </is>
       </c>
       <c r="I1876" s="12" t="inlineStr"/>
@@ -32839,7 +32838,7 @@
     <row r="1877" ht="32" customHeight="1">
       <c r="A1877" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Midi Çek Paketi</t>
+          <t>Yıllık Mini Çek Paketi</t>
         </is>
       </c>
       <c r="B1877" s="12" t="inlineStr"/>
@@ -32850,8 +32849,8 @@
       <c r="G1877" s="12" t="inlineStr"/>
       <c r="H1877" s="12" t="inlineStr">
         <is>
-          <t>35.000 TL / -
-maks: 35.000 TL / -</t>
+          <t>20.000 TL / -
+maks: 20.000 TL / -</t>
         </is>
       </c>
       <c r="I1877" s="12" t="inlineStr"/>
@@ -32859,7 +32858,7 @@
     <row r="1878" ht="32" customHeight="1">
       <c r="A1878" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Maxi Çek Paketi</t>
+          <t>Yıllık Midi Çek Paketi</t>
         </is>
       </c>
       <c r="B1878" s="12" t="inlineStr"/>
@@ -32870,8 +32869,8 @@
       <c r="G1878" s="12" t="inlineStr"/>
       <c r="H1878" s="12" t="inlineStr">
         <is>
-          <t>70.000 TL / -
-maks: 70.000 TL / -</t>
+          <t>35.000 TL / -
+maks: 35.000 TL / -</t>
         </is>
       </c>
       <c r="I1878" s="12" t="inlineStr"/>
@@ -32879,7 +32878,7 @@
     <row r="1879" ht="32" customHeight="1">
       <c r="A1879" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Tahsil Çeki Paketi</t>
+          <t>Yıllık Maxi Çek Paketi</t>
         </is>
       </c>
       <c r="B1879" s="12" t="inlineStr"/>
@@ -32890,43 +32889,43 @@
       <c r="G1879" s="12" t="inlineStr"/>
       <c r="H1879" s="12" t="inlineStr">
         <is>
+          <t>70.000 TL / -
+maks: 70.000 TL / -</t>
+        </is>
+      </c>
+      <c r="I1879" s="12" t="inlineStr"/>
+    </row>
+    <row r="1880" ht="32" customHeight="1">
+      <c r="A1880" s="11" t="inlineStr">
+        <is>
+          <t>Yıllık Tahsil Çeki Paketi</t>
+        </is>
+      </c>
+      <c r="B1880" s="12" t="inlineStr"/>
+      <c r="C1880" s="12" t="inlineStr"/>
+      <c r="D1880" s="12" t="inlineStr"/>
+      <c r="E1880" s="12" t="inlineStr"/>
+      <c r="F1880" s="12" t="inlineStr"/>
+      <c r="G1880" s="12" t="inlineStr"/>
+      <c r="H1880" s="12" t="inlineStr">
+        <is>
           <t>25.000 TL / -
 maks: 25.000 TL / -</t>
         </is>
       </c>
-      <c r="I1879" s="12" t="inlineStr"/>
-    </row>
-    <row r="1880" ht="16" customHeight="1">
-      <c r="A1880" s="10" t="inlineStr">
+      <c r="I1880" s="12" t="inlineStr"/>
+    </row>
+    <row r="1881" ht="16" customHeight="1">
+      <c r="A1881" s="10" t="inlineStr">
         <is>
           <t>Uluslararası Fon Transferi ve Mesajlaşma Ücreti / SWIFT</t>
         </is>
       </c>
-    </row>
-    <row r="1881" ht="32" customHeight="1">
-      <c r="A1881" s="11" t="inlineStr">
-        <is>
-          <t>İnternet / Mobil / Telefon Bankacılığından - Aynı Gün Valörlü</t>
-        </is>
-      </c>
-      <c r="B1881" s="12" t="inlineStr"/>
-      <c r="C1881" s="12" t="inlineStr"/>
-      <c r="D1881" s="12" t="inlineStr"/>
-      <c r="E1881" s="12" t="inlineStr"/>
-      <c r="F1881" s="12" t="inlineStr"/>
-      <c r="G1881" s="12" t="inlineStr"/>
-      <c r="H1881" s="12" t="inlineStr">
-        <is>
-          <t>1.547,62 TL / -
-maks: 3.033,33 TL / 0,7</t>
-        </is>
-      </c>
-      <c r="I1881" s="12" t="inlineStr"/>
     </row>
     <row r="1882" ht="32" customHeight="1">
       <c r="A1882" s="11" t="inlineStr">
         <is>
-          <t>İnternet / Mobil / Telefon Bankacılığından - 1 Gün Valörlü</t>
+          <t>İnternet / Mobil / Telefon Bankacılığından - Aynı Gün Valörlü</t>
         </is>
       </c>
       <c r="B1882" s="12" t="inlineStr"/>
@@ -32937,8 +32936,8 @@
       <c r="G1882" s="12" t="inlineStr"/>
       <c r="H1882" s="12" t="inlineStr">
         <is>
-          <t>1.423,81 TL / -
-maks: 2.909,53 TL / 0,7</t>
+          <t>1.547,62 TL / -
+maks: 3.033,33 TL / 0,7</t>
         </is>
       </c>
       <c r="I1882" s="12" t="inlineStr"/>
@@ -32946,7 +32945,7 @@
     <row r="1883" ht="32" customHeight="1">
       <c r="A1883" s="11" t="inlineStr">
         <is>
-          <t>İnternet / Mobil / Telefon Bankacılığından - İleri Gün Valörlü</t>
+          <t>İnternet / Mobil / Telefon Bankacılığından - 1 Gün Valörlü</t>
         </is>
       </c>
       <c r="B1883" s="12" t="inlineStr"/>
@@ -32957,8 +32956,8 @@
       <c r="G1883" s="12" t="inlineStr"/>
       <c r="H1883" s="12" t="inlineStr">
         <is>
-          <t>1.238,09 TL / -
-maks: 2.785,72 TL / 0,7</t>
+          <t>1.423,81 TL / -
+maks: 2.909,53 TL / 0,7</t>
         </is>
       </c>
       <c r="I1883" s="12" t="inlineStr"/>
@@ -32966,7 +32965,7 @@
     <row r="1884" ht="32" customHeight="1">
       <c r="A1884" s="11" t="inlineStr">
         <is>
-          <t>Şubeden - Aynı Gün Valörlü</t>
+          <t>İnternet / Mobil / Telefon Bankacılığından - İleri Gün Valörlü</t>
         </is>
       </c>
       <c r="B1884" s="12" t="inlineStr"/>
@@ -32975,18 +32974,18 @@
       <c r="E1884" s="12" t="inlineStr"/>
       <c r="F1884" s="12" t="inlineStr"/>
       <c r="G1884" s="12" t="inlineStr"/>
-      <c r="H1884" s="12" t="inlineStr"/>
-      <c r="I1884" s="12" t="inlineStr">
-        <is>
-          <t>2.785,72 TL / -
-maks: 12.380,95 TL / 0,7</t>
-        </is>
-      </c>
+      <c r="H1884" s="12" t="inlineStr">
+        <is>
+          <t>1.238,09 TL / -
+maks: 2.785,72 TL / 0,7</t>
+        </is>
+      </c>
+      <c r="I1884" s="12" t="inlineStr"/>
     </row>
     <row r="1885" ht="32" customHeight="1">
       <c r="A1885" s="11" t="inlineStr">
         <is>
-          <t>Şubeden - 1 Gün Valörlü</t>
+          <t>Şubeden - Aynı Gün Valörlü</t>
         </is>
       </c>
       <c r="B1885" s="12" t="inlineStr"/>
@@ -32998,15 +32997,15 @@
       <c r="H1885" s="12" t="inlineStr"/>
       <c r="I1885" s="12" t="inlineStr">
         <is>
-          <t>2.661,91 TL / -
-maks: 12.195,24 TL / 0,7</t>
+          <t>2.785,72 TL / -
+maks: 12.380,95 TL / 0,7</t>
         </is>
       </c>
     </row>
     <row r="1886" ht="32" customHeight="1">
       <c r="A1886" s="11" t="inlineStr">
         <is>
-          <t>Şubeden - İleri Gün Valörlü</t>
+          <t>Şubeden - 1 Gün Valörlü</t>
         </is>
       </c>
       <c r="B1886" s="12" t="inlineStr"/>
@@ -33018,15 +33017,15 @@
       <c r="H1886" s="12" t="inlineStr"/>
       <c r="I1886" s="12" t="inlineStr">
         <is>
-          <t>2.538,09 TL / -
-maks: 12.071,43 TL / 0,7</t>
+          <t>2.661,91 TL / -
+maks: 12.195,24 TL / 0,7</t>
         </is>
       </c>
     </row>
     <row r="1887" ht="32" customHeight="1">
       <c r="A1887" s="11" t="inlineStr">
         <is>
-          <t>Uluslararası Fon Transferi ve Mesajlaşma Ücreti -  Gelen Döviz Havale</t>
+          <t>Şubeden - İleri Gün Valörlü</t>
         </is>
       </c>
       <c r="B1887" s="12" t="inlineStr"/>
@@ -33035,18 +33034,18 @@
       <c r="E1887" s="12" t="inlineStr"/>
       <c r="F1887" s="12" t="inlineStr"/>
       <c r="G1887" s="12" t="inlineStr"/>
-      <c r="H1887" s="12" t="inlineStr">
-        <is>
-          <t>1.176,19 TL / 0,6
-maks: 7.335,72 TL / 0,6</t>
-        </is>
-      </c>
-      <c r="I1887" s="12" t="inlineStr"/>
+      <c r="H1887" s="12" t="inlineStr"/>
+      <c r="I1887" s="12" t="inlineStr">
+        <is>
+          <t>2.538,09 TL / -
+maks: 12.071,43 TL / 0,7</t>
+        </is>
+      </c>
     </row>
     <row r="1888" ht="32" customHeight="1">
       <c r="A1888" s="11" t="inlineStr">
         <is>
-          <t>Gelen Araştırma/İade</t>
+          <t>Uluslararası Fon Transferi ve Mesajlaşma Ücreti -  Gelen Döviz Havale</t>
         </is>
       </c>
       <c r="B1888" s="12" t="inlineStr"/>
@@ -33057,8 +33056,8 @@
       <c r="G1888" s="12" t="inlineStr"/>
       <c r="H1888" s="12" t="inlineStr">
         <is>
-          <t>795 TL / -
-maks: 4.005 TL / -</t>
+          <t>1.176,19 TL / 0,6
+maks: 7.335,72 TL / 0,6</t>
         </is>
       </c>
       <c r="I1888" s="12" t="inlineStr"/>
@@ -33066,7 +33065,7 @@
     <row r="1889" ht="32" customHeight="1">
       <c r="A1889" s="11" t="inlineStr">
         <is>
-          <t>İsme Gelen EFT</t>
+          <t>Gelen Araştırma/İade</t>
         </is>
       </c>
       <c r="B1889" s="12" t="inlineStr"/>
@@ -33077,8 +33076,8 @@
       <c r="G1889" s="12" t="inlineStr"/>
       <c r="H1889" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: - / -</t>
+          <t>795 TL / -
+maks: 4.005 TL / -</t>
         </is>
       </c>
       <c r="I1889" s="12" t="inlineStr"/>
@@ -33086,7 +33085,7 @@
     <row r="1890" ht="32" customHeight="1">
       <c r="A1890" s="11" t="inlineStr">
         <is>
-          <t>İnternet/Mobil – 399.000,01 TL ve Üzeri</t>
+          <t>İsme Gelen EFT</t>
         </is>
       </c>
       <c r="B1890" s="12" t="inlineStr"/>
@@ -33097,8 +33096,8 @@
       <c r="G1890" s="12" t="inlineStr"/>
       <c r="H1890" s="12" t="inlineStr">
         <is>
-          <t>99,71 TL / -
-maks: 99,71 TL / -</t>
+          <t>- / -
+maks: - / -</t>
         </is>
       </c>
       <c r="I1890" s="12" t="inlineStr"/>
@@ -33106,7 +33105,7 @@
     <row r="1891" ht="32" customHeight="1">
       <c r="A1891" s="11" t="inlineStr">
         <is>
-          <t>Geç - İnternet/Mobil – 0 - 8.300 TL</t>
+          <t>İnternet/Mobil – 399.000,01 TL ve Üzeri</t>
         </is>
       </c>
       <c r="B1891" s="12" t="inlineStr"/>
@@ -33117,8 +33116,8 @@
       <c r="G1891" s="12" t="inlineStr"/>
       <c r="H1891" s="12" t="inlineStr">
         <is>
-          <t>7,97 TL / -
-maks: 7,97 TL / -</t>
+          <t>99,71 TL / -
+maks: 99,71 TL / -</t>
         </is>
       </c>
       <c r="I1891" s="12" t="inlineStr"/>
@@ -33126,7 +33125,7 @@
     <row r="1892" ht="32" customHeight="1">
       <c r="A1892" s="11" t="inlineStr">
         <is>
-          <t>Geç - İnternet/Mobil – 8.300,01 TL – 399.000 TL</t>
+          <t>Geç - İnternet/Mobil – 0 - 8.300 TL</t>
         </is>
       </c>
       <c r="B1892" s="12" t="inlineStr"/>
@@ -33137,8 +33136,8 @@
       <c r="G1892" s="12" t="inlineStr"/>
       <c r="H1892" s="12" t="inlineStr">
         <is>
-          <t>15,96 TL / -
-maks: 15,96 TL / -</t>
+          <t>7,97 TL / -
+maks: 7,97 TL / -</t>
         </is>
       </c>
       <c r="I1892" s="12" t="inlineStr"/>
@@ -33146,7 +33145,7 @@
     <row r="1893" ht="32" customHeight="1">
       <c r="A1893" s="11" t="inlineStr">
         <is>
-          <t>Geç - İnternet/Mobil –  399.000,01 TL ve Üzeri</t>
+          <t>Geç - İnternet/Mobil – 8.300,01 TL – 399.000 TL</t>
         </is>
       </c>
       <c r="B1893" s="12" t="inlineStr"/>
@@ -33157,8 +33156,8 @@
       <c r="G1893" s="12" t="inlineStr"/>
       <c r="H1893" s="12" t="inlineStr">
         <is>
-          <t>199,41 TL / -
-maks: 199,41 TL / -</t>
+          <t>15,96 TL / -
+maks: 15,96 TL / -</t>
         </is>
       </c>
       <c r="I1893" s="12" t="inlineStr"/>
@@ -33166,7 +33165,7 @@
     <row r="1894" ht="32" customHeight="1">
       <c r="A1894" s="11" t="inlineStr">
         <is>
-          <t>Şube/Diğer – 0 - 8.300 TL</t>
+          <t>Geç - İnternet/Mobil –  399.000,01 TL ve Üzeri</t>
         </is>
       </c>
       <c r="B1894" s="12" t="inlineStr"/>
@@ -33175,18 +33174,18 @@
       <c r="E1894" s="12" t="inlineStr"/>
       <c r="F1894" s="12" t="inlineStr"/>
       <c r="G1894" s="12" t="inlineStr"/>
-      <c r="H1894" s="12" t="inlineStr"/>
-      <c r="I1894" s="12" t="inlineStr">
-        <is>
-          <t>19,94 TL / -
-maks: 19,94 TL / -</t>
-        </is>
-      </c>
+      <c r="H1894" s="12" t="inlineStr">
+        <is>
+          <t>199,41 TL / -
+maks: 199,41 TL / -</t>
+        </is>
+      </c>
+      <c r="I1894" s="12" t="inlineStr"/>
     </row>
     <row r="1895" ht="32" customHeight="1">
       <c r="A1895" s="11" t="inlineStr">
         <is>
-          <t>Şube/Diğer – 8.300,01 TL – 399.000 TL</t>
+          <t>Şube/Diğer – 0 - 8.300 TL</t>
         </is>
       </c>
       <c r="B1895" s="12" t="inlineStr"/>
@@ -33198,15 +33197,15 @@
       <c r="H1895" s="12" t="inlineStr"/>
       <c r="I1895" s="12" t="inlineStr">
         <is>
-          <t>39,88 TL / -
-maks: 39,88 TL / -</t>
+          <t>19,94 TL / -
+maks: 19,94 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1896" ht="32" customHeight="1">
       <c r="A1896" s="11" t="inlineStr">
         <is>
-          <t>Şube/Diğer – 399.000,01 TL ve Üzeri</t>
+          <t>Şube/Diğer – 8.300,01 TL – 399.000 TL</t>
         </is>
       </c>
       <c r="B1896" s="12" t="inlineStr"/>
@@ -33218,15 +33217,15 @@
       <c r="H1896" s="12" t="inlineStr"/>
       <c r="I1896" s="12" t="inlineStr">
         <is>
-          <t>398,84 TL / -
-maks: 398,84 TL / -</t>
+          <t>39,88 TL / -
+maks: 39,88 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1897" ht="32" customHeight="1">
       <c r="A1897" s="11" t="inlineStr">
         <is>
-          <t>Geç - Şube/Diğer – 0 - 8.300 TL</t>
+          <t>Şube/Diğer – 399.000,01 TL ve Üzeri</t>
         </is>
       </c>
       <c r="B1897" s="12" t="inlineStr"/>
@@ -33238,15 +33237,15 @@
       <c r="H1897" s="12" t="inlineStr"/>
       <c r="I1897" s="12" t="inlineStr">
         <is>
-          <t>39,87 TL / -
-maks: 39,87 TL / -</t>
+          <t>398,84 TL / -
+maks: 398,84 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1898" ht="32" customHeight="1">
       <c r="A1898" s="11" t="inlineStr">
         <is>
-          <t>Geç - Şube/Diğer – 8.300,01 TL – 399.000 TL</t>
+          <t>Geç - Şube/Diğer – 0 - 8.300 TL</t>
         </is>
       </c>
       <c r="B1898" s="12" t="inlineStr"/>
@@ -33258,15 +33257,15 @@
       <c r="H1898" s="12" t="inlineStr"/>
       <c r="I1898" s="12" t="inlineStr">
         <is>
-          <t>79,76 TL / -
-maks: 79,76 TL / -</t>
+          <t>39,87 TL / -
+maks: 39,87 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1899" ht="32" customHeight="1">
       <c r="A1899" s="11" t="inlineStr">
         <is>
-          <t>Geç - Şube/Diğer – 399.000,01 TL ve Üzeri</t>
+          <t>Geç - Şube/Diğer – 8.300,01 TL – 399.000 TL</t>
         </is>
       </c>
       <c r="B1899" s="12" t="inlineStr"/>
@@ -33278,42 +33277,42 @@
       <c r="H1899" s="12" t="inlineStr"/>
       <c r="I1899" s="12" t="inlineStr">
         <is>
+          <t>79,76 TL / -
+maks: 79,76 TL / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900" ht="32" customHeight="1">
+      <c r="A1900" s="11" t="inlineStr">
+        <is>
+          <t>Geç - Şube/Diğer – 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B1900" s="12" t="inlineStr"/>
+      <c r="C1900" s="12" t="inlineStr"/>
+      <c r="D1900" s="12" t="inlineStr"/>
+      <c r="E1900" s="12" t="inlineStr"/>
+      <c r="F1900" s="12" t="inlineStr"/>
+      <c r="G1900" s="12" t="inlineStr"/>
+      <c r="H1900" s="12" t="inlineStr"/>
+      <c r="I1900" s="12" t="inlineStr">
+        <is>
           <t>797,68 TL / -
 maks: 797,68 TL / -</t>
         </is>
       </c>
     </row>
-    <row r="1900" ht="16" customHeight="1">
-      <c r="A1900" s="10" t="inlineStr">
+    <row r="1901" ht="16" customHeight="1">
+      <c r="A1901" s="10" t="inlineStr">
         <is>
           <t>Havale</t>
         </is>
       </c>
-    </row>
-    <row r="1901" ht="32" customHeight="1">
-      <c r="A1901" s="11" t="inlineStr">
-        <is>
-          <t>ATM – 0 - 8.300 TL</t>
-        </is>
-      </c>
-      <c r="B1901" s="12" t="inlineStr"/>
-      <c r="C1901" s="12" t="inlineStr"/>
-      <c r="D1901" s="12" t="inlineStr"/>
-      <c r="E1901" s="12" t="inlineStr"/>
-      <c r="F1901" s="12" t="inlineStr"/>
-      <c r="G1901" s="12" t="inlineStr"/>
-      <c r="H1901" s="12" t="inlineStr">
-        <is>
-          <t>13,92 TL / -
-maks: 13,92 TL / -</t>
-        </is>
-      </c>
-      <c r="I1901" s="12" t="inlineStr"/>
     </row>
     <row r="1902" ht="32" customHeight="1">
       <c r="A1902" s="11" t="inlineStr">
         <is>
-          <t>ATM – 8.300,01 TL – 399.000 TL</t>
+          <t>ATM – 0 - 8.300 TL</t>
         </is>
       </c>
       <c r="B1902" s="12" t="inlineStr"/>
@@ -33324,8 +33323,8 @@
       <c r="G1902" s="12" t="inlineStr"/>
       <c r="H1902" s="12" t="inlineStr">
         <is>
-          <t>27,85 TL / -
-maks: 27,85 TL / -</t>
+          <t>13,92 TL / -
+maks: 13,92 TL / -</t>
         </is>
       </c>
       <c r="I1902" s="12" t="inlineStr"/>
@@ -33333,7 +33332,7 @@
     <row r="1903" ht="32" customHeight="1">
       <c r="A1903" s="11" t="inlineStr">
         <is>
-          <t>ATM – 399.000,01 TL ve Üzeri</t>
+          <t>ATM – 8.300,01 TL – 399.000 TL</t>
         </is>
       </c>
       <c r="B1903" s="12" t="inlineStr"/>
@@ -33344,48 +33343,43 @@
       <c r="G1903" s="12" t="inlineStr"/>
       <c r="H1903" s="12" t="inlineStr">
         <is>
+          <t>27,85 TL / -
+maks: 27,85 TL / -</t>
+        </is>
+      </c>
+      <c r="I1903" s="12" t="inlineStr"/>
+    </row>
+    <row r="1904" ht="32" customHeight="1">
+      <c r="A1904" s="11" t="inlineStr">
+        <is>
+          <t>ATM – 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B1904" s="12" t="inlineStr"/>
+      <c r="C1904" s="12" t="inlineStr"/>
+      <c r="D1904" s="12" t="inlineStr"/>
+      <c r="E1904" s="12" t="inlineStr"/>
+      <c r="F1904" s="12" t="inlineStr"/>
+      <c r="G1904" s="12" t="inlineStr"/>
+      <c r="H1904" s="12" t="inlineStr">
+        <is>
           <t>199,42 TL / -
 maks: 199,42 TL / -</t>
         </is>
       </c>
-      <c r="I1903" s="12" t="inlineStr"/>
-    </row>
-    <row r="1904" ht="16" customHeight="1">
-      <c r="A1904" s="10" t="inlineStr">
+      <c r="I1904" s="12" t="inlineStr"/>
+    </row>
+    <row r="1905" ht="16" customHeight="1">
+      <c r="A1905" s="10" t="inlineStr">
         <is>
           <t>Banka Kartı</t>
-        </is>
-      </c>
-    </row>
-    <row r="1905" ht="32" customHeight="1">
-      <c r="A1905" s="11" t="inlineStr">
-        <is>
-          <t>TLcard</t>
-        </is>
-      </c>
-      <c r="B1905" s="12" t="inlineStr"/>
-      <c r="C1905" s="12" t="inlineStr"/>
-      <c r="D1905" s="12" t="inlineStr"/>
-      <c r="E1905" s="12" t="inlineStr"/>
-      <c r="F1905" s="12" t="inlineStr"/>
-      <c r="G1905" s="12" t="inlineStr"/>
-      <c r="H1905" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 0,27 TL / -</t>
-        </is>
-      </c>
-      <c r="I1905" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 3 USD / -</t>
         </is>
       </c>
     </row>
     <row r="1906" ht="32" customHeight="1">
       <c r="A1906" s="11" t="inlineStr">
         <is>
-          <t>Play TLcard</t>
+          <t>TLcard</t>
         </is>
       </c>
       <c r="B1906" s="12" t="inlineStr"/>
@@ -33402,15 +33396,15 @@
       </c>
       <c r="I1906" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: 3 USD / -</t>
+          <t>4 USD / 1,5
+maks: 9 USD / -</t>
         </is>
       </c>
     </row>
     <row r="1907" ht="32" customHeight="1">
       <c r="A1907" s="11" t="inlineStr">
         <is>
-          <t>Platinum TLcard</t>
+          <t>Play TLcard</t>
         </is>
       </c>
       <c r="B1907" s="12" t="inlineStr"/>
@@ -33427,15 +33421,15 @@
       </c>
       <c r="I1907" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: 3 USD / -</t>
+          <t>4 USD / 1,5
+maks: 9 USD / -</t>
         </is>
       </c>
     </row>
     <row r="1908" ht="32" customHeight="1">
       <c r="A1908" s="11" t="inlineStr">
         <is>
-          <t>Ortak ATM'lerden Para Çekme</t>
+          <t>Platinum TLcard</t>
         </is>
       </c>
       <c r="B1908" s="12" t="inlineStr"/>
@@ -33447,47 +33441,47 @@
       <c r="H1908" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: 0,27 TL / -</t>
+        </is>
+      </c>
+      <c r="I1908" s="12" t="inlineStr">
+        <is>
+          <t>4 USD / 1,5
+maks: 9 USD / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909" ht="32" customHeight="1">
+      <c r="A1909" s="11" t="inlineStr">
+        <is>
+          <t>Ortak ATM'lerden Para Çekme</t>
+        </is>
+      </c>
+      <c r="B1909" s="12" t="inlineStr"/>
+      <c r="C1909" s="12" t="inlineStr"/>
+      <c r="D1909" s="12" t="inlineStr"/>
+      <c r="E1909" s="12" t="inlineStr"/>
+      <c r="F1909" s="12" t="inlineStr"/>
+      <c r="G1909" s="12" t="inlineStr"/>
+      <c r="H1909" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: - / 1,15</t>
         </is>
       </c>
-      <c r="I1908" s="12" t="inlineStr"/>
-    </row>
-    <row r="1909" ht="16" customHeight="1">
-      <c r="A1909" s="10" t="inlineStr">
+      <c r="I1909" s="12" t="inlineStr"/>
+    </row>
+    <row r="1910" ht="16" customHeight="1">
+      <c r="A1910" s="10" t="inlineStr">
         <is>
           <t>Kredi Kartı Yıllık Üyelik Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="1910" ht="32" customHeight="1">
-      <c r="A1910" s="11" t="inlineStr">
-        <is>
-          <t>World Business Kart</t>
-        </is>
-      </c>
-      <c r="B1910" s="12" t="inlineStr"/>
-      <c r="C1910" s="12" t="inlineStr"/>
-      <c r="D1910" s="12" t="inlineStr"/>
-      <c r="E1910" s="12" t="inlineStr"/>
-      <c r="F1910" s="12" t="inlineStr"/>
-      <c r="G1910" s="12" t="inlineStr"/>
-      <c r="H1910" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / 4,25</t>
-        </is>
-      </c>
-      <c r="I1910" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / 4,55</t>
         </is>
       </c>
     </row>
     <row r="1911" ht="32" customHeight="1">
       <c r="A1911" s="11" t="inlineStr">
         <is>
-          <t>Worldcard</t>
+          <t>World Business Kart</t>
         </is>
       </c>
       <c r="B1911" s="12" t="inlineStr"/>
@@ -33499,20 +33493,20 @@
       <c r="H1911" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.107 TL / -</t>
+maks: - / 4,25</t>
         </is>
       </c>
       <c r="I1911" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 553,5 TL / -</t>
+maks: - / 4,55</t>
         </is>
       </c>
     </row>
     <row r="1912" ht="32" customHeight="1">
       <c r="A1912" s="11" t="inlineStr">
         <is>
-          <t>World Gold</t>
+          <t>Worldcard</t>
         </is>
       </c>
       <c r="B1912" s="12" t="inlineStr"/>
@@ -33524,20 +33518,20 @@
       <c r="H1912" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.258 TL / -</t>
+maks: 1.107 TL / -</t>
         </is>
       </c>
       <c r="I1912" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 629 TL / -</t>
+maks: 553,5 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1913" ht="32" customHeight="1">
       <c r="A1913" s="11" t="inlineStr">
         <is>
-          <t>World Platinum</t>
+          <t>World Gold</t>
         </is>
       </c>
       <c r="B1913" s="12" t="inlineStr"/>
@@ -33549,20 +33543,20 @@
       <c r="H1913" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.420 TL / -</t>
+maks: 1.258 TL / -</t>
         </is>
       </c>
       <c r="I1913" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 710 TL / -</t>
+maks: 629 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1914" ht="32" customHeight="1">
       <c r="A1914" s="11" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>World Platinum</t>
         </is>
       </c>
       <c r="B1914" s="12" t="inlineStr"/>
@@ -33574,20 +33568,20 @@
       <c r="H1914" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 4.800 TL / -</t>
+maks: 1.420 TL / -</t>
         </is>
       </c>
       <c r="I1914" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.590 TL / -</t>
+maks: 710 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1915" ht="32" customHeight="1">
       <c r="A1915" s="11" t="inlineStr">
         <is>
-          <t>Crystal (Metal Kart)</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B1915" s="12" t="inlineStr"/>
@@ -33599,20 +33593,20 @@
       <c r="H1915" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 30.700 TL / -</t>
+maks: 4.800 TL / -</t>
         </is>
       </c>
       <c r="I1915" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 15.350 TL / -</t>
+maks: 1.590 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1916" ht="32" customHeight="1">
       <c r="A1916" s="11" t="inlineStr">
         <is>
-          <t>Play Kart</t>
+          <t>Crystal (Metal Kart)</t>
         </is>
       </c>
       <c r="B1916" s="12" t="inlineStr"/>
@@ -33624,20 +33618,20 @@
       <c r="H1916" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.107 TL / -</t>
+maks: 30.700 TL / -</t>
         </is>
       </c>
       <c r="I1916" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 553,5 TL / -</t>
+maks: 15.350 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1917" ht="32" customHeight="1">
       <c r="A1917" s="11" t="inlineStr">
         <is>
-          <t>Play Kart (Öğrenci)</t>
+          <t>Play Kart</t>
         </is>
       </c>
       <c r="B1917" s="12" t="inlineStr"/>
@@ -33649,15 +33643,20 @@
       <c r="H1917" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / -</t>
-        </is>
-      </c>
-      <c r="I1917" s="12" t="inlineStr"/>
+maks: 1.107 TL / -</t>
+        </is>
+      </c>
+      <c r="I1917" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: 553,5 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="1918" ht="32" customHeight="1">
       <c r="A1918" s="11" t="inlineStr">
         <is>
-          <t>Hepsiburada Premium Worldcard</t>
+          <t>Play Kart (Öğrenci)</t>
         </is>
       </c>
       <c r="B1918" s="12" t="inlineStr"/>
@@ -33669,20 +33668,15 @@
       <c r="H1918" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.258 TL / -</t>
-        </is>
-      </c>
-      <c r="I1918" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 629 TL / -</t>
-        </is>
-      </c>
+maks: - / -</t>
+        </is>
+      </c>
+      <c r="I1918" s="12" t="inlineStr"/>
     </row>
     <row r="1919" ht="32" customHeight="1">
       <c r="A1919" s="11" t="inlineStr">
         <is>
-          <t>Koçtaş Ustabilir Worldcard</t>
+          <t>Hepsiburada Premium Worldcard</t>
         </is>
       </c>
       <c r="B1919" s="12" t="inlineStr"/>
@@ -33694,15 +33688,20 @@
       <c r="H1919" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.308 TL / -</t>
-        </is>
-      </c>
-      <c r="I1919" s="12" t="inlineStr"/>
+maks: 1.258 TL / -</t>
+        </is>
+      </c>
+      <c r="I1919" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: 629 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="1920" ht="32" customHeight="1">
       <c r="A1920" s="11" t="inlineStr">
         <is>
-          <t>Adios</t>
+          <t>Koçtaş Ustabilir Worldcard</t>
         </is>
       </c>
       <c r="B1920" s="12" t="inlineStr"/>
@@ -33714,20 +33713,15 @@
       <c r="H1920" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.465 TL / -</t>
-        </is>
-      </c>
-      <c r="I1920" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 732,5 TL / -</t>
-        </is>
-      </c>
+maks: 1.308 TL / -</t>
+        </is>
+      </c>
+      <c r="I1920" s="12" t="inlineStr"/>
     </row>
     <row r="1921" ht="32" customHeight="1">
       <c r="A1921" s="11" t="inlineStr">
         <is>
-          <t>Adios Premium</t>
+          <t>Adios</t>
         </is>
       </c>
       <c r="B1921" s="12" t="inlineStr"/>
@@ -33739,20 +33733,20 @@
       <c r="H1921" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 2.150 TL / -</t>
+maks: 1.465 TL / -</t>
         </is>
       </c>
       <c r="I1921" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.075 TL / -</t>
+maks: 732,5 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1922" ht="32" customHeight="1">
       <c r="A1922" s="11" t="inlineStr">
         <is>
-          <t>Taksitçi Kart</t>
+          <t>Adios Premium</t>
         </is>
       </c>
       <c r="B1922" s="12" t="inlineStr"/>
@@ -33764,20 +33758,20 @@
       <c r="H1922" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.107 TL / -</t>
+maks: 2.150 TL / -</t>
         </is>
       </c>
       <c r="I1922" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 553,5 TL / -</t>
+maks: 1.075 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1923" ht="32" customHeight="1">
       <c r="A1923" s="11" t="inlineStr">
         <is>
-          <t>Fenerbahçe Worldcard</t>
+          <t>Taksitçi Kart</t>
         </is>
       </c>
       <c r="B1923" s="12" t="inlineStr"/>
@@ -33792,12 +33786,17 @@
 maks: 1.107 TL / -</t>
         </is>
       </c>
-      <c r="I1923" s="12" t="inlineStr"/>
+      <c r="I1923" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: 553,5 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="1924" ht="32" customHeight="1">
       <c r="A1924" s="11" t="inlineStr">
         <is>
-          <t>Fenerbahçe World Gold</t>
+          <t>Fenerbahçe Worldcard</t>
         </is>
       </c>
       <c r="B1924" s="12" t="inlineStr"/>
@@ -33809,7 +33808,7 @@
       <c r="H1924" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.258 TL / -</t>
+maks: 1.107 TL / -</t>
         </is>
       </c>
       <c r="I1924" s="12" t="inlineStr"/>
@@ -33817,7 +33816,7 @@
     <row r="1925" ht="32" customHeight="1">
       <c r="A1925" s="11" t="inlineStr">
         <is>
-          <t>Fenerbahçe World Platinum</t>
+          <t>Fenerbahçe World Gold</t>
         </is>
       </c>
       <c r="B1925" s="12" t="inlineStr"/>
@@ -33829,7 +33828,7 @@
       <c r="H1925" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.420 TL / -</t>
+maks: 1.258 TL / -</t>
         </is>
       </c>
       <c r="I1925" s="12" t="inlineStr"/>
@@ -33837,7 +33836,7 @@
     <row r="1926" ht="32" customHeight="1">
       <c r="A1926" s="11" t="inlineStr">
         <is>
-          <t>Opet Worldcard</t>
+          <t>Fenerbahçe World Platinum</t>
         </is>
       </c>
       <c r="B1926" s="12" t="inlineStr"/>
@@ -33849,20 +33848,15 @@
       <c r="H1926" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.258 TL / -</t>
-        </is>
-      </c>
-      <c r="I1926" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 629 TL / -</t>
-        </is>
-      </c>
+maks: 1.420 TL / -</t>
+        </is>
+      </c>
+      <c r="I1926" s="12" t="inlineStr"/>
     </row>
     <row r="1927" ht="32" customHeight="1">
       <c r="A1927" s="11" t="inlineStr">
         <is>
-          <t>World Eko</t>
+          <t>Opet Worldcard</t>
         </is>
       </c>
       <c r="B1927" s="12" t="inlineStr"/>
@@ -33874,20 +33868,20 @@
       <c r="H1927" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / -</t>
+maks: 1.258 TL / -</t>
         </is>
       </c>
       <c r="I1927" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / -</t>
+maks: 629 TL / -</t>
         </is>
       </c>
     </row>
     <row r="1928" ht="32" customHeight="1">
       <c r="A1928" s="11" t="inlineStr">
         <is>
-          <t>KoçAilem Worldcard</t>
+          <t>World Eko</t>
         </is>
       </c>
       <c r="B1928" s="12" t="inlineStr"/>
@@ -33912,7 +33906,7 @@
     <row r="1929" ht="32" customHeight="1">
       <c r="A1929" s="11" t="inlineStr">
         <is>
-          <t>Fenerclusive Kart</t>
+          <t>KoçAilem Worldcard</t>
         </is>
       </c>
       <c r="B1929" s="12" t="inlineStr"/>
@@ -33927,39 +33921,44 @@
 maks: - / -</t>
         </is>
       </c>
-      <c r="I1929" s="12" t="inlineStr"/>
-    </row>
-    <row r="1930" ht="16" customHeight="1">
-      <c r="A1930" s="10" t="inlineStr">
+      <c r="I1929" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: - / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930" ht="32" customHeight="1">
+      <c r="A1930" s="11" t="inlineStr">
+        <is>
+          <t>Fenerclusive Kart</t>
+        </is>
+      </c>
+      <c r="B1930" s="12" t="inlineStr"/>
+      <c r="C1930" s="12" t="inlineStr"/>
+      <c r="D1930" s="12" t="inlineStr"/>
+      <c r="E1930" s="12" t="inlineStr"/>
+      <c r="F1930" s="12" t="inlineStr"/>
+      <c r="G1930" s="12" t="inlineStr"/>
+      <c r="H1930" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: - / -</t>
+        </is>
+      </c>
+      <c r="I1930" s="12" t="inlineStr"/>
+    </row>
+    <row r="1931" ht="16" customHeight="1">
+      <c r="A1931" s="10" t="inlineStr">
         <is>
           <t>Kredi Kartı Nakit Çekim Ücreti</t>
         </is>
       </c>
-    </row>
-    <row r="1931" ht="32" customHeight="1">
-      <c r="A1931" s="11" t="inlineStr">
-        <is>
-          <t>Kredi Kartı Nakit Çekim Ücreti -İnternet Bankacılığından</t>
-        </is>
-      </c>
-      <c r="B1931" s="12" t="inlineStr"/>
-      <c r="C1931" s="12" t="inlineStr"/>
-      <c r="D1931" s="12" t="inlineStr"/>
-      <c r="E1931" s="12" t="inlineStr"/>
-      <c r="F1931" s="12" t="inlineStr"/>
-      <c r="G1931" s="12" t="inlineStr"/>
-      <c r="H1931" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / 1</t>
-        </is>
-      </c>
-      <c r="I1931" s="12" t="inlineStr"/>
     </row>
     <row r="1932" ht="32" customHeight="1">
       <c r="A1932" s="11" t="inlineStr">
         <is>
-          <t>Döviz Hesap Özeti Nakit Çekim Ücreti (EUR para birimi)</t>
+          <t>Kredi Kartı Nakit Çekim Ücreti -İnternet Bankacılığından</t>
         </is>
       </c>
       <c r="B1932" s="12" t="inlineStr"/>
@@ -33979,7 +33978,7 @@
     <row r="1933" ht="32" customHeight="1">
       <c r="A1933" s="11" t="inlineStr">
         <is>
-          <t>Döviz Hesap Özeti Nakit Çekim Ücreti (USD ve diğer para birimleri (EUR hariç))</t>
+          <t>Döviz Hesap Özeti Nakit Çekim Ücreti (EUR para birimi)</t>
         </is>
       </c>
       <c r="B1933" s="12" t="inlineStr"/>
@@ -33999,7 +33998,7 @@
     <row r="1934" ht="32" customHeight="1">
       <c r="A1934" s="11" t="inlineStr">
         <is>
-          <t>Kredi Kartı Nakit Çekim Ücreti - Mobil Bankacılıktan</t>
+          <t>Döviz Hesap Özeti Nakit Çekim Ücreti (USD ve diğer para birimleri (EUR hariç))</t>
         </is>
       </c>
       <c r="B1934" s="12" t="inlineStr"/>
@@ -34019,7 +34018,7 @@
     <row r="1935" ht="32" customHeight="1">
       <c r="A1935" s="11" t="inlineStr">
         <is>
-          <t>Kredi Kartı Nakit Çekim Ücreti -Telefon Bankacılığından</t>
+          <t>Kredi Kartı Nakit Çekim Ücreti - Mobil Bankacılıktan</t>
         </is>
       </c>
       <c r="B1935" s="12" t="inlineStr"/>
@@ -34039,7 +34038,7 @@
     <row r="1936" ht="32" customHeight="1">
       <c r="A1936" s="11" t="inlineStr">
         <is>
-          <t>Kredi Kartı Nakit Çekim Ücreti -YKB ATM'sinden</t>
+          <t>Kredi Kartı Nakit Çekim Ücreti -Telefon Bankacılığından</t>
         </is>
       </c>
       <c r="B1936" s="12" t="inlineStr"/>
@@ -34059,7 +34058,7 @@
     <row r="1937" ht="32" customHeight="1">
       <c r="A1937" s="11" t="inlineStr">
         <is>
-          <t>Kredi Kartı Nakit Çekim Ücreti -YKB Şubelerinden</t>
+          <t>Kredi Kartı Nakit Çekim Ücreti -YKB ATM'sinden</t>
         </is>
       </c>
       <c r="B1937" s="12" t="inlineStr"/>
@@ -34068,18 +34067,18 @@
       <c r="E1937" s="12" t="inlineStr"/>
       <c r="F1937" s="12" t="inlineStr"/>
       <c r="G1937" s="12" t="inlineStr"/>
-      <c r="H1937" s="12" t="inlineStr"/>
-      <c r="I1937" s="12" t="inlineStr">
+      <c r="H1937" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: - / 1</t>
         </is>
       </c>
+      <c r="I1937" s="12" t="inlineStr"/>
     </row>
     <row r="1938" ht="32" customHeight="1">
       <c r="A1938" s="11" t="inlineStr">
         <is>
-          <t>Kredi Kartı Nakit Çekim Ücreti - Diğer Banka ATM'sinden</t>
+          <t>Kredi Kartı Nakit Çekim Ücreti -YKB Şubelerinden</t>
         </is>
       </c>
       <c r="B1938" s="12" t="inlineStr"/>
@@ -34088,18 +34087,18 @@
       <c r="E1938" s="12" t="inlineStr"/>
       <c r="F1938" s="12" t="inlineStr"/>
       <c r="G1938" s="12" t="inlineStr"/>
-      <c r="H1938" s="12" t="inlineStr">
+      <c r="H1938" s="12" t="inlineStr"/>
+      <c r="I1938" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 0,57 TL / 3,87</t>
-        </is>
-      </c>
-      <c r="I1938" s="12" t="inlineStr"/>
+maks: - / 1</t>
+        </is>
+      </c>
     </row>
     <row r="1939" ht="32" customHeight="1">
       <c r="A1939" s="11" t="inlineStr">
         <is>
-          <t>Karttan Karta ve Karttan Cep Telefonuna Para Transferi</t>
+          <t>Kredi Kartı Nakit Çekim Ücreti - Diğer Banka ATM'sinden</t>
         </is>
       </c>
       <c r="B1939" s="12" t="inlineStr"/>
@@ -34111,42 +34110,42 @@
       <c r="H1939" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: 0,57 TL / 3,87</t>
+        </is>
+      </c>
+      <c r="I1939" s="12" t="inlineStr"/>
+    </row>
+    <row r="1940" ht="32" customHeight="1">
+      <c r="A1940" s="11" t="inlineStr">
+        <is>
+          <t>Karttan Karta ve Karttan Cep Telefonuna Para Transferi</t>
+        </is>
+      </c>
+      <c r="B1940" s="12" t="inlineStr"/>
+      <c r="C1940" s="12" t="inlineStr"/>
+      <c r="D1940" s="12" t="inlineStr"/>
+      <c r="E1940" s="12" t="inlineStr"/>
+      <c r="F1940" s="12" t="inlineStr"/>
+      <c r="G1940" s="12" t="inlineStr"/>
+      <c r="H1940" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: - / 1</t>
         </is>
       </c>
-      <c r="I1939" s="12" t="inlineStr"/>
-    </row>
-    <row r="1940" ht="16" customHeight="1">
-      <c r="A1940" s="10" t="inlineStr">
+      <c r="I1940" s="12" t="inlineStr"/>
+    </row>
+    <row r="1941" ht="16" customHeight="1">
+      <c r="A1941" s="10" t="inlineStr">
         <is>
           <t>Kredi Kartı İşlem Ücretleri</t>
-        </is>
-      </c>
-    </row>
-    <row r="1941" ht="32" customHeight="1">
-      <c r="A1941" s="11" t="inlineStr">
-        <is>
-          <t>Şube veya sgk.gov.tr sitesinden yapılan prim ödemeleri</t>
-        </is>
-      </c>
-      <c r="B1941" s="12" t="inlineStr"/>
-      <c r="C1941" s="12" t="inlineStr"/>
-      <c r="D1941" s="12" t="inlineStr"/>
-      <c r="E1941" s="12" t="inlineStr"/>
-      <c r="F1941" s="12" t="inlineStr"/>
-      <c r="G1941" s="12" t="inlineStr"/>
-      <c r="H1941" s="12" t="inlineStr"/>
-      <c r="I1941" s="12" t="inlineStr">
-        <is>
-          <t>3 TL / -
-maks: - / 3</t>
         </is>
       </c>
     </row>
     <row r="1942" ht="32" customHeight="1">
       <c r="A1942" s="11" t="inlineStr">
         <is>
-          <t>0 - 150 TL arası anlaşmalı kurum fatura ödemeleri</t>
+          <t>Şube veya sgk.gov.tr sitesinden yapılan prim ödemeleri</t>
         </is>
       </c>
       <c r="B1942" s="12" t="inlineStr"/>
@@ -34155,18 +34154,18 @@
       <c r="E1942" s="12" t="inlineStr"/>
       <c r="F1942" s="12" t="inlineStr"/>
       <c r="G1942" s="12" t="inlineStr"/>
-      <c r="H1942" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 5 TL / -</t>
-        </is>
-      </c>
-      <c r="I1942" s="12" t="inlineStr"/>
+      <c r="H1942" s="12" t="inlineStr"/>
+      <c r="I1942" s="12" t="inlineStr">
+        <is>
+          <t>3 TL / -
+maks: - / 3</t>
+        </is>
+      </c>
     </row>
     <row r="1943" ht="32" customHeight="1">
       <c r="A1943" s="11" t="inlineStr">
         <is>
-          <t>150,01 TL ve üzeri anlaşmalı kurum fatura ödemeleri</t>
+          <t>0 - 150 TL arası anlaşmalı kurum fatura ödemeleri</t>
         </is>
       </c>
       <c r="B1943" s="12" t="inlineStr"/>
@@ -34178,47 +34177,42 @@
       <c r="H1943" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: 5 TL / -</t>
+        </is>
+      </c>
+      <c r="I1943" s="12" t="inlineStr"/>
+    </row>
+    <row r="1944" ht="32" customHeight="1">
+      <c r="A1944" s="11" t="inlineStr">
+        <is>
+          <t>150,01 TL ve üzeri anlaşmalı kurum fatura ödemeleri</t>
+        </is>
+      </c>
+      <c r="B1944" s="12" t="inlineStr"/>
+      <c r="C1944" s="12" t="inlineStr"/>
+      <c r="D1944" s="12" t="inlineStr"/>
+      <c r="E1944" s="12" t="inlineStr"/>
+      <c r="F1944" s="12" t="inlineStr"/>
+      <c r="G1944" s="12" t="inlineStr"/>
+      <c r="H1944" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: - / 3,5</t>
         </is>
       </c>
-      <c r="I1943" s="12" t="inlineStr"/>
-    </row>
-    <row r="1944" ht="16" customHeight="1">
-      <c r="A1944" s="10" t="inlineStr">
+      <c r="I1944" s="12" t="inlineStr"/>
+    </row>
+    <row r="1945" ht="16" customHeight="1">
+      <c r="A1945" s="10" t="inlineStr">
         <is>
           <t>Kredi Kartı Faiz Oranları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1945" ht="32" customHeight="1">
-      <c r="A1945" s="11" t="inlineStr">
-        <is>
-          <t>Dönem borcu 30.000 TL altında olan bireysel kredi kartları</t>
-        </is>
-      </c>
-      <c r="B1945" s="12" t="inlineStr"/>
-      <c r="C1945" s="12" t="inlineStr"/>
-      <c r="D1945" s="12" t="inlineStr"/>
-      <c r="E1945" s="12" t="inlineStr"/>
-      <c r="F1945" s="12" t="inlineStr"/>
-      <c r="G1945" s="12" t="inlineStr"/>
-      <c r="H1945" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / 3,25</t>
-        </is>
-      </c>
-      <c r="I1945" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / 3,55</t>
         </is>
       </c>
     </row>
     <row r="1946" ht="32" customHeight="1">
       <c r="A1946" s="11" t="inlineStr">
         <is>
-          <t>Dönem borcu 30.000 - 180.000 TL arasında olan bireysel kredi kartları</t>
+          <t>Dönem borcu 30.000 TL altında olan bireysel kredi kartları</t>
         </is>
       </c>
       <c r="B1946" s="12" t="inlineStr"/>
@@ -34230,20 +34224,20 @@
       <c r="H1946" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 3,75</t>
+maks: - / 3,25</t>
         </is>
       </c>
       <c r="I1946" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 4,05</t>
+maks: - / 3,55</t>
         </is>
       </c>
     </row>
     <row r="1947" ht="32" customHeight="1">
       <c r="A1947" s="11" t="inlineStr">
         <is>
-          <t>Dönem borcu 180.000 TL üzerinde olan bireysel kredi kartları</t>
+          <t>Dönem borcu 30.000 - 180.000 TL arasında olan bireysel kredi kartları</t>
         </is>
       </c>
       <c r="B1947" s="12" t="inlineStr"/>
@@ -34255,20 +34249,20 @@
       <c r="H1947" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 4,25</t>
+maks: - / 3,75</t>
         </is>
       </c>
       <c r="I1947" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 4,55</t>
+maks: - / 4,05</t>
         </is>
       </c>
     </row>
     <row r="1948" ht="32" customHeight="1">
       <c r="A1948" s="11" t="inlineStr">
         <is>
-          <t>Bireysel Kredi Kartı Nakit Çekim Faiz Oranı</t>
+          <t>Dönem borcu 180.000 TL üzerinde olan bireysel kredi kartları</t>
         </is>
       </c>
       <c r="B1948" s="12" t="inlineStr"/>
@@ -34283,12 +34277,17 @@
 maks: - / 4,25</t>
         </is>
       </c>
-      <c r="I1948" s="12" t="inlineStr"/>
+      <c r="I1948" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: - / 4,55</t>
+        </is>
+      </c>
     </row>
     <row r="1949" ht="32" customHeight="1">
       <c r="A1949" s="11" t="inlineStr">
         <is>
-          <t>Bireysel Kredi Kartı Nakit Çekim Gecikme Faiz Oranı</t>
+          <t>Bireysel Kredi Kartı Nakit Çekim Faiz Oranı</t>
         </is>
       </c>
       <c r="B1949" s="12" t="inlineStr"/>
@@ -34300,7 +34299,7 @@
       <c r="H1949" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 4,55</t>
+maks: - / 4,25</t>
         </is>
       </c>
       <c r="I1949" s="12" t="inlineStr"/>
@@ -34308,7 +34307,7 @@
     <row r="1950" ht="32" customHeight="1">
       <c r="A1950" s="11" t="inlineStr">
         <is>
-          <t>2-12 Ay</t>
+          <t>Bireysel Kredi Kartı Nakit Çekim Gecikme Faiz Oranı</t>
         </is>
       </c>
       <c r="B1950" s="12" t="inlineStr"/>
@@ -34320,7 +34319,7 @@
       <c r="H1950" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 4,25</t>
+maks: - / 4,55</t>
         </is>
       </c>
       <c r="I1950" s="12" t="inlineStr"/>
@@ -34328,7 +34327,7 @@
     <row r="1951" ht="32" customHeight="1">
       <c r="A1951" s="11" t="inlineStr">
         <is>
-          <t>Taksitçi: 100 TL ve üzeri işlemlerde +3 taksit için</t>
+          <t>2-12 Ay</t>
         </is>
       </c>
       <c r="B1951" s="12" t="inlineStr"/>
@@ -34340,7 +34339,7 @@
       <c r="H1951" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 3,25</t>
+maks: - / 4,25</t>
         </is>
       </c>
       <c r="I1951" s="12" t="inlineStr"/>
@@ -34348,7 +34347,7 @@
     <row r="1952" ht="32" customHeight="1">
       <c r="A1952" s="11" t="inlineStr">
         <is>
-          <t>Taksitçi: 100 TL ve üzeri işlemlerde +2 taksit için</t>
+          <t>Taksitçi: 100 TL ve üzeri işlemlerde +3 taksit için</t>
         </is>
       </c>
       <c r="B1952" s="12" t="inlineStr"/>
@@ -34368,7 +34367,7 @@
     <row r="1953" ht="32" customHeight="1">
       <c r="A1953" s="11" t="inlineStr">
         <is>
-          <t>Taksitçi: 100 TL ve üzeri işlemlerde +1 taksit için</t>
+          <t>Taksitçi: 100 TL ve üzeri işlemlerde +2 taksit için</t>
         </is>
       </c>
       <c r="B1953" s="12" t="inlineStr"/>
@@ -34380,7 +34379,7 @@
       <c r="H1953" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 1,62</t>
+maks: - / 3,25</t>
         </is>
       </c>
       <c r="I1953" s="12" t="inlineStr"/>
@@ -34388,7 +34387,7 @@
     <row r="1954" ht="32" customHeight="1">
       <c r="A1954" s="11" t="inlineStr">
         <is>
-          <t>Talimatlı Fatura Ödeme</t>
+          <t>Taksitçi: 100 TL ve üzeri işlemlerde +1 taksit için</t>
         </is>
       </c>
       <c r="B1954" s="12" t="inlineStr"/>
@@ -34400,69 +34399,69 @@
       <c r="H1954" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: - / 1,62</t>
+        </is>
+      </c>
+      <c r="I1954" s="12" t="inlineStr"/>
+    </row>
+    <row r="1955" ht="32" customHeight="1">
+      <c r="A1955" s="11" t="inlineStr">
+        <is>
+          <t>Talimatlı Fatura Ödeme</t>
+        </is>
+      </c>
+      <c r="B1955" s="12" t="inlineStr"/>
+      <c r="C1955" s="12" t="inlineStr"/>
+      <c r="D1955" s="12" t="inlineStr"/>
+      <c r="E1955" s="12" t="inlineStr"/>
+      <c r="F1955" s="12" t="inlineStr"/>
+      <c r="G1955" s="12" t="inlineStr"/>
+      <c r="H1955" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: - / 4,25</t>
         </is>
       </c>
-      <c r="I1954" s="12" t="inlineStr"/>
-    </row>
-    <row r="1955" ht="16" customHeight="1">
-      <c r="A1955" s="10" t="inlineStr">
+      <c r="I1955" s="12" t="inlineStr"/>
+    </row>
+    <row r="1956" ht="16" customHeight="1">
+      <c r="A1956" s="10" t="inlineStr">
         <is>
           <t>Para Yatırma</t>
         </is>
       </c>
     </row>
-    <row r="1956" ht="32" customHeight="1">
-      <c r="A1956" s="11" t="inlineStr">
+    <row r="1957" ht="32" customHeight="1">
+      <c r="A1957" s="11" t="inlineStr">
         <is>
           <t>Hesaba Para Yatırma</t>
         </is>
       </c>
-      <c r="B1956" s="12" t="inlineStr"/>
-      <c r="C1956" s="12" t="inlineStr"/>
-      <c r="D1956" s="12" t="inlineStr"/>
-      <c r="E1956" s="12" t="inlineStr"/>
-      <c r="F1956" s="12" t="inlineStr"/>
-      <c r="G1956" s="12" t="inlineStr"/>
-      <c r="H1956" s="12" t="inlineStr">
+      <c r="B1957" s="12" t="inlineStr"/>
+      <c r="C1957" s="12" t="inlineStr"/>
+      <c r="D1957" s="12" t="inlineStr"/>
+      <c r="E1957" s="12" t="inlineStr"/>
+      <c r="F1957" s="12" t="inlineStr"/>
+      <c r="G1957" s="12" t="inlineStr"/>
+      <c r="H1957" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: - / -</t>
         </is>
       </c>
-      <c r="I1956" s="12" t="inlineStr"/>
-    </row>
-    <row r="1957" ht="16" customHeight="1">
-      <c r="A1957" s="10" t="inlineStr">
+      <c r="I1957" s="12" t="inlineStr"/>
+    </row>
+    <row r="1958" ht="16" customHeight="1">
+      <c r="A1958" s="10" t="inlineStr">
         <is>
           <t>Para Çekme</t>
         </is>
       </c>
-    </row>
-    <row r="1958" ht="32" customHeight="1">
-      <c r="A1958" s="11" t="inlineStr">
-        <is>
-          <t>Para Çekme</t>
-        </is>
-      </c>
-      <c r="B1958" s="12" t="inlineStr"/>
-      <c r="C1958" s="12" t="inlineStr"/>
-      <c r="D1958" s="12" t="inlineStr"/>
-      <c r="E1958" s="12" t="inlineStr"/>
-      <c r="F1958" s="12" t="inlineStr"/>
-      <c r="G1958" s="12" t="inlineStr"/>
-      <c r="H1958" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / -</t>
-        </is>
-      </c>
-      <c r="I1958" s="12" t="inlineStr"/>
     </row>
     <row r="1959" ht="32" customHeight="1">
       <c r="A1959" s="11" t="inlineStr">
         <is>
-          <t>Külçe Altın Çekme</t>
+          <t>Para Çekme</t>
         </is>
       </c>
       <c r="B1959" s="12" t="inlineStr"/>
@@ -34473,8 +34472,8 @@
       <c r="G1959" s="12" t="inlineStr"/>
       <c r="H1959" s="12" t="inlineStr">
         <is>
-          <t>- / 10
-maks: - / 10</t>
+          <t>- / -
+maks: - / -</t>
         </is>
       </c>
       <c r="I1959" s="12" t="inlineStr"/>
@@ -34482,7 +34481,7 @@
     <row r="1960" ht="32" customHeight="1">
       <c r="A1960" s="11" t="inlineStr">
         <is>
-          <t>Yurt Dışı Kart ile ATM’den Para Çekme - Kur Dönüşüm Ücreti</t>
+          <t>Külçe Altın Çekme</t>
         </is>
       </c>
       <c r="B1960" s="12" t="inlineStr"/>
@@ -34493,8 +34492,8 @@
       <c r="G1960" s="12" t="inlineStr"/>
       <c r="H1960" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: - / 8</t>
+          <t>- / 10
+maks: - / 10</t>
         </is>
       </c>
       <c r="I1960" s="12" t="inlineStr"/>
@@ -34502,7 +34501,7 @@
     <row r="1961" ht="32" customHeight="1">
       <c r="A1961" s="11" t="inlineStr">
         <is>
-          <t>Yurt Dışı Kart ile ATM’den Para Çekme</t>
+          <t>Yurt Dışı Kart ile ATM’den Para Çekme - Kur Dönüşüm Ücreti</t>
         </is>
       </c>
       <c r="B1961" s="12" t="inlineStr"/>
@@ -34514,7 +34513,7 @@
       <c r="H1961" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 10,52</t>
+maks: - / 8</t>
         </is>
       </c>
       <c r="I1961" s="12" t="inlineStr"/>
@@ -34522,7 +34521,7 @@
     <row r="1962" ht="32" customHeight="1">
       <c r="A1962" s="11" t="inlineStr">
         <is>
-          <t>ATM Günlük Limit Üzeri Para Çekme Ücreti</t>
+          <t>Yurt Dışı Kart ile ATM’den Para Çekme</t>
         </is>
       </c>
       <c r="B1962" s="12" t="inlineStr"/>
@@ -34533,70 +34532,70 @@
       <c r="G1962" s="12" t="inlineStr"/>
       <c r="H1962" s="12" t="inlineStr">
         <is>
+          <t>- / -
+maks: - / 10,52</t>
+        </is>
+      </c>
+      <c r="I1962" s="12" t="inlineStr"/>
+    </row>
+    <row r="1963" ht="32" customHeight="1">
+      <c r="A1963" s="11" t="inlineStr">
+        <is>
+          <t>ATM Günlük Limit Üzeri Para Çekme Ücreti</t>
+        </is>
+      </c>
+      <c r="B1963" s="12" t="inlineStr"/>
+      <c r="C1963" s="12" t="inlineStr"/>
+      <c r="D1963" s="12" t="inlineStr"/>
+      <c r="E1963" s="12" t="inlineStr"/>
+      <c r="F1963" s="12" t="inlineStr"/>
+      <c r="G1963" s="12" t="inlineStr"/>
+      <c r="H1963" s="12" t="inlineStr">
+        <is>
           <t>13,4 TL / -
 maks: - / 2,9</t>
         </is>
       </c>
-      <c r="I1962" s="12" t="inlineStr"/>
-    </row>
-    <row r="1963" ht="16" customHeight="1">
-      <c r="A1963" s="10" t="inlineStr">
+      <c r="I1963" s="12" t="inlineStr"/>
+    </row>
+    <row r="1964" ht="16" customHeight="1">
+      <c r="A1964" s="10" t="inlineStr">
         <is>
           <t>Hesap İşletim Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="1964" ht="32" customHeight="1">
-      <c r="A1964" s="11" t="inlineStr">
+    <row r="1965" ht="32" customHeight="1">
+      <c r="A1965" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B1964" s="12" t="inlineStr"/>
-      <c r="C1964" s="12" t="inlineStr"/>
-      <c r="D1964" s="12" t="inlineStr"/>
-      <c r="E1964" s="12" t="inlineStr"/>
-      <c r="F1964" s="12" t="inlineStr"/>
-      <c r="G1964" s="12" t="inlineStr"/>
-      <c r="H1964" s="12" t="inlineStr">
+      <c r="B1965" s="12" t="inlineStr"/>
+      <c r="C1965" s="12" t="inlineStr"/>
+      <c r="D1965" s="12" t="inlineStr"/>
+      <c r="E1965" s="12" t="inlineStr"/>
+      <c r="F1965" s="12" t="inlineStr"/>
+      <c r="G1965" s="12" t="inlineStr"/>
+      <c r="H1965" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: - / -</t>
         </is>
       </c>
-      <c r="I1964" s="12" t="inlineStr"/>
-    </row>
-    <row r="1965" ht="16" customHeight="1">
-      <c r="A1965" s="10" t="inlineStr">
+      <c r="I1965" s="12" t="inlineStr"/>
+    </row>
+    <row r="1966" ht="16" customHeight="1">
+      <c r="A1966" s="10" t="inlineStr">
         <is>
           <t>Ekstre Masrafı</t>
         </is>
       </c>
-    </row>
-    <row r="1966" ht="32" customHeight="1">
-      <c r="A1966" s="11" t="inlineStr">
-        <is>
-          <t>KMH Hesap Özeti (Esnek Hesap Özeti)</t>
-        </is>
-      </c>
-      <c r="B1966" s="12" t="inlineStr"/>
-      <c r="C1966" s="12" t="inlineStr"/>
-      <c r="D1966" s="12" t="inlineStr"/>
-      <c r="E1966" s="12" t="inlineStr"/>
-      <c r="F1966" s="12" t="inlineStr"/>
-      <c r="G1966" s="12" t="inlineStr"/>
-      <c r="H1966" s="12" t="inlineStr">
-        <is>
-          <t>45 TL / -
-maks: 45 TL / -</t>
-        </is>
-      </c>
-      <c r="I1966" s="12" t="inlineStr"/>
     </row>
     <row r="1967" ht="32" customHeight="1">
       <c r="A1967" s="11" t="inlineStr">
         <is>
-          <t>Ekstre Masrafı (Şubeden Verilen)</t>
+          <t>KMH Hesap Özeti (Esnek Hesap Özeti)</t>
         </is>
       </c>
       <c r="B1967" s="12" t="inlineStr"/>
@@ -34605,18 +34604,18 @@
       <c r="E1967" s="12" t="inlineStr"/>
       <c r="F1967" s="12" t="inlineStr"/>
       <c r="G1967" s="12" t="inlineStr"/>
-      <c r="H1967" s="12" t="inlineStr"/>
-      <c r="I1967" s="12" t="inlineStr">
-        <is>
-          <t>2 TL / -
-maks: 30 TL / -</t>
-        </is>
-      </c>
+      <c r="H1967" s="12" t="inlineStr">
+        <is>
+          <t>45 TL / -
+maks: 45 TL / -</t>
+        </is>
+      </c>
+      <c r="I1967" s="12" t="inlineStr"/>
     </row>
     <row r="1968" ht="32" customHeight="1">
       <c r="A1968" s="11" t="inlineStr">
         <is>
-          <t>Ekstre Masrafı (Merkezi Gönderim)</t>
+          <t>Ekstre Masrafı (Şubeden Verilen)</t>
         </is>
       </c>
       <c r="B1968" s="12" t="inlineStr"/>
@@ -34625,72 +34624,72 @@
       <c r="E1968" s="12" t="inlineStr"/>
       <c r="F1968" s="12" t="inlineStr"/>
       <c r="G1968" s="12" t="inlineStr"/>
-      <c r="H1968" s="12" t="inlineStr">
+      <c r="H1968" s="12" t="inlineStr"/>
+      <c r="I1968" s="12" t="inlineStr">
+        <is>
+          <t>2 TL / -
+maks: 30 TL / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969" ht="32" customHeight="1">
+      <c r="A1969" s="11" t="inlineStr">
+        <is>
+          <t>Ekstre Masrafı (Merkezi Gönderim)</t>
+        </is>
+      </c>
+      <c r="B1969" s="12" t="inlineStr"/>
+      <c r="C1969" s="12" t="inlineStr"/>
+      <c r="D1969" s="12" t="inlineStr"/>
+      <c r="E1969" s="12" t="inlineStr"/>
+      <c r="F1969" s="12" t="inlineStr"/>
+      <c r="G1969" s="12" t="inlineStr"/>
+      <c r="H1969" s="12" t="inlineStr">
         <is>
           <t>3 TL / -
 maks: 30 TL / -</t>
         </is>
       </c>
-      <c r="I1968" s="12" t="inlineStr"/>
-    </row>
-    <row r="1969" ht="16" customHeight="1">
-      <c r="A1969" s="10" t="inlineStr">
+      <c r="I1969" s="12" t="inlineStr"/>
+    </row>
+    <row r="1970" ht="16" customHeight="1">
+      <c r="A1970" s="10" t="inlineStr">
         <is>
           <t>Dekont Masrafı</t>
         </is>
       </c>
     </row>
-    <row r="1970" ht="32" customHeight="1">
-      <c r="A1970" s="11" t="inlineStr">
+    <row r="1971" ht="32" customHeight="1">
+      <c r="A1971" s="11" t="inlineStr">
         <is>
           <t>Dekont Masrafı - Geçmişe Yönelik Olarak Basılan</t>
         </is>
       </c>
-      <c r="B1970" s="12" t="inlineStr"/>
-      <c r="C1970" s="12" t="inlineStr"/>
-      <c r="D1970" s="12" t="inlineStr"/>
-      <c r="E1970" s="12" t="inlineStr"/>
-      <c r="F1970" s="12" t="inlineStr"/>
-      <c r="G1970" s="12" t="inlineStr"/>
-      <c r="H1970" s="12" t="inlineStr">
+      <c r="B1971" s="12" t="inlineStr"/>
+      <c r="C1971" s="12" t="inlineStr"/>
+      <c r="D1971" s="12" t="inlineStr"/>
+      <c r="E1971" s="12" t="inlineStr"/>
+      <c r="F1971" s="12" t="inlineStr"/>
+      <c r="G1971" s="12" t="inlineStr"/>
+      <c r="H1971" s="12" t="inlineStr">
         <is>
           <t>9,52 TL / -
 maks: 95,2 TL / -</t>
         </is>
       </c>
-      <c r="I1970" s="12" t="inlineStr"/>
-    </row>
-    <row r="1971" ht="16" customHeight="1">
-      <c r="A1971" s="10" t="inlineStr">
+      <c r="I1971" s="12" t="inlineStr"/>
+    </row>
+    <row r="1972" ht="16" customHeight="1">
+      <c r="A1972" s="10" t="inlineStr">
         <is>
           <t>ATM Kartlı/Kartsız Havale</t>
         </is>
       </c>
-    </row>
-    <row r="1972" ht="32" customHeight="1">
-      <c r="A1972" s="11" t="inlineStr">
-        <is>
-          <t>ATM Kartlı Havale - 399.000,01 TL ve üzeri</t>
-        </is>
-      </c>
-      <c r="B1972" s="12" t="inlineStr"/>
-      <c r="C1972" s="12" t="inlineStr"/>
-      <c r="D1972" s="12" t="inlineStr"/>
-      <c r="E1972" s="12" t="inlineStr"/>
-      <c r="F1972" s="12" t="inlineStr"/>
-      <c r="G1972" s="12" t="inlineStr"/>
-      <c r="H1972" s="12" t="inlineStr">
-        <is>
-          <t>199,05 TL / -
-maks: 199,05 TL / -</t>
-        </is>
-      </c>
-      <c r="I1972" s="12" t="inlineStr"/>
     </row>
     <row r="1973" ht="32" customHeight="1">
       <c r="A1973" s="11" t="inlineStr">
         <is>
-          <t>ATM Kartlı Havale - 8.300 TL ve altı</t>
+          <t>ATM Kartlı Havale - 399.000,01 TL ve üzeri</t>
         </is>
       </c>
       <c r="B1973" s="12" t="inlineStr"/>
@@ -34701,8 +34700,8 @@
       <c r="G1973" s="12" t="inlineStr"/>
       <c r="H1973" s="12" t="inlineStr">
         <is>
-          <t>13,33 TL / -
-maks: 13,33 TL / -</t>
+          <t>199,05 TL / -
+maks: 199,05 TL / -</t>
         </is>
       </c>
       <c r="I1973" s="12" t="inlineStr"/>
@@ -34710,7 +34709,7 @@
     <row r="1974" ht="32" customHeight="1">
       <c r="A1974" s="11" t="inlineStr">
         <is>
-          <t>ATM Kartlı Havale - 8.300,01 TL - 399.000 TL</t>
+          <t>ATM Kartlı Havale - 8.300 TL ve altı</t>
         </is>
       </c>
       <c r="B1974" s="12" t="inlineStr"/>
@@ -34721,8 +34720,8 @@
       <c r="G1974" s="12" t="inlineStr"/>
       <c r="H1974" s="12" t="inlineStr">
         <is>
-          <t>27,62 TL / -
-maks: 27,62 TL / -</t>
+          <t>13,33 TL / -
+maks: 13,33 TL / -</t>
         </is>
       </c>
       <c r="I1974" s="12" t="inlineStr"/>
@@ -34730,7 +34729,7 @@
     <row r="1975" ht="32" customHeight="1">
       <c r="A1975" s="11" t="inlineStr">
         <is>
-          <t>ATM Kartsız Havale - 399.000,01 TL ve üzeri</t>
+          <t>ATM Kartlı Havale - 8.300,01 TL - 399.000 TL</t>
         </is>
       </c>
       <c r="B1975" s="12" t="inlineStr"/>
@@ -34741,8 +34740,8 @@
       <c r="G1975" s="12" t="inlineStr"/>
       <c r="H1975" s="12" t="inlineStr">
         <is>
-          <t>199,05 TL / -
-maks: 199,05 TL / -</t>
+          <t>27,62 TL / -
+maks: 27,62 TL / -</t>
         </is>
       </c>
       <c r="I1975" s="12" t="inlineStr"/>
@@ -34750,7 +34749,7 @@
     <row r="1976" ht="32" customHeight="1">
       <c r="A1976" s="11" t="inlineStr">
         <is>
-          <t>ATM Kartsız Havale - 8.300 TL ve altı</t>
+          <t>ATM Kartsız Havale - 399.000,01 TL ve üzeri</t>
         </is>
       </c>
       <c r="B1976" s="12" t="inlineStr"/>
@@ -34761,8 +34760,8 @@
       <c r="G1976" s="12" t="inlineStr"/>
       <c r="H1976" s="12" t="inlineStr">
         <is>
-          <t>13,33 TL / -
-maks: 13,33 TL / -</t>
+          <t>199,05 TL / -
+maks: 199,05 TL / -</t>
         </is>
       </c>
       <c r="I1976" s="12" t="inlineStr"/>
@@ -34770,7 +34769,7 @@
     <row r="1977" ht="32" customHeight="1">
       <c r="A1977" s="11" t="inlineStr">
         <is>
-          <t>ATM Kartsız Havale - 8.300,01 TL - 399.000 TL</t>
+          <t>ATM Kartsız Havale - 8.300 TL ve altı</t>
         </is>
       </c>
       <c r="B1977" s="12" t="inlineStr"/>
@@ -34781,43 +34780,43 @@
       <c r="G1977" s="12" t="inlineStr"/>
       <c r="H1977" s="12" t="inlineStr">
         <is>
+          <t>13,33 TL / -
+maks: 13,33 TL / -</t>
+        </is>
+      </c>
+      <c r="I1977" s="12" t="inlineStr"/>
+    </row>
+    <row r="1978" ht="32" customHeight="1">
+      <c r="A1978" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartsız Havale - 8.300,01 TL - 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B1978" s="12" t="inlineStr"/>
+      <c r="C1978" s="12" t="inlineStr"/>
+      <c r="D1978" s="12" t="inlineStr"/>
+      <c r="E1978" s="12" t="inlineStr"/>
+      <c r="F1978" s="12" t="inlineStr"/>
+      <c r="G1978" s="12" t="inlineStr"/>
+      <c r="H1978" s="12" t="inlineStr">
+        <is>
           <t>27,62 TL / -
 maks: 27,62 TL / -</t>
         </is>
       </c>
-      <c r="I1977" s="12" t="inlineStr"/>
-    </row>
-    <row r="1978" ht="16" customHeight="1">
-      <c r="A1978" s="10" t="inlineStr">
+      <c r="I1978" s="12" t="inlineStr"/>
+    </row>
+    <row r="1979" ht="16" customHeight="1">
+      <c r="A1979" s="10" t="inlineStr">
         <is>
           <t>Ortak ATM Kullanımı</t>
         </is>
       </c>
-    </row>
-    <row r="1979" ht="32" customHeight="1">
-      <c r="A1979" s="11" t="inlineStr">
-        <is>
-          <t>Ortak ATM'lerden Limit Sorgulama</t>
-        </is>
-      </c>
-      <c r="B1979" s="12" t="inlineStr"/>
-      <c r="C1979" s="12" t="inlineStr"/>
-      <c r="D1979" s="12" t="inlineStr"/>
-      <c r="E1979" s="12" t="inlineStr"/>
-      <c r="F1979" s="12" t="inlineStr"/>
-      <c r="G1979" s="12" t="inlineStr"/>
-      <c r="H1979" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 0,27 TL / -</t>
-        </is>
-      </c>
-      <c r="I1979" s="12" t="inlineStr"/>
     </row>
     <row r="1980" ht="32" customHeight="1">
       <c r="A1980" s="11" t="inlineStr">
         <is>
-          <t>Ortak ATM'lerden Para Yatırma</t>
+          <t>Ortak ATM'lerden Limit Sorgulama</t>
         </is>
       </c>
       <c r="B1980" s="12" t="inlineStr"/>
@@ -34829,7 +34828,7 @@
       <c r="H1980" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 1,15</t>
+maks: 0,27 TL / -</t>
         </is>
       </c>
       <c r="I1980" s="12" t="inlineStr"/>
@@ -34837,7 +34836,7 @@
     <row r="1981" ht="32" customHeight="1">
       <c r="A1981" s="11" t="inlineStr">
         <is>
-          <t>Ortak ATM'lerden Bakiye Sorgulama</t>
+          <t>Ortak ATM'lerden Para Yatırma</t>
         </is>
       </c>
       <c r="B1981" s="12" t="inlineStr"/>
@@ -34849,42 +34848,42 @@
       <c r="H1981" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: - / 1,15</t>
+        </is>
+      </c>
+      <c r="I1981" s="12" t="inlineStr"/>
+    </row>
+    <row r="1982" ht="32" customHeight="1">
+      <c r="A1982" s="11" t="inlineStr">
+        <is>
+          <t>Ortak ATM'lerden Bakiye Sorgulama</t>
+        </is>
+      </c>
+      <c r="B1982" s="12" t="inlineStr"/>
+      <c r="C1982" s="12" t="inlineStr"/>
+      <c r="D1982" s="12" t="inlineStr"/>
+      <c r="E1982" s="12" t="inlineStr"/>
+      <c r="F1982" s="12" t="inlineStr"/>
+      <c r="G1982" s="12" t="inlineStr"/>
+      <c r="H1982" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: 0,27 TL / -</t>
         </is>
       </c>
-      <c r="I1981" s="12" t="inlineStr"/>
-    </row>
-    <row r="1982" ht="16" customHeight="1">
-      <c r="A1982" s="10" t="inlineStr">
+      <c r="I1982" s="12" t="inlineStr"/>
+    </row>
+    <row r="1983" ht="16" customHeight="1">
+      <c r="A1983" s="10" t="inlineStr">
         <is>
           <t>Kasa24 Ücretleri</t>
         </is>
       </c>
-    </row>
-    <row r="1983" ht="32" customHeight="1">
-      <c r="A1983" s="11" t="inlineStr">
-        <is>
-          <t>E Tipi Kasa24 Depozito Ücreti</t>
-        </is>
-      </c>
-      <c r="B1983" s="12" t="inlineStr"/>
-      <c r="C1983" s="12" t="inlineStr"/>
-      <c r="D1983" s="12" t="inlineStr"/>
-      <c r="E1983" s="12" t="inlineStr"/>
-      <c r="F1983" s="12" t="inlineStr"/>
-      <c r="G1983" s="12" t="inlineStr"/>
-      <c r="H1983" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 45.309,52 TL / -</t>
-        </is>
-      </c>
-      <c r="I1983" s="12" t="inlineStr"/>
     </row>
     <row r="1984" ht="32" customHeight="1">
       <c r="A1984" s="11" t="inlineStr">
         <is>
-          <t>D Tipi Kasa24 Depozito Ücreti</t>
+          <t>E Tipi Kasa24 Depozito Ücreti</t>
         </is>
       </c>
       <c r="B1984" s="12" t="inlineStr"/>
@@ -34896,7 +34895,7 @@
       <c r="H1984" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 39.638,1 TL / -</t>
+maks: 45.309,52 TL / -</t>
         </is>
       </c>
       <c r="I1984" s="12" t="inlineStr"/>
@@ -34904,7 +34903,7 @@
     <row r="1985" ht="32" customHeight="1">
       <c r="A1985" s="11" t="inlineStr">
         <is>
-          <t>C Tipi Kasa24 Depozito Ücreti</t>
+          <t>D Tipi Kasa24 Depozito Ücreti</t>
         </is>
       </c>
       <c r="B1985" s="12" t="inlineStr"/>
@@ -34916,7 +34915,7 @@
       <c r="H1985" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 33.966,67 TL / -</t>
+maks: 39.638,1 TL / -</t>
         </is>
       </c>
       <c r="I1985" s="12" t="inlineStr"/>
@@ -34924,7 +34923,7 @@
     <row r="1986" ht="32" customHeight="1">
       <c r="A1986" s="11" t="inlineStr">
         <is>
-          <t>B Tipi Kasa24 Depozito Ücreti</t>
+          <t>C Tipi Kasa24 Depozito Ücreti</t>
         </is>
       </c>
       <c r="B1986" s="12" t="inlineStr"/>
@@ -34936,7 +34935,7 @@
       <c r="H1986" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 31.161,9 TL / -</t>
+maks: 33.966,67 TL / -</t>
         </is>
       </c>
       <c r="I1986" s="12" t="inlineStr"/>
@@ -34944,7 +34943,7 @@
     <row r="1987" ht="32" customHeight="1">
       <c r="A1987" s="11" t="inlineStr">
         <is>
-          <t>A Tipi Kasa24 Depozito Ücreti</t>
+          <t>B Tipi Kasa24 Depozito Ücreti</t>
         </is>
       </c>
       <c r="B1987" s="12" t="inlineStr"/>
@@ -34956,7 +34955,7 @@
       <c r="H1987" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 28.333,33 TL / -</t>
+maks: 31.161,9 TL / -</t>
         </is>
       </c>
       <c r="I1987" s="12" t="inlineStr"/>
@@ -34964,7 +34963,7 @@
     <row r="1988" ht="32" customHeight="1">
       <c r="A1988" s="11" t="inlineStr">
         <is>
-          <t>E Tipi Kasa24 Ücreti</t>
+          <t>A Tipi Kasa24 Depozito Ücreti</t>
         </is>
       </c>
       <c r="B1988" s="12" t="inlineStr"/>
@@ -34976,7 +34975,7 @@
       <c r="H1988" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 45.309,52 TL / -</t>
+maks: 28.333,33 TL / -</t>
         </is>
       </c>
       <c r="I1988" s="12" t="inlineStr"/>
@@ -34984,7 +34983,7 @@
     <row r="1989" ht="32" customHeight="1">
       <c r="A1989" s="11" t="inlineStr">
         <is>
-          <t>D Tipi Kasa24 Ücreti</t>
+          <t>E Tipi Kasa24 Ücreti</t>
         </is>
       </c>
       <c r="B1989" s="12" t="inlineStr"/>
@@ -34996,7 +34995,7 @@
       <c r="H1989" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 39.638,1 TL / -</t>
+maks: 45.309,52 TL / -</t>
         </is>
       </c>
       <c r="I1989" s="12" t="inlineStr"/>
@@ -35004,7 +35003,7 @@
     <row r="1990" ht="32" customHeight="1">
       <c r="A1990" s="11" t="inlineStr">
         <is>
-          <t>C Tipi Kasa24 Ücreti</t>
+          <t>D Tipi Kasa24 Ücreti</t>
         </is>
       </c>
       <c r="B1990" s="12" t="inlineStr"/>
@@ -35016,7 +35015,7 @@
       <c r="H1990" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 33.966,67 TL / -</t>
+maks: 39.638,1 TL / -</t>
         </is>
       </c>
       <c r="I1990" s="12" t="inlineStr"/>
@@ -35024,7 +35023,7 @@
     <row r="1991" ht="32" customHeight="1">
       <c r="A1991" s="11" t="inlineStr">
         <is>
-          <t>B Tipi Kasa24 Ücreti</t>
+          <t>C Tipi Kasa24 Ücreti</t>
         </is>
       </c>
       <c r="B1991" s="12" t="inlineStr"/>
@@ -35036,7 +35035,7 @@
       <c r="H1991" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 31.161,9 TL / -</t>
+maks: 33.966,67 TL / -</t>
         </is>
       </c>
       <c r="I1991" s="12" t="inlineStr"/>
@@ -35044,7 +35043,7 @@
     <row r="1992" ht="32" customHeight="1">
       <c r="A1992" s="11" t="inlineStr">
         <is>
-          <t>A Tipi Kasa24 Ücreti</t>
+          <t>B Tipi Kasa24 Ücreti</t>
         </is>
       </c>
       <c r="B1992" s="12" t="inlineStr"/>
@@ -35056,42 +35055,42 @@
       <c r="H1992" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 28.333,33 TL / -</t>
+maks: 31.161,9 TL / -</t>
         </is>
       </c>
       <c r="I1992" s="12" t="inlineStr"/>
     </row>
-    <row r="1993" ht="16" customHeight="1">
-      <c r="A1993" s="10" t="inlineStr">
-        <is>
-          <t>Kiralık Kasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="1994" ht="32" customHeight="1">
-      <c r="A1994" s="11" t="inlineStr">
-        <is>
-          <t>Depozito Ücreti Büyük Boy</t>
-        </is>
-      </c>
-      <c r="B1994" s="12" t="inlineStr"/>
-      <c r="C1994" s="12" t="inlineStr"/>
-      <c r="D1994" s="12" t="inlineStr"/>
-      <c r="E1994" s="12" t="inlineStr"/>
-      <c r="F1994" s="12" t="inlineStr"/>
-      <c r="G1994" s="12" t="inlineStr"/>
-      <c r="H1994" s="12" t="inlineStr">
+    <row r="1993" ht="32" customHeight="1">
+      <c r="A1993" s="11" t="inlineStr">
+        <is>
+          <t>A Tipi Kasa24 Ücreti</t>
+        </is>
+      </c>
+      <c r="B1993" s="12" t="inlineStr"/>
+      <c r="C1993" s="12" t="inlineStr"/>
+      <c r="D1993" s="12" t="inlineStr"/>
+      <c r="E1993" s="12" t="inlineStr"/>
+      <c r="F1993" s="12" t="inlineStr"/>
+      <c r="G1993" s="12" t="inlineStr"/>
+      <c r="H1993" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: 28.333,33 TL / -</t>
         </is>
       </c>
-      <c r="I1994" s="12" t="inlineStr"/>
+      <c r="I1993" s="12" t="inlineStr"/>
+    </row>
+    <row r="1994" ht="16" customHeight="1">
+      <c r="A1994" s="10" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa</t>
+        </is>
+      </c>
     </row>
     <row r="1995" ht="32" customHeight="1">
       <c r="A1995" s="11" t="inlineStr">
         <is>
-          <t>Depozito Ücreti Orta Boy</t>
+          <t>Depozito Ücreti Büyük Boy</t>
         </is>
       </c>
       <c r="B1995" s="12" t="inlineStr"/>
@@ -35103,7 +35102,7 @@
       <c r="H1995" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 22.671,43 TL / -</t>
+maks: 28.333,33 TL / -</t>
         </is>
       </c>
       <c r="I1995" s="12" t="inlineStr"/>
@@ -35111,7 +35110,7 @@
     <row r="1996" ht="32" customHeight="1">
       <c r="A1996" s="11" t="inlineStr">
         <is>
-          <t>Depozito Ücreti Küçük Boy</t>
+          <t>Depozito Ücreti Orta Boy</t>
         </is>
       </c>
       <c r="B1996" s="12" t="inlineStr"/>
@@ -35123,7 +35122,7 @@
       <c r="H1996" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 17.000 TL / -</t>
+maks: 22.671,43 TL / -</t>
         </is>
       </c>
       <c r="I1996" s="12" t="inlineStr"/>
@@ -35131,7 +35130,7 @@
     <row r="1997" ht="32" customHeight="1">
       <c r="A1997" s="11" t="inlineStr">
         <is>
-          <t>Büyük Boy</t>
+          <t>Depozito Ücreti Küçük Boy</t>
         </is>
       </c>
       <c r="B1997" s="12" t="inlineStr"/>
@@ -35143,7 +35142,7 @@
       <c r="H1997" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 28.333,33 TL / -</t>
+maks: 17.000 TL / -</t>
         </is>
       </c>
       <c r="I1997" s="12" t="inlineStr"/>
@@ -35151,7 +35150,7 @@
     <row r="1998" ht="32" customHeight="1">
       <c r="A1998" s="11" t="inlineStr">
         <is>
-          <t>Orta Boy</t>
+          <t>Büyük Boy</t>
         </is>
       </c>
       <c r="B1998" s="12" t="inlineStr"/>
@@ -35163,7 +35162,7 @@
       <c r="H1998" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 22.671,43 TL / -</t>
+maks: 28.333,33 TL / -</t>
         </is>
       </c>
       <c r="I1998" s="12" t="inlineStr"/>
@@ -35171,7 +35170,7 @@
     <row r="1999" ht="32" customHeight="1">
       <c r="A1999" s="11" t="inlineStr">
         <is>
-          <t>Küçük Boy</t>
+          <t>Orta Boy</t>
         </is>
       </c>
       <c r="B1999" s="12" t="inlineStr"/>
@@ -35183,42 +35182,42 @@
       <c r="H1999" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: 22.671,43 TL / -</t>
+        </is>
+      </c>
+      <c r="I1999" s="12" t="inlineStr"/>
+    </row>
+    <row r="2000" ht="32" customHeight="1">
+      <c r="A2000" s="11" t="inlineStr">
+        <is>
+          <t>Küçük Boy</t>
+        </is>
+      </c>
+      <c r="B2000" s="12" t="inlineStr"/>
+      <c r="C2000" s="12" t="inlineStr"/>
+      <c r="D2000" s="12" t="inlineStr"/>
+      <c r="E2000" s="12" t="inlineStr"/>
+      <c r="F2000" s="12" t="inlineStr"/>
+      <c r="G2000" s="12" t="inlineStr"/>
+      <c r="H2000" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: 17.000 TL / -</t>
         </is>
       </c>
-      <c r="I1999" s="12" t="inlineStr"/>
-    </row>
-    <row r="2000" ht="16" customHeight="1">
-      <c r="A2000" s="10" t="inlineStr">
+      <c r="I2000" s="12" t="inlineStr"/>
+    </row>
+    <row r="2001" ht="16" customHeight="1">
+      <c r="A2001" s="10" t="inlineStr">
         <is>
           <t>Merkezi Kayıt Kuruluşu Ücretleri</t>
         </is>
       </c>
-    </row>
-    <row r="2001" ht="32" customHeight="1">
-      <c r="A2001" s="11" t="inlineStr">
-        <is>
-          <t>Hesap Açma</t>
-        </is>
-      </c>
-      <c r="B2001" s="12" t="inlineStr"/>
-      <c r="C2001" s="12" t="inlineStr"/>
-      <c r="D2001" s="12" t="inlineStr"/>
-      <c r="E2001" s="12" t="inlineStr"/>
-      <c r="F2001" s="12" t="inlineStr"/>
-      <c r="G2001" s="12" t="inlineStr"/>
-      <c r="H2001" s="12" t="inlineStr">
-        <is>
-          <t>17,75 TL / -
-maks: - / -</t>
-        </is>
-      </c>
-      <c r="I2001" s="12" t="inlineStr"/>
     </row>
     <row r="2002" ht="32" customHeight="1">
       <c r="A2002" s="11" t="inlineStr">
         <is>
-          <t>Yatırımcı Bilgilendirme Hizmeti</t>
+          <t>Hesap Açma</t>
         </is>
       </c>
       <c r="B2002" s="12" t="inlineStr"/>
@@ -35229,7 +35228,7 @@
       <c r="G2002" s="12" t="inlineStr"/>
       <c r="H2002" s="12" t="inlineStr">
         <is>
-          <t>55,68 TL / -
+          <t>17,75 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35238,7 +35237,7 @@
     <row r="2003" ht="32" customHeight="1">
       <c r="A2003" s="11" t="inlineStr">
         <is>
-          <t>Hesap Bakım</t>
+          <t>Yatırımcı Bilgilendirme Hizmeti</t>
         </is>
       </c>
       <c r="B2003" s="12" t="inlineStr"/>
@@ -35249,7 +35248,7 @@
       <c r="G2003" s="12" t="inlineStr"/>
       <c r="H2003" s="12" t="inlineStr">
         <is>
-          <t>0,11 TL / -
+          <t>55,68 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35258,7 +35257,7 @@
     <row r="2004" ht="32" customHeight="1">
       <c r="A2004" s="11" t="inlineStr">
         <is>
-          <t>Pay Senedi ve Katılım Şemsiye Fonuna Bağlı Yatırım Fonları ile Girişim Sermayesi Yatırım Fonları</t>
+          <t>Hesap Bakım</t>
         </is>
       </c>
       <c r="B2004" s="12" t="inlineStr"/>
@@ -35269,8 +35268,8 @@
       <c r="G2004" s="12" t="inlineStr"/>
       <c r="H2004" s="12" t="inlineStr">
         <is>
-          <t>- / 0,0001
-maks: - / 0,0001</t>
+          <t>0,11 TL / -
+maks: - / -</t>
         </is>
       </c>
       <c r="I2004" s="12" t="inlineStr"/>
@@ -35278,7 +35277,7 @@
     <row r="2005" ht="32" customHeight="1">
       <c r="A2005" s="11" t="inlineStr">
         <is>
-          <t>Diğer Yatırım Fonları</t>
+          <t>Pay Senedi ve Katılım Şemsiye Fonuna Bağlı Yatırım Fonları ile Girişim Sermayesi Yatırım Fonları</t>
         </is>
       </c>
       <c r="B2005" s="12" t="inlineStr"/>
@@ -35298,7 +35297,7 @@
     <row r="2006" ht="32" customHeight="1">
       <c r="A2006" s="11" t="inlineStr">
         <is>
-          <t>ÖSBA, VDMK, VTMK, Gayrimenkul Sertifikası, Kira Sertifikası ve DİBS Anapara</t>
+          <t>Diğer Yatırım Fonları</t>
         </is>
       </c>
       <c r="B2006" s="12" t="inlineStr"/>
@@ -35309,8 +35308,8 @@
       <c r="G2006" s="12" t="inlineStr"/>
       <c r="H2006" s="12" t="inlineStr">
         <is>
-          <t>- / 0,000065
-maks: - / 0,000065</t>
+          <t>- / 0,0001
+maks: - / 0,0001</t>
         </is>
       </c>
       <c r="I2006" s="12" t="inlineStr"/>
@@ -35318,7 +35317,7 @@
     <row r="2007" ht="32" customHeight="1">
       <c r="A2007" s="11" t="inlineStr">
         <is>
-          <t>ÖSBA, VDMK, VTMK, Kira Sertifikası ve DİBS Kuponlar</t>
+          <t>ÖSBA, VDMK, VTMK, Gayrimenkul Sertifikası, Kira Sertifikası ve DİBS Anapara</t>
         </is>
       </c>
       <c r="B2007" s="12" t="inlineStr"/>
@@ -35329,8 +35328,8 @@
       <c r="G2007" s="12" t="inlineStr"/>
       <c r="H2007" s="12" t="inlineStr">
         <is>
-          <t>- / 0,000007
-maks: - / 0,000007</t>
+          <t>- / 0,000065
+maks: - / 0,000065</t>
         </is>
       </c>
       <c r="I2007" s="12" t="inlineStr"/>
@@ -35338,7 +35337,7 @@
     <row r="2008" ht="32" customHeight="1">
       <c r="A2008" s="11" t="inlineStr">
         <is>
-          <t>Sermaye Arttırımı - Borsada İşlem Görebilir Nitelikte Pay Senetleri</t>
+          <t>ÖSBA, VDMK, VTMK, Kira Sertifikası ve DİBS Kuponlar</t>
         </is>
       </c>
       <c r="B2008" s="12" t="inlineStr"/>
@@ -35349,8 +35348,8 @@
       <c r="G2008" s="12" t="inlineStr"/>
       <c r="H2008" s="12" t="inlineStr">
         <is>
-          <t>- / 0,00025
-maks: - / 0,00025</t>
+          <t>- / 0,000007
+maks: - / 0,000007</t>
         </is>
       </c>
       <c r="I2008" s="12" t="inlineStr"/>
@@ -35358,7 +35357,7 @@
     <row r="2009" ht="32" customHeight="1">
       <c r="A2009" s="11" t="inlineStr">
         <is>
-          <t>Sermaye Azaltımı - Borsada İşlem Görebilir Nitelikte Pay Senetleri</t>
+          <t>Sermaye Arttırımı - Borsada İşlem Görebilir Nitelikte Pay Senetleri</t>
         </is>
       </c>
       <c r="B2009" s="12" t="inlineStr"/>
@@ -35378,7 +35377,7 @@
     <row r="2010" ht="32" customHeight="1">
       <c r="A2010" s="11" t="inlineStr">
         <is>
-          <t>ÖSBA, VDMK, VTMK, Gayrimenkul Sertifikası, Kira Sertifikası Anapara ve Kupon Ödemesi, Yatirim Fonu Kupon Ödemesi, Varant Nakdi Uzlaşı</t>
+          <t>Sermaye Azaltımı - Borsada İşlem Görebilir Nitelikte Pay Senetleri</t>
         </is>
       </c>
       <c r="B2010" s="12" t="inlineStr"/>
@@ -35389,8 +35388,8 @@
       <c r="G2010" s="12" t="inlineStr"/>
       <c r="H2010" s="12" t="inlineStr">
         <is>
-          <t>- / 0,0001
-maks: - / 0,0001</t>
+          <t>- / 0,00025
+maks: - / 0,00025</t>
         </is>
       </c>
       <c r="I2010" s="12" t="inlineStr"/>
@@ -35398,7 +35397,7 @@
     <row r="2011" ht="32" customHeight="1">
       <c r="A2011" s="11" t="inlineStr">
         <is>
-          <t>Borsada İşlem Görebilir Nitelikte Pay Senetleri</t>
+          <t>ÖSBA, VDMK, VTMK, Gayrimenkul Sertifikası, Kira Sertifikası Anapara ve Kupon Ödemesi, Yatirim Fonu Kupon Ödemesi, Varant Nakdi Uzlaşı</t>
         </is>
       </c>
       <c r="B2011" s="12" t="inlineStr"/>
@@ -35409,8 +35408,8 @@
       <c r="G2011" s="12" t="inlineStr"/>
       <c r="H2011" s="12" t="inlineStr">
         <is>
-          <t>- / 0,00025
-maks: - / 0,00025</t>
+          <t>- / 0,0001
+maks: - / 0,0001</t>
         </is>
       </c>
       <c r="I2011" s="12" t="inlineStr"/>
@@ -35418,7 +35417,7 @@
     <row r="2012" ht="32" customHeight="1">
       <c r="A2012" s="11" t="inlineStr">
         <is>
-          <t>Borsa İstanbul’da gerçekleşen Pay Senedi, Varant, Gayrimenkul Sertifikası, ÖSBA, VDMK,VTMK, BYF,Kira Sertifikası, Girişim Sermayesi Yatırım Fonu ve Gayrimenkul Yatırım Fonları alım satım kayıtları</t>
+          <t>Borsada İşlem Görebilir Nitelikte Pay Senetleri</t>
         </is>
       </c>
       <c r="B2012" s="12" t="inlineStr"/>
@@ -35429,8 +35428,8 @@
       <c r="G2012" s="12" t="inlineStr"/>
       <c r="H2012" s="12" t="inlineStr">
         <is>
-          <t>0,21 TL / -
-maks: - / -</t>
+          <t>- / 0,00025
+maks: - / 0,00025</t>
         </is>
       </c>
       <c r="I2012" s="12" t="inlineStr"/>
@@ -35438,7 +35437,7 @@
     <row r="2013" ht="32" customHeight="1">
       <c r="A2013" s="11" t="inlineStr">
         <is>
-          <t>Yatırım Fonu Payı Alım Satım İşlemleri</t>
+          <t>Borsa İstanbul’da gerçekleşen Pay Senedi, Varant, Gayrimenkul Sertifikası, ÖSBA, VDMK,VTMK, BYF,Kira Sertifikası, Girişim Sermayesi Yatırım Fonu ve Gayrimenkul Yatırım Fonları alım satım kayıtları</t>
         </is>
       </c>
       <c r="B2013" s="12" t="inlineStr"/>
@@ -35449,7 +35448,7 @@
       <c r="G2013" s="12" t="inlineStr"/>
       <c r="H2013" s="12" t="inlineStr">
         <is>
-          <t>0,01 TL / 0,00001
+          <t>0,21 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35458,7 +35457,7 @@
     <row r="2014" ht="32" customHeight="1">
       <c r="A2014" s="11" t="inlineStr">
         <is>
-          <t>DİBS alım satım işlemleri</t>
+          <t>Yatırım Fonu Payı Alım Satım İşlemleri</t>
         </is>
       </c>
       <c r="B2014" s="12" t="inlineStr"/>
@@ -35469,7 +35468,7 @@
       <c r="G2014" s="12" t="inlineStr"/>
       <c r="H2014" s="12" t="inlineStr">
         <is>
-          <t>0,15 TL / -
+          <t>0,01 TL / 0,00001
 maks: - / -</t>
         </is>
       </c>
@@ -35478,7 +35477,7 @@
     <row r="2015" ht="32" customHeight="1">
       <c r="A2015" s="11" t="inlineStr">
         <is>
-          <t>Borsada İşlem Göremeyen Nitelikten Borsada İşlem Görebilir Nitelikte paya dönüşüm</t>
+          <t>DİBS alım satım işlemleri</t>
         </is>
       </c>
       <c r="B2015" s="12" t="inlineStr"/>
@@ -35489,7 +35488,7 @@
       <c r="G2015" s="12" t="inlineStr"/>
       <c r="H2015" s="12" t="inlineStr">
         <is>
-          <t>189 TL / 0,00001
+          <t>0,15 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35498,7 +35497,7 @@
     <row r="2016" ht="32" customHeight="1">
       <c r="A2016" s="11" t="inlineStr">
         <is>
-          <t>Rehin/Teminat İşlemi</t>
+          <t>Borsada İşlem Göremeyen Nitelikten Borsada İşlem Görebilir Nitelikte paya dönüşüm</t>
         </is>
       </c>
       <c r="B2016" s="12" t="inlineStr"/>
@@ -35509,7 +35508,7 @@
       <c r="G2016" s="12" t="inlineStr"/>
       <c r="H2016" s="12" t="inlineStr">
         <is>
-          <t>1,39 TL / -
+          <t>189 TL / 0,00001
 maks: - / -</t>
         </is>
       </c>
@@ -35518,7 +35517,7 @@
     <row r="2017" ht="32" customHeight="1">
       <c r="A2017" s="11" t="inlineStr">
         <is>
-          <t>İntifa İşlemi</t>
+          <t>Rehin/Teminat İşlemi</t>
         </is>
       </c>
       <c r="B2017" s="12" t="inlineStr"/>
@@ -35529,7 +35528,7 @@
       <c r="G2017" s="12" t="inlineStr"/>
       <c r="H2017" s="12" t="inlineStr">
         <is>
-          <t>139,21 TL / -
+          <t>1,39 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35538,7 +35537,7 @@
     <row r="2018" ht="32" customHeight="1">
       <c r="A2018" s="11" t="inlineStr">
         <is>
-          <t>Hapis İşlemi</t>
+          <t>İntifa İşlemi</t>
         </is>
       </c>
       <c r="B2018" s="12" t="inlineStr"/>
@@ -35549,7 +35548,7 @@
       <c r="G2018" s="12" t="inlineStr"/>
       <c r="H2018" s="12" t="inlineStr">
         <is>
-          <t>1,39 TL / -
+          <t>139,21 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35558,7 +35557,7 @@
     <row r="2019" ht="32" customHeight="1">
       <c r="A2019" s="11" t="inlineStr">
         <is>
-          <t>EMKT üzerinden depo devri</t>
+          <t>Hapis İşlemi</t>
         </is>
       </c>
       <c r="B2019" s="12" t="inlineStr"/>
@@ -35569,7 +35568,7 @@
       <c r="G2019" s="12" t="inlineStr"/>
       <c r="H2019" s="12" t="inlineStr">
         <is>
-          <t>9,74 TL / -
+          <t>1,39 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35578,7 +35577,7 @@
     <row r="2020" ht="32" customHeight="1">
       <c r="A2020" s="11" t="inlineStr">
         <is>
-          <t>Üyelerarası menkul kıymet transferi</t>
+          <t>EMKT üzerinden depo devri</t>
         </is>
       </c>
       <c r="B2020" s="12" t="inlineStr"/>
@@ -35589,7 +35588,7 @@
       <c r="G2020" s="12" t="inlineStr"/>
       <c r="H2020" s="12" t="inlineStr">
         <is>
-          <t>13,05 TL / -
+          <t>9,74 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35598,7 +35597,7 @@
     <row r="2021" ht="32" customHeight="1">
       <c r="A2021" s="11" t="inlineStr">
         <is>
-          <t>Üye İçi hesaplararası menkul kıymet  transferi</t>
+          <t>Üyelerarası menkul kıymet transferi</t>
         </is>
       </c>
       <c r="B2021" s="12" t="inlineStr"/>
@@ -35609,7 +35608,7 @@
       <c r="G2021" s="12" t="inlineStr"/>
       <c r="H2021" s="12" t="inlineStr">
         <is>
-          <t>2,61 TL / -
+          <t>13,05 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35618,7 +35617,7 @@
     <row r="2022" ht="32" customHeight="1">
       <c r="A2022" s="11" t="inlineStr">
         <is>
-          <t>Üyeler arası menkul kıymet transfer öneşleşme talimatı</t>
+          <t>Üye İçi hesaplararası menkul kıymet  transferi</t>
         </is>
       </c>
       <c r="B2022" s="12" t="inlineStr"/>
@@ -35629,7 +35628,7 @@
       <c r="G2022" s="12" t="inlineStr"/>
       <c r="H2022" s="12" t="inlineStr">
         <is>
-          <t>8,7 TL / -
+          <t>2,61 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35638,7 +35637,7 @@
     <row r="2023" ht="32" customHeight="1">
       <c r="A2023" s="11" t="inlineStr">
         <is>
-          <t>Öneşleşme sonrası üyelerarası menkul kıymet transferi</t>
+          <t>Üyeler arası menkul kıymet transfer öneşleşme talimatı</t>
         </is>
       </c>
       <c r="B2023" s="12" t="inlineStr"/>
@@ -35658,7 +35657,7 @@
     <row r="2024" ht="32" customHeight="1">
       <c r="A2024" s="11" t="inlineStr">
         <is>
-          <t>Uluslararası sermaye piyasası aracı  gönderimi/kabulü</t>
+          <t>Öneşleşme sonrası üyelerarası menkul kıymet transferi</t>
         </is>
       </c>
       <c r="B2024" s="12" t="inlineStr"/>
@@ -35669,7 +35668,7 @@
       <c r="G2024" s="12" t="inlineStr"/>
       <c r="H2024" s="12" t="inlineStr">
         <is>
-          <t>208,81 TL / -
+          <t>8,7 TL / -
 maks: - / -</t>
         </is>
       </c>
@@ -35678,7 +35677,7 @@
     <row r="2025" ht="32" customHeight="1">
       <c r="A2025" s="11" t="inlineStr">
         <is>
-          <t>Transfer nedeni “Devir” ve “Ödünç” seçilerek borsada işlem görebilir nitelikteki pay senetlerinin üyeler arası ve üye içi transferi</t>
+          <t>Uluslararası sermaye piyasası aracı  gönderimi/kabulü</t>
         </is>
       </c>
       <c r="B2025" s="12" t="inlineStr"/>
@@ -35689,43 +35688,43 @@
       <c r="G2025" s="12" t="inlineStr"/>
       <c r="H2025" s="12" t="inlineStr">
         <is>
+          <t>208,81 TL / -
+maks: - / -</t>
+        </is>
+      </c>
+      <c r="I2025" s="12" t="inlineStr"/>
+    </row>
+    <row r="2026" ht="32" customHeight="1">
+      <c r="A2026" s="11" t="inlineStr">
+        <is>
+          <t>Transfer nedeni “Devir” ve “Ödünç” seçilerek borsada işlem görebilir nitelikteki pay senetlerinin üyeler arası ve üye içi transferi</t>
+        </is>
+      </c>
+      <c r="B2026" s="12" t="inlineStr"/>
+      <c r="C2026" s="12" t="inlineStr"/>
+      <c r="D2026" s="12" t="inlineStr"/>
+      <c r="E2026" s="12" t="inlineStr"/>
+      <c r="F2026" s="12" t="inlineStr"/>
+      <c r="G2026" s="12" t="inlineStr"/>
+      <c r="H2026" s="12" t="inlineStr">
+        <is>
           <t>46 TL / 0,00003
 maks: 230 TL / -</t>
         </is>
       </c>
-      <c r="I2025" s="12" t="inlineStr"/>
-    </row>
-    <row r="2026" ht="16" customHeight="1">
-      <c r="A2026" s="10" t="inlineStr">
+      <c r="I2026" s="12" t="inlineStr"/>
+    </row>
+    <row r="2027" ht="16" customHeight="1">
+      <c r="A2027" s="10" t="inlineStr">
         <is>
           <t>Sabit Getirili Menkul Kıymet İşlem Ücretleri</t>
         </is>
       </c>
-    </row>
-    <row r="2027" ht="32" customHeight="1">
-      <c r="A2027" s="11" t="inlineStr">
-        <is>
-          <t>BİST Emir İletimi Aracılık Ücreti</t>
-        </is>
-      </c>
-      <c r="B2027" s="12" t="inlineStr"/>
-      <c r="C2027" s="12" t="inlineStr"/>
-      <c r="D2027" s="12" t="inlineStr"/>
-      <c r="E2027" s="12" t="inlineStr"/>
-      <c r="F2027" s="12" t="inlineStr"/>
-      <c r="G2027" s="12" t="inlineStr"/>
-      <c r="H2027" s="12" t="inlineStr">
-        <is>
-          <t>- / 0,02
-maks: - / -</t>
-        </is>
-      </c>
-      <c r="I2027" s="12" t="inlineStr"/>
     </row>
     <row r="2028" ht="32" customHeight="1">
       <c r="A2028" s="11" t="inlineStr">
         <is>
-          <t>T.C. Hazine ve Maliye Bakanlığı Tarafından Yapılan İhalelere Aracılık Ücreti</t>
+          <t>BİST Emir İletimi Aracılık Ücreti</t>
         </is>
       </c>
       <c r="B2028" s="12" t="inlineStr"/>
@@ -35745,7 +35744,7 @@
     <row r="2029" ht="32" customHeight="1">
       <c r="A2029" s="11" t="inlineStr">
         <is>
-          <t>Başka Kuruma Bono/Tahvil Virmanı</t>
+          <t>T.C. Hazine ve Maliye Bakanlığı Tarafından Yapılan İhalelere Aracılık Ücreti</t>
         </is>
       </c>
       <c r="B2029" s="12" t="inlineStr"/>
@@ -35756,8 +35755,8 @@
       <c r="G2029" s="12" t="inlineStr"/>
       <c r="H2029" s="12" t="inlineStr">
         <is>
-          <t>450 TL / -
-maks: 450 TL / -</t>
+          <t>- / 0,02
+maks: - / -</t>
         </is>
       </c>
       <c r="I2029" s="12" t="inlineStr"/>
@@ -35765,7 +35764,7 @@
     <row r="2030" ht="32" customHeight="1">
       <c r="A2030" s="11" t="inlineStr">
         <is>
-          <t>Başka Kuruma Eurobond Virmanı</t>
+          <t>Başka Kuruma Bono/Tahvil Virmanı</t>
         </is>
       </c>
       <c r="B2030" s="12" t="inlineStr"/>
@@ -35776,43 +35775,43 @@
       <c r="G2030" s="12" t="inlineStr"/>
       <c r="H2030" s="12" t="inlineStr">
         <is>
+          <t>450 TL / -
+maks: 450 TL / -</t>
+        </is>
+      </c>
+      <c r="I2030" s="12" t="inlineStr"/>
+    </row>
+    <row r="2031" ht="32" customHeight="1">
+      <c r="A2031" s="11" t="inlineStr">
+        <is>
+          <t>Başka Kuruma Eurobond Virmanı</t>
+        </is>
+      </c>
+      <c r="B2031" s="12" t="inlineStr"/>
+      <c r="C2031" s="12" t="inlineStr"/>
+      <c r="D2031" s="12" t="inlineStr"/>
+      <c r="E2031" s="12" t="inlineStr"/>
+      <c r="F2031" s="12" t="inlineStr"/>
+      <c r="G2031" s="12" t="inlineStr"/>
+      <c r="H2031" s="12" t="inlineStr">
+        <is>
           <t>20 USD / -
 maks: 20 USD / -</t>
         </is>
       </c>
-      <c r="I2030" s="12" t="inlineStr"/>
-    </row>
-    <row r="2031" ht="16" customHeight="1">
-      <c r="A2031" s="10" t="inlineStr">
+      <c r="I2031" s="12" t="inlineStr"/>
+    </row>
+    <row r="2032" ht="16" customHeight="1">
+      <c r="A2032" s="10" t="inlineStr">
         <is>
           <t>Hisse Senedi İşlemleri</t>
         </is>
       </c>
-    </row>
-    <row r="2032" ht="32" customHeight="1">
-      <c r="A2032" s="11" t="inlineStr">
-        <is>
-          <t>Temettü Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B2032" s="12" t="inlineStr"/>
-      <c r="C2032" s="12" t="inlineStr"/>
-      <c r="D2032" s="12" t="inlineStr"/>
-      <c r="E2032" s="12" t="inlineStr"/>
-      <c r="F2032" s="12" t="inlineStr"/>
-      <c r="G2032" s="12" t="inlineStr"/>
-      <c r="H2032" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / -</t>
-        </is>
-      </c>
-      <c r="I2032" s="12" t="inlineStr"/>
     </row>
     <row r="2033" ht="32" customHeight="1">
       <c r="A2033" s="11" t="inlineStr">
         <is>
-          <t>Virman</t>
+          <t>Temettü Ödemeleri</t>
         </is>
       </c>
       <c r="B2033" s="12" t="inlineStr"/>
@@ -35832,7 +35831,7 @@
     <row r="2034" ht="32" customHeight="1">
       <c r="A2034" s="11" t="inlineStr">
         <is>
-          <t>İnternet Bankacılığı / Mobil Bankacılık</t>
+          <t>Virman</t>
         </is>
       </c>
       <c r="B2034" s="12" t="inlineStr"/>
@@ -35852,7 +35851,7 @@
     <row r="2035" ht="32" customHeight="1">
       <c r="A2035" s="11" t="inlineStr">
         <is>
-          <t>Diğer Kanallar</t>
+          <t>İnternet Bankacılığı / Mobil Bankacılık</t>
         </is>
       </c>
       <c r="B2035" s="12" t="inlineStr"/>
@@ -35872,7 +35871,7 @@
     <row r="2036" ht="32" customHeight="1">
       <c r="A2036" s="11" t="inlineStr">
         <is>
-          <t>Sermaye Artırma Komisyonu</t>
+          <t>Diğer Kanallar</t>
         </is>
       </c>
       <c r="B2036" s="12" t="inlineStr"/>
@@ -35889,37 +35888,37 @@
       </c>
       <c r="I2036" s="12" t="inlineStr"/>
     </row>
-    <row r="2037" ht="16" customHeight="1">
-      <c r="A2037" s="10" t="inlineStr">
+    <row r="2037" ht="32" customHeight="1">
+      <c r="A2037" s="11" t="inlineStr">
+        <is>
+          <t>Sermaye Artırma Komisyonu</t>
+        </is>
+      </c>
+      <c r="B2037" s="12" t="inlineStr"/>
+      <c r="C2037" s="12" t="inlineStr"/>
+      <c r="D2037" s="12" t="inlineStr"/>
+      <c r="E2037" s="12" t="inlineStr"/>
+      <c r="F2037" s="12" t="inlineStr"/>
+      <c r="G2037" s="12" t="inlineStr"/>
+      <c r="H2037" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: - / -</t>
+        </is>
+      </c>
+      <c r="I2037" s="12" t="inlineStr"/>
+    </row>
+    <row r="2038" ht="16" customHeight="1">
+      <c r="A2038" s="10" t="inlineStr">
         <is>
           <t>Senetler</t>
         </is>
       </c>
-    </row>
-    <row r="2038" ht="32" customHeight="1">
-      <c r="A2038" s="11" t="inlineStr">
-        <is>
-          <t>Senet Tahsili (Muhabir Bankada)</t>
-        </is>
-      </c>
-      <c r="B2038" s="12" t="inlineStr"/>
-      <c r="C2038" s="12" t="inlineStr"/>
-      <c r="D2038" s="12" t="inlineStr"/>
-      <c r="E2038" s="12" t="inlineStr"/>
-      <c r="F2038" s="12" t="inlineStr"/>
-      <c r="G2038" s="12" t="inlineStr"/>
-      <c r="H2038" s="12" t="inlineStr">
-        <is>
-          <t>600 TL / -
-maks: 600 TL / -</t>
-        </is>
-      </c>
-      <c r="I2038" s="12" t="inlineStr"/>
     </row>
     <row r="2039" ht="32" customHeight="1">
       <c r="A2039" s="11" t="inlineStr">
         <is>
-          <t>Senet Tahsili (Bankamızda)</t>
+          <t>Senet Tahsili (Muhabir Bankada)</t>
         </is>
       </c>
       <c r="B2039" s="12" t="inlineStr"/>
@@ -35939,7 +35938,7 @@
     <row r="2040" ht="32" customHeight="1">
       <c r="A2040" s="11" t="inlineStr">
         <is>
-          <t>Senet İade (Protestolu/Protestosuz)</t>
+          <t>Senet Tahsili (Bankamızda)</t>
         </is>
       </c>
       <c r="B2040" s="12" t="inlineStr"/>
@@ -35956,37 +35955,37 @@
       </c>
       <c r="I2040" s="12" t="inlineStr"/>
     </row>
-    <row r="2041" ht="16" customHeight="1">
-      <c r="A2041" s="10" t="inlineStr">
+    <row r="2041" ht="32" customHeight="1">
+      <c r="A2041" s="11" t="inlineStr">
+        <is>
+          <t>Senet İade (Protestolu/Protestosuz)</t>
+        </is>
+      </c>
+      <c r="B2041" s="12" t="inlineStr"/>
+      <c r="C2041" s="12" t="inlineStr"/>
+      <c r="D2041" s="12" t="inlineStr"/>
+      <c r="E2041" s="12" t="inlineStr"/>
+      <c r="F2041" s="12" t="inlineStr"/>
+      <c r="G2041" s="12" t="inlineStr"/>
+      <c r="H2041" s="12" t="inlineStr">
+        <is>
+          <t>600 TL / -
+maks: 600 TL / -</t>
+        </is>
+      </c>
+      <c r="I2041" s="12" t="inlineStr"/>
+    </row>
+    <row r="2042" ht="16" customHeight="1">
+      <c r="A2042" s="10" t="inlineStr">
         <is>
           <t>Çekler</t>
-        </is>
-      </c>
-    </row>
-    <row r="2042" ht="32" customHeight="1">
-      <c r="A2042" s="11" t="inlineStr">
-        <is>
-          <t>Aynı Şube Karşılıksız Çek Elden Ödeme Tl</t>
-        </is>
-      </c>
-      <c r="B2042" s="12" t="inlineStr"/>
-      <c r="C2042" s="12" t="inlineStr"/>
-      <c r="D2042" s="12" t="inlineStr"/>
-      <c r="E2042" s="12" t="inlineStr"/>
-      <c r="F2042" s="12" t="inlineStr"/>
-      <c r="G2042" s="12" t="inlineStr"/>
-      <c r="H2042" s="12" t="inlineStr"/>
-      <c r="I2042" s="12" t="inlineStr">
-        <is>
-          <t>427,62 TL / -
-maks: 427,62 TL / -</t>
         </is>
       </c>
     </row>
     <row r="2043" ht="32" customHeight="1">
       <c r="A2043" s="11" t="inlineStr">
         <is>
-          <t>Aynı Şube Karşılıksız Çek Elden Ödeme Yp</t>
+          <t>Aynı Şube Karşılıksız Çek Elden Ödeme Tl</t>
         </is>
       </c>
       <c r="B2043" s="12" t="inlineStr"/>
@@ -36006,7 +36005,7 @@
     <row r="2044" ht="32" customHeight="1">
       <c r="A2044" s="11" t="inlineStr">
         <is>
-          <t>Aynı Şube Çek Ödeme TL / YP</t>
+          <t>Aynı Şube Karşılıksız Çek Elden Ödeme Yp</t>
         </is>
       </c>
       <c r="B2044" s="12" t="inlineStr"/>
@@ -36026,7 +36025,7 @@
     <row r="2045" ht="32" customHeight="1">
       <c r="A2045" s="11" t="inlineStr">
         <is>
-          <t>Başka Şube Çek Ödeme TL/YP</t>
+          <t>Aynı Şube Çek Ödeme TL / YP</t>
         </is>
       </c>
       <c r="B2045" s="12" t="inlineStr"/>
@@ -36038,15 +36037,15 @@
       <c r="H2045" s="12" t="inlineStr"/>
       <c r="I2045" s="12" t="inlineStr">
         <is>
-          <t>576,19 TL / 0,8
-maks: 3.930,48 TL / -</t>
+          <t>427,62 TL / -
+maks: 427,62 TL / -</t>
         </is>
       </c>
     </row>
     <row r="2046" ht="32" customHeight="1">
       <c r="A2046" s="11" t="inlineStr">
         <is>
-          <t>Başka Şube Karşılıksız Çek Elden Ödeme Tl</t>
+          <t>Başka Şube Çek Ödeme TL/YP</t>
         </is>
       </c>
       <c r="B2046" s="12" t="inlineStr"/>
@@ -36058,7 +36057,7 @@
       <c r="H2046" s="12" t="inlineStr"/>
       <c r="I2046" s="12" t="inlineStr">
         <is>
-          <t>576,19 TL / 0,6
+          <t>576,19 TL / 0,8
 maks: 3.930,48 TL / -</t>
         </is>
       </c>
@@ -36066,7 +36065,7 @@
     <row r="2047" ht="32" customHeight="1">
       <c r="A2047" s="11" t="inlineStr">
         <is>
-          <t>Başka Şube Karşılıksız Çek Elden Ödeme Yp</t>
+          <t>Başka Şube Karşılıksız Çek Elden Ödeme Tl</t>
         </is>
       </c>
       <c r="B2047" s="12" t="inlineStr"/>
@@ -36086,7 +36085,7 @@
     <row r="2048" ht="32" customHeight="1">
       <c r="A2048" s="11" t="inlineStr">
         <is>
-          <t>KKB Çek Sorgu Raporu</t>
+          <t>Başka Şube Karşılıksız Çek Elden Ödeme Yp</t>
         </is>
       </c>
       <c r="B2048" s="12" t="inlineStr"/>
@@ -36095,18 +36094,18 @@
       <c r="E2048" s="12" t="inlineStr"/>
       <c r="F2048" s="12" t="inlineStr"/>
       <c r="G2048" s="12" t="inlineStr"/>
-      <c r="H2048" s="12" t="inlineStr">
-        <is>
-          <t>47,5 TL / -
-maks: 47,5 TL / -</t>
-        </is>
-      </c>
-      <c r="I2048" s="12" t="inlineStr"/>
+      <c r="H2048" s="12" t="inlineStr"/>
+      <c r="I2048" s="12" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6
+maks: 3.930,48 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="2049" ht="32" customHeight="1">
       <c r="A2049" s="11" t="inlineStr">
         <is>
-          <t>KKB Risk Raporu Sorgulama Ücreti (Bireysel)</t>
+          <t>KKB Çek Sorgu Raporu</t>
         </is>
       </c>
       <c r="B2049" s="12" t="inlineStr"/>
@@ -36117,8 +36116,8 @@
       <c r="G2049" s="12" t="inlineStr"/>
       <c r="H2049" s="12" t="inlineStr">
         <is>
-          <t>94,29 TL / -
-maks: 94,29 TL / -</t>
+          <t>47,5 TL / -
+maks: 47,5 TL / -</t>
         </is>
       </c>
       <c r="I2049" s="12" t="inlineStr"/>
@@ -36126,7 +36125,7 @@
     <row r="2050" ht="32" customHeight="1">
       <c r="A2050" s="11" t="inlineStr">
         <is>
-          <t>Karşılıksız Çek Düzeltme Hakkı Kullandırma</t>
+          <t>KKB Risk Raporu Sorgulama Ücreti (Bireysel)</t>
         </is>
       </c>
       <c r="B2050" s="12" t="inlineStr"/>
@@ -36137,8 +36136,8 @@
       <c r="G2050" s="12" t="inlineStr"/>
       <c r="H2050" s="12" t="inlineStr">
         <is>
-          <t>371,43 TL / -
-maks: 371,43 TL / -</t>
+          <t>94,29 TL / -
+maks: 94,29 TL / -</t>
         </is>
       </c>
       <c r="I2050" s="12" t="inlineStr"/>
@@ -36146,7 +36145,7 @@
     <row r="2051" ht="32" customHeight="1">
       <c r="A2051" s="11" t="inlineStr">
         <is>
-          <t>Yurt Dışına Müşteri Çeki Ödemesi</t>
+          <t>Karşılıksız Çek Düzeltme Hakkı Kullandırma</t>
         </is>
       </c>
       <c r="B2051" s="12" t="inlineStr"/>
@@ -36157,8 +36156,8 @@
       <c r="G2051" s="12" t="inlineStr"/>
       <c r="H2051" s="12" t="inlineStr">
         <is>
-          <t>675,24 TL / 0,5
-maks: 3.404,76 TL / -</t>
+          <t>371,43 TL / -
+maks: 371,43 TL / -</t>
         </is>
       </c>
       <c r="I2051" s="12" t="inlineStr"/>
@@ -36166,7 +36165,7 @@
     <row r="2052" ht="32" customHeight="1">
       <c r="A2052" s="11" t="inlineStr">
         <is>
-          <t>Diğer Banka YP Çek Takas Masrafı</t>
+          <t>Yurt Dışına Müşteri Çeki Ödemesi</t>
         </is>
       </c>
       <c r="B2052" s="12" t="inlineStr"/>
@@ -36177,8 +36176,8 @@
       <c r="G2052" s="12" t="inlineStr"/>
       <c r="H2052" s="12" t="inlineStr">
         <is>
-          <t>1.469,52 TL / -
-maks: 1.469,52 TL / -</t>
+          <t>675,24 TL / 0,5
+maks: 3.404,76 TL / -</t>
         </is>
       </c>
       <c r="I2052" s="12" t="inlineStr"/>
@@ -36186,7 +36185,7 @@
     <row r="2053" ht="32" customHeight="1">
       <c r="A2053" s="11" t="inlineStr">
         <is>
-          <t>Hesaba Ödeme</t>
+          <t>Diğer Banka YP Çek Takas Masrafı</t>
         </is>
       </c>
       <c r="B2053" s="12" t="inlineStr"/>
@@ -36197,8 +36196,8 @@
       <c r="G2053" s="12" t="inlineStr"/>
       <c r="H2053" s="12" t="inlineStr">
         <is>
-          <t>427,62 TL / 0,5
-maks: 1.669,52 TL / -</t>
+          <t>1.469,52 TL / -
+maks: 1.469,52 TL / -</t>
         </is>
       </c>
       <c r="I2053" s="12" t="inlineStr"/>
@@ -36206,7 +36205,7 @@
     <row r="2054" ht="32" customHeight="1">
       <c r="A2054" s="11" t="inlineStr">
         <is>
-          <t>Efektif Ödeme</t>
+          <t>Hesaba Ödeme</t>
         </is>
       </c>
       <c r="B2054" s="12" t="inlineStr"/>
@@ -36226,7 +36225,7 @@
     <row r="2055" ht="32" customHeight="1">
       <c r="A2055" s="11" t="inlineStr">
         <is>
-          <t>Seyahat Çeki Ödeme</t>
+          <t>Efektif Ödeme</t>
         </is>
       </c>
       <c r="B2055" s="12" t="inlineStr"/>
@@ -36237,8 +36236,8 @@
       <c r="G2055" s="12" t="inlineStr"/>
       <c r="H2055" s="12" t="inlineStr">
         <is>
-          <t>190,48 TL / 0,5
-maks: 666,67 TL / -</t>
+          <t>427,62 TL / 0,5
+maks: 1.669,52 TL / -</t>
         </is>
       </c>
       <c r="I2055" s="12" t="inlineStr"/>
@@ -36246,7 +36245,7 @@
     <row r="2056" ht="32" customHeight="1">
       <c r="A2056" s="11" t="inlineStr">
         <is>
-          <t>Muhabir Bankalar Tarafından Bankamız Üzerine Keşide Edilen Çekler</t>
+          <t>Seyahat Çeki Ödeme</t>
         </is>
       </c>
       <c r="B2056" s="12" t="inlineStr"/>
@@ -36257,8 +36256,8 @@
       <c r="G2056" s="12" t="inlineStr"/>
       <c r="H2056" s="12" t="inlineStr">
         <is>
-          <t>160,95 TL / 0,5
-maks: 1.300 TL / -</t>
+          <t>190,48 TL / 0,5
+maks: 666,67 TL / -</t>
         </is>
       </c>
       <c r="I2056" s="12" t="inlineStr"/>
@@ -36266,7 +36265,7 @@
     <row r="2057" ht="32" customHeight="1">
       <c r="A2057" s="11" t="inlineStr">
         <is>
-          <t>Keşide Çeki / Bloke Çek Düzenleme</t>
+          <t>Muhabir Bankalar Tarafından Bankamız Üzerine Keşide Edilen Çekler</t>
         </is>
       </c>
       <c r="B2057" s="12" t="inlineStr"/>
@@ -36277,8 +36276,8 @@
       <c r="G2057" s="12" t="inlineStr"/>
       <c r="H2057" s="12" t="inlineStr">
         <is>
-          <t>544,76 TL / 0,5
-maks: 3.157,14 TL / -</t>
+          <t>160,95 TL / 0,5
+maks: 1.300 TL / -</t>
         </is>
       </c>
       <c r="I2057" s="12" t="inlineStr"/>
@@ -36286,7 +36285,7 @@
     <row r="2058" ht="32" customHeight="1">
       <c r="A2058" s="11" t="inlineStr">
         <is>
-          <t>Kurye Masrafı (Tahsil - İştira YP Çek İşlemleri ) / Çek Başına</t>
+          <t>Keşide Çeki / Bloke Çek Düzenleme</t>
         </is>
       </c>
       <c r="B2058" s="12" t="inlineStr"/>
@@ -36297,8 +36296,8 @@
       <c r="G2058" s="12" t="inlineStr"/>
       <c r="H2058" s="12" t="inlineStr">
         <is>
-          <t>5 USD / -
-maks: 5 USD / -</t>
+          <t>544,76 TL / 0,5
+maks: 3.157,14 TL / -</t>
         </is>
       </c>
       <c r="I2058" s="12" t="inlineStr"/>
@@ -36306,7 +36305,7 @@
     <row r="2059" ht="32" customHeight="1">
       <c r="A2059" s="11" t="inlineStr">
         <is>
-          <t>İştira Kaydıyla Alınan YP Çekler- Ülke ve Döviz Cinsi Farklı Olan</t>
+          <t>Kurye Masrafı (Tahsil - İştira YP Çek İşlemleri ) / Çek Başına</t>
         </is>
       </c>
       <c r="B2059" s="12" t="inlineStr"/>
@@ -36317,8 +36316,8 @@
       <c r="G2059" s="12" t="inlineStr"/>
       <c r="H2059" s="12" t="inlineStr">
         <is>
-          <t>440 TL / 1
-maks: 1.720,95 TL / -</t>
+          <t>5 USD / -
+maks: 5 USD / -</t>
         </is>
       </c>
       <c r="I2059" s="12" t="inlineStr"/>
@@ -36326,7 +36325,7 @@
     <row r="2060" ht="32" customHeight="1">
       <c r="A2060" s="11" t="inlineStr">
         <is>
-          <t>İştira Kaydıyla Alınan YP Çekler- TL Ödeme</t>
+          <t>İştira Kaydıyla Alınan YP Çekler- Ülke ve Döviz Cinsi Farklı Olan</t>
         </is>
       </c>
       <c r="B2060" s="12" t="inlineStr"/>
@@ -36337,7 +36336,7 @@
       <c r="G2060" s="12" t="inlineStr"/>
       <c r="H2060" s="12" t="inlineStr">
         <is>
-          <t>440 TL / 0,5
+          <t>440 TL / 1
 maks: 1.720,95 TL / -</t>
         </is>
       </c>
@@ -36346,7 +36345,7 @@
     <row r="2061" ht="32" customHeight="1">
       <c r="A2061" s="11" t="inlineStr">
         <is>
-          <t>İştira Kaydıyla Alınan YP Çekler- Efektif Ödeme</t>
+          <t>İştira Kaydıyla Alınan YP Çekler- TL Ödeme</t>
         </is>
       </c>
       <c r="B2061" s="12" t="inlineStr"/>
@@ -36357,7 +36356,7 @@
       <c r="G2061" s="12" t="inlineStr"/>
       <c r="H2061" s="12" t="inlineStr">
         <is>
-          <t>440 TL / 1
+          <t>440 TL / 0,5
 maks: 1.720,95 TL / -</t>
         </is>
       </c>
@@ -36366,7 +36365,7 @@
     <row r="2062" ht="32" customHeight="1">
       <c r="A2062" s="11" t="inlineStr">
         <is>
-          <t>Tahsile Verilen Çekin İşlemsiz İadesi</t>
+          <t>İştira Kaydıyla Alınan YP Çekler- Efektif Ödeme</t>
         </is>
       </c>
       <c r="B2062" s="12" t="inlineStr"/>
@@ -36377,8 +36376,8 @@
       <c r="G2062" s="12" t="inlineStr"/>
       <c r="H2062" s="12" t="inlineStr">
         <is>
-          <t>123,81 TL / -
-maks: 123,81 TL / -</t>
+          <t>440 TL / 1
+maks: 1.720,95 TL / -</t>
         </is>
       </c>
       <c r="I2062" s="12" t="inlineStr"/>
@@ -36386,7 +36385,7 @@
     <row r="2063" ht="32" customHeight="1">
       <c r="A2063" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilatı- YKB Çeki (YP)</t>
+          <t>Tahsile Verilen Çekin İşlemsiz İadesi</t>
         </is>
       </c>
       <c r="B2063" s="12" t="inlineStr"/>
@@ -36397,8 +36396,8 @@
       <c r="G2063" s="12" t="inlineStr"/>
       <c r="H2063" s="12" t="inlineStr">
         <is>
-          <t>361,9 TL / -
-maks: 361,9 TL / -</t>
+          <t>123,81 TL / -
+maks: 123,81 TL / -</t>
         </is>
       </c>
       <c r="I2063" s="12" t="inlineStr"/>
@@ -36406,7 +36405,7 @@
     <row r="2064" ht="32" customHeight="1">
       <c r="A2064" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilatı- YKB Çeki (TL)</t>
+          <t>Çek Tahsilatı- YKB Çeki (YP)</t>
         </is>
       </c>
       <c r="B2064" s="12" t="inlineStr"/>
@@ -36426,7 +36425,7 @@
     <row r="2065" ht="32" customHeight="1">
       <c r="A2065" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilatı -Yurtiçi Banka Çeki (YP)</t>
+          <t>Çek Tahsilatı- YKB Çeki (TL)</t>
         </is>
       </c>
       <c r="B2065" s="12" t="inlineStr"/>
@@ -36446,7 +36445,7 @@
     <row r="2066" ht="32" customHeight="1">
       <c r="A2066" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilatı - Yurtiçi Banka Çeki (TL)</t>
+          <t>Çek Tahsilatı -Yurtiçi Banka Çeki (YP)</t>
         </is>
       </c>
       <c r="B2066" s="12" t="inlineStr"/>
@@ -36466,7 +36465,7 @@
     <row r="2067" ht="32" customHeight="1">
       <c r="A2067" s="11" t="inlineStr">
         <is>
-          <t>Çek Karnesi Komisyonu- 10'luk Çek Karnesi</t>
+          <t>Çek Tahsilatı - Yurtiçi Banka Çeki (TL)</t>
         </is>
       </c>
       <c r="B2067" s="12" t="inlineStr"/>
@@ -36477,8 +36476,8 @@
       <c r="G2067" s="12" t="inlineStr"/>
       <c r="H2067" s="12" t="inlineStr">
         <is>
-          <t>866,67 TL / -
-maks: 866,67 TL / -</t>
+          <t>361,9 TL / -
+maks: 361,9 TL / -</t>
         </is>
       </c>
       <c r="I2067" s="12" t="inlineStr"/>
@@ -36486,7 +36485,7 @@
     <row r="2068" ht="32" customHeight="1">
       <c r="A2068" s="11" t="inlineStr">
         <is>
-          <t>Çek Karnesi Komisyonu- 25'lik Çek Karnesi</t>
+          <t>Çek Karnesi Komisyonu- 10'luk Çek Karnesi</t>
         </is>
       </c>
       <c r="B2068" s="12" t="inlineStr"/>
@@ -36497,8 +36496,8 @@
       <c r="G2068" s="12" t="inlineStr"/>
       <c r="H2068" s="12" t="inlineStr">
         <is>
-          <t>2.166,67 TL / -
-maks: 2.166,67 TL / -</t>
+          <t>866,67 TL / -
+maks: 866,67 TL / -</t>
         </is>
       </c>
       <c r="I2068" s="12" t="inlineStr"/>
@@ -36506,7 +36505,7 @@
     <row r="2069" ht="32" customHeight="1">
       <c r="A2069" s="11" t="inlineStr">
         <is>
-          <t>Çek Karnesi Komisyonu- 100'lük Sürekli Form</t>
+          <t>Çek Karnesi Komisyonu- 25'lik Çek Karnesi</t>
         </is>
       </c>
       <c r="B2069" s="12" t="inlineStr"/>
@@ -36517,8 +36516,8 @@
       <c r="G2069" s="12" t="inlineStr"/>
       <c r="H2069" s="12" t="inlineStr">
         <is>
-          <t>8.666,67 TL / -
-maks: 8.666,67 TL / -</t>
+          <t>2.166,67 TL / -
+maks: 2.166,67 TL / -</t>
         </is>
       </c>
       <c r="I2069" s="12" t="inlineStr"/>
@@ -36526,7 +36525,7 @@
     <row r="2070" ht="32" customHeight="1">
       <c r="A2070" s="11" t="inlineStr">
         <is>
-          <t>Dövizi Natık Çek Ödemeyi Durdurma İşlemi</t>
+          <t>Çek Karnesi Komisyonu- 100'lük Sürekli Form</t>
         </is>
       </c>
       <c r="B2070" s="12" t="inlineStr"/>
@@ -36537,8 +36536,8 @@
       <c r="G2070" s="12" t="inlineStr"/>
       <c r="H2070" s="12" t="inlineStr">
         <is>
-          <t>260 TL / -
-maks: 260 TL / -</t>
+          <t>8.666,67 TL / -
+maks: 8.666,67 TL / -</t>
         </is>
       </c>
       <c r="I2070" s="12" t="inlineStr"/>
@@ -36546,7 +36545,7 @@
     <row r="2071" ht="32" customHeight="1">
       <c r="A2071" s="11" t="inlineStr">
         <is>
-          <t>Dövizi Natık Çek Düzenleme</t>
+          <t>Dövizi Natık Çek Ödemeyi Durdurma İşlemi</t>
         </is>
       </c>
       <c r="B2071" s="12" t="inlineStr"/>
@@ -36557,8 +36556,8 @@
       <c r="G2071" s="12" t="inlineStr"/>
       <c r="H2071" s="12" t="inlineStr">
         <is>
-          <t>359,05 TL / -
-maks: 359,05 TL / -</t>
+          <t>260 TL / -
+maks: 260 TL / -</t>
         </is>
       </c>
       <c r="I2071" s="12" t="inlineStr"/>
@@ -36566,7 +36565,7 @@
     <row r="2072" ht="32" customHeight="1">
       <c r="A2072" s="11" t="inlineStr">
         <is>
-          <t>Armağan çeki Düzenleme</t>
+          <t>Dövizi Natık Çek Düzenleme</t>
         </is>
       </c>
       <c r="B2072" s="12" t="inlineStr"/>
@@ -36577,43 +36576,43 @@
       <c r="G2072" s="12" t="inlineStr"/>
       <c r="H2072" s="12" t="inlineStr">
         <is>
+          <t>359,05 TL / -
+maks: 359,05 TL / -</t>
+        </is>
+      </c>
+      <c r="I2072" s="12" t="inlineStr"/>
+    </row>
+    <row r="2073" ht="32" customHeight="1">
+      <c r="A2073" s="11" t="inlineStr">
+        <is>
+          <t>Armağan çeki Düzenleme</t>
+        </is>
+      </c>
+      <c r="B2073" s="12" t="inlineStr"/>
+      <c r="C2073" s="12" t="inlineStr"/>
+      <c r="D2073" s="12" t="inlineStr"/>
+      <c r="E2073" s="12" t="inlineStr"/>
+      <c r="F2073" s="12" t="inlineStr"/>
+      <c r="G2073" s="12" t="inlineStr"/>
+      <c r="H2073" s="12" t="inlineStr">
+        <is>
           <t>104,76 TL / -
 maks: 104,76 TL / -</t>
         </is>
       </c>
-      <c r="I2072" s="12" t="inlineStr"/>
-    </row>
-    <row r="2073" ht="16" customHeight="1">
-      <c r="A2073" s="10" t="inlineStr">
+      <c r="I2073" s="12" t="inlineStr"/>
+    </row>
+    <row r="2074" ht="16" customHeight="1">
+      <c r="A2074" s="10" t="inlineStr">
         <is>
           <t>Global Fast Para Aktarma İşlemleri</t>
         </is>
       </c>
-    </row>
-    <row r="2074" ht="32" customHeight="1">
-      <c r="A2074" s="11" t="inlineStr">
-        <is>
-          <t>Global Fast - Karta Para Gönderim İşlemleri</t>
-        </is>
-      </c>
-      <c r="B2074" s="12" t="inlineStr"/>
-      <c r="C2074" s="12" t="inlineStr"/>
-      <c r="D2074" s="12" t="inlineStr"/>
-      <c r="E2074" s="12" t="inlineStr"/>
-      <c r="F2074" s="12" t="inlineStr"/>
-      <c r="G2074" s="12" t="inlineStr"/>
-      <c r="H2074" s="12" t="inlineStr">
-        <is>
-          <t>15 TL / 4
-maks: 2.000 TL / 8</t>
-        </is>
-      </c>
-      <c r="I2074" s="12" t="inlineStr"/>
     </row>
     <row r="2075" ht="32" customHeight="1">
       <c r="A2075" s="11" t="inlineStr">
         <is>
-          <t>Global Fast - Hesaba Para Gönderim İşlemleri</t>
+          <t>Global Fast - Karta Para Gönderim İşlemleri</t>
         </is>
       </c>
       <c r="B2075" s="12" t="inlineStr"/>
@@ -36624,48 +36623,43 @@
       <c r="G2075" s="12" t="inlineStr"/>
       <c r="H2075" s="12" t="inlineStr">
         <is>
+          <t>15 TL / 4
+maks: 2.000 TL / 8</t>
+        </is>
+      </c>
+      <c r="I2075" s="12" t="inlineStr"/>
+    </row>
+    <row r="2076" ht="32" customHeight="1">
+      <c r="A2076" s="11" t="inlineStr">
+        <is>
+          <t>Global Fast - Hesaba Para Gönderim İşlemleri</t>
+        </is>
+      </c>
+      <c r="B2076" s="12" t="inlineStr"/>
+      <c r="C2076" s="12" t="inlineStr"/>
+      <c r="D2076" s="12" t="inlineStr"/>
+      <c r="E2076" s="12" t="inlineStr"/>
+      <c r="F2076" s="12" t="inlineStr"/>
+      <c r="G2076" s="12" t="inlineStr"/>
+      <c r="H2076" s="12" t="inlineStr">
+        <is>
           <t>200 TL / 0,4
 maks: 1.200 TL / 0,4</t>
         </is>
       </c>
-      <c r="I2075" s="12" t="inlineStr"/>
-    </row>
-    <row r="2076" ht="16" customHeight="1">
-      <c r="A2076" s="10" t="inlineStr">
+      <c r="I2076" s="12" t="inlineStr"/>
+    </row>
+    <row r="2077" ht="16" customHeight="1">
+      <c r="A2077" s="10" t="inlineStr">
         <is>
           <t>Western Union Para Gönderme İşlemleri</t>
-        </is>
-      </c>
-    </row>
-    <row r="2077" ht="32" customHeight="1">
-      <c r="A2077" s="11" t="inlineStr">
-        <is>
-          <t>EUR Gönderimlerde</t>
-        </is>
-      </c>
-      <c r="B2077" s="12" t="inlineStr"/>
-      <c r="C2077" s="12" t="inlineStr"/>
-      <c r="D2077" s="12" t="inlineStr"/>
-      <c r="E2077" s="12" t="inlineStr"/>
-      <c r="F2077" s="12" t="inlineStr"/>
-      <c r="G2077" s="12" t="inlineStr"/>
-      <c r="H2077" s="12" t="inlineStr">
-        <is>
-          <t>4 EUR / -
-maks: 240 EUR / -</t>
-        </is>
-      </c>
-      <c r="I2077" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 1,5 EUR / -</t>
         </is>
       </c>
     </row>
     <row r="2078" ht="32" customHeight="1">
       <c r="A2078" s="11" t="inlineStr">
         <is>
-          <t>USD Gönderimlerde</t>
+          <t>EUR Gönderimlerde</t>
         </is>
       </c>
       <c r="B2078" s="12" t="inlineStr"/>
@@ -36676,21 +36670,21 @@
       <c r="G2078" s="12" t="inlineStr"/>
       <c r="H2078" s="12" t="inlineStr">
         <is>
-          <t>3 USD / -
-maks: 337,5 USD / -</t>
+          <t>4 EUR / -
+maks: 240 EUR / -</t>
         </is>
       </c>
       <c r="I2078" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 2 USD / -</t>
+maks: 1,5 EUR / -</t>
         </is>
       </c>
     </row>
     <row r="2079" ht="32" customHeight="1">
       <c r="A2079" s="11" t="inlineStr">
         <is>
-          <t>TL Gönderimlerde</t>
+          <t>USD Gönderimlerde</t>
         </is>
       </c>
       <c r="B2079" s="12" t="inlineStr"/>
@@ -36701,48 +36695,53 @@
       <c r="G2079" s="12" t="inlineStr"/>
       <c r="H2079" s="12" t="inlineStr">
         <is>
+          <t>3 USD / -
+maks: 337,5 USD / -</t>
+        </is>
+      </c>
+      <c r="I2079" s="12" t="inlineStr">
+        <is>
+          <t>- / -
+maks: 2 USD / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080" ht="32" customHeight="1">
+      <c r="A2080" s="11" t="inlineStr">
+        <is>
+          <t>TL Gönderimlerde</t>
+        </is>
+      </c>
+      <c r="B2080" s="12" t="inlineStr"/>
+      <c r="C2080" s="12" t="inlineStr"/>
+      <c r="D2080" s="12" t="inlineStr"/>
+      <c r="E2080" s="12" t="inlineStr"/>
+      <c r="F2080" s="12" t="inlineStr"/>
+      <c r="G2080" s="12" t="inlineStr"/>
+      <c r="H2080" s="12" t="inlineStr">
+        <is>
           <t>15 TL / -
 maks: 6.000 TL / -</t>
         </is>
       </c>
-      <c r="I2079" s="12" t="inlineStr">
+      <c r="I2080" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: 3,5 TL / -</t>
         </is>
       </c>
     </row>
-    <row r="2080" ht="16" customHeight="1">
-      <c r="A2080" s="10" t="inlineStr">
+    <row r="2081" ht="16" customHeight="1">
+      <c r="A2081" s="10" t="inlineStr">
         <is>
           <t>Findeks Paket Ücretleri</t>
         </is>
       </c>
-    </row>
-    <row r="2081" ht="32" customHeight="1">
-      <c r="A2081" s="11" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B2081" s="12" t="inlineStr"/>
-      <c r="C2081" s="12" t="inlineStr"/>
-      <c r="D2081" s="12" t="inlineStr"/>
-      <c r="E2081" s="12" t="inlineStr"/>
-      <c r="F2081" s="12" t="inlineStr"/>
-      <c r="G2081" s="12" t="inlineStr"/>
-      <c r="H2081" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 1.200 TL / -</t>
-        </is>
-      </c>
-      <c r="I2081" s="12" t="inlineStr"/>
     </row>
     <row r="2082" ht="32" customHeight="1">
       <c r="A2082" s="11" t="inlineStr">
         <is>
-          <t>Ticari Karma Paket</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="B2082" s="12" t="inlineStr"/>
@@ -36754,7 +36753,7 @@
       <c r="H2082" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 3.900 TL / -</t>
+maks: 1.200 TL / -</t>
         </is>
       </c>
       <c r="I2082" s="12" t="inlineStr"/>
@@ -36762,7 +36761,7 @@
     <row r="2083" ht="32" customHeight="1">
       <c r="A2083" s="11" t="inlineStr">
         <is>
-          <t>Yılda 50 Rapor</t>
+          <t>Ticari Karma Paket</t>
         </is>
       </c>
       <c r="B2083" s="12" t="inlineStr"/>
@@ -36774,7 +36773,7 @@
       <c r="H2083" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.740 TL / -</t>
+maks: 3.900 TL / -</t>
         </is>
       </c>
       <c r="I2083" s="12" t="inlineStr"/>
@@ -36782,7 +36781,7 @@
     <row r="2084" ht="32" customHeight="1">
       <c r="A2084" s="11" t="inlineStr">
         <is>
-          <t>Yılda 100 Rapor</t>
+          <t>Yılda 50 Rapor</t>
         </is>
       </c>
       <c r="B2084" s="12" t="inlineStr"/>
@@ -36794,7 +36793,7 @@
       <c r="H2084" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 3.000 TL / -</t>
+maks: 1.740 TL / -</t>
         </is>
       </c>
       <c r="I2084" s="12" t="inlineStr"/>
@@ -36802,7 +36801,7 @@
     <row r="2085" ht="32" customHeight="1">
       <c r="A2085" s="11" t="inlineStr">
         <is>
-          <t>Yılda 500 Rapor</t>
+          <t>Yılda 100 Rapor</t>
         </is>
       </c>
       <c r="B2085" s="12" t="inlineStr"/>
@@ -36814,7 +36813,7 @@
       <c r="H2085" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 13.200 TL / -</t>
+maks: 3.000 TL / -</t>
         </is>
       </c>
       <c r="I2085" s="12" t="inlineStr"/>
@@ -36822,7 +36821,7 @@
     <row r="2086" ht="32" customHeight="1">
       <c r="A2086" s="11" t="inlineStr">
         <is>
-          <t>Yılda 1.000 Rapor</t>
+          <t>Yılda 500 Rapor</t>
         </is>
       </c>
       <c r="B2086" s="12" t="inlineStr"/>
@@ -36834,7 +36833,7 @@
       <c r="H2086" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 25.200 TL / -</t>
+maks: 13.200 TL / -</t>
         </is>
       </c>
       <c r="I2086" s="12" t="inlineStr"/>
@@ -36842,7 +36841,7 @@
     <row r="2087" ht="32" customHeight="1">
       <c r="A2087" s="11" t="inlineStr">
         <is>
-          <t>Yılda 5.000 Rapor</t>
+          <t>Yılda 1.000 Rapor</t>
         </is>
       </c>
       <c r="B2087" s="12" t="inlineStr"/>
@@ -36854,7 +36853,7 @@
       <c r="H2087" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 114.000 TL / -</t>
+maks: 25.200 TL / -</t>
         </is>
       </c>
       <c r="I2087" s="12" t="inlineStr"/>
@@ -36862,7 +36861,7 @@
     <row r="2088" ht="32" customHeight="1">
       <c r="A2088" s="11" t="inlineStr">
         <is>
-          <t>Yılda 10.000 Rapor</t>
+          <t>Yılda 5.000 Rapor</t>
         </is>
       </c>
       <c r="B2088" s="12" t="inlineStr"/>
@@ -36874,7 +36873,7 @@
       <c r="H2088" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 198.000 TL / -</t>
+maks: 114.000 TL / -</t>
         </is>
       </c>
       <c r="I2088" s="12" t="inlineStr"/>
@@ -36882,7 +36881,7 @@
     <row r="2089" ht="32" customHeight="1">
       <c r="A2089" s="11" t="inlineStr">
         <is>
-          <t>Yılda 50.000 Rapor</t>
+          <t>Yılda 10.000 Rapor</t>
         </is>
       </c>
       <c r="B2089" s="12" t="inlineStr"/>
@@ -36894,7 +36893,7 @@
       <c r="H2089" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 930.000 TL / -</t>
+maks: 198.000 TL / -</t>
         </is>
       </c>
       <c r="I2089" s="12" t="inlineStr"/>
@@ -36902,7 +36901,7 @@
     <row r="2090" ht="32" customHeight="1">
       <c r="A2090" s="11" t="inlineStr">
         <is>
-          <t>Yılda 100.000 Rapor</t>
+          <t>Yılda 50.000 Rapor</t>
         </is>
       </c>
       <c r="B2090" s="12" t="inlineStr"/>
@@ -36914,7 +36913,7 @@
       <c r="H2090" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.860.000 TL / -</t>
+maks: 930.000 TL / -</t>
         </is>
       </c>
       <c r="I2090" s="12" t="inlineStr"/>
@@ -36922,7 +36921,7 @@
     <row r="2091" ht="32" customHeight="1">
       <c r="A2091" s="11" t="inlineStr">
         <is>
-          <t>Yılda 50 Çek Raporu</t>
+          <t>Yılda 100.000 Rapor</t>
         </is>
       </c>
       <c r="B2091" s="12" t="inlineStr"/>
@@ -36934,7 +36933,7 @@
       <c r="H2091" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.500 TL / -</t>
+maks: 1.860.000 TL / -</t>
         </is>
       </c>
       <c r="I2091" s="12" t="inlineStr"/>
@@ -36942,7 +36941,7 @@
     <row r="2092" ht="32" customHeight="1">
       <c r="A2092" s="11" t="inlineStr">
         <is>
-          <t>Yılda 250 Çek Raporu</t>
+          <t>Yılda 50 Çek Raporu</t>
         </is>
       </c>
       <c r="B2092" s="12" t="inlineStr"/>
@@ -36954,7 +36953,7 @@
       <c r="H2092" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 4.200 TL / -</t>
+maks: 1.500 TL / -</t>
         </is>
       </c>
       <c r="I2092" s="12" t="inlineStr"/>
@@ -36962,7 +36961,7 @@
     <row r="2093" ht="32" customHeight="1">
       <c r="A2093" s="11" t="inlineStr">
         <is>
-          <t>Yılda 100 Karekodlu Çek Raporu</t>
+          <t>Yılda 250 Çek Raporu</t>
         </is>
       </c>
       <c r="B2093" s="12" t="inlineStr"/>
@@ -36974,7 +36973,7 @@
       <c r="H2093" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 600 TL / -</t>
+maks: 4.200 TL / -</t>
         </is>
       </c>
       <c r="I2093" s="12" t="inlineStr"/>
@@ -36982,7 +36981,7 @@
     <row r="2094" ht="32" customHeight="1">
       <c r="A2094" s="11" t="inlineStr">
         <is>
-          <t>Yılda 250 Karekodlu Çek Raporu</t>
+          <t>Yılda 100 Karekodlu Çek Raporu</t>
         </is>
       </c>
       <c r="B2094" s="12" t="inlineStr"/>
@@ -36994,7 +36993,7 @@
       <c r="H2094" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.500 TL / -</t>
+maks: 600 TL / -</t>
         </is>
       </c>
       <c r="I2094" s="12" t="inlineStr"/>
@@ -37002,7 +37001,7 @@
     <row r="2095" ht="32" customHeight="1">
       <c r="A2095" s="11" t="inlineStr">
         <is>
-          <t>Yılda 1.000 Karekodlu Çek Raporu</t>
+          <t>Yılda 250 Karekodlu Çek Raporu</t>
         </is>
       </c>
       <c r="B2095" s="12" t="inlineStr"/>
@@ -37014,7 +37013,7 @@
       <c r="H2095" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 6.000 TL / -</t>
+maks: 1.500 TL / -</t>
         </is>
       </c>
       <c r="I2095" s="12" t="inlineStr"/>
@@ -37022,7 +37021,7 @@
     <row r="2096" ht="32" customHeight="1">
       <c r="A2096" s="11" t="inlineStr">
         <is>
-          <t>Yılda 100 Teminat Mektubu Durum Sorgulama</t>
+          <t>Yılda 1.000 Karekodlu Çek Raporu</t>
         </is>
       </c>
       <c r="B2096" s="12" t="inlineStr"/>
@@ -37034,7 +37033,7 @@
       <c r="H2096" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 1.770 TL / -</t>
+maks: 6.000 TL / -</t>
         </is>
       </c>
       <c r="I2096" s="12" t="inlineStr"/>
@@ -37042,7 +37041,7 @@
     <row r="2097" ht="32" customHeight="1">
       <c r="A2097" s="11" t="inlineStr">
         <is>
-          <t>Yılda 500 Teminat Mektubu Durum Sorgulama</t>
+          <t>Yılda 100 Teminat Mektubu Durum Sorgulama</t>
         </is>
       </c>
       <c r="B2097" s="12" t="inlineStr"/>
@@ -37054,7 +37053,7 @@
       <c r="H2097" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 7.218 TL / -</t>
+maks: 1.770 TL / -</t>
         </is>
       </c>
       <c r="I2097" s="12" t="inlineStr"/>
@@ -37062,7 +37061,7 @@
     <row r="2098" ht="32" customHeight="1">
       <c r="A2098" s="11" t="inlineStr">
         <is>
-          <t>Yılda 1.000 Teminat Mektubu Durum Sorgulama</t>
+          <t>Yılda 500 Teminat Mektubu Durum Sorgulama</t>
         </is>
       </c>
       <c r="B2098" s="12" t="inlineStr"/>
@@ -37074,7 +37073,7 @@
       <c r="H2098" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 10.752 TL / -</t>
+maks: 7.218 TL / -</t>
         </is>
       </c>
       <c r="I2098" s="12" t="inlineStr"/>
@@ -37082,7 +37081,7 @@
     <row r="2099" ht="32" customHeight="1">
       <c r="A2099" s="11" t="inlineStr">
         <is>
-          <t>Kur Dönüşüm Hizmeti Ücreti POS</t>
+          <t>Yılda 1.000 Teminat Mektubu Durum Sorgulama</t>
         </is>
       </c>
       <c r="B2099" s="12" t="inlineStr"/>
@@ -37094,7 +37093,7 @@
       <c r="H2099" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 4</t>
+maks: 10.752 TL / -</t>
         </is>
       </c>
       <c r="I2099" s="12" t="inlineStr"/>
@@ -37102,7 +37101,7 @@
     <row r="2100" ht="32" customHeight="1">
       <c r="A2100" s="11" t="inlineStr">
         <is>
-          <t>HGS Kartı Satış Bedeli</t>
+          <t>Kur Dönüşüm Hizmeti Ücreti POS</t>
         </is>
       </c>
       <c r="B2100" s="12" t="inlineStr"/>
@@ -37113,8 +37112,8 @@
       <c r="G2100" s="12" t="inlineStr"/>
       <c r="H2100" s="12" t="inlineStr">
         <is>
-          <t>550 TL / -
-maks: 550 TL / -</t>
+          <t>- / -
+maks: - / 4</t>
         </is>
       </c>
       <c r="I2100" s="12" t="inlineStr"/>
@@ -37122,7 +37121,7 @@
     <row r="2101" ht="32" customHeight="1">
       <c r="A2101" s="11" t="inlineStr">
         <is>
-          <t>HGS Etiketi Satış Bedeli</t>
+          <t>HGS Kartı Satış Bedeli</t>
         </is>
       </c>
       <c r="B2101" s="12" t="inlineStr"/>
@@ -37133,8 +37132,8 @@
       <c r="G2101" s="12" t="inlineStr"/>
       <c r="H2101" s="12" t="inlineStr">
         <is>
-          <t>275 TL / -
-maks: 275 TL / -</t>
+          <t>550 TL / -
+maks: 550 TL / -</t>
         </is>
       </c>
       <c r="I2101" s="12" t="inlineStr"/>
@@ -37142,7 +37141,7 @@
     <row r="2102" ht="32" customHeight="1">
       <c r="A2102" s="11" t="inlineStr">
         <is>
-          <t>Yurtdışı Araştırma (Swift'le)</t>
+          <t>HGS Etiketi Satış Bedeli</t>
         </is>
       </c>
       <c r="B2102" s="12" t="inlineStr"/>
@@ -37153,8 +37152,8 @@
       <c r="G2102" s="12" t="inlineStr"/>
       <c r="H2102" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: 30 USD / -</t>
+          <t>275 TL / -
+maks: 275 TL / -</t>
         </is>
       </c>
       <c r="I2102" s="12" t="inlineStr"/>
@@ -37162,7 +37161,7 @@
     <row r="2103" ht="32" customHeight="1">
       <c r="A2103" s="11" t="inlineStr">
         <is>
-          <t>Yurtdışı Araştırma (Telefonla)</t>
+          <t>Yurtdışı Araştırma (Swift'le)</t>
         </is>
       </c>
       <c r="B2103" s="12" t="inlineStr"/>
@@ -37174,7 +37173,7 @@
       <c r="H2103" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 50 USD / -</t>
+maks: 30 USD / -</t>
         </is>
       </c>
       <c r="I2103" s="12" t="inlineStr"/>
@@ -37182,7 +37181,7 @@
     <row r="2104" ht="32" customHeight="1">
       <c r="A2104" s="11" t="inlineStr">
         <is>
-          <t>Vergi Numarası Alma ( Yabancı müşteriler için)</t>
+          <t>Yurtdışı Araştırma (Telefonla)</t>
         </is>
       </c>
       <c r="B2104" s="12" t="inlineStr"/>
@@ -37193,8 +37192,8 @@
       <c r="G2104" s="12" t="inlineStr"/>
       <c r="H2104" s="12" t="inlineStr">
         <is>
-          <t>50 TL / -
-maks: 500 TL / -</t>
+          <t>- / -
+maks: 50 USD / -</t>
         </is>
       </c>
       <c r="I2104" s="12" t="inlineStr"/>
@@ -37202,7 +37201,7 @@
     <row r="2105" ht="32" customHeight="1">
       <c r="A2105" s="11" t="inlineStr">
         <is>
-          <t>İstihbarat Bilgisi Düzeltme (Düzeltme hakkını kullanan müşteriler)</t>
+          <t>Vergi Numarası Alma ( Yabancı müşteriler için)</t>
         </is>
       </c>
       <c r="B2105" s="12" t="inlineStr"/>
@@ -37213,8 +37212,8 @@
       <c r="G2105" s="12" t="inlineStr"/>
       <c r="H2105" s="12" t="inlineStr">
         <is>
-          <t>- / -
-maks: 10 TL / -</t>
+          <t>50 TL / -
+maks: 500 TL / -</t>
         </is>
       </c>
       <c r="I2105" s="12" t="inlineStr"/>
@@ -37222,7 +37221,7 @@
     <row r="2106" ht="32" customHeight="1">
       <c r="A2106" s="11" t="inlineStr">
         <is>
-          <t>Konsolosluk İçin Mektup Düzenleme</t>
+          <t>İstihbarat Bilgisi Düzeltme (Düzeltme hakkını kullanan müşteriler)</t>
         </is>
       </c>
       <c r="B2106" s="12" t="inlineStr"/>
@@ -37234,7 +37233,7 @@
       <c r="H2106" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: 50 TL / -</t>
+maks: 10 TL / -</t>
         </is>
       </c>
       <c r="I2106" s="12" t="inlineStr"/>
@@ -37242,7 +37241,7 @@
     <row r="2107" ht="32" customHeight="1">
       <c r="A2107" s="11" t="inlineStr">
         <is>
-          <t>Geniş Kapsamlı Hizmet Paketi Ücreti</t>
+          <t>Konsolosluk İçin Mektup Düzenleme</t>
         </is>
       </c>
       <c r="B2107" s="12" t="inlineStr"/>
@@ -37253,43 +37252,43 @@
       <c r="G2107" s="12" t="inlineStr"/>
       <c r="H2107" s="12" t="inlineStr">
         <is>
+          <t>- / -
+maks: 50 TL / -</t>
+        </is>
+      </c>
+      <c r="I2107" s="12" t="inlineStr"/>
+    </row>
+    <row r="2108" ht="32" customHeight="1">
+      <c r="A2108" s="11" t="inlineStr">
+        <is>
+          <t>Geniş Kapsamlı Hizmet Paketi Ücreti</t>
+        </is>
+      </c>
+      <c r="B2108" s="12" t="inlineStr"/>
+      <c r="C2108" s="12" t="inlineStr"/>
+      <c r="D2108" s="12" t="inlineStr"/>
+      <c r="E2108" s="12" t="inlineStr"/>
+      <c r="F2108" s="12" t="inlineStr"/>
+      <c r="G2108" s="12" t="inlineStr"/>
+      <c r="H2108" s="12" t="inlineStr">
+        <is>
           <t>339 TL / -
 maks: 339 TL / -</t>
         </is>
       </c>
-      <c r="I2107" s="12" t="inlineStr"/>
-    </row>
-    <row r="2108" ht="16" customHeight="1">
-      <c r="A2108" s="10" t="inlineStr">
+      <c r="I2108" s="12" t="inlineStr"/>
+    </row>
+    <row r="2109" ht="16" customHeight="1">
+      <c r="A2109" s="10" t="inlineStr">
         <is>
           <t>Kurum Tahsilatları</t>
         </is>
       </c>
-    </row>
-    <row r="2109" ht="32" customHeight="1">
-      <c r="A2109" s="11" t="inlineStr">
-        <is>
-          <t>Fatura ve Anlaşmalı Kurum Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B2109" s="12" t="inlineStr"/>
-      <c r="C2109" s="12" t="inlineStr"/>
-      <c r="D2109" s="12" t="inlineStr"/>
-      <c r="E2109" s="12" t="inlineStr"/>
-      <c r="F2109" s="12" t="inlineStr"/>
-      <c r="G2109" s="12" t="inlineStr"/>
-      <c r="H2109" s="12" t="inlineStr">
-        <is>
-          <t>0,63 TL / -
-maks: 45 TL / -</t>
-        </is>
-      </c>
-      <c r="I2109" s="12" t="inlineStr"/>
     </row>
     <row r="2110" ht="32" customHeight="1">
       <c r="A2110" s="11" t="inlineStr">
         <is>
-          <t>Konsolosluk Vize Randevu Bedeli Tahsilat Komisyonu</t>
+          <t>Fatura ve Anlaşmalı Kurum Ödemeleri</t>
         </is>
       </c>
       <c r="B2110" s="12" t="inlineStr"/>
@@ -37300,43 +37299,43 @@
       <c r="G2110" s="12" t="inlineStr"/>
       <c r="H2110" s="12" t="inlineStr">
         <is>
+          <t>0,63 TL / -
+maks: 45 TL / -</t>
+        </is>
+      </c>
+      <c r="I2110" s="12" t="inlineStr"/>
+    </row>
+    <row r="2111" ht="32" customHeight="1">
+      <c r="A2111" s="11" t="inlineStr">
+        <is>
+          <t>Konsolosluk Vize Randevu Bedeli Tahsilat Komisyonu</t>
+        </is>
+      </c>
+      <c r="B2111" s="12" t="inlineStr"/>
+      <c r="C2111" s="12" t="inlineStr"/>
+      <c r="D2111" s="12" t="inlineStr"/>
+      <c r="E2111" s="12" t="inlineStr"/>
+      <c r="F2111" s="12" t="inlineStr"/>
+      <c r="G2111" s="12" t="inlineStr"/>
+      <c r="H2111" s="12" t="inlineStr">
+        <is>
           <t>200 TL / -
 maks: 1.000 TL / -</t>
         </is>
       </c>
-      <c r="I2110" s="12" t="inlineStr"/>
-    </row>
-    <row r="2111" ht="16" customHeight="1">
-      <c r="A2111" s="10" t="inlineStr">
+      <c r="I2111" s="12" t="inlineStr"/>
+    </row>
+    <row r="2112" ht="16" customHeight="1">
+      <c r="A2112" s="10" t="inlineStr">
         <is>
           <t>Mutabakat / Teyit yazıları</t>
         </is>
       </c>
-    </row>
-    <row r="2112" ht="32" customHeight="1">
-      <c r="A2112" s="11" t="inlineStr">
-        <is>
-          <t>Denetim Firmalarına Verilen Mutabakatlar</t>
-        </is>
-      </c>
-      <c r="B2112" s="12" t="inlineStr"/>
-      <c r="C2112" s="12" t="inlineStr"/>
-      <c r="D2112" s="12" t="inlineStr"/>
-      <c r="E2112" s="12" t="inlineStr"/>
-      <c r="F2112" s="12" t="inlineStr"/>
-      <c r="G2112" s="12" t="inlineStr"/>
-      <c r="H2112" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: 150 TL / -</t>
-        </is>
-      </c>
-      <c r="I2112" s="12" t="inlineStr"/>
     </row>
     <row r="2113" ht="32" customHeight="1">
       <c r="A2113" s="11" t="inlineStr">
         <is>
-          <t>Müşterilere Verilen Vergi Yazısı(Vergi/Stopaj)</t>
+          <t>Denetim Firmalarına Verilen Mutabakatlar</t>
         </is>
       </c>
       <c r="B2113" s="12" t="inlineStr"/>
@@ -37348,42 +37347,42 @@
       <c r="H2113" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: 150 TL / -</t>
+        </is>
+      </c>
+      <c r="I2113" s="12" t="inlineStr"/>
+    </row>
+    <row r="2114" ht="32" customHeight="1">
+      <c r="A2114" s="11" t="inlineStr">
+        <is>
+          <t>Müşterilere Verilen Vergi Yazısı(Vergi/Stopaj)</t>
+        </is>
+      </c>
+      <c r="B2114" s="12" t="inlineStr"/>
+      <c r="C2114" s="12" t="inlineStr"/>
+      <c r="D2114" s="12" t="inlineStr"/>
+      <c r="E2114" s="12" t="inlineStr"/>
+      <c r="F2114" s="12" t="inlineStr"/>
+      <c r="G2114" s="12" t="inlineStr"/>
+      <c r="H2114" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: 100 TL / -</t>
         </is>
       </c>
-      <c r="I2113" s="12" t="inlineStr"/>
-    </row>
-    <row r="2114" ht="16" customHeight="1">
-      <c r="A2114" s="10" t="inlineStr">
+      <c r="I2114" s="12" t="inlineStr"/>
+    </row>
+    <row r="2115" ht="16" customHeight="1">
+      <c r="A2115" s="10" t="inlineStr">
         <is>
           <t>Taksitli Ticari Kredi</t>
         </is>
       </c>
-    </row>
-    <row r="2115" ht="32" customHeight="1">
-      <c r="A2115" s="11" t="inlineStr">
-        <is>
-          <t>Nakdi Kredi Erken Kapama (Değişken Faizli Döviz Cinsi veya Dövize Endeksli Krediler)</t>
-        </is>
-      </c>
-      <c r="B2115" s="12" t="inlineStr"/>
-      <c r="C2115" s="12" t="inlineStr"/>
-      <c r="D2115" s="12" t="inlineStr"/>
-      <c r="E2115" s="12" t="inlineStr"/>
-      <c r="F2115" s="12" t="inlineStr"/>
-      <c r="G2115" s="12" t="inlineStr"/>
-      <c r="H2115" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / 2</t>
-        </is>
-      </c>
-      <c r="I2115" s="12" t="inlineStr"/>
     </row>
     <row r="2116" ht="32" customHeight="1">
       <c r="A2116" s="11" t="inlineStr">
         <is>
-          <t>Nakdi Kredi Erken Kapama (Değişken Faizli Türk Lirası Krediler)</t>
+          <t>Nakdi Kredi Erken Kapama (Değişken Faizli Döviz Cinsi veya Dövize Endeksli Krediler)</t>
         </is>
       </c>
       <c r="B2116" s="12" t="inlineStr"/>
@@ -37403,7 +37402,7 @@
     <row r="2117" ht="32" customHeight="1">
       <c r="A2117" s="11" t="inlineStr">
         <is>
-          <t>1 Temmuz 2024 - 5 Ocak 2025 Arasında Kullanılan Krediler</t>
+          <t>Nakdi Kredi Erken Kapama (Değişken Faizli Türk Lirası Krediler)</t>
         </is>
       </c>
       <c r="B2117" s="12" t="inlineStr"/>
@@ -37415,7 +37414,7 @@
       <c r="H2117" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / -</t>
+maks: - / 2</t>
         </is>
       </c>
       <c r="I2117" s="12" t="inlineStr"/>
@@ -37423,7 +37422,7 @@
     <row r="2118" ht="32" customHeight="1">
       <c r="A2118" s="11" t="inlineStr">
         <is>
-          <t>6 Ocak 2025 Sonrası Kullanılan Krediler</t>
+          <t>1 Temmuz 2024 - 5 Ocak 2025 Arasında Kullanılan Krediler</t>
         </is>
       </c>
       <c r="B2118" s="12" t="inlineStr"/>
@@ -37443,7 +37442,7 @@
     <row r="2119" ht="32" customHeight="1">
       <c r="A2119" s="11" t="inlineStr">
         <is>
-          <t>Nakdi Kredi Erken Kapama (Sabit Faizli Türk Lirası Krediler)(1.7.2024 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
+          <t>6 Ocak 2025 Sonrası Kullanılan Krediler</t>
         </is>
       </c>
       <c r="B2119" s="12" t="inlineStr"/>
@@ -37463,7 +37462,7 @@
     <row r="2120" ht="32" customHeight="1">
       <c r="A2120" s="11" t="inlineStr">
         <is>
-          <t>Nakdi Kredi Ara/Kısmi Ödeme</t>
+          <t>Nakdi Kredi Erken Kapama (Sabit Faizli Türk Lirası Krediler)(1.7.2024 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
       <c r="B2120" s="12" t="inlineStr"/>
@@ -37475,7 +37474,7 @@
       <c r="H2120" s="12" t="inlineStr">
         <is>
           <t>- / -
-maks: - / 5</t>
+maks: - / -</t>
         </is>
       </c>
       <c r="I2120" s="12" t="inlineStr"/>
@@ -37483,7 +37482,7 @@
     <row r="2121" ht="32" customHeight="1">
       <c r="A2121" s="11" t="inlineStr">
         <is>
-          <t>Faiz Oranı(1-36 ay)</t>
+          <t>Nakdi Kredi Ara/Kısmi Ödeme</t>
         </is>
       </c>
       <c r="B2121" s="12" t="inlineStr"/>
@@ -37494,77 +37493,77 @@
       <c r="G2121" s="12" t="inlineStr"/>
       <c r="H2121" s="12" t="inlineStr">
         <is>
+          <t>- / -
+maks: - / 5</t>
+        </is>
+      </c>
+      <c r="I2121" s="12" t="inlineStr"/>
+    </row>
+    <row r="2122" ht="32" customHeight="1">
+      <c r="A2122" s="11" t="inlineStr">
+        <is>
+          <t>Faiz Oranı(1-36 ay)</t>
+        </is>
+      </c>
+      <c r="B2122" s="12" t="inlineStr"/>
+      <c r="C2122" s="12" t="inlineStr"/>
+      <c r="D2122" s="12" t="inlineStr"/>
+      <c r="E2122" s="12" t="inlineStr"/>
+      <c r="F2122" s="12" t="inlineStr"/>
+      <c r="G2122" s="12" t="inlineStr"/>
+      <c r="H2122" s="12" t="inlineStr">
+        <is>
           <t>- / 4,55
 maks: - / 4,55</t>
         </is>
       </c>
-      <c r="I2121" s="12" t="inlineStr"/>
-    </row>
-    <row r="2122" ht="16" customHeight="1">
-      <c r="A2122" s="10" t="inlineStr">
+      <c r="I2122" s="12" t="inlineStr"/>
+    </row>
+    <row r="2123" ht="16" customHeight="1">
+      <c r="A2123" s="10" t="inlineStr">
         <is>
           <t>Esnek Ticari Hesap</t>
         </is>
       </c>
     </row>
-    <row r="2123" ht="32" customHeight="1">
-      <c r="A2123" s="11" t="inlineStr">
+    <row r="2124" ht="32" customHeight="1">
+      <c r="A2124" s="11" t="inlineStr">
         <is>
           <t>Basılı Ticari KMH Hesap Özeti (Esnek Ticari Hesap Özeti Ücreti)</t>
         </is>
       </c>
-      <c r="B2123" s="12" t="inlineStr"/>
-      <c r="C2123" s="12" t="inlineStr"/>
-      <c r="D2123" s="12" t="inlineStr"/>
-      <c r="E2123" s="12" t="inlineStr"/>
-      <c r="F2123" s="12" t="inlineStr"/>
-      <c r="G2123" s="12" t="inlineStr"/>
-      <c r="H2123" s="12" t="inlineStr">
+      <c r="B2124" s="12" t="inlineStr"/>
+      <c r="C2124" s="12" t="inlineStr"/>
+      <c r="D2124" s="12" t="inlineStr"/>
+      <c r="E2124" s="12" t="inlineStr"/>
+      <c r="F2124" s="12" t="inlineStr"/>
+      <c r="G2124" s="12" t="inlineStr"/>
+      <c r="H2124" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: 45 TL / -</t>
         </is>
       </c>
-      <c r="I2123" s="12" t="inlineStr"/>
-    </row>
-    <row r="2124" ht="16" customHeight="1">
-      <c r="A2124" s="10" t="inlineStr">
-        <is>
-          <t>Borçlu Cari Hesap</t>
-        </is>
-      </c>
+      <c r="I2124" s="12" t="inlineStr"/>
     </row>
     <row r="2125" ht="16" customHeight="1">
       <c r="A2125" s="10" t="inlineStr">
         <is>
+          <t>Borçlu Cari Hesap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126" ht="16" customHeight="1">
+      <c r="A2126" s="10" t="inlineStr">
+        <is>
           <t>Spot Kredi</t>
         </is>
       </c>
-    </row>
-    <row r="2126" ht="32" customHeight="1">
-      <c r="A2126" s="11" t="inlineStr">
-        <is>
-          <t>Nakdi Kredi Erken Kapama (Sabit Faizli Türk Lirası Krediler)  (1.7.2024 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
-        </is>
-      </c>
-      <c r="B2126" s="12" t="inlineStr"/>
-      <c r="C2126" s="12" t="inlineStr"/>
-      <c r="D2126" s="12" t="inlineStr"/>
-      <c r="E2126" s="12" t="inlineStr"/>
-      <c r="F2126" s="12" t="inlineStr"/>
-      <c r="G2126" s="12" t="inlineStr"/>
-      <c r="H2126" s="12" t="inlineStr">
-        <is>
-          <t>- / -
-maks: - / -</t>
-        </is>
-      </c>
-      <c r="I2126" s="12" t="inlineStr"/>
     </row>
     <row r="2127" ht="32" customHeight="1">
       <c r="A2127" s="11" t="inlineStr">
         <is>
-          <t>Nakdi Kredi Erken Kapama Ücreti</t>
+          <t>Nakdi Kredi Erken Kapama (Sabit Faizli Türk Lirası Krediler)  (1.7.2024 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
       <c r="B2127" s="12" t="inlineStr"/>
@@ -37576,69 +37575,69 @@
       <c r="H2127" s="12" t="inlineStr">
         <is>
           <t>- / -
+maks: - / -</t>
+        </is>
+      </c>
+      <c r="I2127" s="12" t="inlineStr"/>
+    </row>
+    <row r="2128" ht="32" customHeight="1">
+      <c r="A2128" s="11" t="inlineStr">
+        <is>
+          <t>Nakdi Kredi Erken Kapama Ücreti</t>
+        </is>
+      </c>
+      <c r="B2128" s="12" t="inlineStr"/>
+      <c r="C2128" s="12" t="inlineStr"/>
+      <c r="D2128" s="12" t="inlineStr"/>
+      <c r="E2128" s="12" t="inlineStr"/>
+      <c r="F2128" s="12" t="inlineStr"/>
+      <c r="G2128" s="12" t="inlineStr"/>
+      <c r="H2128" s="12" t="inlineStr">
+        <is>
+          <t>- / -
 maks: - / 2</t>
         </is>
       </c>
-      <c r="I2127" s="12" t="inlineStr"/>
-    </row>
-    <row r="2128" ht="16" customHeight="1">
-      <c r="A2128" s="10" t="inlineStr">
+      <c r="I2128" s="12" t="inlineStr"/>
+    </row>
+    <row r="2129" ht="16" customHeight="1">
+      <c r="A2129" s="10" t="inlineStr">
         <is>
           <t>İskonto İştira Kredisi</t>
         </is>
       </c>
     </row>
-    <row r="2129" ht="32" customHeight="1">
-      <c r="A2129" s="11" t="inlineStr">
+    <row r="2130" ht="32" customHeight="1">
+      <c r="A2130" s="11" t="inlineStr">
         <is>
           <t>Nakdi Kredi Erken Kapama Ücreti (Sabit Faizli Türk Lirası Krediler) (1.7.2024 Tarihinden İtibaren Kullandırılan Kredilerde)</t>
         </is>
       </c>
-      <c r="B2129" s="12" t="inlineStr"/>
-      <c r="C2129" s="12" t="inlineStr"/>
-      <c r="D2129" s="12" t="inlineStr"/>
-      <c r="E2129" s="12" t="inlineStr"/>
-      <c r="F2129" s="12" t="inlineStr"/>
-      <c r="G2129" s="12" t="inlineStr"/>
-      <c r="H2129" s="12" t="inlineStr">
+      <c r="B2130" s="12" t="inlineStr"/>
+      <c r="C2130" s="12" t="inlineStr"/>
+      <c r="D2130" s="12" t="inlineStr"/>
+      <c r="E2130" s="12" t="inlineStr"/>
+      <c r="F2130" s="12" t="inlineStr"/>
+      <c r="G2130" s="12" t="inlineStr"/>
+      <c r="H2130" s="12" t="inlineStr">
         <is>
           <t>- / -
 maks: - / -</t>
         </is>
       </c>
-      <c r="I2129" s="12" t="inlineStr"/>
-    </row>
-    <row r="2130" ht="16" customHeight="1">
-      <c r="A2130" s="10" t="inlineStr">
+      <c r="I2130" s="12" t="inlineStr"/>
+    </row>
+    <row r="2131" ht="16" customHeight="1">
+      <c r="A2131" s="10" t="inlineStr">
         <is>
           <t>Teminat Mektubu</t>
         </is>
       </c>
-    </row>
-    <row r="2131" ht="32" customHeight="1">
-      <c r="A2131" s="11" t="inlineStr">
-        <is>
-          <t>TL Teminat Mektubu</t>
-        </is>
-      </c>
-      <c r="B2131" s="12" t="inlineStr"/>
-      <c r="C2131" s="12" t="inlineStr"/>
-      <c r="D2131" s="12" t="inlineStr"/>
-      <c r="E2131" s="12" t="inlineStr"/>
-      <c r="F2131" s="12" t="inlineStr"/>
-      <c r="G2131" s="12" t="inlineStr"/>
-      <c r="H2131" s="12" t="inlineStr">
-        <is>
-          <t>6.000 TL / -
-maks: - / 6</t>
-        </is>
-      </c>
-      <c r="I2131" s="12" t="inlineStr"/>
     </row>
     <row r="2132" ht="32" customHeight="1">
       <c r="A2132" s="11" t="inlineStr">
         <is>
-          <t>YP Teminat Mektubu</t>
+          <t>TL Teminat Mektubu</t>
         </is>
       </c>
       <c r="B2132" s="12" t="inlineStr"/>
@@ -37658,7 +37657,7 @@
     <row r="2133" ht="32" customHeight="1">
       <c r="A2133" s="11" t="inlineStr">
         <is>
-          <t>Doğrudan Borçlandırma Sistemi (Yıllık)</t>
+          <t>YP Teminat Mektubu</t>
         </is>
       </c>
       <c r="B2133" s="12" t="inlineStr"/>
@@ -37669,43 +37668,43 @@
       <c r="G2133" s="12" t="inlineStr"/>
       <c r="H2133" s="12" t="inlineStr">
         <is>
+          <t>6.000 TL / -
+maks: - / 6</t>
+        </is>
+      </c>
+      <c r="I2133" s="12" t="inlineStr"/>
+    </row>
+    <row r="2134" ht="32" customHeight="1">
+      <c r="A2134" s="11" t="inlineStr">
+        <is>
+          <t>Doğrudan Borçlandırma Sistemi (Yıllık)</t>
+        </is>
+      </c>
+      <c r="B2134" s="12" t="inlineStr"/>
+      <c r="C2134" s="12" t="inlineStr"/>
+      <c r="D2134" s="12" t="inlineStr"/>
+      <c r="E2134" s="12" t="inlineStr"/>
+      <c r="F2134" s="12" t="inlineStr"/>
+      <c r="G2134" s="12" t="inlineStr"/>
+      <c r="H2134" s="12" t="inlineStr">
+        <is>
           <t>5.000 TL / -
 maks: - / 4</t>
         </is>
       </c>
-      <c r="I2133" s="12" t="inlineStr"/>
-    </row>
-    <row r="2134" ht="16" customHeight="1">
-      <c r="A2134" s="10" t="inlineStr">
+      <c r="I2134" s="12" t="inlineStr"/>
+    </row>
+    <row r="2135" ht="16" customHeight="1">
+      <c r="A2135" s="10" t="inlineStr">
         <is>
           <t>Yapı Kredi BANKO</t>
         </is>
       </c>
-    </row>
-    <row r="2135" ht="32" customHeight="1">
-      <c r="A2135" s="11" t="inlineStr">
-        <is>
-          <t>Banko Devir Ücreti (Garantili Ödeme Sistemi Ücreti)</t>
-        </is>
-      </c>
-      <c r="B2135" s="12" t="inlineStr"/>
-      <c r="C2135" s="12" t="inlineStr"/>
-      <c r="D2135" s="12" t="inlineStr"/>
-      <c r="E2135" s="12" t="inlineStr"/>
-      <c r="F2135" s="12" t="inlineStr"/>
-      <c r="G2135" s="12" t="inlineStr"/>
-      <c r="H2135" s="12" t="inlineStr">
-        <is>
-          <t>100 TL / -
-maks: 1.000 TL / 0,1</t>
-        </is>
-      </c>
-      <c r="I2135" s="12" t="inlineStr"/>
     </row>
     <row r="2136" ht="32" customHeight="1">
       <c r="A2136" s="11" t="inlineStr">
         <is>
-          <t>Banko Ücreti (Garantili Ödeme Sistemi Ücreti)</t>
+          <t>Banko Devir Ücreti (Garantili Ödeme Sistemi Ücreti)</t>
         </is>
       </c>
       <c r="B2136" s="12" t="inlineStr"/>
@@ -37716,43 +37715,43 @@
       <c r="G2136" s="12" t="inlineStr"/>
       <c r="H2136" s="12" t="inlineStr">
         <is>
+          <t>100 TL / -
+maks: 1.000 TL / 0,1</t>
+        </is>
+      </c>
+      <c r="I2136" s="12" t="inlineStr"/>
+    </row>
+    <row r="2137" ht="32" customHeight="1">
+      <c r="A2137" s="11" t="inlineStr">
+        <is>
+          <t>Banko Ücreti (Garantili Ödeme Sistemi Ücreti)</t>
+        </is>
+      </c>
+      <c r="B2137" s="12" t="inlineStr"/>
+      <c r="C2137" s="12" t="inlineStr"/>
+      <c r="D2137" s="12" t="inlineStr"/>
+      <c r="E2137" s="12" t="inlineStr"/>
+      <c r="F2137" s="12" t="inlineStr"/>
+      <c r="G2137" s="12" t="inlineStr"/>
+      <c r="H2137" s="12" t="inlineStr">
+        <is>
           <t>- / -
 maks: - / 0,5</t>
         </is>
       </c>
-      <c r="I2136" s="12" t="inlineStr"/>
-    </row>
-    <row r="2137" ht="16" customHeight="1">
-      <c r="A2137" s="10" t="inlineStr">
+      <c r="I2137" s="12" t="inlineStr"/>
+    </row>
+    <row r="2138" ht="16" customHeight="1">
+      <c r="A2138" s="10" t="inlineStr">
         <is>
           <t>Ödeme Planı</t>
         </is>
       </c>
-    </row>
-    <row r="2138" ht="32" customHeight="1">
-      <c r="A2138" s="11" t="inlineStr">
-        <is>
-          <t>Döviz Cinsi</t>
-        </is>
-      </c>
-      <c r="B2138" s="12" t="inlineStr"/>
-      <c r="C2138" s="12" t="inlineStr"/>
-      <c r="D2138" s="12" t="inlineStr"/>
-      <c r="E2138" s="12" t="inlineStr"/>
-      <c r="F2138" s="12" t="inlineStr"/>
-      <c r="G2138" s="12" t="inlineStr"/>
-      <c r="H2138" s="12" t="inlineStr">
-        <is>
-          <t>TL / Kredi Taksit Sayısı
-maks: AY</t>
-        </is>
-      </c>
-      <c r="I2138" s="12" t="inlineStr"/>
     </row>
     <row r="2139" ht="32" customHeight="1">
       <c r="A2139" s="11" t="inlineStr">
         <is>
-          <t>Faiz Oranı (Aylık)</t>
+          <t>Döviz Cinsi</t>
         </is>
       </c>
       <c r="B2139" s="12" t="inlineStr"/>
@@ -37763,7 +37762,8 @@
       <c r="G2139" s="12" t="inlineStr"/>
       <c r="H2139" s="12" t="inlineStr">
         <is>
-          <t>KKDF Oranı</t>
+          <t>TL / Kredi Taksit Sayısı
+maks: AY</t>
         </is>
       </c>
       <c r="I2139" s="12" t="inlineStr"/>
@@ -37771,7 +37771,7 @@
     <row r="2140" ht="32" customHeight="1">
       <c r="A2140" s="11" t="inlineStr">
         <is>
-          <t>BSMV Oranı</t>
+          <t>Faiz Oranı (Aylık)</t>
         </is>
       </c>
       <c r="B2140" s="12" t="inlineStr"/>
@@ -37782,7 +37782,7 @@
       <c r="G2140" s="12" t="inlineStr"/>
       <c r="H2140" s="12" t="inlineStr">
         <is>
-          <t>İlk Taksit Tutarı</t>
+          <t>KKDF Oranı</t>
         </is>
       </c>
       <c r="I2140" s="12" t="inlineStr"/>
@@ -37790,7 +37790,7 @@
     <row r="2141" ht="32" customHeight="1">
       <c r="A2141" s="11" t="inlineStr">
         <is>
-          <t>Aylık Maliyet Oranı</t>
+          <t>BSMV Oranı</t>
         </is>
       </c>
       <c r="B2141" s="12" t="inlineStr"/>
@@ -37801,7 +37801,7 @@
       <c r="G2141" s="12" t="inlineStr"/>
       <c r="H2141" s="12" t="inlineStr">
         <is>
-          <t>Yıllık Maliyet Oranı</t>
+          <t>İlk Taksit Tutarı</t>
         </is>
       </c>
       <c r="I2141" s="12" t="inlineStr"/>
@@ -37809,7 +37809,7 @@
     <row r="2142" ht="32" customHeight="1">
       <c r="A2142" s="11" t="inlineStr">
         <is>
-          <t>Müşteri Tipi</t>
+          <t>Aylık Maliyet Oranı</t>
         </is>
       </c>
       <c r="B2142" s="12" t="inlineStr"/>
@@ -37820,7 +37820,7 @@
       <c r="G2142" s="12" t="inlineStr"/>
       <c r="H2142" s="12" t="inlineStr">
         <is>
-          <t>Kredi Türü</t>
+          <t>Yıllık Maliyet Oranı</t>
         </is>
       </c>
       <c r="I2142" s="12" t="inlineStr"/>
@@ -37828,7 +37828,7 @@
     <row r="2143" ht="32" customHeight="1">
       <c r="A2143" s="11" t="inlineStr">
         <is>
-          <t>Kampanya</t>
+          <t>Müşteri Tipi</t>
         </is>
       </c>
       <c r="B2143" s="12" t="inlineStr"/>
@@ -37839,41 +37839,41 @@
       <c r="G2143" s="12" t="inlineStr"/>
       <c r="H2143" s="12" t="inlineStr">
         <is>
+          <t>Kredi Türü</t>
+        </is>
+      </c>
+      <c r="I2143" s="12" t="inlineStr"/>
+    </row>
+    <row r="2144" ht="32" customHeight="1">
+      <c r="A2144" s="11" t="inlineStr">
+        <is>
+          <t>Kampanya</t>
+        </is>
+      </c>
+      <c r="B2144" s="12" t="inlineStr"/>
+      <c r="C2144" s="12" t="inlineStr"/>
+      <c r="D2144" s="12" t="inlineStr"/>
+      <c r="E2144" s="12" t="inlineStr"/>
+      <c r="F2144" s="12" t="inlineStr"/>
+      <c r="G2144" s="12" t="inlineStr"/>
+      <c r="H2144" s="12" t="inlineStr">
+        <is>
           <t>Toplam Geri Ödeme Tutarı</t>
         </is>
       </c>
-      <c r="I2143" s="12" t="inlineStr"/>
-    </row>
-    <row r="2144" ht="16" customHeight="1">
-      <c r="A2144" s="10" t="inlineStr">
+      <c r="I2144" s="12" t="inlineStr"/>
+    </row>
+    <row r="2145" ht="16" customHeight="1">
+      <c r="A2145" s="10" t="inlineStr">
         <is>
           <t>Hazır Kredi Paketleri</t>
         </is>
       </c>
-    </row>
-    <row r="2145" ht="32" customHeight="1">
-      <c r="A2145" s="11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B2145" s="12" t="inlineStr"/>
-      <c r="C2145" s="12" t="inlineStr"/>
-      <c r="D2145" s="12" t="inlineStr"/>
-      <c r="E2145" s="12" t="inlineStr"/>
-      <c r="F2145" s="12" t="inlineStr"/>
-      <c r="G2145" s="12" t="inlineStr"/>
-      <c r="H2145" s="12" t="inlineStr">
-        <is>
-          <t>2.515,00 TL / % 0.01790</t>
-        </is>
-      </c>
-      <c r="I2145" s="12" t="inlineStr"/>
     </row>
     <row r="2146" ht="32" customHeight="1">
       <c r="A2146" s="11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B2146" s="12" t="inlineStr"/>
@@ -37892,7 +37892,7 @@
     <row r="2147" ht="32" customHeight="1">
       <c r="A2147" s="11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B2147" s="12" t="inlineStr"/>
@@ -37906,16 +37906,12 @@
           <t>2.515,00 TL / % 0.01790</t>
         </is>
       </c>
-      <c r="I2147" s="12" t="inlineStr">
-        <is>
-          <t>2.515,00 TL / % 0.01790</t>
-        </is>
-      </c>
+      <c r="I2147" s="12" t="inlineStr"/>
     </row>
     <row r="2148" ht="32" customHeight="1">
       <c r="A2148" s="11" t="inlineStr">
         <is>
-          <t>Seçiniz123Seçiniz</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B2148" s="12" t="inlineStr"/>
@@ -37926,15 +37922,38 @@
       <c r="G2148" s="12" t="inlineStr"/>
       <c r="H2148" s="12" t="inlineStr">
         <is>
+          <t>2.515,00 TL / % 0.01790</t>
+        </is>
+      </c>
+      <c r="I2148" s="12" t="inlineStr">
+        <is>
+          <t>2.515,00 TL / % 0.01790</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149" ht="32" customHeight="1">
+      <c r="A2149" s="11" t="inlineStr">
+        <is>
+          <t>Seçiniz123Seçiniz</t>
+        </is>
+      </c>
+      <c r="B2149" s="12" t="inlineStr"/>
+      <c r="C2149" s="12" t="inlineStr"/>
+      <c r="D2149" s="12" t="inlineStr"/>
+      <c r="E2149" s="12" t="inlineStr"/>
+      <c r="F2149" s="12" t="inlineStr"/>
+      <c r="G2149" s="12" t="inlineStr"/>
+      <c r="H2149" s="12" t="inlineStr">
+        <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I2148" s="12" t="inlineStr"/>
-    </row>
-    <row r="2150">
-      <c r="A2150" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 10.08.2026 13:04</t>
+      <c r="I2149" s="12" t="inlineStr"/>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 11.08.2026 11:35</t>
         </is>
       </c>
     </row>
@@ -37948,6 +37967,7 @@
     <mergeCell ref="A843:I843"/>
     <mergeCell ref="A259:I259"/>
     <mergeCell ref="A1014:I1014"/>
+    <mergeCell ref="A2138:I2138"/>
     <mergeCell ref="A1079:I1079"/>
     <mergeCell ref="A1250:I1250"/>
     <mergeCell ref="B1:C1"/>
@@ -37956,6 +37976,7 @@
     <mergeCell ref="A482:I482"/>
     <mergeCell ref="A609:I609"/>
     <mergeCell ref="A780:I780"/>
+    <mergeCell ref="A1833:I1833"/>
     <mergeCell ref="A774:I774"/>
     <mergeCell ref="A945:I945"/>
     <mergeCell ref="A845:I845"/>
@@ -37963,25 +37984,27 @@
     <mergeCell ref="A1249:I1249"/>
     <mergeCell ref="A117:I117"/>
     <mergeCell ref="A1314:I1314"/>
-    <mergeCell ref="A1904:I1904"/>
+    <mergeCell ref="A1964:I1964"/>
     <mergeCell ref="A1612:I1612"/>
     <mergeCell ref="A724:I724"/>
-    <mergeCell ref="A2026:I2026"/>
-    <mergeCell ref="A2041:I2041"/>
+    <mergeCell ref="A1835:I1835"/>
     <mergeCell ref="A1251:I1251"/>
+    <mergeCell ref="A1772:I1772"/>
     <mergeCell ref="A1576:I1576"/>
     <mergeCell ref="A1390:I1390"/>
     <mergeCell ref="A806:I806"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="A808:I808"/>
     <mergeCell ref="A664:I664"/>
-    <mergeCell ref="A2128:I2128"/>
     <mergeCell ref="A1367:I1367"/>
     <mergeCell ref="A210:I210"/>
     <mergeCell ref="A1158:I1158"/>
+    <mergeCell ref="A1901:I1901"/>
     <mergeCell ref="A630:I630"/>
     <mergeCell ref="A793:I793"/>
     <mergeCell ref="A1175:I1175"/>
+    <mergeCell ref="A2123:I2123"/>
+    <mergeCell ref="A1983:I1983"/>
     <mergeCell ref="A755:I755"/>
     <mergeCell ref="A1320:I1320"/>
     <mergeCell ref="A350:I350"/>
@@ -37990,10 +38013,9 @@
     <mergeCell ref="A496:I496"/>
     <mergeCell ref="A1322:I1322"/>
     <mergeCell ref="A1378:I1378"/>
+    <mergeCell ref="A2077:I2077"/>
     <mergeCell ref="A982:I982"/>
     <mergeCell ref="A561:I561"/>
-    <mergeCell ref="A1978:I1978"/>
-    <mergeCell ref="A2076:I2076"/>
     <mergeCell ref="A1315:I1315"/>
     <mergeCell ref="A256:I256"/>
     <mergeCell ref="A498:I498"/>
@@ -38024,12 +38046,14 @@
     <mergeCell ref="A1325:I1325"/>
     <mergeCell ref="A591:I591"/>
     <mergeCell ref="A1104:I1104"/>
+    <mergeCell ref="A1979:I1979"/>
     <mergeCell ref="A1196:I1196"/>
-    <mergeCell ref="A2144:I2144"/>
     <mergeCell ref="A1383:I1383"/>
     <mergeCell ref="A161:I161"/>
     <mergeCell ref="A459:I459"/>
+    <mergeCell ref="A1910:I1910"/>
     <mergeCell ref="A751:I751"/>
+    <mergeCell ref="A1812:I1812"/>
     <mergeCell ref="A582:I582"/>
     <mergeCell ref="A283:I283"/>
     <mergeCell ref="A581:I581"/>
@@ -38041,13 +38065,14 @@
     <mergeCell ref="A988:I988"/>
     <mergeCell ref="A611:I611"/>
     <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A2001:I2001"/>
+    <mergeCell ref="A2112:I2112"/>
     <mergeCell ref="A214:I214"/>
     <mergeCell ref="A285:I285"/>
     <mergeCell ref="A512:I512"/>
     <mergeCell ref="A1338:I1338"/>
     <mergeCell ref="A754:I754"/>
     <mergeCell ref="A1117:I1117"/>
-    <mergeCell ref="A1834:I1834"/>
     <mergeCell ref="A1362:I1362"/>
     <mergeCell ref="A764:I764"/>
     <mergeCell ref="A9:I9"/>
@@ -38056,8 +38081,10 @@
     <mergeCell ref="A937:I937"/>
     <mergeCell ref="A986:I986"/>
     <mergeCell ref="A225:I225"/>
+    <mergeCell ref="A1931:I1931"/>
     <mergeCell ref="A728:I728"/>
     <mergeCell ref="A678:I678"/>
+    <mergeCell ref="A1802:I1802"/>
     <mergeCell ref="A227:I227"/>
     <mergeCell ref="A1692:I1692"/>
     <mergeCell ref="A1344:I1344"/>
@@ -38065,35 +38092,36 @@
     <mergeCell ref="A660:I660"/>
     <mergeCell ref="A818:I818"/>
     <mergeCell ref="A1060:I1060"/>
-    <mergeCell ref="A1880:I1880"/>
     <mergeCell ref="A155:I155"/>
     <mergeCell ref="A1181:I1181"/>
     <mergeCell ref="A1041:I1041"/>
     <mergeCell ref="A820:I820"/>
     <mergeCell ref="A676:I676"/>
-    <mergeCell ref="A1944:I1944"/>
+    <mergeCell ref="A2115:I2115"/>
     <mergeCell ref="A599:I599"/>
     <mergeCell ref="A1055:I1055"/>
+    <mergeCell ref="A1881:I1881"/>
     <mergeCell ref="A1120:I1120"/>
     <mergeCell ref="A628:I628"/>
     <mergeCell ref="A1057:I1057"/>
-    <mergeCell ref="A1955:I1955"/>
     <mergeCell ref="A246:I246"/>
     <mergeCell ref="A317:I317"/>
     <mergeCell ref="A233:I233"/>
     <mergeCell ref="A640:I640"/>
+    <mergeCell ref="A1970:I1970"/>
     <mergeCell ref="A838:I838"/>
     <mergeCell ref="A1236:I1236"/>
-    <mergeCell ref="A1957:I1957"/>
     <mergeCell ref="A1307:I1307"/>
     <mergeCell ref="A248:I248"/>
     <mergeCell ref="A235:I235"/>
     <mergeCell ref="A704:I704"/>
     <mergeCell ref="A946:I946"/>
+    <mergeCell ref="A1972:I1972"/>
     <mergeCell ref="A1244:I1244"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A1073:I1073"/>
     <mergeCell ref="A508:I508"/>
+    <mergeCell ref="A2126:I2126"/>
     <mergeCell ref="A1309:I1309"/>
     <mergeCell ref="A106:I106"/>
     <mergeCell ref="A597:I597"/>
@@ -38113,36 +38141,34 @@
     <mergeCell ref="A221:I221"/>
     <mergeCell ref="A196:I196"/>
     <mergeCell ref="A1218:I1218"/>
+    <mergeCell ref="A1945:I1945"/>
     <mergeCell ref="A1282:I1282"/>
     <mergeCell ref="A198:I198"/>
     <mergeCell ref="A636:I636"/>
+    <mergeCell ref="A2074:I2074"/>
     <mergeCell ref="A318:I318"/>
     <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A1971:I1971"/>
+    <mergeCell ref="A2042:I2042"/>
     <mergeCell ref="A646:I646"/>
     <mergeCell ref="A127:I127"/>
     <mergeCell ref="A249:I249"/>
     <mergeCell ref="A1246:I1246"/>
-    <mergeCell ref="A1963:I1963"/>
     <mergeCell ref="A1373:I1373"/>
-    <mergeCell ref="A2134:I2134"/>
     <mergeCell ref="A783:I783"/>
     <mergeCell ref="A605:I605"/>
     <mergeCell ref="A648:I648"/>
-    <mergeCell ref="A1900:I1900"/>
     <mergeCell ref="A1012:I1012"/>
     <mergeCell ref="A1310:I1310"/>
     <mergeCell ref="A555:I555"/>
-    <mergeCell ref="A1965:I1965"/>
-    <mergeCell ref="A2111:I2111"/>
-    <mergeCell ref="A2037:I2037"/>
     <mergeCell ref="A905:I905"/>
     <mergeCell ref="A1076:I1076"/>
-    <mergeCell ref="A2073:I2073"/>
+    <mergeCell ref="A1958:I1958"/>
+    <mergeCell ref="A2129:I2129"/>
     <mergeCell ref="A1337:I1337"/>
     <mergeCell ref="A1312:I1312"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A836:I836"/>
+    <mergeCell ref="A2131:I2131"/>
     <mergeCell ref="A930:I930"/>
     <mergeCell ref="A1145:I1145"/>
     <mergeCell ref="A204:I204"/>
@@ -38154,14 +38180,13 @@
     <mergeCell ref="A1094:I1094"/>
     <mergeCell ref="A700:I700"/>
     <mergeCell ref="A802:I802"/>
-    <mergeCell ref="A2122:I2122"/>
     <mergeCell ref="A1234:I1234"/>
     <mergeCell ref="A789:I789"/>
     <mergeCell ref="A1221:I1221"/>
+    <mergeCell ref="A2032:I2032"/>
     <mergeCell ref="A506:I506"/>
     <mergeCell ref="A1000:I1000"/>
     <mergeCell ref="A245:I245"/>
-    <mergeCell ref="A2124:I2124"/>
     <mergeCell ref="A791:I791"/>
     <mergeCell ref="A1089:I1089"/>
     <mergeCell ref="A1356:I1356"/>
@@ -38175,7 +38200,7 @@
     <mergeCell ref="A842:I842"/>
     <mergeCell ref="A1018:I1018"/>
     <mergeCell ref="A1311:I1311"/>
-    <mergeCell ref="A2137:I2137"/>
+    <mergeCell ref="A1966:I1966"/>
     <mergeCell ref="A1316:I1316"/>
     <mergeCell ref="A1376:I1376"/>
     <mergeCell ref="A1176:I1176"/>
@@ -38187,13 +38212,14 @@
     <mergeCell ref="A1191:I1191"/>
     <mergeCell ref="A1313:I1313"/>
     <mergeCell ref="A1384:I1384"/>
-    <mergeCell ref="A2114:I2114"/>
     <mergeCell ref="A715:I715"/>
+    <mergeCell ref="A1905:I1905"/>
     <mergeCell ref="A510:I510"/>
     <mergeCell ref="A860:I860"/>
     <mergeCell ref="A1202:I1202"/>
     <mergeCell ref="A1394:I1394"/>
     <mergeCell ref="A810:I810"/>
+    <mergeCell ref="A1994:I1994"/>
     <mergeCell ref="A505:I505"/>
     <mergeCell ref="A570:I570"/>
     <mergeCell ref="A1039:I1039"/>
@@ -38214,17 +38240,15 @@
     <mergeCell ref="A1230:I1230"/>
     <mergeCell ref="A1019:I1019"/>
     <mergeCell ref="A994:I994"/>
-    <mergeCell ref="A1771:I1771"/>
+    <mergeCell ref="A2038:I2038"/>
     <mergeCell ref="A500:I500"/>
     <mergeCell ref="A220:I220"/>
     <mergeCell ref="A736:I736"/>
-    <mergeCell ref="A1982:I1982"/>
-    <mergeCell ref="A1909:I1909"/>
-    <mergeCell ref="A2080:I2080"/>
-    <mergeCell ref="A1969:I1969"/>
     <mergeCell ref="A1319:I1319"/>
+    <mergeCell ref="A2145:I2145"/>
     <mergeCell ref="A502:I502"/>
     <mergeCell ref="A787:I787"/>
+    <mergeCell ref="A1784:I1784"/>
     <mergeCell ref="A1321:I1321"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A447:I447"/>
@@ -38238,12 +38262,12 @@
     <mergeCell ref="A1397:I1397"/>
     <mergeCell ref="A813:I813"/>
     <mergeCell ref="A607:I607"/>
-    <mergeCell ref="A2108:I2108"/>
     <mergeCell ref="A734:I734"/>
     <mergeCell ref="A150:I150"/>
     <mergeCell ref="A321:I321"/>
     <mergeCell ref="A215:I215"/>
     <mergeCell ref="A1334:I1334"/>
+    <mergeCell ref="A2135:I2135"/>
     <mergeCell ref="A152:I152"/>
     <mergeCell ref="A323:I323"/>
     <mergeCell ref="A621:I621"/>
@@ -38261,6 +38285,7 @@
     <mergeCell ref="A1418:I1418"/>
     <mergeCell ref="A1211:I1211"/>
     <mergeCell ref="A1276:I1276"/>
+    <mergeCell ref="A2109:I2109"/>
     <mergeCell ref="A1050:I1050"/>
     <mergeCell ref="A1419:I1419"/>
     <mergeCell ref="A216:I216"/>
@@ -38270,13 +38295,11 @@
     <mergeCell ref="A623:I623"/>
     <mergeCell ref="A821:I821"/>
     <mergeCell ref="A992:I992"/>
-    <mergeCell ref="A1940:I1940"/>
     <mergeCell ref="A1179:I1179"/>
     <mergeCell ref="A979:I979"/>
     <mergeCell ref="A218:I218"/>
     <mergeCell ref="A316:I316"/>
     <mergeCell ref="A1342:I1342"/>
-    <mergeCell ref="A1811:I1811"/>
     <mergeCell ref="A1208:I1208"/>
     <mergeCell ref="A1450:I1450"/>
     <mergeCell ref="A1735:I1735"/>
@@ -38297,11 +38320,9 @@
     <mergeCell ref="A77:I77"/>
     <mergeCell ref="A769:I769"/>
     <mergeCell ref="A166:I166"/>
-    <mergeCell ref="A1801:I1801"/>
     <mergeCell ref="A595:I595"/>
     <mergeCell ref="A168:I168"/>
     <mergeCell ref="A781:I781"/>
-    <mergeCell ref="A1930:I1930"/>
     <mergeCell ref="A1210:I1210"/>
     <mergeCell ref="A255:I255"/>
     <mergeCell ref="A758:I758"/>
@@ -38311,10 +38332,9 @@
     <mergeCell ref="A1043:I1043"/>
     <mergeCell ref="A847:I847"/>
     <mergeCell ref="A1341:I1341"/>
-    <mergeCell ref="A1783:I1783"/>
     <mergeCell ref="A499:I499"/>
     <mergeCell ref="A822:I822"/>
-    <mergeCell ref="A1819:I1819"/>
+    <mergeCell ref="A1941:I1941"/>
     <mergeCell ref="A303:I303"/>
     <mergeCell ref="A601:I601"/>
     <mergeCell ref="A219:I219"/>
@@ -38326,9 +38346,7 @@
     <mergeCell ref="A1293:I1293"/>
     <mergeCell ref="A617:I617"/>
     <mergeCell ref="A615:I615"/>
-    <mergeCell ref="A1832:I1832"/>
     <mergeCell ref="A1011:I1011"/>
-    <mergeCell ref="A2130:I2130"/>
     <mergeCell ref="A1369:I1369"/>
     <mergeCell ref="A998:I998"/>
     <mergeCell ref="A237:I237"/>
@@ -38340,21 +38358,22 @@
     <mergeCell ref="A708:I708"/>
     <mergeCell ref="A1006:I1006"/>
     <mergeCell ref="A1199:I1199"/>
-    <mergeCell ref="A2000:I2000"/>
     <mergeCell ref="A1112:I1112"/>
+    <mergeCell ref="A1956:I1956"/>
     <mergeCell ref="A1387:I1387"/>
     <mergeCell ref="A1324:I1324"/>
-    <mergeCell ref="A2031:I2031"/>
     <mergeCell ref="A563:I563"/>
+    <mergeCell ref="A2027:I2027"/>
     <mergeCell ref="A2125:I2125"/>
     <mergeCell ref="A1084:I1084"/>
+    <mergeCell ref="A2081:I2081"/>
+    <mergeCell ref="A1820:I1820"/>
     <mergeCell ref="A832:I832"/>
     <mergeCell ref="A1003:I1003"/>
     <mergeCell ref="A1301:I1301"/>
     <mergeCell ref="A638:I638"/>
     <mergeCell ref="A632:I632"/>
     <mergeCell ref="A825:I825"/>
-    <mergeCell ref="A1993:I1993"/>
     <mergeCell ref="A1365:I1365"/>
     <mergeCell ref="A1346:I1346"/>
   </mergeCells>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -37953,7 +37953,7 @@
     <row r="2151">
       <c r="A2151" t="inlineStr">
         <is>
-          <t>Son güncelleme: 11.08.2026 11:35</t>
+          <t>Son güncelleme: 12.08.2026 11:58</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -33131,7 +33131,7 @@
     <row r="1783">
       <c r="A1783" s="13" t="inlineStr">
         <is>
-          <t>Son güncelleme: 13.08.2026 13:47</t>
+          <t>Son güncelleme: 13.08.2026 13:55</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -33131,7 +33131,7 @@
     <row r="1783">
       <c r="A1783" s="13" t="inlineStr">
         <is>
-          <t>Son güncelleme: 13.08.2026 13:55</t>
+          <t>Son güncelleme: 13.08.2026 14:36</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -33131,7 +33131,7 @@
     <row r="1783">
       <c r="A1783" s="13" t="inlineStr">
         <is>
-          <t>Son güncelleme: 13.08.2026 14:36</t>
+          <t>Son güncelleme: 13.08.2026 15:00</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -632,9 +632,9 @@
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr"/>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>39.87TL / 797.68TL</t>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>39.87TL</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr"/>
@@ -642,11 +642,7 @@
       <c r="F4" s="12" t="inlineStr"/>
       <c r="G4" s="12" t="inlineStr"/>
       <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="I4" s="12" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -654,13 +650,13 @@
           <t>Düzenli EFT - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>7,97TL</t>
         </is>
@@ -677,19 +673,19 @@
           <t>Düzenli EFT - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>199.41TL</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>199,41TL</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>199,41 TL</t>
         </is>
@@ -736,7 +732,7 @@
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>797.68TL</t>
         </is>
@@ -752,7 +748,7 @@
           <t>398,83 TL</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>797,68 TL</t>
         </is>
@@ -823,13 +819,13 @@
           <t>Düzenli Havale - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>3.99TL</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>3,99TL</t>
         </is>
@@ -846,19 +842,19 @@
           <t>Düzenli Havale - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>99.71TL</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>99,71TL</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
@@ -882,7 +878,7 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>19.94TL</t>
         </is>
@@ -895,8 +891,16 @@
       <c r="E15" s="12" t="inlineStr"/>
       <c r="F15" s="12" t="inlineStr"/>
       <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>13,92 TL / -</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>19,94 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -922,20 +926,24 @@
       <c r="E16" s="12" t="inlineStr"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
+          <t>199,42</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
           <t>398,84 TL</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>398,84 TL</t>
-        </is>
-      </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
           <t>27,62 TL / -</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>398,84 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -945,17 +953,17 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>1900.00TL / 0.70% / 2950.00TL</t>
+          <t>1900.00TL / 0.70%</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>3676.20TL / 0.70% / 13457.15TL</t>
+          <t>3676.20TL / 0.70%</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>150TL / 245TL</t>
+          <t>150TL</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -970,7 +978,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>19,94 TL</t>
+          <t>39,88 TL</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1018,7 +1026,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>380.95TL / 0.48% / 1523.81TL</t>
+          <t>380.95TL / 0.48%</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr"/>
@@ -1028,7 +1036,7 @@
       <c r="G21" s="12" t="inlineStr"/>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>200 TL / 0,4 / 1.200 TL</t>
+          <t>200 TL / 0,4</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr"/>
@@ -1039,7 +1047,7 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -1049,7 +1057,11 @@
       <c r="E22" s="12" t="inlineStr"/>
       <c r="F22" s="12" t="inlineStr"/>
       <c r="G22" s="12" t="inlineStr"/>
-      <c r="H22" s="12" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>7,97 TL / -</t>
+        </is>
+      </c>
       <c r="I22" s="12" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -1058,7 +1070,7 @@
           <t>FAST - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -1068,7 +1080,11 @@
       <c r="E23" s="12" t="inlineStr"/>
       <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>15,96 TL / -</t>
+        </is>
+      </c>
       <c r="I23" s="12" t="inlineStr"/>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -1096,13 +1112,13 @@
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr"/>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>26.990,48 TL</t>
-        </is>
-      </c>
+      <c r="F26" s="12" t="inlineStr"/>
       <c r="G26" s="12" t="inlineStr"/>
-      <c r="H26" s="12" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
       <c r="I26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1123,13 +1139,13 @@
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr"/>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>16.190,48 TL</t>
-        </is>
-      </c>
+      <c r="F27" s="12" t="inlineStr"/>
       <c r="G27" s="12" t="inlineStr"/>
-      <c r="H27" s="12" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
       <c r="I27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1150,13 +1166,13 @@
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr"/>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>21.595,24 TL</t>
-        </is>
-      </c>
+      <c r="F28" s="12" t="inlineStr"/>
       <c r="G28" s="12" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
       <c r="I28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1165,7 +1181,7 @@
           <t>Kasa Depozito - büyük</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
@@ -1175,7 +1191,11 @@
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr"/>
       <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="12" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
       <c r="I29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1184,7 +1204,7 @@
           <t>Kasa Depozito - orta</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
@@ -1194,7 +1214,11 @@
       <c r="E30" s="12" t="inlineStr"/>
       <c r="F30" s="12" t="inlineStr"/>
       <c r="G30" s="12" t="inlineStr"/>
-      <c r="H30" s="12" t="inlineStr"/>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
       <c r="I30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1203,7 +1227,7 @@
           <t>Kasa Depozito - küçük</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
@@ -1213,7 +1237,11 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr"/>
       <c r="G31" s="12" t="inlineStr"/>
-      <c r="H31" s="12" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
       <c r="I31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1222,7 +1250,7 @@
           <t>Yıllık Kasa Ücreti - genel</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>1469.52TL</t>
         </is>
@@ -1232,11 +1260,7 @@
       <c r="E32" s="12" t="inlineStr"/>
       <c r="F32" s="12" t="inlineStr"/>
       <c r="G32" s="12" t="inlineStr"/>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 28.333,33 TL</t>
-        </is>
-      </c>
+      <c r="H32" s="12" t="inlineStr"/>
       <c r="I32" s="12" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -1247,7 +1271,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr"/>
       <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>9420TL</t>
         </is>
@@ -1255,11 +1279,7 @@
       <c r="E33" s="12" t="inlineStr"/>
       <c r="F33" s="12" t="inlineStr"/>
       <c r="G33" s="12" t="inlineStr"/>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 28.333,33 TL</t>
-        </is>
-      </c>
+      <c r="H33" s="12" t="inlineStr"/>
       <c r="I33" s="12" t="inlineStr"/>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -1272,18 +1292,26 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 0-100</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>50.00TL</t>
+          <t>Altın Transfer</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>100.00TL</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="12" t="inlineStr"/>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>415TL</t>
+        </is>
+      </c>
       <c r="E36" s="12" t="inlineStr"/>
-      <c r="F36" s="12" t="inlineStr"/>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>0.00018</t>
+        </is>
+      </c>
       <c r="G36" s="12" t="inlineStr"/>
       <c r="H36" s="12" t="inlineStr"/>
       <c r="I36" s="12" t="inlineStr"/>
@@ -1291,767 +1319,719 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>637.00TL</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>10.00%</t>
-        </is>
-      </c>
+          <t>Altın Transfer - 1-10gr</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr"/>
+      <c r="C37" s="12" t="inlineStr"/>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>415TL</t>
+          <t>57,5TL</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr"/>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>60 TL</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr"/>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>- / 10</t>
-        </is>
-      </c>
+      <c r="H37" s="12" t="inlineStr"/>
       <c r="I37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 1-10gr</t>
+          <t>Altın Transfer - 11-100gr</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr"/>
       <c r="C38" s="12" t="inlineStr"/>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>57,5TL</t>
+          <t>115TL</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr"/>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>60 TL</t>
+          <t>120 TL</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr"/>
       <c r="H38" s="12" t="inlineStr"/>
       <c r="I38" s="12" t="inlineStr"/>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Altın Transfer - 11-100gr</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr"/>
-      <c r="C39" s="12" t="inlineStr"/>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>115TL</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr"/>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>120 TL</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr"/>
-      <c r="H39" s="12" t="inlineStr"/>
-      <c r="I39" s="12" t="inlineStr"/>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr"/>
-      <c r="F42" s="13" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr"/>
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>94,29 TL / -</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr"/>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>339 TL / -</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri - Kart</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>0.00TL / 50.00TL</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>0TL / 2,86TL</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr"/>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>0.5 TL / 55 TL</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>0.5 TL / 55 TL</t>
-        </is>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>0,63 TL / - / 45 TL</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr"/>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>0.00TL</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>0.5 TL</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>0.5 TL</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>0,63 TL / -</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>3.50TL / 3.50%</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr"/>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>0TL / 3,1%</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr"/>
-      <c r="F48" s="13" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr"/>
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>2 TL / 3,5%</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>3 TL / - / 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr"/>
+      <c r="H47" s="12" t="inlineStr"/>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>3 TL / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr"/>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr"/>
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr"/>
-      <c r="F51" s="13" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr"/>
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr"/>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>275 TL / -</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr"/>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr"/>
+      <c r="I50" s="12" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr"/>
-      <c r="C54" s="12" t="inlineStr"/>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>26TL / 30TL</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr"/>
-      <c r="F54" s="13" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr"/>
+      <c r="C53" s="12" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>26TL</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr"/>
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr"/>
-      <c r="H54" s="12" t="inlineStr"/>
-      <c r="I54" s="12" t="inlineStr"/>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr"/>
+      <c r="H53" s="12" t="inlineStr"/>
+      <c r="I53" s="12" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr"/>
-      <c r="C57" s="12" t="inlineStr"/>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr"/>
+      <c r="C56" s="12" t="inlineStr"/>
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr"/>
-      <c r="F57" s="12" t="inlineStr"/>
-      <c r="G57" s="12" t="inlineStr"/>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="12" t="inlineStr"/>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr"/>
+      <c r="F56" s="12" t="inlineStr"/>
+      <c r="G56" s="12" t="inlineStr"/>
+      <c r="H56" s="12" t="inlineStr"/>
+      <c r="I56" s="12" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri Aracılık</t>
         </is>
       </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Telefon Ödemeleri</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr"/>
+      <c r="C59" s="12" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr"/>
+      <c r="E59" s="12" t="inlineStr"/>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>1 %</t>
+        </is>
+      </c>
+      <c r="G59" s="12" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr"/>
+      <c r="I59" s="12" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>Telefon Ödemeleri</t>
+          <t>Telefon - 399000+ TRY</t>
         </is>
       </c>
       <c r="B60" s="12" t="inlineStr"/>
       <c r="C60" s="12" t="inlineStr"/>
       <c r="D60" s="12" t="inlineStr"/>
       <c r="E60" s="12" t="inlineStr"/>
-      <c r="F60" s="13" t="inlineStr">
-        <is>
-          <t>1 %</t>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr"/>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 50 USD</t>
-        </is>
-      </c>
+      <c r="H60" s="12" t="inlineStr"/>
       <c r="I60" s="12" t="inlineStr"/>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>Telefon - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="inlineStr"/>
-      <c r="C61" s="12" t="inlineStr"/>
-      <c r="D61" s="12" t="inlineStr"/>
-      <c r="E61" s="12" t="inlineStr"/>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>99,71 TL</t>
-        </is>
-      </c>
-      <c r="G61" s="12" t="inlineStr"/>
-      <c r="H61" s="12" t="inlineStr"/>
-      <c r="I61" s="12" t="inlineStr"/>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Vergi Tahsilat Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Vergi Tahsilat</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>0.00TL / 0.00%</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="inlineStr"/>
-      <c r="D64" s="12" t="inlineStr"/>
-      <c r="E64" s="12" t="inlineStr"/>
-      <c r="F64" s="12" t="inlineStr"/>
-      <c r="G64" s="12" t="inlineStr"/>
-      <c r="H64" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 100 TL</t>
-        </is>
-      </c>
-      <c r="I64" s="12" t="inlineStr"/>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr"/>
+      <c r="C63" s="12" t="inlineStr"/>
+      <c r="D63" s="12" t="inlineStr"/>
+      <c r="E63" s="12" t="inlineStr"/>
+      <c r="F63" s="12" t="inlineStr"/>
+      <c r="G63" s="12" t="inlineStr"/>
+      <c r="H63" s="12" t="inlineStr"/>
+      <c r="I63" s="12" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr"/>
-      <c r="D67" s="12" t="inlineStr"/>
-      <c r="E67" s="12" t="inlineStr"/>
-      <c r="F67" s="12" t="inlineStr"/>
-      <c r="G67" s="12" t="inlineStr"/>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 18,9 TL</t>
-        </is>
-      </c>
-      <c r="I67" s="12" t="inlineStr"/>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr"/>
+      <c r="D66" s="12" t="inlineStr"/>
+      <c r="E66" s="12" t="inlineStr"/>
+      <c r="F66" s="12" t="inlineStr"/>
+      <c r="G66" s="12" t="inlineStr"/>
+      <c r="H66" s="12" t="inlineStr"/>
+      <c r="I66" s="12" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Mevduat Araştırma</t>
         </is>
       </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Referans Mektubu -</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr"/>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>770TL</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr"/>
+      <c r="F69" s="12" t="inlineStr"/>
+      <c r="G69" s="12" t="inlineStr"/>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>50 TL / -</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="inlineStr"/>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>Referans Mektubu -</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>2.00%</t>
-        </is>
-      </c>
+          <t>Hesap Özeti Verilmesi -</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr"/>
       <c r="C70" s="12" t="inlineStr"/>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>770TL / 0.1%</t>
+          <t>190TL</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr"/>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>5000 TL</t>
+          <t>12 TL</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr"/>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H70" s="12" t="inlineStr"/>
       <c r="I70" s="12" t="inlineStr"/>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>Hesap Özeti Verilmesi -</t>
+          <t>Borcu Yoktur Yazısı</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr"/>
       <c r="C71" s="12" t="inlineStr"/>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>190TL</t>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>390TL</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr"/>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>12 TL</t>
-        </is>
-      </c>
+      <c r="F71" s="12" t="inlineStr"/>
       <c r="G71" s="12" t="inlineStr"/>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 45 TL</t>
-        </is>
-      </c>
+      <c r="H71" s="12" t="inlineStr"/>
       <c r="I71" s="12" t="inlineStr"/>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>Borcu Yoktur Yazısı</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="inlineStr"/>
-      <c r="C72" s="12" t="inlineStr"/>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr"/>
-      <c r="F72" s="12" t="inlineStr"/>
-      <c r="G72" s="12" t="inlineStr"/>
-      <c r="H72" s="12" t="inlineStr"/>
-      <c r="I72" s="12" t="inlineStr"/>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr"/>
-      <c r="C75" s="12" t="inlineStr"/>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr"/>
+      <c r="C74" s="12" t="inlineStr"/>
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr"/>
-      <c r="F75" s="12" t="inlineStr"/>
-      <c r="G75" s="12" t="inlineStr"/>
-      <c r="H75" s="12" t="inlineStr"/>
-      <c r="I75" s="12" t="inlineStr"/>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr"/>
+      <c r="F74" s="12" t="inlineStr"/>
+      <c r="G74" s="12" t="inlineStr"/>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="inlineStr"/>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr"/>
-      <c r="C78" s="12" t="inlineStr"/>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr"/>
+      <c r="C77" s="12" t="inlineStr"/>
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="E78" s="12" t="inlineStr"/>
-      <c r="F78" s="13" t="inlineStr">
+      <c r="E77" s="12" t="inlineStr"/>
+      <c r="F77" s="13" t="inlineStr">
         <is>
           <t>0.27 TL</t>
         </is>
       </c>
-      <c r="G78" s="12" t="inlineStr"/>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>- / - / 0,27 TL</t>
-        </is>
-      </c>
-      <c r="I78" s="12" t="inlineStr"/>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="G77" s="12" t="inlineStr"/>
+      <c r="H77" s="12" t="inlineStr"/>
+      <c r="I77" s="12" t="inlineStr"/>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
         </is>
       </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>Çek Düzenleme -</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>9.52TL / 0.10%</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr"/>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>290TL / 1.10%</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr"/>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>761,90 TL</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr"/>
+      <c r="H80" s="13" t="inlineStr">
+        <is>
+          <t>104,76 TL / -</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>Çek Düzenleme -</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>9.52TL / 0.10% / 9523.81TL</t>
-        </is>
-      </c>
+          <t>Çek Defteri (Yaprak Başı) -</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr"/>
       <c r="C81" s="12" t="inlineStr"/>
-      <c r="D81" s="13" t="inlineStr">
-        <is>
-          <t>290TL / 1.10%</t>
-        </is>
-      </c>
+      <c r="D81" s="12" t="inlineStr"/>
       <c r="E81" s="12" t="inlineStr"/>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>761,90 TL / 7.619,05 TL / 0.5 %</t>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>2.380,95 TL</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr"/>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t>104,76 TL / -</t>
-        </is>
-      </c>
+      <c r="H81" s="12" t="inlineStr"/>
       <c r="I81" s="12" t="inlineStr"/>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>Çek Defteri (Yaprak Başı) -</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr"/>
-      <c r="C82" s="12" t="inlineStr"/>
-      <c r="D82" s="12" t="inlineStr"/>
-      <c r="E82" s="12" t="inlineStr"/>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>2.380,95 TL</t>
-        </is>
-      </c>
-      <c r="G82" s="12" t="inlineStr"/>
-      <c r="H82" s="12" t="inlineStr"/>
-      <c r="I82" s="12" t="inlineStr"/>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
         </is>
       </c>
-      <c r="B85" s="13" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr"/>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr"/>
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr"/>
-      <c r="F85" s="13" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr"/>
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>380,95 TL</t>
         </is>
       </c>
-      <c r="G85" s="12" t="inlineStr"/>
-      <c r="H85" s="13" t="inlineStr">
+      <c r="G84" s="12" t="inlineStr"/>
+      <c r="H84" s="13" t="inlineStr">
         <is>
           <t>123,81 TL / -</t>
         </is>
       </c>
-      <c r="I85" s="12" t="inlineStr"/>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="I84" s="12" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>Çek Tahsilat Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>45USD</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77%</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr"/>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>714,29 TL</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>260 TL / -</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilat</t>
+          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>45USD / 0.15%</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="inlineStr">
-        <is>
-          <t>590.48TL / 0.77% / 3904.77TL</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr"/>
+          <t>257.15TL</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr"/>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>390TL / 0.2%</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>714,29 TL</t>
-        </is>
-      </c>
-      <c r="G88" s="12" t="inlineStr"/>
-      <c r="H88" s="13" t="inlineStr">
-        <is>
-          <t>25.000 TL / -</t>
-        </is>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>576,19 TL / 0,6 / 3.930,48 TL / -</t>
-        </is>
-      </c>
+          <t>1.666,67 TL</t>
+        </is>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>585,71 TL</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr"/>
+      <c r="I88" s="12" t="inlineStr"/>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
+          <t>Diğer Banka Çeki -</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>257.15TL</t>
+          <t>390.48TL</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr"/>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>2940TL / 1% / 29450TL</t>
-        </is>
-      </c>
-      <c r="E89" s="13" t="inlineStr">
-        <is>
-          <t>390TL / 0.2% / 1950TL</t>
-        </is>
-      </c>
-      <c r="F89" s="13" t="inlineStr">
-        <is>
-          <t>1.666,67 TL / 9.904,77 TL / 0.5 %</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr">
-        <is>
-          <t>585,71 TL / 4.000 TL / 0.8 %</t>
-        </is>
-      </c>
-      <c r="H89" s="13" t="inlineStr">
-        <is>
-          <t>260 TL / -</t>
-        </is>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>576,19 TL / 0,6 / 3.930,48 TL / -</t>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr"/>
+      <c r="F89" s="12" t="inlineStr"/>
+      <c r="G89" s="12" t="inlineStr"/>
+      <c r="H89" s="12" t="inlineStr"/>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>Diğer Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>390.48TL</t>
-        </is>
-      </c>
+          <t>Aynı Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr"/>
       <c r="C90" s="12" t="inlineStr"/>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>350TL</t>
-        </is>
-      </c>
+      <c r="D90" s="12" t="inlineStr"/>
       <c r="E90" s="12" t="inlineStr"/>
       <c r="F90" s="12" t="inlineStr"/>
       <c r="G90" s="12" t="inlineStr"/>
       <c r="H90" s="12" t="inlineStr"/>
-      <c r="I90" s="12" t="inlineStr"/>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>427,62 TL / -</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
@@ -2220,81 +2200,96 @@
       </c>
       <c r="I103" s="12" t="inlineStr"/>
     </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="10" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr"/>
+      <c r="C104" s="12" t="inlineStr"/>
+      <c r="D104" s="12" t="inlineStr"/>
+      <c r="E104" s="12" t="inlineStr"/>
+      <c r="F104" s="12" t="inlineStr"/>
+      <c r="G104" s="12" t="inlineStr"/>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="inlineStr"/>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>HGS</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B106" s="13" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr"/>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="C107" s="12" t="inlineStr"/>
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E106" s="12" t="inlineStr"/>
-      <c r="F106" s="13" t="inlineStr">
+      <c r="E107" s="12" t="inlineStr"/>
+      <c r="F107" s="13" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G106" s="12" t="inlineStr"/>
-      <c r="H106" s="13" t="inlineStr">
-        <is>
-          <t>550 TL / -</t>
-        </is>
-      </c>
-      <c r="I106" s="12" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="14" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 13.08.2026 16:12</t>
+      <c r="G107" s="12" t="inlineStr"/>
+      <c r="H107" s="12" t="inlineStr"/>
+      <c r="I107" s="12" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 13.08.2026 16:28</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A84:I84"/>
-    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A46:I46"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A105:I105"/>
-    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A86:I86"/>
     <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A106:I106"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A83:I83"/>
     <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A59:I59"/>
     <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A79:I79"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -1505,19 +1505,19 @@
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr"/>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="13" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
@@ -2256,7 +2256,7 @@
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>Son güncelleme: 13.08.2026 16:28</t>
+          <t>Son güncelleme: 13.08.2026 16:50</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -62,7 +62,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -97,12 +97,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00003087"/>
         <bgColor rgb="00003087"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +164,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -878,7 +872,7 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>19.94TL</t>
         </is>
@@ -893,12 +887,12 @@
       <c r="G15" s="12" t="inlineStr"/>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>13,92 TL / -</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>19,94 TL / -</t>
+          <t>13,92 TL</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>19,94 TL</t>
         </is>
       </c>
     </row>
@@ -913,7 +907,7 @@
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>398.84TL</t>
         </is>
@@ -929,19 +923,19 @@
           <t>199,42</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>398,84 TL</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>27,62 TL / -</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>398,84 TL / -</t>
+          <t>27,62 TL</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
         </is>
       </c>
     </row>
@@ -983,7 +977,7 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>13,33 TL / -</t>
+          <t>13,33 TL</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr"/>
@@ -1047,7 +1041,7 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -1057,9 +1051,9 @@
       <c r="E22" s="12" t="inlineStr"/>
       <c r="F22" s="12" t="inlineStr"/>
       <c r="G22" s="12" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>7,97 TL / -</t>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>7,97 TL</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr"/>
@@ -1070,7 +1064,7 @@
           <t>FAST - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -1080,9 +1074,9 @@
       <c r="E23" s="12" t="inlineStr"/>
       <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>15,96 TL / -</t>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>15,96 TL</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr"/>
@@ -1114,11 +1108,7 @@
       <c r="E26" s="12" t="inlineStr"/>
       <c r="F26" s="12" t="inlineStr"/>
       <c r="G26" s="12" t="inlineStr"/>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H26" s="12" t="inlineStr"/>
       <c r="I26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -1141,11 +1131,7 @@
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="12" t="inlineStr"/>
       <c r="G27" s="12" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H27" s="12" t="inlineStr"/>
       <c r="I27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1168,11 +1154,7 @@
       <c r="E28" s="12" t="inlineStr"/>
       <c r="F28" s="12" t="inlineStr"/>
       <c r="G28" s="12" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H28" s="12" t="inlineStr"/>
       <c r="I28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -1181,7 +1163,7 @@
           <t>Kasa Depozito - büyük</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
@@ -1191,11 +1173,7 @@
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr"/>
       <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H29" s="12" t="inlineStr"/>
       <c r="I29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -1204,7 +1182,7 @@
           <t>Kasa Depozito - orta</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
@@ -1214,11 +1192,7 @@
       <c r="E30" s="12" t="inlineStr"/>
       <c r="F30" s="12" t="inlineStr"/>
       <c r="G30" s="12" t="inlineStr"/>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H30" s="12" t="inlineStr"/>
       <c r="I30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -1227,7 +1201,7 @@
           <t>Kasa Depozito - küçük</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
@@ -1237,11 +1211,7 @@
       <c r="E31" s="12" t="inlineStr"/>
       <c r="F31" s="12" t="inlineStr"/>
       <c r="G31" s="12" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H31" s="12" t="inlineStr"/>
       <c r="I31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -1403,7 +1373,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>339 TL / -</t>
+          <t>339 TL</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr"/>
@@ -1449,7 +1419,7 @@
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>0,63 TL / -</t>
+          <t>0,63 TL</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr"/>
@@ -1488,7 +1458,7 @@
       <c r="H47" s="12" t="inlineStr"/>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>3 TL / -</t>
+          <t>3 TL</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1674,7 @@
       <c r="G69" s="12" t="inlineStr"/>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>50 TL / -</t>
+          <t>50 TL</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr"/>
@@ -1766,7 +1736,7 @@
       </c>
       <c r="B74" s="12" t="inlineStr"/>
       <c r="C74" s="12" t="inlineStr"/>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
@@ -1774,11 +1744,7 @@
       <c r="E74" s="12" t="inlineStr"/>
       <c r="F74" s="12" t="inlineStr"/>
       <c r="G74" s="12" t="inlineStr"/>
-      <c r="H74" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+      <c r="H74" s="12" t="inlineStr"/>
       <c r="I74" s="12" t="inlineStr"/>
     </row>
     <row r="76" ht="16" customHeight="1">
@@ -1844,7 +1810,7 @@
       <c r="G80" s="12" t="inlineStr"/>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>104,76 TL / -</t>
+          <t>104,76 TL</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr"/>
@@ -1901,7 +1867,7 @@
       <c r="G84" s="12" t="inlineStr"/>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>123,81 TL / -</t>
+          <t>123,81 TL</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr"/>
@@ -1943,14 +1909,10 @@
       <c r="G87" s="12" t="inlineStr"/>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>260 TL / -</t>
-        </is>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
+          <t>260 TL</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="inlineStr"/>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
@@ -2029,7 +1991,7 @@
       <c r="H90" s="12" t="inlineStr"/>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>427,62 TL / -</t>
+          <t>427,62 TL</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2016,7 @@
       <c r="G93" s="12" t="inlineStr"/>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>371,43 TL / -</t>
+          <t>371,43 TL</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr"/>
@@ -2092,7 +2054,7 @@
       <c r="G96" s="12" t="inlineStr"/>
       <c r="H96" s="13" t="inlineStr">
         <is>
-          <t>600 TL / -</t>
+          <t>600 TL</t>
         </is>
       </c>
       <c r="I96" s="12" t="inlineStr"/>
@@ -2130,7 +2092,7 @@
       <c r="G99" s="12" t="inlineStr"/>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>551,43 TL / -</t>
+          <t>551,43 TL</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr"/>
@@ -2161,7 +2123,7 @@
       <c r="G100" s="12" t="inlineStr"/>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>600 TL / -</t>
+          <t>600 TL</t>
         </is>
       </c>
       <c r="I100" s="12" t="inlineStr"/>
@@ -2195,7 +2157,7 @@
       <c r="G103" s="12" t="inlineStr"/>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>600 TL / -</t>
+          <t>600 TL</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr"/>
@@ -2214,7 +2176,7 @@
       <c r="G104" s="12" t="inlineStr"/>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>600 TL / -</t>
+          <t>600 TL</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr"/>
@@ -2256,7 +2218,7 @@
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>Son güncelleme: 13.08.2026 16:50</t>
+          <t>Son güncelleme: 13.08.2026 17:05</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -525,18 +525,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -614,15 +614,15 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>İsme Gelen EFT</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr"/>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>39.87TL</t>
-        </is>
-      </c>
+          <t>Düzenli EFT (0 - 8300 TL)</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>7.97TL</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr"/>
       <c r="D4" s="12" t="inlineStr"/>
       <c r="E4" s="12" t="inlineStr"/>
       <c r="F4" s="12" t="inlineStr"/>
@@ -633,22 +633,18 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Düzenli EFT - 0 - 8.300 TL</t>
+          <t>Düzenli EFT (8300,01 - 399000TL)</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>7.97TL</t>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr"/>
       <c r="D5" s="12" t="inlineStr"/>
       <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>7,97 TL</t>
-        </is>
-      </c>
+      <c r="F5" s="12" t="inlineStr"/>
       <c r="G5" s="12" t="inlineStr"/>
       <c r="H5" s="12" t="inlineStr"/>
       <c r="I5" s="12" t="inlineStr"/>
@@ -656,7 +652,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Düzenli EFT - 399.000,01 TL ve Üzeri</t>
+          <t>Düzenli EFT (399000,01 TL ve üstü)</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -667,11 +663,7 @@
       <c r="C6" s="12" t="inlineStr"/>
       <c r="D6" s="12" t="inlineStr"/>
       <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>199,41 TL</t>
-        </is>
-      </c>
+      <c r="F6" s="12" t="inlineStr"/>
       <c r="G6" s="12" t="inlineStr"/>
       <c r="H6" s="12" t="inlineStr"/>
       <c r="I6" s="12" t="inlineStr"/>
@@ -679,81 +671,88 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>0 - 8.300 TL</t>
+          <t>EFT ATM (0-8300 TL)</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>7.97TL</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>39.87TL</t>
-        </is>
-      </c>
+          <t>27.84TL</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr"/>
       <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>39,87 TL</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>39,87 TL</t>
-        </is>
-      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
       <c r="H7" s="12" t="inlineStr"/>
       <c r="I7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>399.000,01 TL ve Üzeri</t>
+          <t>EFT ATM (8300,01-399000 TL)</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>199.41TL</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>797.68TL</t>
-        </is>
-      </c>
+          <t>55.69TL</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr"/>
       <c r="D8" s="12" t="inlineStr"/>
       <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>797,68 TL</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>797,68 TL</t>
-        </is>
-      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
       <c r="H8" s="12" t="inlineStr"/>
       <c r="I8" s="12" t="inlineStr"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Havale Gönderimi</t>
-        </is>
-      </c>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>EFT ATM (399000 TL ve üstü)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>398.83TL</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr"/>
+      <c r="E9" s="12" t="inlineStr"/>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>EFT Garanti BBVA Mobil / İnternet (0-8300 TL)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>7.97TL</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr"/>
+      <c r="E10" s="12" t="inlineStr"/>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Cebe Para Gönderme</t>
+          <t>EFT Garanti BBVA Mobil / İnternet (8300,01-399000 TL)</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>3.99TL</t>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
@@ -767,223 +766,166 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Düzenli Havale - 0 - 8.300 TL</t>
+          <t>EFT Garanti BBVA Mobil / İnternet (399000 TL ve üstü)</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>3.99TL</t>
+          <t>199.41TL</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>3,99TL</t>
-        </is>
-      </c>
+      <c r="D12" s="12" t="inlineStr"/>
       <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>3,99 TL</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>3,99 TL</t>
-        </is>
-      </c>
+      <c r="F12" s="12" t="inlineStr"/>
+      <c r="G12" s="12" t="inlineStr"/>
       <c r="H12" s="12" t="inlineStr"/>
       <c r="I12" s="12" t="inlineStr"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Düzenli Havale - 399.000,01 TL ve Üzeri</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>99.71TL</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>99,71TL</t>
-        </is>
-      </c>
+          <t>EFT Şube / Müşteri İletişim Merkezi (0- 8300 TL)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr"/>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>39.87TL</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr"/>
       <c r="E13" s="12" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>99,71 TL</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>99,71 TL</t>
-        </is>
-      </c>
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="12" t="inlineStr"/>
       <c r="H13" s="12" t="inlineStr"/>
       <c r="I13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>0 - 8.300 TL</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>3.99TL</t>
-        </is>
-      </c>
+          <t>EFT Şube / Müşteri İletişim Merkezi (8300,01 - 399000 TL)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>19.94TL</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>3,99TL</t>
-        </is>
-      </c>
+          <t>79.76TL</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr"/>
       <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>13,92 TL</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>19,94 TL</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>13,33 TL</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>19,94 TL</t>
-        </is>
-      </c>
+      <c r="F14" s="12" t="inlineStr"/>
+      <c r="G14" s="12" t="inlineStr"/>
+      <c r="H14" s="12" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>399.000,01 TL ve Üzeri</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>99.71TL</t>
-        </is>
-      </c>
+          <t>EFT Şube / Müşteri İletişim Merkezi (399000,01 TL ve üstü)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>398.84TL</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>99,71TL</t>
-        </is>
-      </c>
+          <t>797.68TL</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr"/>
       <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>199,42 TL</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>398,84 TL</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>27,62 TL</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>398,84 TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
+      <c r="F15" s="12" t="inlineStr"/>
+      <c r="G15" s="12" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>EFT Gönderilmesi - 0- 8.300 TL</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr"/>
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>27,84TL</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="inlineStr"/>
+      <c r="G16" s="12" t="inlineStr"/>
+      <c r="H16" s="12" t="inlineStr"/>
+      <c r="I16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>EFT Gönderilmesi - 8.300,01-399.000 TL</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr"/>
+      <c r="C17" s="12" t="inlineStr"/>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>55,69TL</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="12" t="inlineStr"/>
+      <c r="H17" s="12" t="inlineStr"/>
+      <c r="I17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>0 - 8.300 TL</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>7.97TL</t>
-        </is>
-      </c>
+          <t>EFT Gönderilmesi - 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr"/>
       <c r="C18" s="12" t="inlineStr"/>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>7,97TL</t>
+          <t>398,83TL</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr"/>
       <c r="F18" s="12" t="inlineStr"/>
       <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>7,97 TL</t>
-        </is>
-      </c>
+      <c r="H18" s="12" t="inlineStr"/>
       <c r="I18" s="12" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>399.000,01 TL ve Üzeri</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>15.96TL</t>
-        </is>
-      </c>
+          <t>Düzenli EFT / Süpürme Talimatı  Verilmesi- 0-8.300 TL</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr"/>
       <c r="C19" s="12" t="inlineStr"/>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>199,41TL</t>
+          <t>7,97TL</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr"/>
       <c r="F19" s="12" t="inlineStr"/>
       <c r="G19" s="12" t="inlineStr"/>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>15,96 TL</t>
-        </is>
-      </c>
+      <c r="H19" s="12" t="inlineStr"/>
       <c r="I19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>1 - 10 gr</t>
+          <t>Düzenli EFT /Süpürme Talimatı Verilmesi - 8.300,01-399.000 TL</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr"/>
       <c r="C20" s="12" t="inlineStr"/>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>57,5TL</t>
+          <t>15,96TL</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr"/>
@@ -995,14 +937,14 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>11 - 100 gr</t>
+          <t>Düzenli EFT / Süpürme Talimatı Verilmesi - 399.000,01 TL ve Üzeri</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr"/>
       <c r="C21" s="12" t="inlineStr"/>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>115TL</t>
+          <t>199,41TL</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr"/>
@@ -1011,28 +953,55 @@
       <c r="H21" s="12" t="inlineStr"/>
       <c r="I21" s="12" t="inlineStr"/>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Kiralık Kasa</t>
-        </is>
-      </c>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli EFT Talimatı Verilmesi- 0- 8.300 TL</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr"/>
+      <c r="C22" s="12" t="inlineStr"/>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>7,97TL</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="12" t="inlineStr"/>
+      <c r="G22" s="12" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli EFT Talimatı Verilmesi - 8.300,01-399.000 TL</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr"/>
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>15,96TL</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
+      <c r="G23" s="12" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Büyük Boy</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>30000.00TL</t>
-        </is>
-      </c>
+          <t>Düzenli EFT Talimatı Verilmesi - 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr"/>
       <c r="C24" s="12" t="inlineStr"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>4140TL</t>
+          <t>199,41TL</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr"/>
@@ -1044,18 +1013,14 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Küçük Boy</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>22000.00TL</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Diğer Banka Kartlarına 0 – 1.000 TL</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr"/>
       <c r="C25" s="12" t="inlineStr"/>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2610TL</t>
+          <t>4,22TL</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr"/>
@@ -1067,18 +1032,14 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Orta Boy</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>25000.00TL</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Diğer Banka Kartlarına 1.000,01 -2000 TL</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr"/>
       <c r="C26" s="12" t="inlineStr"/>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>3390TL</t>
+          <t>4,22TL</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr"/>
@@ -1090,16 +1051,16 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Depozito - Büyük Boy</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>28570.00TL</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Diğer Banka Kartlarına 10-500 TL (KKKTC)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr"/>
       <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="12" t="inlineStr"/>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>1.35TL</t>
+        </is>
+      </c>
       <c r="E27" s="12" t="inlineStr"/>
       <c r="F27" s="12" t="inlineStr"/>
       <c r="G27" s="12" t="inlineStr"/>
@@ -1109,16 +1070,16 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Depozito - Orta Boy</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>23805.00TL</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Diğer Banka Kartlarına 500,01 -1000 TL (KKTC)</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr"/>
       <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="12" t="inlineStr"/>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>2.70TL</t>
+        </is>
+      </c>
       <c r="E28" s="12" t="inlineStr"/>
       <c r="F28" s="12" t="inlineStr"/>
       <c r="G28" s="12" t="inlineStr"/>
@@ -1128,33 +1089,64 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Depozito - Küçük Boy</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>20950.00TL</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Diğer Banka Kartlarına 1.000,01 -2000 TL (KKTC)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr"/>
       <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="12" t="inlineStr"/>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>4.10TL</t>
+        </is>
+      </c>
       <c r="E29" s="12" t="inlineStr"/>
       <c r="F29" s="12" t="inlineStr"/>
       <c r="G29" s="12" t="inlineStr"/>
       <c r="H29" s="12" t="inlineStr"/>
       <c r="I29" s="12" t="inlineStr"/>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Kıymetli Maden Transferi</t>
-        </is>
-      </c>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den, İnternet'ten ve Asistan'dan EFT-Düzenli EFT (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr"/>
+      <c r="C30" s="12" t="inlineStr"/>
+      <c r="D30" s="12" t="inlineStr"/>
+      <c r="E30" s="12" t="inlineStr"/>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>7,97 TL</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr"/>
+      <c r="H30" s="12" t="inlineStr"/>
+      <c r="I30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den, İnternet'ten ve Asistan'dan EFT - Düzenli EFT (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr"/>
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>15,96 TL</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr"/>
+      <c r="H31" s="12" t="inlineStr"/>
+      <c r="I31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>1 - 10 gr</t>
+          <t>Akbank Mobil'den, İnternet'ten ve Asistan'dan EFT-Düzenli EFT (399.000,01 TL ve Üstü)</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr"/>
@@ -1163,7 +1155,7 @@
       <c r="E32" s="12" t="inlineStr"/>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>60 TL</t>
+          <t>199,41 TL</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr"/>
@@ -1173,7 +1165,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>11 - 100 gr</t>
+          <t>Akbank Mobil'den, İnternet'ten ve Asistan'dan Geç EFT (8.300 TL ve Altı / 16:00 -17:15 arasında)</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr"/>
@@ -1182,248 +1174,370 @@
       <c r="E33" s="12" t="inlineStr"/>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>120 TL</t>
+          <t>7,97 TL</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr"/>
       <c r="H33" s="12" t="inlineStr"/>
       <c r="I33" s="12" t="inlineStr"/>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Kredi Risk Raporu</t>
-        </is>
-      </c>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den, İnternet'ten ve Asistan'dan Geç EFT (8.300,01 TL - 399.000 TL arasında) / 16:00 -17:15 arasında)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr"/>
+      <c r="C34" s="12" t="inlineStr"/>
+      <c r="D34" s="12" t="inlineStr"/>
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>15,96 TL</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr"/>
+      <c r="I34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den, İnternet'ten ve Asistan'dan Geç EFT (399.000,01 TL ve Üstü/ 16:00 -17:15 arasında)</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr"/>
+      <c r="C35" s="12" t="inlineStr"/>
+      <c r="D35" s="12" t="inlineStr"/>
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>199,41 TL</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr"/>
+      <c r="H35" s="12" t="inlineStr"/>
+      <c r="I35" s="12" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Kredi Risk Raporu</t>
+          <t>ATM'den EFT Gönderme ve Başka Banka Kredi Kartı Borcu Ödeme (8.300 TL ve Altı)</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr"/>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>95.24TL</t>
-        </is>
-      </c>
+      <c r="C36" s="12" t="inlineStr"/>
       <c r="D36" s="12" t="inlineStr"/>
       <c r="E36" s="12" t="inlineStr"/>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>65 TL</t>
-        </is>
-      </c>
-      <c r="G36" s="12" t="inlineStr">
-        <is>
-          <t>95,24 TL</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>339 TL</t>
-        </is>
-      </c>
+          <t>27,84 TL</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr"/>
+      <c r="H36" s="12" t="inlineStr"/>
       <c r="I36" s="12" t="inlineStr"/>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>Fatura Ödemeleri</t>
-        </is>
-      </c>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>ATM'den EFT Gönderme ve Başka Banka Kredi Kartı Borcu Ödeme (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr"/>
+      <c r="C37" s="12" t="inlineStr"/>
+      <c r="D37" s="12" t="inlineStr"/>
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>55,69 TL</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr"/>
+      <c r="H37" s="12" t="inlineStr"/>
+      <c r="I37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>ATM'den EFT Gönderme ve Başka Banka Kredi Kartı Borcu Ödeme (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr"/>
+      <c r="C38" s="12" t="inlineStr"/>
+      <c r="D38" s="12" t="inlineStr"/>
+      <c r="E38" s="12" t="inlineStr"/>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>398,83 TL</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr"/>
+      <c r="I38" s="12" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>Fatura Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>5.00TL / 3.50%</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>0.00TL</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
+          <t>Müşteri İletişim Merkezi'den EFT ve Başka Banka Kredi Kartı Borcu Ödeme (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr"/>
+      <c r="C39" s="12" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr"/>
       <c r="E39" s="12" t="inlineStr"/>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>0.5 TL</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>0.5 TL</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>0,63 TL</t>
-        </is>
-      </c>
+          <t>39,87 TL</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr"/>
+      <c r="H39" s="12" t="inlineStr"/>
       <c r="I39" s="12" t="inlineStr"/>
     </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>SGK Prim Ödemeleri</t>
-        </is>
-      </c>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Müşteri İletişim Merkezi'den EFT ve Başka Banka Kredi Kartı Borcu Ödeme (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr"/>
+      <c r="C40" s="12" t="inlineStr"/>
+      <c r="D40" s="12" t="inlineStr"/>
+      <c r="E40" s="12" t="inlineStr"/>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>79,76 TL</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr"/>
+      <c r="H40" s="12" t="inlineStr"/>
+      <c r="I40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Müşteri İletişim Merkezi'den EFT ve Başka Banka Kredi Kartı Borcu Ödeme (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr"/>
+      <c r="C41" s="12" t="inlineStr"/>
+      <c r="D41" s="12" t="inlineStr"/>
+      <c r="E41" s="12" t="inlineStr"/>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>797,68 TL</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr"/>
+      <c r="H41" s="12" t="inlineStr"/>
+      <c r="I41" s="12" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>SGK Prim Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>3.50TL / 3.50%</t>
-        </is>
-      </c>
+          <t>Şubeden Hesaptan &amp; Nakit  Gönderilen EFT/İleri Vadeli EFT (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr"/>
       <c r="C42" s="12" t="inlineStr"/>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>422TL</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>2 TL / 3,5%</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr"/>
+      <c r="E42" s="12" t="inlineStr"/>
+      <c r="F42" s="12" t="inlineStr"/>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>39,87 TL</t>
+        </is>
+      </c>
       <c r="H42" s="12" t="inlineStr"/>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>3 TL</t>
-        </is>
-      </c>
+      <c r="I42" s="12" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Orta Boy</t>
+          <t>Şubeden Hesaptan &amp; Nakit Gönderilen  EFT/İleri Vadeli  EFT (8.300,01 TL - 399.000 TL arasında)</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr"/>
       <c r="C43" s="12" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>422TL</t>
-        </is>
-      </c>
+      <c r="D43" s="12" t="inlineStr"/>
       <c r="E43" s="12" t="inlineStr"/>
       <c r="F43" s="12" t="inlineStr"/>
-      <c r="G43" s="12" t="inlineStr"/>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>79,76 TL</t>
+        </is>
+      </c>
       <c r="H43" s="12" t="inlineStr"/>
       <c r="I43" s="12" t="inlineStr"/>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>HGS</t>
-        </is>
-      </c>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Şubeden Hesaptan &amp; Nakit  Gönderilen EFT/İleri Vadeli  EFT (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr"/>
+      <c r="C44" s="12" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>797,68 TL</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr"/>
+      <c r="I44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Şubeden Geç EFT (Hesaptan/Kasadan - Hesaba/isme/Kredi Kartına Yapılan EFT'ler) (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr"/>
+      <c r="C45" s="12" t="inlineStr"/>
+      <c r="D45" s="12" t="inlineStr"/>
+      <c r="E45" s="12" t="inlineStr"/>
+      <c r="F45" s="12" t="inlineStr"/>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>39,87 TL</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr"/>
+      <c r="I45" s="12" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>HGS Etiket/Kart Bedeli</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>550.00TL</t>
-        </is>
-      </c>
+          <t>Şubeden Geç EFT (Hesaptan/Kasadan - Hesaba/isme/Kredi Kartına Yapılan EFT'ler) (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr"/>
       <c r="C46" s="12" t="inlineStr"/>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>550TL</t>
-        </is>
-      </c>
+      <c r="D46" s="12" t="inlineStr"/>
       <c r="E46" s="12" t="inlineStr"/>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>500 TL</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr"/>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>275 TL</t>
-        </is>
-      </c>
+      <c r="F46" s="12" t="inlineStr"/>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>79,76 TL</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr"/>
       <c r="I46" s="12" t="inlineStr"/>
     </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Şans Oyunu Ödemeleri</t>
-        </is>
-      </c>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Şubeden Geç EFT (Hesaptan/Kasadan - Hesaba/isme/Kredi Kartına Yapılan EFT'ler) (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr"/>
+      <c r="C47" s="12" t="inlineStr"/>
+      <c r="D47" s="12" t="inlineStr"/>
+      <c r="E47" s="12" t="inlineStr"/>
+      <c r="F47" s="12" t="inlineStr"/>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>797,68 TL</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr"/>
+      <c r="I47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Bireysel Kredi Kartından Anlık EFT İşlem Ücreti</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr"/>
+      <c r="C48" s="12" t="inlineStr"/>
+      <c r="D48" s="12" t="inlineStr"/>
+      <c r="E48" s="12" t="inlineStr"/>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>7,97 TL / 1 %</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr"/>
+      <c r="H48" s="12" t="inlineStr"/>
+      <c r="I48" s="12" t="inlineStr"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>Şans Oyunu Ödemeleri</t>
+          <t>Bireysel Kredi Kartından Talimatlı EFT İşlem Ücreti</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr"/>
       <c r="C49" s="12" t="inlineStr"/>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>26TL</t>
-        </is>
-      </c>
+      <c r="D49" s="12" t="inlineStr"/>
       <c r="E49" s="12" t="inlineStr"/>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>38,10 TL</t>
+          <t>7,97 TL / 1 %</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr"/>
       <c r="H49" s="12" t="inlineStr"/>
       <c r="I49" s="12" t="inlineStr"/>
     </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>Aidat Ödemeleri</t>
-        </is>
-      </c>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Müşteri İletişim Merkezi'den Geç EFT ve Başka Banka Kredi Kartı Borcu Ödeme (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr"/>
+      <c r="C50" s="12" t="inlineStr"/>
+      <c r="D50" s="12" t="inlineStr"/>
+      <c r="E50" s="12" t="inlineStr"/>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>39,87 TL</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr"/>
+      <c r="I50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Müşteri İletişim Merkezi'den Geç EFT ve Başka Banka Kredi Kartı Borcu Ödeme (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr"/>
+      <c r="C51" s="12" t="inlineStr"/>
+      <c r="D51" s="12" t="inlineStr"/>
+      <c r="E51" s="12" t="inlineStr"/>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>79,76 TL</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr"/>
+      <c r="H51" s="12" t="inlineStr"/>
+      <c r="I51" s="12" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>Aidat Ödemeleri</t>
+          <t>Müşteri İletişim Merkezi'den Geç EFT ve Başka Banka Kredi Kartı Borcu Ödeme (399.000,01 TL ve Üstü</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr"/>
       <c r="C52" s="12" t="inlineStr"/>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
+      <c r="D52" s="12" t="inlineStr"/>
       <c r="E52" s="12" t="inlineStr"/>
-      <c r="F52" s="12" t="inlineStr"/>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>797,68 TL</t>
+        </is>
+      </c>
       <c r="G52" s="12" t="inlineStr"/>
       <c r="H52" s="12" t="inlineStr"/>
       <c r="I52" s="12" t="inlineStr"/>
@@ -1431,142 +1545,250 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Özel Okul Ödemeleri</t>
+          <t>Havale Gönderimi</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>Özel Okul Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="inlineStr"/>
+          <t>Cebe Para Gönderme Garanti BBVA ATM</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>13.92TL</t>
+        </is>
+      </c>
       <c r="C55" s="12" t="inlineStr"/>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
+      <c r="D55" s="12" t="inlineStr"/>
       <c r="E55" s="12" t="inlineStr"/>
       <c r="F55" s="12" t="inlineStr"/>
       <c r="G55" s="12" t="inlineStr"/>
       <c r="H55" s="12" t="inlineStr"/>
       <c r="I55" s="12" t="inlineStr"/>
     </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>Telefon Ödemeleri</t>
-        </is>
-      </c>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Cebe Para Gönderme Mobil / İnternet</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>3.99TL</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr"/>
+      <c r="D56" s="12" t="inlineStr"/>
+      <c r="E56" s="12" t="inlineStr"/>
+      <c r="F56" s="12" t="inlineStr"/>
+      <c r="G56" s="12" t="inlineStr"/>
+      <c r="H56" s="12" t="inlineStr"/>
+      <c r="I56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli Havale (0 - 8300 TL)</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>3.99TL</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr"/>
+      <c r="D57" s="12" t="inlineStr"/>
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="12" t="inlineStr"/>
+      <c r="G57" s="12" t="inlineStr"/>
+      <c r="H57" s="12" t="inlineStr"/>
+      <c r="I57" s="12" t="inlineStr"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>Telefon Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr"/>
+          <t>Düzenli Havale  (8300,01 - 399000 TL)</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>7.98TL</t>
+        </is>
+      </c>
       <c r="C58" s="12" t="inlineStr"/>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
+      <c r="D58" s="12" t="inlineStr"/>
       <c r="E58" s="12" t="inlineStr"/>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>1 %</t>
-        </is>
-      </c>
+      <c r="F58" s="12" t="inlineStr"/>
       <c r="G58" s="12" t="inlineStr"/>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>1.238,09 TL</t>
-        </is>
-      </c>
+      <c r="H58" s="12" t="inlineStr"/>
       <c r="I58" s="12" t="inlineStr"/>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Vergi Tahsilat</t>
-        </is>
-      </c>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli Havale (399000,01 TL ve üstü)</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>99.71TL</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr"/>
+      <c r="E59" s="12" t="inlineStr"/>
+      <c r="F59" s="12" t="inlineStr"/>
+      <c r="G59" s="12" t="inlineStr"/>
+      <c r="H59" s="12" t="inlineStr"/>
+      <c r="I59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Havale ATM (0-8300 TL)</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>13.92TL</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr"/>
+      <c r="D60" s="12" t="inlineStr"/>
+      <c r="E60" s="12" t="inlineStr"/>
+      <c r="F60" s="12" t="inlineStr"/>
+      <c r="G60" s="12" t="inlineStr"/>
+      <c r="H60" s="12" t="inlineStr"/>
+      <c r="I60" s="12" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>Vergi Tahsilat</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="inlineStr"/>
+          <t>Havale ATM (8300,01-399000 TL)</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>27.85TL</t>
+        </is>
+      </c>
       <c r="C61" s="12" t="inlineStr"/>
       <c r="D61" s="12" t="inlineStr"/>
       <c r="E61" s="12" t="inlineStr"/>
       <c r="F61" s="12" t="inlineStr"/>
       <c r="G61" s="12" t="inlineStr"/>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>50 TL</t>
-        </is>
-      </c>
+      <c r="H61" s="12" t="inlineStr"/>
       <c r="I61" s="12" t="inlineStr"/>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>Arşiv Araştırma</t>
-        </is>
-      </c>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Havale ATM (399000,01 TL ve üstü)</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>199.42TL</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr"/>
+      <c r="D62" s="12" t="inlineStr"/>
+      <c r="E62" s="12" t="inlineStr"/>
+      <c r="F62" s="12" t="inlineStr"/>
+      <c r="G62" s="12" t="inlineStr"/>
+      <c r="H62" s="12" t="inlineStr"/>
+      <c r="I62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Havale Mobil / Internet (0-8300 TL)</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>3.99TL</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr"/>
+      <c r="D63" s="12" t="inlineStr"/>
+      <c r="E63" s="12" t="inlineStr"/>
+      <c r="F63" s="12" t="inlineStr"/>
+      <c r="G63" s="12" t="inlineStr"/>
+      <c r="H63" s="12" t="inlineStr"/>
+      <c r="I63" s="12" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>Arşiv Araştırma Ücreti</t>
+          <t>Havale Mobil / İnternet  (8300,01-399000 TL)</t>
         </is>
       </c>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>287.62TL</t>
+          <t>7.98TL</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr"/>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>4.20TL</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>250TL</t>
-        </is>
-      </c>
+      <c r="D64" s="12" t="inlineStr"/>
+      <c r="E64" s="12" t="inlineStr"/>
       <c r="F64" s="12" t="inlineStr"/>
       <c r="G64" s="12" t="inlineStr"/>
       <c r="H64" s="12" t="inlineStr"/>
       <c r="I64" s="12" t="inlineStr"/>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Mevduat Araştırma</t>
-        </is>
-      </c>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Havale Mobil / İnternet (399000,01 TL ve üstü)</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>99.71TL</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr"/>
+      <c r="D65" s="12" t="inlineStr"/>
+      <c r="E65" s="12" t="inlineStr"/>
+      <c r="F65" s="12" t="inlineStr"/>
+      <c r="G65" s="12" t="inlineStr"/>
+      <c r="H65" s="12" t="inlineStr"/>
+      <c r="I65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Havale Şube / Müşteri İletişim Merkezi (0 - 8300 TL)</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr"/>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>19.94TL</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr"/>
+      <c r="E66" s="12" t="inlineStr"/>
+      <c r="F66" s="12" t="inlineStr"/>
+      <c r="G66" s="12" t="inlineStr"/>
+      <c r="H66" s="12" t="inlineStr"/>
+      <c r="I66" s="12" t="inlineStr"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>Mutabakat/Teyit Yazısı</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>150USD</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr"/>
+          <t>Havale Şube / Müşteri İletişim Merkezi (8300,01 - 399000 TL)</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr"/>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>39.88TL</t>
+        </is>
+      </c>
       <c r="D67" s="12" t="inlineStr"/>
       <c r="E67" s="12" t="inlineStr"/>
       <c r="F67" s="12" t="inlineStr"/>
@@ -1577,83 +1799,94 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>Referans Mektubu</t>
+          <t>Havale Sube / Musteri Iletisim Merkezi (399000,01 TL ve ustu)</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>4000.00TL</t>
+          <t>398.84TL</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr"/>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>770TL</t>
-        </is>
-      </c>
+      <c r="D68" s="12" t="inlineStr"/>
       <c r="E68" s="12" t="inlineStr"/>
       <c r="F68" s="12" t="inlineStr"/>
       <c r="G68" s="12" t="inlineStr"/>
-      <c r="H68" s="12" t="inlineStr">
-        <is>
-          <t>50 TL</t>
-        </is>
-      </c>
+      <c r="H68" s="12" t="inlineStr"/>
       <c r="I68" s="12" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>Hesap Özeti</t>
+          <t>Havale Gönderilmesi - 0-8.300 TL</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr"/>
       <c r="C69" s="12" t="inlineStr"/>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>190TL</t>
+          <t>3,99TL</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr"/>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>12 TL</t>
-        </is>
-      </c>
+      <c r="F69" s="12" t="inlineStr"/>
       <c r="G69" s="12" t="inlineStr"/>
-      <c r="H69" s="12" t="inlineStr">
-        <is>
-          <t>45 TL</t>
-        </is>
-      </c>
+      <c r="H69" s="12" t="inlineStr"/>
       <c r="I69" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>Bakiye Sorgulama - ATM</t>
-        </is>
-      </c>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>Havale Gönderilmesi - 8.300,01- 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr"/>
+      <c r="C70" s="12" t="inlineStr"/>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>39,88TL</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr"/>
+      <c r="F70" s="12" t="inlineStr"/>
+      <c r="G70" s="12" t="inlineStr"/>
+      <c r="H70" s="12" t="inlineStr"/>
+      <c r="I70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>Havale Gönderilmesi - 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr"/>
+      <c r="C71" s="12" t="inlineStr"/>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>99,71TL</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr"/>
+      <c r="F71" s="12" t="inlineStr"/>
+      <c r="G71" s="12" t="inlineStr"/>
+      <c r="H71" s="12" t="inlineStr"/>
+      <c r="I71" s="12" t="inlineStr"/>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>Yurtiçi ATM Bakiye Sorgulama</t>
+          <t>Düzenli Havale / Süpürme Talimatı Verilmesi- 0-8.300 TL</t>
         </is>
       </c>
       <c r="B72" s="12" t="inlineStr"/>
       <c r="C72" s="12" t="inlineStr"/>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.41TL</t>
+          <t>3,99TL</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr"/>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>0.27 TL</t>
-        </is>
-      </c>
+      <c r="F72" s="12" t="inlineStr"/>
       <c r="G72" s="12" t="inlineStr"/>
       <c r="H72" s="12" t="inlineStr"/>
       <c r="I72" s="12" t="inlineStr"/>
@@ -1661,14 +1894,14 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>Yurtdışı ATM Bakiye Sorgulama</t>
+          <t>Düzenli Havale / Süpürme Talimatı Verilmesi - 8.300,01-399.000 TL</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr"/>
       <c r="C73" s="12" t="inlineStr"/>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.45EUR</t>
+          <t>7,98TL</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr"/>
@@ -1677,214 +1910,247 @@
       <c r="H73" s="12" t="inlineStr"/>
       <c r="I73" s="12" t="inlineStr"/>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Çek Defteri ve Düzenleme</t>
-        </is>
-      </c>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli Havale / Süpürme Talimatı Verilmesi - 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr"/>
+      <c r="C74" s="12" t="inlineStr"/>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>99,71TL</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr"/>
+      <c r="F74" s="12" t="inlineStr"/>
+      <c r="G74" s="12" t="inlineStr"/>
+      <c r="H74" s="12" t="inlineStr"/>
+      <c r="I74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>TC-KKTC/KKTC-TC Şubeleri Arası Havale</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr"/>
+      <c r="C75" s="12" t="inlineStr"/>
+      <c r="D75" s="12" t="inlineStr"/>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>125TL</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr"/>
+      <c r="G75" s="12" t="inlineStr"/>
+      <c r="H75" s="12" t="inlineStr"/>
+      <c r="I75" s="12" t="inlineStr"/>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>Çek Düzenleme</t>
+          <t>Havale Gönderilmesi - 8.300,01-399.000 TL</t>
         </is>
       </c>
       <c r="B76" s="12" t="inlineStr"/>
       <c r="C76" s="12" t="inlineStr"/>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>290TL / 1.10%</t>
+          <t>7,98TL</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr"/>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>761,90 TL</t>
-        </is>
-      </c>
+      <c r="F76" s="12" t="inlineStr"/>
       <c r="G76" s="12" t="inlineStr"/>
-      <c r="H76" s="12" t="inlineStr">
-        <is>
-          <t>104,76 TL</t>
-        </is>
-      </c>
+      <c r="H76" s="12" t="inlineStr"/>
       <c r="I76" s="12" t="inlineStr"/>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>Çek Defteri (Yaprak Başı)</t>
+          <t>Düzenli Havale Talimatı Verilmesi- 0-8.300 TL</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr"/>
       <c r="C77" s="12" t="inlineStr"/>
-      <c r="D77" s="12" t="inlineStr"/>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>3,99TL</t>
+        </is>
+      </c>
       <c r="E77" s="12" t="inlineStr"/>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>2.380,95 TL</t>
-        </is>
-      </c>
+      <c r="F77" s="12" t="inlineStr"/>
       <c r="G77" s="12" t="inlineStr"/>
       <c r="H77" s="12" t="inlineStr"/>
       <c r="I77" s="12" t="inlineStr"/>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Çek Tahsilat</t>
-        </is>
-      </c>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli Havale Talimatı Verilmesi - 8.300,01-399.000 TL</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr"/>
+      <c r="C78" s="12" t="inlineStr"/>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>7,98TL</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr"/>
+      <c r="F78" s="12" t="inlineStr"/>
+      <c r="G78" s="12" t="inlineStr"/>
+      <c r="H78" s="12" t="inlineStr"/>
+      <c r="I78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Düzenli Havale Talimatı Verilmesi - 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr"/>
+      <c r="C79" s="12" t="inlineStr"/>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>99,71TL</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr"/>
+      <c r="F79" s="12" t="inlineStr"/>
+      <c r="G79" s="12" t="inlineStr"/>
+      <c r="H79" s="12" t="inlineStr"/>
+      <c r="I79" s="12" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>Diğer Banka Çeki</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>390.48TL</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>590.48TL / 0.77%</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Bankamız Diğer Kartlarına 0 – 1.000 TL</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr"/>
+      <c r="C80" s="12" t="inlineStr"/>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>1543TL</t>
+          <t>0.57TL</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr"/>
       <c r="F80" s="12" t="inlineStr"/>
       <c r="G80" s="12" t="inlineStr"/>
       <c r="H80" s="12" t="inlineStr"/>
-      <c r="I80" s="12" t="inlineStr">
-        <is>
-          <t>576,19 TL / 0,8</t>
-        </is>
-      </c>
+      <c r="I80" s="12" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>Aynı Banka Çeki</t>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Bankamız Diğer Kartlarına 1.000,01 -2000 TL</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr"/>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>438.10TL</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr"/>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>390TL / 0.2%</t>
-        </is>
-      </c>
+      <c r="C81" s="12" t="inlineStr"/>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>1.14TL</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr"/>
       <c r="F81" s="12" t="inlineStr"/>
       <c r="G81" s="12" t="inlineStr"/>
       <c r="H81" s="12" t="inlineStr"/>
-      <c r="I81" s="12" t="inlineStr">
-        <is>
-          <t>427,62 TL</t>
-        </is>
-      </c>
+      <c r="I81" s="12" t="inlineStr"/>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilat</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>45USD</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Bankamız Diğer Kartlarına 10-500 TL (KKKTC)</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr"/>
       <c r="C82" s="12" t="inlineStr"/>
-      <c r="D82" s="12" t="inlineStr"/>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>1.35TL</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr"/>
+      <c r="F82" s="12" t="inlineStr"/>
       <c r="G82" s="12" t="inlineStr"/>
-      <c r="H82" s="12" t="inlineStr">
-        <is>
-          <t>25.000 TL</t>
-        </is>
-      </c>
+      <c r="H82" s="12" t="inlineStr"/>
       <c r="I82" s="12" t="inlineStr"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>Döviz Çeki Tahsilatı</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>257.15TL</t>
-        </is>
-      </c>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Bankamız Diğer Kartlarına 500,01 -1000 TL (KKTC)</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr"/>
       <c r="C83" s="12" t="inlineStr"/>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>1040TL / 0.5%</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>780TL / 0.6%</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G83" s="12" t="inlineStr">
-        <is>
-          <t>585,71 TL</t>
-        </is>
-      </c>
-      <c r="H83" s="12" t="inlineStr">
-        <is>
-          <t>260 TL</t>
-        </is>
-      </c>
+          <t>2.70TL</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr"/>
+      <c r="F83" s="12" t="inlineStr"/>
+      <c r="G83" s="12" t="inlineStr"/>
+      <c r="H83" s="12" t="inlineStr"/>
       <c r="I83" s="12" t="inlineStr"/>
     </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Çek Belgelendirme</t>
-        </is>
-      </c>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Ticari Bankamatik/Ön Ödemeli Kartlardan Bankamız Diğer Kartlarına 1.000,01 -2000 TL (KKTC)</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr"/>
+      <c r="C84" s="12" t="inlineStr"/>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>4.1TL</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr"/>
+      <c r="F84" s="12" t="inlineStr"/>
+      <c r="G84" s="12" t="inlineStr"/>
+      <c r="H84" s="12" t="inlineStr"/>
+      <c r="I84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>Kartlı / Kartsız Para Gönderilmesi - 0-8.300 TL</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr"/>
+      <c r="C85" s="12" t="inlineStr"/>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>13,92TL</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr"/>
+      <c r="F85" s="12" t="inlineStr"/>
+      <c r="G85" s="12" t="inlineStr"/>
+      <c r="H85" s="12" t="inlineStr"/>
+      <c r="I85" s="12" t="inlineStr"/>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>Çek Düzeltme Hakkı</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>390.48TL / 0.58%</t>
-        </is>
-      </c>
+          <t>Kartlı / Kartsız Para Gönderilmesi - 8.300,01-399.000 TL</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr"/>
       <c r="C86" s="12" t="inlineStr"/>
-      <c r="D86" s="12" t="inlineStr"/>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>27,85TL</t>
+        </is>
+      </c>
       <c r="E86" s="12" t="inlineStr"/>
       <c r="F86" s="12" t="inlineStr"/>
       <c r="G86" s="12" t="inlineStr"/>
@@ -1894,214 +2160,3827 @@
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>Karşılıksız Çek Belgelendirme</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>390.48TL</t>
-        </is>
-      </c>
+          <t>Kartlı / Kartsız Para Gönderilmesi -  399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr"/>
       <c r="C87" s="12" t="inlineStr"/>
-      <c r="D87" s="12" t="inlineStr"/>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>199,42TL</t>
+        </is>
+      </c>
       <c r="E87" s="12" t="inlineStr"/>
       <c r="F87" s="12" t="inlineStr"/>
       <c r="G87" s="12" t="inlineStr"/>
-      <c r="H87" s="12" t="inlineStr">
-        <is>
-          <t>371,43 TL</t>
-        </is>
-      </c>
-      <c r="I87" s="12" t="inlineStr">
-        <is>
-          <t>576,19 TL / 0,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Senet İade</t>
-        </is>
-      </c>
+      <c r="H87" s="12" t="inlineStr"/>
+      <c r="I87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>İş Bankası İle Ödeme</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr"/>
+      <c r="C88" s="12" t="inlineStr"/>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr"/>
+      <c r="F88" s="12" t="inlineStr"/>
+      <c r="G88" s="12" t="inlineStr"/>
+      <c r="H88" s="12" t="inlineStr"/>
+      <c r="I88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>İşlem Ücreti</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr"/>
+      <c r="C89" s="12" t="inlineStr"/>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr"/>
+      <c r="F89" s="12" t="inlineStr"/>
+      <c r="G89" s="12" t="inlineStr"/>
+      <c r="H89" s="12" t="inlineStr"/>
+      <c r="I89" s="12" t="inlineStr"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>Senet İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>495.24TL</t>
-        </is>
-      </c>
+          <t>Akbank Mobil'den ve İnternet'ten Hesaptan Hesaba / İsme TL ve YP Havale-Düzenli Havale (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr"/>
       <c r="C90" s="12" t="inlineStr"/>
       <c r="D90" s="12" t="inlineStr"/>
       <c r="E90" s="12" t="inlineStr"/>
-      <c r="F90" s="12" t="inlineStr"/>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
       <c r="G90" s="12" t="inlineStr"/>
-      <c r="H90" s="12" t="inlineStr">
-        <is>
-          <t>600 TL</t>
-        </is>
-      </c>
+      <c r="H90" s="12" t="inlineStr"/>
       <c r="I90" s="12" t="inlineStr"/>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Senet Protesto</t>
-        </is>
-      </c>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den ve İnternet'ten Hesaptan Hesaba / İsme TL ve YP Havale-Düzenli Havale (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr"/>
+      <c r="C91" s="12" t="inlineStr"/>
+      <c r="D91" s="12" t="inlineStr"/>
+      <c r="E91" s="12" t="inlineStr"/>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>7,98 TL</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr"/>
+      <c r="H91" s="12" t="inlineStr"/>
+      <c r="I91" s="12" t="inlineStr"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den ve İnternet'ten Hesaptan Hesaba / İsme TL ve YP Havale-Düzenli Havale (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr"/>
+      <c r="C92" s="12" t="inlineStr"/>
+      <c r="D92" s="12" t="inlineStr"/>
+      <c r="E92" s="12" t="inlineStr"/>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="G92" s="12" t="inlineStr"/>
+      <c r="H92" s="12" t="inlineStr"/>
+      <c r="I92" s="12" t="inlineStr"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Senet Protesto Kaldırma</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>533.34TL</t>
-        </is>
-      </c>
+          <t>Müşteri İletişim Merkezi'nden Hesaptan Hesaba / İsme TL ve YP Havale (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr"/>
       <c r="C93" s="12" t="inlineStr"/>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
+      <c r="D93" s="12" t="inlineStr"/>
       <c r="E93" s="12" t="inlineStr"/>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>619,05 TL</t>
+          <t>19,94 TL</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr"/>
-      <c r="H93" s="12" t="inlineStr">
-        <is>
-          <t>551,43 TL</t>
-        </is>
-      </c>
+      <c r="H93" s="12" t="inlineStr"/>
       <c r="I93" s="12" t="inlineStr"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>Senet Protesto Ücreti</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
+          <t>Müşteri İletişim Merkezi'nden Hesaptan Hesaba / İsme TL ve YP Havale (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr"/>
       <c r="C94" s="12" t="inlineStr"/>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
+      <c r="D94" s="12" t="inlineStr"/>
       <c r="E94" s="12" t="inlineStr"/>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>666,67 TL</t>
+          <t>39,88 TL</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr"/>
-      <c r="H94" s="12" t="inlineStr">
-        <is>
-          <t>600 TL</t>
-        </is>
-      </c>
+      <c r="H94" s="12" t="inlineStr"/>
       <c r="I94" s="12" t="inlineStr"/>
     </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Senet Tahsil</t>
-        </is>
-      </c>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>Müşteri İletişim Merkezi'nden Hesaptan Hesaba / İsme TL ve YP Havale (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr"/>
+      <c r="C95" s="12" t="inlineStr"/>
+      <c r="D95" s="12" t="inlineStr"/>
+      <c r="E95" s="12" t="inlineStr"/>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr"/>
+      <c r="H95" s="12" t="inlineStr"/>
+      <c r="I95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den Havale (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr"/>
+      <c r="C96" s="12" t="inlineStr"/>
+      <c r="D96" s="12" t="inlineStr"/>
+      <c r="E96" s="12" t="inlineStr"/>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>13,92 TL</t>
+        </is>
+      </c>
+      <c r="G96" s="12" t="inlineStr"/>
+      <c r="H96" s="12" t="inlineStr"/>
+      <c r="I96" s="12" t="inlineStr"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Muhabir Banka Senet Tahsili</t>
+          <t>ATM/BTM'den Havale (8.300,01 TL - 399.000 TL arasında)</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr"/>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
+      <c r="C97" s="12" t="inlineStr"/>
       <c r="D97" s="12" t="inlineStr"/>
       <c r="E97" s="12" t="inlineStr"/>
-      <c r="F97" s="12" t="inlineStr"/>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>27,85 TL</t>
+        </is>
+      </c>
       <c r="G97" s="12" t="inlineStr"/>
-      <c r="H97" s="12" t="inlineStr">
-        <is>
-          <t>600 TL</t>
-        </is>
-      </c>
+      <c r="H97" s="12" t="inlineStr"/>
       <c r="I97" s="12" t="inlineStr"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Aynı Banka Senet Tahsili</t>
+          <t>ATM/BTM'den Havale (399.000,01 TL ve Üstü)</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr"/>
       <c r="C98" s="12" t="inlineStr"/>
       <c r="D98" s="12" t="inlineStr"/>
       <c r="E98" s="12" t="inlineStr"/>
-      <c r="F98" s="12" t="inlineStr"/>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>199,42</t>
+        </is>
+      </c>
       <c r="G98" s="12" t="inlineStr"/>
-      <c r="H98" s="12" t="inlineStr">
+      <c r="H98" s="12" t="inlineStr"/>
+      <c r="I98" s="12" t="inlineStr"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>ATM'den Cebe Havale (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr"/>
+      <c r="C99" s="12" t="inlineStr"/>
+      <c r="D99" s="12" t="inlineStr"/>
+      <c r="E99" s="12" t="inlineStr"/>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>13,92 TL</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr"/>
+      <c r="H99" s="12" t="inlineStr"/>
+      <c r="I99" s="12" t="inlineStr"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>ATM'den Cebe Havale (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr"/>
+      <c r="C100" s="12" t="inlineStr"/>
+      <c r="D100" s="12" t="inlineStr"/>
+      <c r="E100" s="12" t="inlineStr"/>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>27,85 TL</t>
+        </is>
+      </c>
+      <c r="G100" s="12" t="inlineStr"/>
+      <c r="H100" s="12" t="inlineStr"/>
+      <c r="I100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>ATM'den Cebe Havale (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr"/>
+      <c r="C101" s="12" t="inlineStr"/>
+      <c r="D101" s="12" t="inlineStr"/>
+      <c r="E101" s="12" t="inlineStr"/>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>199,42</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr"/>
+      <c r="H101" s="12" t="inlineStr"/>
+      <c r="I101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den kartlı para yatırma (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr"/>
+      <c r="C102" s="12" t="inlineStr"/>
+      <c r="D102" s="12" t="inlineStr"/>
+      <c r="E102" s="12" t="inlineStr"/>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>13,92 TL</t>
+        </is>
+      </c>
+      <c r="G102" s="12" t="inlineStr"/>
+      <c r="H102" s="12" t="inlineStr"/>
+      <c r="I102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den kartlı para yatırma (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr"/>
+      <c r="C103" s="12" t="inlineStr"/>
+      <c r="D103" s="12" t="inlineStr"/>
+      <c r="E103" s="12" t="inlineStr"/>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>27,85 TL</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr"/>
+      <c r="H103" s="12" t="inlineStr"/>
+      <c r="I103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den kartlı para yatırma (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr"/>
+      <c r="C104" s="12" t="inlineStr"/>
+      <c r="D104" s="12" t="inlineStr"/>
+      <c r="E104" s="12" t="inlineStr"/>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>199,42 TL</t>
+        </is>
+      </c>
+      <c r="G104" s="12" t="inlineStr"/>
+      <c r="H104" s="12" t="inlineStr"/>
+      <c r="I104" s="12" t="inlineStr"/>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den ve İnternet'ten Cep Telefonu Numarası İle Hesaba / ATM'ye Para Transferi (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr"/>
+      <c r="C105" s="12" t="inlineStr"/>
+      <c r="D105" s="12" t="inlineStr"/>
+      <c r="E105" s="12" t="inlineStr"/>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr"/>
+      <c r="H105" s="12" t="inlineStr"/>
+      <c r="I105" s="12" t="inlineStr"/>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den ve İnternet'ten Cep Telefonu Numarası İle Hesaba / ATM'ye Para Transferi (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr"/>
+      <c r="C106" s="12" t="inlineStr"/>
+      <c r="D106" s="12" t="inlineStr"/>
+      <c r="E106" s="12" t="inlineStr"/>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>7,98 TL</t>
+        </is>
+      </c>
+      <c r="G106" s="12" t="inlineStr"/>
+      <c r="H106" s="12" t="inlineStr"/>
+      <c r="I106" s="12" t="inlineStr"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil'den ve İnternet'ten Cep Telefonu Numarası İle Hesaba / ATM'ye Para Transferi (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr"/>
+      <c r="C107" s="12" t="inlineStr"/>
+      <c r="D107" s="12" t="inlineStr"/>
+      <c r="E107" s="12" t="inlineStr"/>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="G107" s="12" t="inlineStr"/>
+      <c r="H107" s="12" t="inlineStr"/>
+      <c r="I107" s="12" t="inlineStr"/>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den Kartsız Para Yatırma (8.300 TL ve Altı))</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr"/>
+      <c r="C108" s="12" t="inlineStr"/>
+      <c r="D108" s="12" t="inlineStr"/>
+      <c r="E108" s="12" t="inlineStr"/>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>13,92 TL</t>
+        </is>
+      </c>
+      <c r="G108" s="12" t="inlineStr"/>
+      <c r="H108" s="12" t="inlineStr"/>
+      <c r="I108" s="12" t="inlineStr"/>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den Kartsız Para Yatırma (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr"/>
+      <c r="C109" s="12" t="inlineStr"/>
+      <c r="D109" s="12" t="inlineStr"/>
+      <c r="E109" s="12" t="inlineStr"/>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>27,85 TL</t>
+        </is>
+      </c>
+      <c r="G109" s="12" t="inlineStr"/>
+      <c r="H109" s="12" t="inlineStr"/>
+      <c r="I109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Bireysel Kredi Kartından Talimatlı Havale İşlem Ücreti</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr"/>
+      <c r="C110" s="12" t="inlineStr"/>
+      <c r="D110" s="12" t="inlineStr"/>
+      <c r="E110" s="12" t="inlineStr"/>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>3.99 TL / 1 %</t>
+        </is>
+      </c>
+      <c r="G110" s="12" t="inlineStr"/>
+      <c r="H110" s="12" t="inlineStr"/>
+      <c r="I110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>Bireysel Kredi Kartından Anlık Havale İşlem Ücreti</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr"/>
+      <c r="C111" s="12" t="inlineStr"/>
+      <c r="D111" s="12" t="inlineStr"/>
+      <c r="E111" s="12" t="inlineStr"/>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>3,99 TL / 1 %</t>
+        </is>
+      </c>
+      <c r="G111" s="12" t="inlineStr"/>
+      <c r="H111" s="12" t="inlineStr"/>
+      <c r="I111" s="12" t="inlineStr"/>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>ATM/BTM'den Kartsız Para Yatırma (399.000 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr"/>
+      <c r="C112" s="12" t="inlineStr"/>
+      <c r="D112" s="12" t="inlineStr"/>
+      <c r="E112" s="12" t="inlineStr"/>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>199,42 TL</t>
+        </is>
+      </c>
+      <c r="G112" s="12" t="inlineStr"/>
+      <c r="H112" s="12" t="inlineStr"/>
+      <c r="I112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>Hesaptan Hesaba / İsme TL ve YP Havale-Şubeden (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr"/>
+      <c r="C113" s="12" t="inlineStr"/>
+      <c r="D113" s="12" t="inlineStr"/>
+      <c r="E113" s="12" t="inlineStr"/>
+      <c r="F113" s="12" t="inlineStr"/>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>19,94 TL</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="inlineStr"/>
+      <c r="I113" s="12" t="inlineStr"/>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>Hesaptan Hesaba / İsme TL ve YP Havale-Şubeden (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr"/>
+      <c r="C114" s="12" t="inlineStr"/>
+      <c r="D114" s="12" t="inlineStr"/>
+      <c r="E114" s="12" t="inlineStr"/>
+      <c r="F114" s="12" t="inlineStr"/>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>39,88 TL</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="inlineStr"/>
+      <c r="I114" s="12" t="inlineStr"/>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>Hesaptan Hesaba / İsme TL ve YP Havale-Şubeden  (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr"/>
+      <c r="C115" s="12" t="inlineStr"/>
+      <c r="D115" s="12" t="inlineStr"/>
+      <c r="E115" s="12" t="inlineStr"/>
+      <c r="F115" s="12" t="inlineStr"/>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr"/>
+      <c r="I115" s="12" t="inlineStr"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>Kasadan Hesaba / İsme TL/YP Havale / Farklı Şubeden Vadesiz Hesaba 3.Şahıs Para Yatırma (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr"/>
+      <c r="C116" s="12" t="inlineStr"/>
+      <c r="D116" s="12" t="inlineStr"/>
+      <c r="E116" s="12" t="inlineStr"/>
+      <c r="F116" s="12" t="inlineStr"/>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>19,94 TL</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr"/>
+      <c r="I116" s="12" t="inlineStr"/>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>Kasadan Hesaba / İsme  TL/YP Havale / Farklı Şubeden Vadesiz Hesaba 3.Şahıs Para Yatırma (8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr"/>
+      <c r="C117" s="12" t="inlineStr"/>
+      <c r="D117" s="12" t="inlineStr"/>
+      <c r="E117" s="12" t="inlineStr"/>
+      <c r="F117" s="12" t="inlineStr"/>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>39,88 TL</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr"/>
+      <c r="I117" s="12" t="inlineStr"/>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Kasadan Hesaba / İsme TL/YP Havale / Farklı Şubeden Vadesiz Hesaba 3.Şahıs Para Yatırma (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr"/>
+      <c r="C118" s="12" t="inlineStr"/>
+      <c r="D118" s="12" t="inlineStr"/>
+      <c r="E118" s="12" t="inlineStr"/>
+      <c r="F118" s="12" t="inlineStr"/>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr"/>
+      <c r="I118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>TL ve YP İleri Vadeli Havale-Şubeden (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr"/>
+      <c r="C119" s="12" t="inlineStr"/>
+      <c r="D119" s="12" t="inlineStr"/>
+      <c r="E119" s="12" t="inlineStr"/>
+      <c r="F119" s="12" t="inlineStr"/>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>19,94 TL</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr"/>
+      <c r="I119" s="12" t="inlineStr"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>TL ve YP İleri Vadeli Havale-Şubeden (8.300,01 TL - 399.800 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr"/>
+      <c r="C120" s="12" t="inlineStr"/>
+      <c r="D120" s="12" t="inlineStr"/>
+      <c r="E120" s="12" t="inlineStr"/>
+      <c r="F120" s="12" t="inlineStr"/>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>39,88 TL</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr"/>
+      <c r="I120" s="12" t="inlineStr"/>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>TL ve YP İleri Vadeli Havale-Şubeden (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr"/>
+      <c r="C121" s="12" t="inlineStr"/>
+      <c r="D121" s="12" t="inlineStr"/>
+      <c r="E121" s="12" t="inlineStr"/>
+      <c r="F121" s="12" t="inlineStr"/>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr"/>
+      <c r="I121" s="12" t="inlineStr"/>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Şubeden Hesaptan Düzenli Havale  (8.300 TL ve Altı)</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr"/>
+      <c r="C122" s="12" t="inlineStr"/>
+      <c r="D122" s="12" t="inlineStr"/>
+      <c r="E122" s="12" t="inlineStr"/>
+      <c r="F122" s="12" t="inlineStr"/>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr"/>
+      <c r="I122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Şubeden Hesaptan Düzenli Havale  8.300,01 TL - 399.000 TL arasında)</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr"/>
+      <c r="C123" s="12" t="inlineStr"/>
+      <c r="D123" s="12" t="inlineStr"/>
+      <c r="E123" s="12" t="inlineStr"/>
+      <c r="F123" s="12" t="inlineStr"/>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>7,98 TL</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr"/>
+      <c r="I123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Şubeden Hesaptan Düzenli Havale (399.000,01 TL ve Üstü)</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr"/>
+      <c r="C124" s="12" t="inlineStr"/>
+      <c r="D124" s="12" t="inlineStr"/>
+      <c r="E124" s="12" t="inlineStr"/>
+      <c r="F124" s="12" t="inlineStr"/>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="inlineStr"/>
+      <c r="I124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>İnternet/Mobil – 0 - 8.300 TL</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr"/>
+      <c r="C125" s="12" t="inlineStr"/>
+      <c r="D125" s="12" t="inlineStr"/>
+      <c r="E125" s="12" t="inlineStr"/>
+      <c r="F125" s="12" t="inlineStr"/>
+      <c r="G125" s="12" t="inlineStr"/>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr"/>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>İnternet/Mobil – 8.300,01 TL – 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr"/>
+      <c r="C126" s="12" t="inlineStr"/>
+      <c r="D126" s="12" t="inlineStr"/>
+      <c r="E126" s="12" t="inlineStr"/>
+      <c r="F126" s="12" t="inlineStr"/>
+      <c r="G126" s="12" t="inlineStr"/>
+      <c r="H126" s="12" t="inlineStr">
+        <is>
+          <t>7,98 TL</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="inlineStr"/>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>İnternet/Mobil – 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr"/>
+      <c r="C127" s="12" t="inlineStr"/>
+      <c r="D127" s="12" t="inlineStr"/>
+      <c r="E127" s="12" t="inlineStr"/>
+      <c r="F127" s="12" t="inlineStr"/>
+      <c r="G127" s="12" t="inlineStr"/>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>ATM – 0 - 8.300 TL</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr"/>
+      <c r="C128" s="12" t="inlineStr"/>
+      <c r="D128" s="12" t="inlineStr"/>
+      <c r="E128" s="12" t="inlineStr"/>
+      <c r="F128" s="12" t="inlineStr"/>
+      <c r="G128" s="12" t="inlineStr"/>
+      <c r="H128" s="12" t="inlineStr">
+        <is>
+          <t>13,92 TL</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="inlineStr"/>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>ATM – 8.300,01 TL – 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr"/>
+      <c r="C129" s="12" t="inlineStr"/>
+      <c r="D129" s="12" t="inlineStr"/>
+      <c r="E129" s="12" t="inlineStr"/>
+      <c r="F129" s="12" t="inlineStr"/>
+      <c r="G129" s="12" t="inlineStr"/>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>27,85 TL</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="inlineStr"/>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>ATM – 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr"/>
+      <c r="C130" s="12" t="inlineStr"/>
+      <c r="D130" s="12" t="inlineStr"/>
+      <c r="E130" s="12" t="inlineStr"/>
+      <c r="F130" s="12" t="inlineStr"/>
+      <c r="G130" s="12" t="inlineStr"/>
+      <c r="H130" s="12" t="inlineStr">
+        <is>
+          <t>199,42 TL</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="inlineStr"/>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>Şube/Diğer – 0 - 8.300 TL</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr"/>
+      <c r="C131" s="12" t="inlineStr"/>
+      <c r="D131" s="12" t="inlineStr"/>
+      <c r="E131" s="12" t="inlineStr"/>
+      <c r="F131" s="12" t="inlineStr"/>
+      <c r="G131" s="12" t="inlineStr"/>
+      <c r="H131" s="12" t="inlineStr"/>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>19,94 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>Şube/Diğer – 8.300,01 TL – 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr"/>
+      <c r="C132" s="12" t="inlineStr"/>
+      <c r="D132" s="12" t="inlineStr"/>
+      <c r="E132" s="12" t="inlineStr"/>
+      <c r="F132" s="12" t="inlineStr"/>
+      <c r="G132" s="12" t="inlineStr"/>
+      <c r="H132" s="12" t="inlineStr"/>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>39,88 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>Şube/Diğer – 399.000,01 TL ve Üzeri</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr"/>
+      <c r="C133" s="12" t="inlineStr"/>
+      <c r="D133" s="12" t="inlineStr"/>
+      <c r="E133" s="12" t="inlineStr"/>
+      <c r="F133" s="12" t="inlineStr"/>
+      <c r="G133" s="12" t="inlineStr"/>
+      <c r="H133" s="12" t="inlineStr"/>
+      <c r="I133" s="12" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartlı Havale - 399.000,01 TL ve üzeri</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr"/>
+      <c r="C134" s="12" t="inlineStr"/>
+      <c r="D134" s="12" t="inlineStr"/>
+      <c r="E134" s="12" t="inlineStr"/>
+      <c r="F134" s="12" t="inlineStr"/>
+      <c r="G134" s="12" t="inlineStr"/>
+      <c r="H134" s="12" t="inlineStr">
+        <is>
+          <t>199,05 TL</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="inlineStr"/>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartlı Havale - 8.300 TL ve altı</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr"/>
+      <c r="C135" s="12" t="inlineStr"/>
+      <c r="D135" s="12" t="inlineStr"/>
+      <c r="E135" s="12" t="inlineStr"/>
+      <c r="F135" s="12" t="inlineStr"/>
+      <c r="G135" s="12" t="inlineStr"/>
+      <c r="H135" s="12" t="inlineStr">
+        <is>
+          <t>13,33 TL</t>
+        </is>
+      </c>
+      <c r="I135" s="12" t="inlineStr"/>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartlı Havale - 8.300,01 TL - 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="inlineStr"/>
+      <c r="C136" s="12" t="inlineStr"/>
+      <c r="D136" s="12" t="inlineStr"/>
+      <c r="E136" s="12" t="inlineStr"/>
+      <c r="F136" s="12" t="inlineStr"/>
+      <c r="G136" s="12" t="inlineStr"/>
+      <c r="H136" s="12" t="inlineStr">
+        <is>
+          <t>27,62 TL</t>
+        </is>
+      </c>
+      <c r="I136" s="12" t="inlineStr"/>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartsız Havale - 399.000,01 TL ve üzeri</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr"/>
+      <c r="C137" s="12" t="inlineStr"/>
+      <c r="D137" s="12" t="inlineStr"/>
+      <c r="E137" s="12" t="inlineStr"/>
+      <c r="F137" s="12" t="inlineStr"/>
+      <c r="G137" s="12" t="inlineStr"/>
+      <c r="H137" s="12" t="inlineStr">
+        <is>
+          <t>199,05 TL</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="inlineStr"/>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartsız Havale - 8.300 TL ve altı</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr"/>
+      <c r="C138" s="12" t="inlineStr"/>
+      <c r="D138" s="12" t="inlineStr"/>
+      <c r="E138" s="12" t="inlineStr"/>
+      <c r="F138" s="12" t="inlineStr"/>
+      <c r="G138" s="12" t="inlineStr"/>
+      <c r="H138" s="12" t="inlineStr">
+        <is>
+          <t>13,33 TL</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="inlineStr"/>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>ATM Kartsız Havale - 8.300,01 TL - 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr"/>
+      <c r="C139" s="12" t="inlineStr"/>
+      <c r="D139" s="12" t="inlineStr"/>
+      <c r="E139" s="12" t="inlineStr"/>
+      <c r="F139" s="12" t="inlineStr"/>
+      <c r="G139" s="12" t="inlineStr"/>
+      <c r="H139" s="12" t="inlineStr">
+        <is>
+          <t>27,62 TL</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>FAST İşlemleri - Mobil /İnternet Şubesi (0-8300 TL)</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="inlineStr">
+        <is>
+          <t>7.97TL</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr"/>
+      <c r="D142" s="12" t="inlineStr"/>
+      <c r="E142" s="12" t="inlineStr"/>
+      <c r="F142" s="12" t="inlineStr"/>
+      <c r="G142" s="12" t="inlineStr"/>
+      <c r="H142" s="12" t="inlineStr"/>
+      <c r="I142" s="12" t="inlineStr"/>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>FAST İşlemleri - Mobil /İnternet Şubesi (8300,01-399000 TL)</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>15.96TL</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr"/>
+      <c r="D143" s="12" t="inlineStr"/>
+      <c r="E143" s="12" t="inlineStr"/>
+      <c r="F143" s="12" t="inlineStr"/>
+      <c r="G143" s="12" t="inlineStr"/>
+      <c r="H143" s="12" t="inlineStr"/>
+      <c r="I143" s="12" t="inlineStr"/>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>ATS ile altın gönderimi 1-10 gr</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="inlineStr"/>
+      <c r="C144" s="12" t="inlineStr"/>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>57,5TL</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr"/>
+      <c r="F144" s="12" t="inlineStr"/>
+      <c r="G144" s="12" t="inlineStr"/>
+      <c r="H144" s="12" t="inlineStr"/>
+      <c r="I144" s="12" t="inlineStr"/>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>ATS ile altın gönderimi 11-100 gr</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr"/>
+      <c r="C145" s="12" t="inlineStr"/>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>115TL</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr"/>
+      <c r="F145" s="12" t="inlineStr"/>
+      <c r="G145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr"/>
+      <c r="I145" s="12" t="inlineStr"/>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>İnternet/Mobil – 0 - 8.300 TL</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr"/>
+      <c r="C146" s="12" t="inlineStr"/>
+      <c r="D146" s="12" t="inlineStr"/>
+      <c r="E146" s="12" t="inlineStr"/>
+      <c r="F146" s="12" t="inlineStr"/>
+      <c r="G146" s="12" t="inlineStr"/>
+      <c r="H146" s="12" t="inlineStr">
+        <is>
+          <t>7,97 TL</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="inlineStr"/>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>İnternet/Mobil – 8.300,01 TL – 399.000 TL</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr"/>
+      <c r="C147" s="12" t="inlineStr"/>
+      <c r="D147" s="12" t="inlineStr"/>
+      <c r="E147" s="12" t="inlineStr"/>
+      <c r="F147" s="12" t="inlineStr"/>
+      <c r="G147" s="12" t="inlineStr"/>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>15,96 TL</t>
+        </is>
+      </c>
+      <c r="I147" s="12" t="inlineStr"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>Global Fast - Karta Para Gönderim İşlemleri</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="inlineStr"/>
+      <c r="C148" s="12" t="inlineStr"/>
+      <c r="D148" s="12" t="inlineStr"/>
+      <c r="E148" s="12" t="inlineStr"/>
+      <c r="F148" s="12" t="inlineStr"/>
+      <c r="G148" s="12" t="inlineStr"/>
+      <c r="H148" s="12" t="inlineStr">
+        <is>
+          <t>15 TL / 4</t>
+        </is>
+      </c>
+      <c r="I148" s="12" t="inlineStr"/>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>Global Fast - Hesaba Para Gönderim İşlemleri</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr"/>
+      <c r="C149" s="12" t="inlineStr"/>
+      <c r="D149" s="12" t="inlineStr"/>
+      <c r="E149" s="12" t="inlineStr"/>
+      <c r="F149" s="12" t="inlineStr"/>
+      <c r="G149" s="12" t="inlineStr"/>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>200 TL / 0,4</t>
+        </is>
+      </c>
+      <c r="I149" s="12" t="inlineStr"/>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>Hesaptan Yıllık Kasa Ücreti (Büyük)</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="inlineStr">
+        <is>
+          <t>30000.00TL</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr"/>
+      <c r="D152" s="12" t="inlineStr"/>
+      <c r="E152" s="12" t="inlineStr"/>
+      <c r="F152" s="12" t="inlineStr"/>
+      <c r="G152" s="12" t="inlineStr"/>
+      <c r="H152" s="12" t="inlineStr"/>
+      <c r="I152" s="12" t="inlineStr"/>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>Hesaptan Yıllık Kasa Ücreti (Küçük)</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>22000.00TL</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr"/>
+      <c r="D153" s="12" t="inlineStr"/>
+      <c r="E153" s="12" t="inlineStr"/>
+      <c r="F153" s="12" t="inlineStr"/>
+      <c r="G153" s="12" t="inlineStr"/>
+      <c r="H153" s="12" t="inlineStr"/>
+      <c r="I153" s="12" t="inlineStr"/>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>Hesaptan Yıllık Kasa Ücreti (Orta)</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="inlineStr">
+        <is>
+          <t>25000.00TL</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr"/>
+      <c r="D154" s="12" t="inlineStr"/>
+      <c r="E154" s="12" t="inlineStr"/>
+      <c r="F154" s="12" t="inlineStr"/>
+      <c r="G154" s="12" t="inlineStr"/>
+      <c r="H154" s="12" t="inlineStr"/>
+      <c r="I154" s="12" t="inlineStr"/>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa Depozito Ücreti (Büyük)</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>28570.00TL</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr"/>
+      <c r="D155" s="12" t="inlineStr"/>
+      <c r="E155" s="12" t="inlineStr"/>
+      <c r="F155" s="12" t="inlineStr"/>
+      <c r="G155" s="12" t="inlineStr"/>
+      <c r="H155" s="12" t="inlineStr"/>
+      <c r="I155" s="12" t="inlineStr"/>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa Depozito Ücreti (Orta)</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="inlineStr">
+        <is>
+          <t>23805.00TL</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr"/>
+      <c r="D156" s="12" t="inlineStr"/>
+      <c r="E156" s="12" t="inlineStr"/>
+      <c r="F156" s="12" t="inlineStr"/>
+      <c r="G156" s="12" t="inlineStr"/>
+      <c r="H156" s="12" t="inlineStr"/>
+      <c r="I156" s="12" t="inlineStr"/>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa Depozito Ücreti (Küçük)</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>20950.00TL</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr"/>
+      <c r="D157" s="12" t="inlineStr"/>
+      <c r="E157" s="12" t="inlineStr"/>
+      <c r="F157" s="12" t="inlineStr"/>
+      <c r="G157" s="12" t="inlineStr"/>
+      <c r="H157" s="12" t="inlineStr"/>
+      <c r="I157" s="12" t="inlineStr"/>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>Kredi Kartından Yıllık Kasa Ücreti (Büyük)</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>30000.00TL</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr"/>
+      <c r="D158" s="12" t="inlineStr"/>
+      <c r="E158" s="12" t="inlineStr"/>
+      <c r="F158" s="12" t="inlineStr"/>
+      <c r="G158" s="12" t="inlineStr"/>
+      <c r="H158" s="12" t="inlineStr"/>
+      <c r="I158" s="12" t="inlineStr"/>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>Kredi Kartından Yıllık Kasa Ücreti (Orta)</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>25000.00TL</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr"/>
+      <c r="D159" s="12" t="inlineStr"/>
+      <c r="E159" s="12" t="inlineStr"/>
+      <c r="F159" s="12" t="inlineStr"/>
+      <c r="G159" s="12" t="inlineStr"/>
+      <c r="H159" s="12" t="inlineStr"/>
+      <c r="I159" s="12" t="inlineStr"/>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>Kredi Kartından Yıllık Kasa Ücreti (Küçük)</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="inlineStr">
+        <is>
+          <t>22000.00TL</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr"/>
+      <c r="D160" s="12" t="inlineStr"/>
+      <c r="E160" s="12" t="inlineStr"/>
+      <c r="F160" s="12" t="inlineStr"/>
+      <c r="G160" s="12" t="inlineStr"/>
+      <c r="H160" s="12" t="inlineStr"/>
+      <c r="I160" s="12" t="inlineStr"/>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>Büyük Boy Kasa</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr"/>
+      <c r="C161" s="12" t="inlineStr"/>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>2150TL</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr"/>
+      <c r="F161" s="12" t="inlineStr"/>
+      <c r="G161" s="12" t="inlineStr"/>
+      <c r="H161" s="12" t="inlineStr"/>
+      <c r="I161" s="12" t="inlineStr"/>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>Orta Boy Kasa</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="inlineStr"/>
+      <c r="C162" s="12" t="inlineStr"/>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>1830TL</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr"/>
+      <c r="F162" s="12" t="inlineStr"/>
+      <c r="G162" s="12" t="inlineStr"/>
+      <c r="H162" s="12" t="inlineStr"/>
+      <c r="I162" s="12" t="inlineStr"/>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>Küçük Boy Kasa</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr"/>
+      <c r="C163" s="12" t="inlineStr"/>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>1340TL</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr"/>
+      <c r="F163" s="12" t="inlineStr"/>
+      <c r="G163" s="12" t="inlineStr"/>
+      <c r="H163" s="12" t="inlineStr"/>
+      <c r="I163" s="12" t="inlineStr"/>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>Büyük Boy Özel Kasa</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="inlineStr"/>
+      <c r="C164" s="12" t="inlineStr"/>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>4140TL</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr"/>
+      <c r="F164" s="12" t="inlineStr"/>
+      <c r="G164" s="12" t="inlineStr"/>
+      <c r="H164" s="12" t="inlineStr"/>
+      <c r="I164" s="12" t="inlineStr"/>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>Orta Boy Özel Kasa</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr"/>
+      <c r="C165" s="12" t="inlineStr"/>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>3390TL</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr"/>
+      <c r="F165" s="12" t="inlineStr"/>
+      <c r="G165" s="12" t="inlineStr"/>
+      <c r="H165" s="12" t="inlineStr"/>
+      <c r="I165" s="12" t="inlineStr"/>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>Küçük Boy Özel Kasa</t>
+        </is>
+      </c>
+      <c r="B166" s="12" t="inlineStr"/>
+      <c r="C166" s="12" t="inlineStr"/>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>2610TL</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr"/>
+      <c r="F166" s="12" t="inlineStr"/>
+      <c r="G166" s="12" t="inlineStr"/>
+      <c r="H166" s="12" t="inlineStr"/>
+      <c r="I166" s="12" t="inlineStr"/>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa - Standart Kasa Depozito</t>
+        </is>
+      </c>
+      <c r="B167" s="12" t="inlineStr"/>
+      <c r="C167" s="12" t="inlineStr"/>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>5620TL</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="inlineStr"/>
+      <c r="F167" s="12" t="inlineStr"/>
+      <c r="G167" s="12" t="inlineStr"/>
+      <c r="H167" s="12" t="inlineStr"/>
+      <c r="I167" s="12" t="inlineStr"/>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa - Özel Kasa Depozito</t>
+        </is>
+      </c>
+      <c r="B168" s="12" t="inlineStr"/>
+      <c r="C168" s="12" t="inlineStr"/>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>9420TL</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr"/>
+      <c r="F168" s="12" t="inlineStr"/>
+      <c r="G168" s="12" t="inlineStr"/>
+      <c r="H168" s="12" t="inlineStr"/>
+      <c r="I168" s="12" t="inlineStr"/>
+    </row>
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>Kredi Risk Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>HGS Kartı Satış Bedeli</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr"/>
+      <c r="C171" s="12" t="inlineStr"/>
+      <c r="D171" s="12" t="inlineStr"/>
+      <c r="E171" s="12" t="inlineStr"/>
+      <c r="F171" s="12" t="inlineStr"/>
+      <c r="G171" s="12" t="inlineStr"/>
+      <c r="H171" s="12" t="inlineStr">
+        <is>
+          <t>550 TL</t>
+        </is>
+      </c>
+      <c r="I171" s="12" t="inlineStr"/>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>Güvenli Ödeme Sistemi</t>
+        </is>
+      </c>
+      <c r="B172" s="12" t="inlineStr"/>
+      <c r="C172" s="12" t="inlineStr"/>
+      <c r="D172" s="12" t="inlineStr"/>
+      <c r="E172" s="12" t="inlineStr"/>
+      <c r="F172" s="12" t="inlineStr"/>
+      <c r="G172" s="12" t="inlineStr"/>
+      <c r="H172" s="12" t="inlineStr">
+        <is>
+          <t>97,53 TL</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="inlineStr"/>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>HGS Etiketi Satış Bedeli</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr"/>
+      <c r="C173" s="12" t="inlineStr"/>
+      <c r="D173" s="12" t="inlineStr"/>
+      <c r="E173" s="12" t="inlineStr"/>
+      <c r="F173" s="12" t="inlineStr"/>
+      <c r="G173" s="12" t="inlineStr"/>
+      <c r="H173" s="12" t="inlineStr">
+        <is>
+          <t>275 TL</t>
+        </is>
+      </c>
+      <c r="I173" s="12" t="inlineStr"/>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>Vergi Numarası Alma ( Yabancı müşteriler için)</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr"/>
+      <c r="C174" s="12" t="inlineStr"/>
+      <c r="D174" s="12" t="inlineStr"/>
+      <c r="E174" s="12" t="inlineStr"/>
+      <c r="F174" s="12" t="inlineStr"/>
+      <c r="G174" s="12" t="inlineStr"/>
+      <c r="H174" s="12" t="inlineStr">
+        <is>
+          <t>50 TL</t>
+        </is>
+      </c>
+      <c r="I174" s="12" t="inlineStr"/>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>Geniş Kapsamlı Hizmet Paketi Ücreti</t>
+        </is>
+      </c>
+      <c r="B175" s="12" t="inlineStr"/>
+      <c r="C175" s="12" t="inlineStr"/>
+      <c r="D175" s="12" t="inlineStr"/>
+      <c r="E175" s="12" t="inlineStr"/>
+      <c r="F175" s="12" t="inlineStr"/>
+      <c r="G175" s="12" t="inlineStr"/>
+      <c r="H175" s="12" t="inlineStr">
+        <is>
+          <t>339 TL</t>
+        </is>
+      </c>
+      <c r="I175" s="12" t="inlineStr"/>
+    </row>
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="10" t="inlineStr">
+        <is>
+          <t>Fatura Ödemeleri - Kart</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>Fatura ve Anlaşmalı Kurum Ödemeleri</t>
+        </is>
+      </c>
+      <c r="B178" s="12" t="inlineStr"/>
+      <c r="C178" s="12" t="inlineStr"/>
+      <c r="D178" s="12" t="inlineStr"/>
+      <c r="E178" s="12" t="inlineStr"/>
+      <c r="F178" s="12" t="inlineStr"/>
+      <c r="G178" s="12" t="inlineStr"/>
+      <c r="H178" s="12" t="inlineStr">
+        <is>
+          <t>0,63 TL</t>
+        </is>
+      </c>
+      <c r="I178" s="12" t="inlineStr"/>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>Konsolosluk Vize Randevu Bedeli Tahsilat Komisyonu</t>
+        </is>
+      </c>
+      <c r="B179" s="12" t="inlineStr"/>
+      <c r="C179" s="12" t="inlineStr"/>
+      <c r="D179" s="12" t="inlineStr"/>
+      <c r="E179" s="12" t="inlineStr"/>
+      <c r="F179" s="12" t="inlineStr"/>
+      <c r="G179" s="12" t="inlineStr"/>
+      <c r="H179" s="12" t="inlineStr">
+        <is>
+          <t>200 TL</t>
+        </is>
+      </c>
+      <c r="I179" s="12" t="inlineStr"/>
+    </row>
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" s="10" t="inlineStr">
+        <is>
+          <t>HGS Etiket Bedeli</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>HGS Etiket Ücreti</t>
+        </is>
+      </c>
+      <c r="B182" s="12" t="inlineStr">
+        <is>
+          <t>275.00TL</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr"/>
+      <c r="D182" s="12" t="inlineStr"/>
+      <c r="E182" s="12" t="inlineStr"/>
+      <c r="F182" s="12" t="inlineStr"/>
+      <c r="G182" s="12" t="inlineStr"/>
+      <c r="H182" s="12" t="inlineStr"/>
+      <c r="I182" s="12" t="inlineStr"/>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>HGS Kart Ücreti</t>
+        </is>
+      </c>
+      <c r="B183" s="12" t="inlineStr">
+        <is>
+          <t>550.00TL</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr"/>
+      <c r="D183" s="12" t="inlineStr"/>
+      <c r="E183" s="12" t="inlineStr"/>
+      <c r="F183" s="12" t="inlineStr"/>
+      <c r="G183" s="12" t="inlineStr"/>
+      <c r="H183" s="12" t="inlineStr"/>
+      <c r="I183" s="12" t="inlineStr"/>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>HGS Etiket Ücretleri</t>
+        </is>
+      </c>
+      <c r="B184" s="12" t="inlineStr"/>
+      <c r="C184" s="12" t="inlineStr"/>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>275TL</t>
+        </is>
+      </c>
+      <c r="E184" s="12" t="inlineStr"/>
+      <c r="F184" s="12" t="inlineStr"/>
+      <c r="G184" s="12" t="inlineStr"/>
+      <c r="H184" s="12" t="inlineStr"/>
+      <c r="I184" s="12" t="inlineStr"/>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>HGS Kart Ücretleri</t>
+        </is>
+      </c>
+      <c r="B185" s="12" t="inlineStr"/>
+      <c r="C185" s="12" t="inlineStr"/>
+      <c r="D185" s="12" t="inlineStr">
+        <is>
+          <t>550TL</t>
+        </is>
+      </c>
+      <c r="E185" s="12" t="inlineStr"/>
+      <c r="F185" s="12" t="inlineStr"/>
+      <c r="G185" s="12" t="inlineStr"/>
+      <c r="H185" s="12" t="inlineStr"/>
+      <c r="I185" s="12" t="inlineStr"/>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="10" t="inlineStr">
+        <is>
+          <t>Arşiv Araştırma Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
+          <t>Arşiv Araştırma Ücreti</t>
+        </is>
+      </c>
+      <c r="B188" s="12" t="inlineStr">
+        <is>
+          <t>287.62TL</t>
+        </is>
+      </c>
+      <c r="C188" s="12" t="inlineStr"/>
+      <c r="D188" s="12" t="inlineStr"/>
+      <c r="E188" s="12" t="inlineStr"/>
+      <c r="F188" s="12" t="inlineStr"/>
+      <c r="G188" s="12" t="inlineStr"/>
+      <c r="H188" s="12" t="inlineStr"/>
+      <c r="I188" s="12" t="inlineStr"/>
+    </row>
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="10" t="inlineStr">
+        <is>
+          <t>Mevduat Araştırma</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>İtibar/Niyet/Referans Mektubu Düzenleme Ücreti</t>
+        </is>
+      </c>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr"/>
+      <c r="D191" s="12" t="inlineStr"/>
+      <c r="E191" s="12" t="inlineStr"/>
+      <c r="F191" s="12" t="inlineStr"/>
+      <c r="G191" s="12" t="inlineStr"/>
+      <c r="H191" s="12" t="inlineStr"/>
+      <c r="I191" s="12" t="inlineStr"/>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>İtibar Mektubu Düzenleme Ücreti</t>
+        </is>
+      </c>
+      <c r="B192" s="12" t="inlineStr"/>
+      <c r="C192" s="12" t="inlineStr"/>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>10000TL</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="inlineStr"/>
+      <c r="F192" s="12" t="inlineStr"/>
+      <c r="G192" s="12" t="inlineStr"/>
+      <c r="H192" s="12" t="inlineStr"/>
+      <c r="I192" s="12" t="inlineStr"/>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>Referans Mektubu Düzenleme Ücreti</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr"/>
+      <c r="C193" s="12" t="inlineStr"/>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>10000TL</t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="inlineStr"/>
+      <c r="F193" s="12" t="inlineStr"/>
+      <c r="G193" s="12" t="inlineStr"/>
+      <c r="H193" s="12" t="inlineStr"/>
+      <c r="I193" s="12" t="inlineStr"/>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>Niyet Mektubu Düzenleme Ücreti (Türkiye İhracat Kredi Bankasına)</t>
+        </is>
+      </c>
+      <c r="B194" s="12" t="inlineStr"/>
+      <c r="C194" s="12" t="inlineStr"/>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>3500TL</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="inlineStr"/>
+      <c r="F194" s="12" t="inlineStr"/>
+      <c r="G194" s="12" t="inlineStr"/>
+      <c r="H194" s="12" t="inlineStr"/>
+      <c r="I194" s="12" t="inlineStr"/>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>Niyet Mektubu Düzenleme Ücreti (Tarım ve Kırsal Kalkınmayı Destekleme Kurumuna)</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr"/>
+      <c r="C195" s="12" t="inlineStr"/>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>770TL</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="inlineStr"/>
+      <c r="F195" s="12" t="inlineStr"/>
+      <c r="G195" s="12" t="inlineStr"/>
+      <c r="H195" s="12" t="inlineStr"/>
+      <c r="I195" s="12" t="inlineStr"/>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>Bireysel Müşteriler için Referans Mektubu / Yazısı</t>
+        </is>
+      </c>
+      <c r="B196" s="12" t="inlineStr"/>
+      <c r="C196" s="12" t="inlineStr"/>
+      <c r="D196" s="12" t="inlineStr"/>
+      <c r="E196" s="12" t="inlineStr"/>
+      <c r="F196" s="12" t="inlineStr"/>
+      <c r="G196" s="12" t="inlineStr"/>
+      <c r="H196" s="12" t="inlineStr">
+        <is>
+          <t>50 TL</t>
+        </is>
+      </c>
+      <c r="I196" s="12" t="inlineStr"/>
+    </row>
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>Bloke/ Keşide Çeki Düzenleme</t>
+        </is>
+      </c>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.58%</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr"/>
+      <c r="D199" s="12" t="inlineStr"/>
+      <c r="E199" s="12" t="inlineStr"/>
+      <c r="F199" s="12" t="inlineStr"/>
+      <c r="G199" s="12" t="inlineStr"/>
+      <c r="H199" s="12" t="inlineStr"/>
+      <c r="I199" s="12" t="inlineStr"/>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>Çek Defteri Teslimi (Yaprak Başına)</t>
+        </is>
+      </c>
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t>85.72TL</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr"/>
+      <c r="D200" s="12" t="inlineStr"/>
+      <c r="E200" s="12" t="inlineStr"/>
+      <c r="F200" s="12" t="inlineStr"/>
+      <c r="G200" s="12" t="inlineStr"/>
+      <c r="H200" s="12" t="inlineStr"/>
+      <c r="I200" s="12" t="inlineStr"/>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>Hediye Çeki Düzenleme</t>
+        </is>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>133.34TL</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr"/>
+      <c r="D201" s="12" t="inlineStr"/>
+      <c r="E201" s="12" t="inlineStr"/>
+      <c r="F201" s="12" t="inlineStr"/>
+      <c r="G201" s="12" t="inlineStr"/>
+      <c r="H201" s="12" t="inlineStr"/>
+      <c r="I201" s="12" t="inlineStr"/>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="11" t="inlineStr">
+        <is>
+          <t>Seyahat Çeki Düzenleme</t>
+        </is>
+      </c>
+      <c r="B202" s="12" t="inlineStr">
+        <is>
+          <t>9.52TL / 0.10%</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr"/>
+      <c r="D202" s="12" t="inlineStr"/>
+      <c r="E202" s="12" t="inlineStr"/>
+      <c r="F202" s="12" t="inlineStr"/>
+      <c r="G202" s="12" t="inlineStr"/>
+      <c r="H202" s="12" t="inlineStr"/>
+      <c r="I202" s="12" t="inlineStr"/>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="11" t="inlineStr">
+        <is>
+          <t>Farklı Şube Çek Ödeme - TP/YP</t>
+        </is>
+      </c>
+      <c r="B203" s="12" t="inlineStr"/>
+      <c r="C203" s="12" t="inlineStr"/>
+      <c r="D203" s="12" t="inlineStr"/>
+      <c r="E203" s="12" t="inlineStr">
+        <is>
+          <t>780TL / 0.6%</t>
+        </is>
+      </c>
+      <c r="F203" s="12" t="inlineStr"/>
+      <c r="G203" s="12" t="inlineStr"/>
+      <c r="H203" s="12" t="inlineStr"/>
+      <c r="I203" s="12" t="inlineStr"/>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Şube Çek Ödeme - TP/YP</t>
+        </is>
+      </c>
+      <c r="B204" s="12" t="inlineStr"/>
+      <c r="C204" s="12" t="inlineStr"/>
+      <c r="D204" s="12" t="inlineStr"/>
+      <c r="E204" s="12" t="inlineStr">
+        <is>
+          <t>390TL / 0.2%</t>
+        </is>
+      </c>
+      <c r="F204" s="12" t="inlineStr"/>
+      <c r="G204" s="12" t="inlineStr"/>
+      <c r="H204" s="12" t="inlineStr"/>
+      <c r="I204" s="12" t="inlineStr"/>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t>Tahsile Alınan Bankamız Çeki - TP/YP</t>
+        </is>
+      </c>
+      <c r="B205" s="12" t="inlineStr"/>
+      <c r="C205" s="12" t="inlineStr"/>
+      <c r="D205" s="12" t="inlineStr">
+        <is>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E205" s="12" t="inlineStr"/>
+      <c r="F205" s="12" t="inlineStr"/>
+      <c r="G205" s="12" t="inlineStr"/>
+      <c r="H205" s="12" t="inlineStr"/>
+      <c r="I205" s="12" t="inlineStr"/>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="11" t="inlineStr">
+        <is>
+          <t>Teminata Alınan Bankamız Çeki - TP/YP</t>
+        </is>
+      </c>
+      <c r="B206" s="12" t="inlineStr"/>
+      <c r="C206" s="12" t="inlineStr"/>
+      <c r="D206" s="12" t="inlineStr">
+        <is>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E206" s="12" t="inlineStr"/>
+      <c r="F206" s="12" t="inlineStr"/>
+      <c r="G206" s="12" t="inlineStr"/>
+      <c r="H206" s="12" t="inlineStr"/>
+      <c r="I206" s="12" t="inlineStr"/>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="11" t="inlineStr">
+        <is>
+          <t>Tahsile Alınan Diğer Banka Çeki - TP</t>
+        </is>
+      </c>
+      <c r="B207" s="12" t="inlineStr"/>
+      <c r="C207" s="12" t="inlineStr"/>
+      <c r="D207" s="12" t="inlineStr">
+        <is>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E207" s="12" t="inlineStr"/>
+      <c r="F207" s="12" t="inlineStr"/>
+      <c r="G207" s="12" t="inlineStr"/>
+      <c r="H207" s="12" t="inlineStr"/>
+      <c r="I207" s="12" t="inlineStr"/>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="11" t="inlineStr">
+        <is>
+          <t>Teminata Alınan Diğer Banka Çeki - TP</t>
+        </is>
+      </c>
+      <c r="B208" s="12" t="inlineStr"/>
+      <c r="C208" s="12" t="inlineStr"/>
+      <c r="D208" s="12" t="inlineStr">
+        <is>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E208" s="12" t="inlineStr"/>
+      <c r="F208" s="12" t="inlineStr"/>
+      <c r="G208" s="12" t="inlineStr"/>
+      <c r="H208" s="12" t="inlineStr"/>
+      <c r="I208" s="12" t="inlineStr"/>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="11" t="inlineStr">
+        <is>
+          <t>Diğer Banka - Tahsile Alınan - YP</t>
+        </is>
+      </c>
+      <c r="B209" s="12" t="inlineStr"/>
+      <c r="C209" s="12" t="inlineStr"/>
+      <c r="D209" s="12" t="inlineStr">
+        <is>
+          <t>1543TL</t>
+        </is>
+      </c>
+      <c r="E209" s="12" t="inlineStr"/>
+      <c r="F209" s="12" t="inlineStr"/>
+      <c r="G209" s="12" t="inlineStr"/>
+      <c r="H209" s="12" t="inlineStr"/>
+      <c r="I209" s="12" t="inlineStr"/>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>Bankamız Üzerine Keşideli Dövizli Çek Alışı</t>
+        </is>
+      </c>
+      <c r="B210" s="12" t="inlineStr"/>
+      <c r="C210" s="12" t="inlineStr"/>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
+      <c r="E210" s="12" t="inlineStr"/>
+      <c r="F210" s="12" t="inlineStr"/>
+      <c r="G210" s="12" t="inlineStr"/>
+      <c r="H210" s="12" t="inlineStr"/>
+      <c r="I210" s="12" t="inlineStr"/>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>Yabancı Banka Üzerine Keşideli Döviz Çeki Alışı - YP</t>
+        </is>
+      </c>
+      <c r="B211" s="12" t="inlineStr"/>
+      <c r="C211" s="12" t="inlineStr"/>
+      <c r="D211" s="12" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
+      <c r="E211" s="12" t="inlineStr"/>
+      <c r="F211" s="12" t="inlineStr"/>
+      <c r="G211" s="12" t="inlineStr"/>
+      <c r="H211" s="12" t="inlineStr"/>
+      <c r="I211" s="12" t="inlineStr"/>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>Yurt Dışı Yabancı Banka Döviz Çeki Tahsile Alınması</t>
+        </is>
+      </c>
+      <c r="B212" s="12" t="inlineStr"/>
+      <c r="C212" s="12" t="inlineStr"/>
+      <c r="D212" s="12" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
+      <c r="E212" s="12" t="inlineStr"/>
+      <c r="F212" s="12" t="inlineStr"/>
+      <c r="G212" s="12" t="inlineStr"/>
+      <c r="H212" s="12" t="inlineStr"/>
+      <c r="I212" s="12" t="inlineStr"/>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>Dövizli Çek Düzenleme - YP</t>
+        </is>
+      </c>
+      <c r="B213" s="12" t="inlineStr"/>
+      <c r="C213" s="12" t="inlineStr"/>
+      <c r="D213" s="12" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
+      <c r="E213" s="12" t="inlineStr"/>
+      <c r="F213" s="12" t="inlineStr"/>
+      <c r="G213" s="12" t="inlineStr"/>
+      <c r="H213" s="12" t="inlineStr"/>
+      <c r="I213" s="12" t="inlineStr"/>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="11" t="inlineStr">
+        <is>
+          <t>Ödeme - TP/YP</t>
+        </is>
+      </c>
+      <c r="B214" s="12" t="inlineStr"/>
+      <c r="C214" s="12" t="inlineStr"/>
+      <c r="D214" s="12" t="inlineStr">
+        <is>
+          <t>1040TL / 0.5%</t>
+        </is>
+      </c>
+      <c r="E214" s="12" t="inlineStr"/>
+      <c r="F214" s="12" t="inlineStr"/>
+      <c r="G214" s="12" t="inlineStr"/>
+      <c r="H214" s="12" t="inlineStr"/>
+      <c r="I214" s="12" t="inlineStr"/>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="11" t="inlineStr">
+        <is>
+          <t>Düzenleme - TP/YP</t>
+        </is>
+      </c>
+      <c r="B215" s="12" t="inlineStr"/>
+      <c r="C215" s="12" t="inlineStr"/>
+      <c r="D215" s="12" t="inlineStr">
+        <is>
+          <t>1630TL / 0.5%</t>
+        </is>
+      </c>
+      <c r="E215" s="12" t="inlineStr"/>
+      <c r="F215" s="12" t="inlineStr"/>
+      <c r="G215" s="12" t="inlineStr"/>
+      <c r="H215" s="12" t="inlineStr"/>
+      <c r="I215" s="12" t="inlineStr"/>
+    </row>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="11" t="inlineStr">
+        <is>
+          <t>Karşılıklı Çek Düzenleme</t>
+        </is>
+      </c>
+      <c r="B216" s="12" t="inlineStr"/>
+      <c r="C216" s="12" t="inlineStr"/>
+      <c r="D216" s="12" t="inlineStr">
+        <is>
+          <t>290TL / 1.10%</t>
+        </is>
+      </c>
+      <c r="E216" s="12" t="inlineStr"/>
+      <c r="F216" s="12" t="inlineStr"/>
+      <c r="G216" s="12" t="inlineStr"/>
+      <c r="H216" s="12" t="inlineStr"/>
+      <c r="I216" s="12" t="inlineStr"/>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>Çek Muamelesiz İade</t>
+        </is>
+      </c>
+      <c r="B217" s="12" t="inlineStr"/>
+      <c r="C217" s="12" t="inlineStr"/>
+      <c r="D217" s="12" t="inlineStr">
+        <is>
+          <t>390TL</t>
+        </is>
+      </c>
+      <c r="E217" s="12" t="inlineStr"/>
+      <c r="F217" s="12" t="inlineStr"/>
+      <c r="G217" s="12" t="inlineStr"/>
+      <c r="H217" s="12" t="inlineStr"/>
+      <c r="I217" s="12" t="inlineStr"/>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="11" t="inlineStr">
+        <is>
+          <t>10 Yapraklı</t>
+        </is>
+      </c>
+      <c r="B218" s="12" t="inlineStr"/>
+      <c r="C218" s="12" t="inlineStr"/>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>750TL</t>
+        </is>
+      </c>
+      <c r="E218" s="12" t="inlineStr"/>
+      <c r="F218" s="12" t="inlineStr"/>
+      <c r="G218" s="12" t="inlineStr"/>
+      <c r="H218" s="12" t="inlineStr"/>
+      <c r="I218" s="12" t="inlineStr"/>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t>25 Yapraklı</t>
+        </is>
+      </c>
+      <c r="B219" s="12" t="inlineStr"/>
+      <c r="C219" s="12" t="inlineStr"/>
+      <c r="D219" s="12" t="inlineStr">
+        <is>
+          <t>1875TL</t>
+        </is>
+      </c>
+      <c r="E219" s="12" t="inlineStr"/>
+      <c r="F219" s="12" t="inlineStr"/>
+      <c r="G219" s="12" t="inlineStr"/>
+      <c r="H219" s="12" t="inlineStr"/>
+      <c r="I219" s="12" t="inlineStr"/>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="11" t="inlineStr">
+        <is>
+          <t>50-350 Yapraklı</t>
+        </is>
+      </c>
+      <c r="B220" s="12" t="inlineStr"/>
+      <c r="C220" s="12" t="inlineStr"/>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>75TL</t>
+        </is>
+      </c>
+      <c r="E220" s="12" t="inlineStr"/>
+      <c r="F220" s="12" t="inlineStr"/>
+      <c r="G220" s="12" t="inlineStr"/>
+      <c r="H220" s="12" t="inlineStr"/>
+      <c r="I220" s="12" t="inlineStr"/>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Şube - TP/YP</t>
+        </is>
+      </c>
+      <c r="B221" s="12" t="inlineStr"/>
+      <c r="C221" s="12" t="inlineStr"/>
+      <c r="D221" s="12" t="inlineStr"/>
+      <c r="E221" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="F221" s="12" t="inlineStr"/>
+      <c r="G221" s="12" t="inlineStr"/>
+      <c r="H221" s="12" t="inlineStr"/>
+      <c r="I221" s="12" t="inlineStr"/>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>Diğer Şube - TP/YP</t>
+        </is>
+      </c>
+      <c r="B222" s="12" t="inlineStr"/>
+      <c r="C222" s="12" t="inlineStr"/>
+      <c r="D222" s="12" t="inlineStr"/>
+      <c r="E222" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="F222" s="12" t="inlineStr"/>
+      <c r="G222" s="12" t="inlineStr"/>
+      <c r="H222" s="12" t="inlineStr"/>
+      <c r="I222" s="12" t="inlineStr"/>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="11" t="inlineStr">
+        <is>
+          <t>Senet İade - TP/YP</t>
+        </is>
+      </c>
+      <c r="B223" s="12" t="inlineStr"/>
+      <c r="C223" s="12" t="inlineStr"/>
+      <c r="D223" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E223" s="12" t="inlineStr"/>
+      <c r="F223" s="12" t="inlineStr"/>
+      <c r="G223" s="12" t="inlineStr"/>
+      <c r="H223" s="12" t="inlineStr"/>
+      <c r="I223" s="12" t="inlineStr"/>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto Kaldırma</t>
+        </is>
+      </c>
+      <c r="B224" s="12" t="inlineStr"/>
+      <c r="C224" s="12" t="inlineStr"/>
+      <c r="D224" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E224" s="12" t="inlineStr"/>
+      <c r="F224" s="12" t="inlineStr"/>
+      <c r="G224" s="12" t="inlineStr"/>
+      <c r="H224" s="12" t="inlineStr"/>
+      <c r="I224" s="12" t="inlineStr"/>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protestosu - TP/YP</t>
+        </is>
+      </c>
+      <c r="B225" s="12" t="inlineStr"/>
+      <c r="C225" s="12" t="inlineStr"/>
+      <c r="D225" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E225" s="12" t="inlineStr"/>
+      <c r="F225" s="12" t="inlineStr"/>
+      <c r="G225" s="12" t="inlineStr"/>
+      <c r="H225" s="12" t="inlineStr"/>
+      <c r="I225" s="12" t="inlineStr"/>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="11" t="inlineStr">
+        <is>
+          <t>10 Yapraklı Çek Karnesi</t>
+        </is>
+      </c>
+      <c r="B226" s="12" t="inlineStr"/>
+      <c r="C226" s="12" t="inlineStr"/>
+      <c r="D226" s="12" t="inlineStr"/>
+      <c r="E226" s="12" t="inlineStr"/>
+      <c r="F226" s="12" t="inlineStr">
+        <is>
+          <t>952,38 TL</t>
+        </is>
+      </c>
+      <c r="G226" s="12" t="inlineStr"/>
+      <c r="H226" s="12" t="inlineStr"/>
+      <c r="I226" s="12" t="inlineStr"/>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>25 yapraklı çek karnesi</t>
+        </is>
+      </c>
+      <c r="B227" s="12" t="inlineStr"/>
+      <c r="C227" s="12" t="inlineStr"/>
+      <c r="D227" s="12" t="inlineStr"/>
+      <c r="E227" s="12" t="inlineStr"/>
+      <c r="F227" s="12" t="inlineStr">
+        <is>
+          <t>2.380,95 TL</t>
+        </is>
+      </c>
+      <c r="G227" s="12" t="inlineStr"/>
+      <c r="H227" s="12" t="inlineStr"/>
+      <c r="I227" s="12" t="inlineStr"/>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>TL ve YP Tahsile Alınan Çek (hesaba yatan)</t>
+        </is>
+      </c>
+      <c r="B228" s="12" t="inlineStr"/>
+      <c r="C228" s="12" t="inlineStr"/>
+      <c r="D228" s="12" t="inlineStr"/>
+      <c r="E228" s="12" t="inlineStr"/>
+      <c r="F228" s="12" t="inlineStr">
+        <is>
+          <t>380,95 TL</t>
+        </is>
+      </c>
+      <c r="G228" s="12" t="inlineStr"/>
+      <c r="H228" s="12" t="inlineStr"/>
+      <c r="I228" s="12" t="inlineStr"/>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>TL ve YP Tahsile Alınan Çek (nakit ödenen)</t>
+        </is>
+      </c>
+      <c r="B229" s="12" t="inlineStr"/>
+      <c r="C229" s="12" t="inlineStr"/>
+      <c r="D229" s="12" t="inlineStr"/>
+      <c r="E229" s="12" t="inlineStr"/>
+      <c r="F229" s="12" t="inlineStr">
+        <is>
+          <t>571,43 TL</t>
+        </is>
+      </c>
+      <c r="G229" s="12" t="inlineStr"/>
+      <c r="H229" s="12" t="inlineStr"/>
+      <c r="I229" s="12" t="inlineStr"/>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="11" t="inlineStr">
+        <is>
+          <t>Bloke Çek Ödeme</t>
+        </is>
+      </c>
+      <c r="B230" s="12" t="inlineStr"/>
+      <c r="C230" s="12" t="inlineStr"/>
+      <c r="D230" s="12" t="inlineStr"/>
+      <c r="E230" s="12" t="inlineStr"/>
+      <c r="F230" s="12" t="inlineStr">
+        <is>
+          <t>714,29 TL</t>
+        </is>
+      </c>
+      <c r="G230" s="12" t="inlineStr"/>
+      <c r="H230" s="12" t="inlineStr"/>
+      <c r="I230" s="12" t="inlineStr"/>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>Başka Banka YP Çek (Anlaşmalı Bankalar)</t>
+        </is>
+      </c>
+      <c r="B231" s="12" t="inlineStr"/>
+      <c r="C231" s="12" t="inlineStr"/>
+      <c r="D231" s="12" t="inlineStr"/>
+      <c r="E231" s="12" t="inlineStr"/>
+      <c r="F231" s="12" t="inlineStr">
+        <is>
+          <t>1.543 TL</t>
+        </is>
+      </c>
+      <c r="G231" s="12" t="inlineStr"/>
+      <c r="H231" s="12" t="inlineStr"/>
+      <c r="I231" s="12" t="inlineStr"/>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="11" t="inlineStr">
+        <is>
+          <t>Bloke Çek Düzenleme</t>
+        </is>
+      </c>
+      <c r="B232" s="12" t="inlineStr"/>
+      <c r="C232" s="12" t="inlineStr"/>
+      <c r="D232" s="12" t="inlineStr"/>
+      <c r="E232" s="12" t="inlineStr"/>
+      <c r="F232" s="12" t="inlineStr">
+        <is>
+          <t>761,90 TL</t>
+        </is>
+      </c>
+      <c r="G232" s="12" t="inlineStr"/>
+      <c r="H232" s="12" t="inlineStr"/>
+      <c r="I232" s="12" t="inlineStr"/>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>KKB Çek Bilgileri Raporu Ücreti (Rapor Başına)</t>
+        </is>
+      </c>
+      <c r="B233" s="12" t="inlineStr"/>
+      <c r="C233" s="12" t="inlineStr"/>
+      <c r="D233" s="12" t="inlineStr"/>
+      <c r="E233" s="12" t="inlineStr"/>
+      <c r="F233" s="12" t="inlineStr">
+        <is>
+          <t>95,24 TL</t>
+        </is>
+      </c>
+      <c r="G233" s="12" t="inlineStr"/>
+      <c r="H233" s="12" t="inlineStr"/>
+      <c r="I233" s="12" t="inlineStr"/>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="11" t="inlineStr">
+        <is>
+          <t>Akbank Mobil ve İnternet*KKB Çek Risk Raporu</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr"/>
+      <c r="C234" s="12" t="inlineStr"/>
+      <c r="D234" s="12" t="inlineStr"/>
+      <c r="E234" s="12" t="inlineStr"/>
+      <c r="F234" s="12" t="inlineStr">
+        <is>
+          <t>95,24 TL</t>
+        </is>
+      </c>
+      <c r="G234" s="12" t="inlineStr"/>
+      <c r="H234" s="12" t="inlineStr"/>
+      <c r="I234" s="12" t="inlineStr"/>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>Çeklerin İşlemsiz İadesini İsteme</t>
+        </is>
+      </c>
+      <c r="B235" s="12" t="inlineStr"/>
+      <c r="C235" s="12" t="inlineStr"/>
+      <c r="D235" s="12" t="inlineStr"/>
+      <c r="E235" s="12" t="inlineStr"/>
+      <c r="F235" s="12" t="inlineStr">
+        <is>
+          <t>380,95 TL</t>
+        </is>
+      </c>
+      <c r="G235" s="12" t="inlineStr"/>
+      <c r="H235" s="12" t="inlineStr"/>
+      <c r="I235" s="12" t="inlineStr"/>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>TL ve YP Farklı Şubeden Tahsile Alınan Çek (nakit ödenen)</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="inlineStr"/>
+      <c r="C236" s="12" t="inlineStr"/>
+      <c r="D236" s="12" t="inlineStr"/>
+      <c r="E236" s="12" t="inlineStr"/>
+      <c r="F236" s="12" t="inlineStr"/>
+      <c r="G236" s="12" t="inlineStr">
+        <is>
+          <t>585,71 TL</t>
+        </is>
+      </c>
+      <c r="H236" s="12" t="inlineStr"/>
+      <c r="I236" s="12" t="inlineStr"/>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>DTH'dan Çek Düzenlenmesi</t>
+        </is>
+      </c>
+      <c r="B237" s="12" t="inlineStr"/>
+      <c r="C237" s="12" t="inlineStr"/>
+      <c r="D237" s="12" t="inlineStr"/>
+      <c r="E237" s="12" t="inlineStr"/>
+      <c r="F237" s="12" t="inlineStr">
+        <is>
+          <t>571,43 TL / 1 %</t>
+        </is>
+      </c>
+      <c r="G237" s="12" t="inlineStr"/>
+      <c r="H237" s="12" t="inlineStr"/>
+      <c r="I237" s="12" t="inlineStr"/>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="11" t="inlineStr">
+        <is>
+          <t>Seyahat Çek İştirası (TL/YP Ödemeler)</t>
+        </is>
+      </c>
+      <c r="B238" s="12" t="inlineStr"/>
+      <c r="C238" s="12" t="inlineStr"/>
+      <c r="D238" s="12" t="inlineStr"/>
+      <c r="E238" s="12" t="inlineStr"/>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>571,43 TL / 1 %</t>
+        </is>
+      </c>
+      <c r="G238" s="12" t="inlineStr"/>
+      <c r="H238" s="12" t="inlineStr"/>
+      <c r="I238" s="12" t="inlineStr"/>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="11" t="inlineStr">
+        <is>
+          <t>Tahsile Alınan Dövizli Çekler</t>
+        </is>
+      </c>
+      <c r="B239" s="12" t="inlineStr"/>
+      <c r="C239" s="12" t="inlineStr"/>
+      <c r="D239" s="12" t="inlineStr"/>
+      <c r="E239" s="12" t="inlineStr"/>
+      <c r="F239" s="12" t="inlineStr">
+        <is>
+          <t>1.666,67 TL</t>
+        </is>
+      </c>
+      <c r="G239" s="12" t="inlineStr"/>
+      <c r="H239" s="12" t="inlineStr"/>
+      <c r="I239" s="12" t="inlineStr"/>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="11" t="inlineStr">
+        <is>
+          <t>İbrazında Ödenen Dövizli Çekler</t>
+        </is>
+      </c>
+      <c r="B240" s="12" t="inlineStr"/>
+      <c r="C240" s="12" t="inlineStr"/>
+      <c r="D240" s="12" t="inlineStr"/>
+      <c r="E240" s="12" t="inlineStr"/>
+      <c r="F240" s="12" t="inlineStr">
+        <is>
+          <t>2.095,24 TL / 1 %</t>
+        </is>
+      </c>
+      <c r="G240" s="12" t="inlineStr"/>
+      <c r="H240" s="12" t="inlineStr"/>
+      <c r="I240" s="12" t="inlineStr"/>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>Senet tahsili</t>
+        </is>
+      </c>
+      <c r="B241" s="12" t="inlineStr"/>
+      <c r="C241" s="12" t="inlineStr"/>
+      <c r="D241" s="12" t="inlineStr"/>
+      <c r="E241" s="12" t="inlineStr"/>
+      <c r="F241" s="12" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G241" s="12" t="inlineStr"/>
+      <c r="H241" s="12" t="inlineStr"/>
+      <c r="I241" s="12" t="inlineStr"/>
+    </row>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protestosu</t>
+        </is>
+      </c>
+      <c r="B242" s="12" t="inlineStr"/>
+      <c r="C242" s="12" t="inlineStr"/>
+      <c r="D242" s="12" t="inlineStr"/>
+      <c r="E242" s="12" t="inlineStr"/>
+      <c r="F242" s="12" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G242" s="12" t="inlineStr"/>
+      <c r="H242" s="12" t="inlineStr"/>
+      <c r="I242" s="12" t="inlineStr"/>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>Teminat Senet Tahsili(TL ve YP)</t>
+        </is>
+      </c>
+      <c r="B243" s="12" t="inlineStr"/>
+      <c r="C243" s="12" t="inlineStr"/>
+      <c r="D243" s="12" t="inlineStr"/>
+      <c r="E243" s="12" t="inlineStr"/>
+      <c r="F243" s="12" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G243" s="12" t="inlineStr"/>
+      <c r="H243" s="12" t="inlineStr"/>
+      <c r="I243" s="12" t="inlineStr"/>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protestosu Kaldırı Ücreti</t>
+        </is>
+      </c>
+      <c r="B244" s="12" t="inlineStr"/>
+      <c r="C244" s="12" t="inlineStr"/>
+      <c r="D244" s="12" t="inlineStr"/>
+      <c r="E244" s="12" t="inlineStr"/>
+      <c r="F244" s="12" t="inlineStr">
+        <is>
+          <t>619,05 TL</t>
+        </is>
+      </c>
+      <c r="G244" s="12" t="inlineStr"/>
+      <c r="H244" s="12" t="inlineStr"/>
+      <c r="I244" s="12" t="inlineStr"/>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="11" t="inlineStr">
+        <is>
+          <t>Senet İadesi</t>
+        </is>
+      </c>
+      <c r="B245" s="12" t="inlineStr"/>
+      <c r="C245" s="12" t="inlineStr"/>
+      <c r="D245" s="12" t="inlineStr"/>
+      <c r="E245" s="12" t="inlineStr"/>
+      <c r="F245" s="12" t="inlineStr">
+        <is>
+          <t>571,43 TL</t>
+        </is>
+      </c>
+      <c r="G245" s="12" t="inlineStr"/>
+      <c r="H245" s="12" t="inlineStr"/>
+      <c r="I245" s="12" t="inlineStr"/>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>Teminat Senet Protestosu</t>
+        </is>
+      </c>
+      <c r="B246" s="12" t="inlineStr"/>
+      <c r="C246" s="12" t="inlineStr"/>
+      <c r="D246" s="12" t="inlineStr"/>
+      <c r="E246" s="12" t="inlineStr"/>
+      <c r="F246" s="12" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G246" s="12" t="inlineStr"/>
+      <c r="H246" s="12" t="inlineStr"/>
+      <c r="I246" s="12" t="inlineStr"/>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="11" t="inlineStr">
+        <is>
+          <t>Teminat Senet İadesi</t>
+        </is>
+      </c>
+      <c r="B247" s="12" t="inlineStr"/>
+      <c r="C247" s="12" t="inlineStr"/>
+      <c r="D247" s="12" t="inlineStr"/>
+      <c r="E247" s="12" t="inlineStr"/>
+      <c r="F247" s="12" t="inlineStr">
+        <is>
+          <t>571,43 TL</t>
+        </is>
+      </c>
+      <c r="G247" s="12" t="inlineStr"/>
+      <c r="H247" s="12" t="inlineStr"/>
+      <c r="I247" s="12" t="inlineStr"/>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Şube Karşılıksız Çek Elden Ödeme Tl</t>
+        </is>
+      </c>
+      <c r="B248" s="12" t="inlineStr"/>
+      <c r="C248" s="12" t="inlineStr"/>
+      <c r="D248" s="12" t="inlineStr"/>
+      <c r="E248" s="12" t="inlineStr"/>
+      <c r="F248" s="12" t="inlineStr"/>
+      <c r="G248" s="12" t="inlineStr"/>
+      <c r="H248" s="12" t="inlineStr"/>
+      <c r="I248" s="12" t="inlineStr">
+        <is>
+          <t>427,62 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Şube Karşılıksız Çek Elden Ödeme Yp</t>
+        </is>
+      </c>
+      <c r="B249" s="12" t="inlineStr"/>
+      <c r="C249" s="12" t="inlineStr"/>
+      <c r="D249" s="12" t="inlineStr"/>
+      <c r="E249" s="12" t="inlineStr"/>
+      <c r="F249" s="12" t="inlineStr"/>
+      <c r="G249" s="12" t="inlineStr"/>
+      <c r="H249" s="12" t="inlineStr"/>
+      <c r="I249" s="12" t="inlineStr">
+        <is>
+          <t>427,62 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Şube Çek Ödeme TL / YP</t>
+        </is>
+      </c>
+      <c r="B250" s="12" t="inlineStr"/>
+      <c r="C250" s="12" t="inlineStr"/>
+      <c r="D250" s="12" t="inlineStr"/>
+      <c r="E250" s="12" t="inlineStr"/>
+      <c r="F250" s="12" t="inlineStr"/>
+      <c r="G250" s="12" t="inlineStr"/>
+      <c r="H250" s="12" t="inlineStr"/>
+      <c r="I250" s="12" t="inlineStr">
+        <is>
+          <t>427,62 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="11" t="inlineStr">
+        <is>
+          <t>Başka Şube Çek Ödeme TL/YP</t>
+        </is>
+      </c>
+      <c r="B251" s="12" t="inlineStr"/>
+      <c r="C251" s="12" t="inlineStr"/>
+      <c r="D251" s="12" t="inlineStr"/>
+      <c r="E251" s="12" t="inlineStr"/>
+      <c r="F251" s="12" t="inlineStr"/>
+      <c r="G251" s="12" t="inlineStr"/>
+      <c r="H251" s="12" t="inlineStr"/>
+      <c r="I251" s="12" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>Başka Şube Karşılıksız Çek Elden Ödeme Tl</t>
+        </is>
+      </c>
+      <c r="B252" s="12" t="inlineStr"/>
+      <c r="C252" s="12" t="inlineStr"/>
+      <c r="D252" s="12" t="inlineStr"/>
+      <c r="E252" s="12" t="inlineStr"/>
+      <c r="F252" s="12" t="inlineStr"/>
+      <c r="G252" s="12" t="inlineStr"/>
+      <c r="H252" s="12" t="inlineStr"/>
+      <c r="I252" s="12" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>Başka Şube Karşılıksız Çek Elden Ödeme Yp</t>
+        </is>
+      </c>
+      <c r="B253" s="12" t="inlineStr"/>
+      <c r="C253" s="12" t="inlineStr"/>
+      <c r="D253" s="12" t="inlineStr"/>
+      <c r="E253" s="12" t="inlineStr"/>
+      <c r="F253" s="12" t="inlineStr"/>
+      <c r="G253" s="12" t="inlineStr"/>
+      <c r="H253" s="12" t="inlineStr"/>
+      <c r="I253" s="12" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>KKB Çek Sorgu Raporu</t>
+        </is>
+      </c>
+      <c r="B254" s="12" t="inlineStr"/>
+      <c r="C254" s="12" t="inlineStr"/>
+      <c r="D254" s="12" t="inlineStr"/>
+      <c r="E254" s="12" t="inlineStr"/>
+      <c r="F254" s="12" t="inlineStr"/>
+      <c r="G254" s="12" t="inlineStr"/>
+      <c r="H254" s="12" t="inlineStr">
+        <is>
+          <t>47,5 TL</t>
+        </is>
+      </c>
+      <c r="I254" s="12" t="inlineStr"/>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="11" t="inlineStr">
+        <is>
+          <t>KKB Risk Raporu Sorgulama Ücreti (Bireysel)</t>
+        </is>
+      </c>
+      <c r="B255" s="12" t="inlineStr"/>
+      <c r="C255" s="12" t="inlineStr"/>
+      <c r="D255" s="12" t="inlineStr"/>
+      <c r="E255" s="12" t="inlineStr"/>
+      <c r="F255" s="12" t="inlineStr"/>
+      <c r="G255" s="12" t="inlineStr"/>
+      <c r="H255" s="12" t="inlineStr">
+        <is>
+          <t>94,29 TL</t>
+        </is>
+      </c>
+      <c r="I255" s="12" t="inlineStr"/>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="11" t="inlineStr">
+        <is>
+          <t>Karşılıksız Çek Düzeltme Hakkı Kullandırma</t>
+        </is>
+      </c>
+      <c r="B256" s="12" t="inlineStr"/>
+      <c r="C256" s="12" t="inlineStr"/>
+      <c r="D256" s="12" t="inlineStr"/>
+      <c r="E256" s="12" t="inlineStr"/>
+      <c r="F256" s="12" t="inlineStr"/>
+      <c r="G256" s="12" t="inlineStr"/>
+      <c r="H256" s="12" t="inlineStr">
+        <is>
+          <t>371,43 TL</t>
+        </is>
+      </c>
+      <c r="I256" s="12" t="inlineStr"/>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="11" t="inlineStr">
+        <is>
+          <t>Yurt Dışına Müşteri Çeki Ödemesi</t>
+        </is>
+      </c>
+      <c r="B257" s="12" t="inlineStr"/>
+      <c r="C257" s="12" t="inlineStr"/>
+      <c r="D257" s="12" t="inlineStr"/>
+      <c r="E257" s="12" t="inlineStr"/>
+      <c r="F257" s="12" t="inlineStr"/>
+      <c r="G257" s="12" t="inlineStr"/>
+      <c r="H257" s="12" t="inlineStr">
+        <is>
+          <t>675,24 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I257" s="12" t="inlineStr"/>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>Diğer Banka YP Çek Takas Masrafı</t>
+        </is>
+      </c>
+      <c r="B258" s="12" t="inlineStr"/>
+      <c r="C258" s="12" t="inlineStr"/>
+      <c r="D258" s="12" t="inlineStr"/>
+      <c r="E258" s="12" t="inlineStr"/>
+      <c r="F258" s="12" t="inlineStr"/>
+      <c r="G258" s="12" t="inlineStr"/>
+      <c r="H258" s="12" t="inlineStr">
+        <is>
+          <t>1.469,52 TL</t>
+        </is>
+      </c>
+      <c r="I258" s="12" t="inlineStr"/>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="11" t="inlineStr">
+        <is>
+          <t>Hesaba Ödeme</t>
+        </is>
+      </c>
+      <c r="B259" s="12" t="inlineStr"/>
+      <c r="C259" s="12" t="inlineStr"/>
+      <c r="D259" s="12" t="inlineStr"/>
+      <c r="E259" s="12" t="inlineStr"/>
+      <c r="F259" s="12" t="inlineStr"/>
+      <c r="G259" s="12" t="inlineStr"/>
+      <c r="H259" s="12" t="inlineStr">
+        <is>
+          <t>427,62 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I259" s="12" t="inlineStr"/>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t>Efektif Ödeme</t>
+        </is>
+      </c>
+      <c r="B260" s="12" t="inlineStr"/>
+      <c r="C260" s="12" t="inlineStr"/>
+      <c r="D260" s="12" t="inlineStr"/>
+      <c r="E260" s="12" t="inlineStr"/>
+      <c r="F260" s="12" t="inlineStr"/>
+      <c r="G260" s="12" t="inlineStr"/>
+      <c r="H260" s="12" t="inlineStr">
+        <is>
+          <t>427,62 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I260" s="12" t="inlineStr"/>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>Seyahat Çeki Ödeme</t>
+        </is>
+      </c>
+      <c r="B261" s="12" t="inlineStr"/>
+      <c r="C261" s="12" t="inlineStr"/>
+      <c r="D261" s="12" t="inlineStr"/>
+      <c r="E261" s="12" t="inlineStr"/>
+      <c r="F261" s="12" t="inlineStr"/>
+      <c r="G261" s="12" t="inlineStr"/>
+      <c r="H261" s="12" t="inlineStr">
+        <is>
+          <t>190,48 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I261" s="12" t="inlineStr"/>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>Muhabir Bankalar Tarafından Bankamız Üzerine Keşide Edilen Çekler</t>
+        </is>
+      </c>
+      <c r="B262" s="12" t="inlineStr"/>
+      <c r="C262" s="12" t="inlineStr"/>
+      <c r="D262" s="12" t="inlineStr"/>
+      <c r="E262" s="12" t="inlineStr"/>
+      <c r="F262" s="12" t="inlineStr"/>
+      <c r="G262" s="12" t="inlineStr"/>
+      <c r="H262" s="12" t="inlineStr">
+        <is>
+          <t>160,95 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I262" s="12" t="inlineStr"/>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="A263" s="11" t="inlineStr">
+        <is>
+          <t>Keşide Çeki / Bloke Çek Düzenleme</t>
+        </is>
+      </c>
+      <c r="B263" s="12" t="inlineStr"/>
+      <c r="C263" s="12" t="inlineStr"/>
+      <c r="D263" s="12" t="inlineStr"/>
+      <c r="E263" s="12" t="inlineStr"/>
+      <c r="F263" s="12" t="inlineStr"/>
+      <c r="G263" s="12" t="inlineStr"/>
+      <c r="H263" s="12" t="inlineStr">
+        <is>
+          <t>544,76 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I263" s="12" t="inlineStr"/>
+    </row>
+    <row r="264" ht="20" customHeight="1">
+      <c r="A264" s="11" t="inlineStr">
+        <is>
+          <t>Kurye Masrafı (Tahsil - İştira YP Çek İşlemleri ) / Çek Başına</t>
+        </is>
+      </c>
+      <c r="B264" s="12" t="inlineStr"/>
+      <c r="C264" s="12" t="inlineStr"/>
+      <c r="D264" s="12" t="inlineStr"/>
+      <c r="E264" s="12" t="inlineStr"/>
+      <c r="F264" s="12" t="inlineStr"/>
+      <c r="G264" s="12" t="inlineStr"/>
+      <c r="H264" s="12" t="inlineStr">
+        <is>
+          <t>5 USD</t>
+        </is>
+      </c>
+      <c r="I264" s="12" t="inlineStr"/>
+    </row>
+    <row r="265" ht="20" customHeight="1">
+      <c r="A265" s="11" t="inlineStr">
+        <is>
+          <t>İştira Kaydıyla Alınan YP Çekler- Ülke ve Döviz Cinsi Farklı Olan</t>
+        </is>
+      </c>
+      <c r="B265" s="12" t="inlineStr"/>
+      <c r="C265" s="12" t="inlineStr"/>
+      <c r="D265" s="12" t="inlineStr"/>
+      <c r="E265" s="12" t="inlineStr"/>
+      <c r="F265" s="12" t="inlineStr"/>
+      <c r="G265" s="12" t="inlineStr"/>
+      <c r="H265" s="12" t="inlineStr">
+        <is>
+          <t>440 TL / 1</t>
+        </is>
+      </c>
+      <c r="I265" s="12" t="inlineStr"/>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="11" t="inlineStr">
+        <is>
+          <t>İştira Kaydıyla Alınan YP Çekler- TL Ödeme</t>
+        </is>
+      </c>
+      <c r="B266" s="12" t="inlineStr"/>
+      <c r="C266" s="12" t="inlineStr"/>
+      <c r="D266" s="12" t="inlineStr"/>
+      <c r="E266" s="12" t="inlineStr"/>
+      <c r="F266" s="12" t="inlineStr"/>
+      <c r="G266" s="12" t="inlineStr"/>
+      <c r="H266" s="12" t="inlineStr">
+        <is>
+          <t>440 TL / 0,5</t>
+        </is>
+      </c>
+      <c r="I266" s="12" t="inlineStr"/>
+    </row>
+    <row r="267" ht="20" customHeight="1">
+      <c r="A267" s="11" t="inlineStr">
+        <is>
+          <t>İştira Kaydıyla Alınan YP Çekler- Efektif Ödeme</t>
+        </is>
+      </c>
+      <c r="B267" s="12" t="inlineStr"/>
+      <c r="C267" s="12" t="inlineStr"/>
+      <c r="D267" s="12" t="inlineStr"/>
+      <c r="E267" s="12" t="inlineStr"/>
+      <c r="F267" s="12" t="inlineStr"/>
+      <c r="G267" s="12" t="inlineStr"/>
+      <c r="H267" s="12" t="inlineStr">
+        <is>
+          <t>440 TL / 1</t>
+        </is>
+      </c>
+      <c r="I267" s="12" t="inlineStr"/>
+    </row>
+    <row r="268" ht="20" customHeight="1">
+      <c r="A268" s="11" t="inlineStr">
+        <is>
+          <t>Tahsile Verilen Çekin İşlemsiz İadesi</t>
+        </is>
+      </c>
+      <c r="B268" s="12" t="inlineStr"/>
+      <c r="C268" s="12" t="inlineStr"/>
+      <c r="D268" s="12" t="inlineStr"/>
+      <c r="E268" s="12" t="inlineStr"/>
+      <c r="F268" s="12" t="inlineStr"/>
+      <c r="G268" s="12" t="inlineStr"/>
+      <c r="H268" s="12" t="inlineStr">
+        <is>
+          <t>123,81 TL</t>
+        </is>
+      </c>
+      <c r="I268" s="12" t="inlineStr"/>
+    </row>
+    <row r="269" ht="20" customHeight="1">
+      <c r="A269" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilatı- YKB Çeki (YP)</t>
+        </is>
+      </c>
+      <c r="B269" s="12" t="inlineStr"/>
+      <c r="C269" s="12" t="inlineStr"/>
+      <c r="D269" s="12" t="inlineStr"/>
+      <c r="E269" s="12" t="inlineStr"/>
+      <c r="F269" s="12" t="inlineStr"/>
+      <c r="G269" s="12" t="inlineStr"/>
+      <c r="H269" s="12" t="inlineStr">
+        <is>
+          <t>361,9 TL</t>
+        </is>
+      </c>
+      <c r="I269" s="12" t="inlineStr"/>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilatı- YKB Çeki (TL)</t>
+        </is>
+      </c>
+      <c r="B270" s="12" t="inlineStr"/>
+      <c r="C270" s="12" t="inlineStr"/>
+      <c r="D270" s="12" t="inlineStr"/>
+      <c r="E270" s="12" t="inlineStr"/>
+      <c r="F270" s="12" t="inlineStr"/>
+      <c r="G270" s="12" t="inlineStr"/>
+      <c r="H270" s="12" t="inlineStr">
+        <is>
+          <t>361,9 TL</t>
+        </is>
+      </c>
+      <c r="I270" s="12" t="inlineStr"/>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilatı -Yurtiçi Banka Çeki (YP)</t>
+        </is>
+      </c>
+      <c r="B271" s="12" t="inlineStr"/>
+      <c r="C271" s="12" t="inlineStr"/>
+      <c r="D271" s="12" t="inlineStr"/>
+      <c r="E271" s="12" t="inlineStr"/>
+      <c r="F271" s="12" t="inlineStr"/>
+      <c r="G271" s="12" t="inlineStr"/>
+      <c r="H271" s="12" t="inlineStr">
+        <is>
+          <t>361,9 TL</t>
+        </is>
+      </c>
+      <c r="I271" s="12" t="inlineStr"/>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilatı - Yurtiçi Banka Çeki (TL)</t>
+        </is>
+      </c>
+      <c r="B272" s="12" t="inlineStr"/>
+      <c r="C272" s="12" t="inlineStr"/>
+      <c r="D272" s="12" t="inlineStr"/>
+      <c r="E272" s="12" t="inlineStr"/>
+      <c r="F272" s="12" t="inlineStr"/>
+      <c r="G272" s="12" t="inlineStr"/>
+      <c r="H272" s="12" t="inlineStr">
+        <is>
+          <t>361,9 TL</t>
+        </is>
+      </c>
+      <c r="I272" s="12" t="inlineStr"/>
+    </row>
+    <row r="273" ht="20" customHeight="1">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Komisyonu- 10'luk Çek Karnesi</t>
+        </is>
+      </c>
+      <c r="B273" s="12" t="inlineStr"/>
+      <c r="C273" s="12" t="inlineStr"/>
+      <c r="D273" s="12" t="inlineStr"/>
+      <c r="E273" s="12" t="inlineStr"/>
+      <c r="F273" s="12" t="inlineStr"/>
+      <c r="G273" s="12" t="inlineStr"/>
+      <c r="H273" s="12" t="inlineStr">
+        <is>
+          <t>866,67 TL</t>
+        </is>
+      </c>
+      <c r="I273" s="12" t="inlineStr"/>
+    </row>
+    <row r="274" ht="20" customHeight="1">
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Komisyonu- 25'lik Çek Karnesi</t>
+        </is>
+      </c>
+      <c r="B274" s="12" t="inlineStr"/>
+      <c r="C274" s="12" t="inlineStr"/>
+      <c r="D274" s="12" t="inlineStr"/>
+      <c r="E274" s="12" t="inlineStr"/>
+      <c r="F274" s="12" t="inlineStr"/>
+      <c r="G274" s="12" t="inlineStr"/>
+      <c r="H274" s="12" t="inlineStr">
+        <is>
+          <t>2.166,67 TL</t>
+        </is>
+      </c>
+      <c r="I274" s="12" t="inlineStr"/>
+    </row>
+    <row r="275" ht="20" customHeight="1">
+      <c r="A275" s="11" t="inlineStr">
+        <is>
+          <t>Çek Karnesi Komisyonu- 100'lük Sürekli Form</t>
+        </is>
+      </c>
+      <c r="B275" s="12" t="inlineStr"/>
+      <c r="C275" s="12" t="inlineStr"/>
+      <c r="D275" s="12" t="inlineStr"/>
+      <c r="E275" s="12" t="inlineStr"/>
+      <c r="F275" s="12" t="inlineStr"/>
+      <c r="G275" s="12" t="inlineStr"/>
+      <c r="H275" s="12" t="inlineStr">
+        <is>
+          <t>8.666,67 TL</t>
+        </is>
+      </c>
+      <c r="I275" s="12" t="inlineStr"/>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="11" t="inlineStr">
+        <is>
+          <t>Dövizi Natık Çek Ödemeyi Durdurma İşlemi</t>
+        </is>
+      </c>
+      <c r="B276" s="12" t="inlineStr"/>
+      <c r="C276" s="12" t="inlineStr"/>
+      <c r="D276" s="12" t="inlineStr"/>
+      <c r="E276" s="12" t="inlineStr"/>
+      <c r="F276" s="12" t="inlineStr"/>
+      <c r="G276" s="12" t="inlineStr"/>
+      <c r="H276" s="12" t="inlineStr">
+        <is>
+          <t>260 TL</t>
+        </is>
+      </c>
+      <c r="I276" s="12" t="inlineStr"/>
+    </row>
+    <row r="277" ht="20" customHeight="1">
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>Dövizi Natık Çek Düzenleme</t>
+        </is>
+      </c>
+      <c r="B277" s="12" t="inlineStr"/>
+      <c r="C277" s="12" t="inlineStr"/>
+      <c r="D277" s="12" t="inlineStr"/>
+      <c r="E277" s="12" t="inlineStr"/>
+      <c r="F277" s="12" t="inlineStr"/>
+      <c r="G277" s="12" t="inlineStr"/>
+      <c r="H277" s="12" t="inlineStr">
+        <is>
+          <t>359,05 TL</t>
+        </is>
+      </c>
+      <c r="I277" s="12" t="inlineStr"/>
+    </row>
+    <row r="278" ht="20" customHeight="1">
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>Armağan çeki Düzenleme</t>
+        </is>
+      </c>
+      <c r="B278" s="12" t="inlineStr"/>
+      <c r="C278" s="12" t="inlineStr"/>
+      <c r="D278" s="12" t="inlineStr"/>
+      <c r="E278" s="12" t="inlineStr"/>
+      <c r="F278" s="12" t="inlineStr"/>
+      <c r="G278" s="12" t="inlineStr"/>
+      <c r="H278" s="12" t="inlineStr">
+        <is>
+          <t>104,76 TL</t>
+        </is>
+      </c>
+      <c r="I278" s="12" t="inlineStr"/>
+    </row>
+    <row r="280" ht="16" customHeight="1">
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1">
+      <c r="A281" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Şube Gişeden Çek Ödemesi</t>
+        </is>
+      </c>
+      <c r="B281" s="12" t="inlineStr"/>
+      <c r="C281" s="12" t="inlineStr">
+        <is>
+          <t>438.10TL</t>
+        </is>
+      </c>
+      <c r="D281" s="12" t="inlineStr"/>
+      <c r="E281" s="12" t="inlineStr"/>
+      <c r="F281" s="12" t="inlineStr"/>
+      <c r="G281" s="12" t="inlineStr"/>
+      <c r="H281" s="12" t="inlineStr"/>
+      <c r="I281" s="12" t="inlineStr"/>
+    </row>
+    <row r="282" ht="20" customHeight="1">
+      <c r="A282" s="11" t="inlineStr">
+        <is>
+          <t>Başka Banka YP Çek Takasa Gönderme (Anlaşmalı Bankalar)</t>
+        </is>
+      </c>
+      <c r="B282" s="12" t="inlineStr">
+        <is>
+          <t>1469.52TL</t>
+        </is>
+      </c>
+      <c r="C282" s="12" t="inlineStr"/>
+      <c r="D282" s="12" t="inlineStr"/>
+      <c r="E282" s="12" t="inlineStr"/>
+      <c r="F282" s="12" t="inlineStr"/>
+      <c r="G282" s="12" t="inlineStr"/>
+      <c r="H282" s="12" t="inlineStr"/>
+      <c r="I282" s="12" t="inlineStr"/>
+    </row>
+    <row r="283" ht="20" customHeight="1">
+      <c r="A283" s="11" t="inlineStr">
+        <is>
+          <t>Başka Şube Gişeden Çek Ödemesi</t>
+        </is>
+      </c>
+      <c r="B283" s="12" t="inlineStr"/>
+      <c r="C283" s="12" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77%</t>
+        </is>
+      </c>
+      <c r="D283" s="12" t="inlineStr"/>
+      <c r="E283" s="12" t="inlineStr"/>
+      <c r="F283" s="12" t="inlineStr"/>
+      <c r="G283" s="12" t="inlineStr"/>
+      <c r="H283" s="12" t="inlineStr"/>
+      <c r="I283" s="12" t="inlineStr"/>
+    </row>
+    <row r="284" ht="20" customHeight="1">
+      <c r="A284" s="11" t="inlineStr">
+        <is>
+          <t>Bloke/Keşide Çeki Ödemesi</t>
+        </is>
+      </c>
+      <c r="B284" s="12" t="inlineStr">
+        <is>
+          <t>323.81TL</t>
+        </is>
+      </c>
+      <c r="C284" s="12" t="inlineStr"/>
+      <c r="D284" s="12" t="inlineStr"/>
+      <c r="E284" s="12" t="inlineStr"/>
+      <c r="F284" s="12" t="inlineStr"/>
+      <c r="G284" s="12" t="inlineStr"/>
+      <c r="H284" s="12" t="inlineStr"/>
+      <c r="I284" s="12" t="inlineStr"/>
+    </row>
+    <row r="285" ht="20" customHeight="1">
+      <c r="A285" s="11" t="inlineStr">
+        <is>
+          <t>Seyahat Çeki Ödemesi</t>
+        </is>
+      </c>
+      <c r="B285" s="12" t="inlineStr">
+        <is>
+          <t>323.81TL</t>
+        </is>
+      </c>
+      <c r="C285" s="12" t="inlineStr"/>
+      <c r="D285" s="12" t="inlineStr"/>
+      <c r="E285" s="12" t="inlineStr"/>
+      <c r="F285" s="12" t="inlineStr"/>
+      <c r="G285" s="12" t="inlineStr"/>
+      <c r="H285" s="12" t="inlineStr"/>
+      <c r="I285" s="12" t="inlineStr"/>
+    </row>
+    <row r="286" ht="20" customHeight="1">
+      <c r="A286" s="11" t="inlineStr">
+        <is>
+          <t>YP Çek Tahsilatı</t>
+        </is>
+      </c>
+      <c r="B286" s="12" t="inlineStr">
+        <is>
+          <t>45.00USD</t>
+        </is>
+      </c>
+      <c r="C286" s="12" t="inlineStr"/>
+      <c r="D286" s="12" t="inlineStr"/>
+      <c r="E286" s="12" t="inlineStr"/>
+      <c r="F286" s="12" t="inlineStr"/>
+      <c r="G286" s="12" t="inlineStr"/>
+      <c r="H286" s="12" t="inlineStr"/>
+      <c r="I286" s="12" t="inlineStr"/>
+    </row>
+    <row r="287" ht="20" customHeight="1">
+      <c r="A287" s="11" t="inlineStr">
+        <is>
+          <t>Bankamız Çeki (TL-YP) Tahsile Alma</t>
+        </is>
+      </c>
+      <c r="B287" s="12" t="inlineStr">
+        <is>
+          <t>257.15TL</t>
+        </is>
+      </c>
+      <c r="C287" s="12" t="inlineStr"/>
+      <c r="D287" s="12" t="inlineStr"/>
+      <c r="E287" s="12" t="inlineStr"/>
+      <c r="F287" s="12" t="inlineStr"/>
+      <c r="G287" s="12" t="inlineStr"/>
+      <c r="H287" s="12" t="inlineStr"/>
+      <c r="I287" s="12" t="inlineStr"/>
+    </row>
+    <row r="288" ht="20" customHeight="1">
+      <c r="A288" s="11" t="inlineStr">
+        <is>
+          <t>Başka Banka Çeki (TL-YP) Tahsile Alma</t>
+        </is>
+      </c>
+      <c r="B288" s="12" t="inlineStr">
+        <is>
+          <t>390.48TL</t>
+        </is>
+      </c>
+      <c r="C288" s="12" t="inlineStr"/>
+      <c r="D288" s="12" t="inlineStr"/>
+      <c r="E288" s="12" t="inlineStr"/>
+      <c r="F288" s="12" t="inlineStr"/>
+      <c r="G288" s="12" t="inlineStr"/>
+      <c r="H288" s="12" t="inlineStr"/>
+      <c r="I288" s="12" t="inlineStr"/>
+    </row>
+    <row r="290" ht="16" customHeight="1">
+      <c r="A290" s="10" t="inlineStr">
+        <is>
+          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="20" customHeight="1">
+      <c r="A291" s="11" t="inlineStr">
+        <is>
+          <t>Düzeltme Hakkı Kullandırma / Kısmi Ödeme</t>
+        </is>
+      </c>
+      <c r="B291" s="12" t="inlineStr">
+        <is>
+          <t>390.48TL / 0.58%</t>
+        </is>
+      </c>
+      <c r="C291" s="12" t="inlineStr"/>
+      <c r="D291" s="12" t="inlineStr"/>
+      <c r="E291" s="12" t="inlineStr"/>
+      <c r="F291" s="12" t="inlineStr"/>
+      <c r="G291" s="12" t="inlineStr"/>
+      <c r="H291" s="12" t="inlineStr"/>
+      <c r="I291" s="12" t="inlineStr"/>
+    </row>
+    <row r="292" ht="20" customHeight="1">
+      <c r="A292" s="11" t="inlineStr">
+        <is>
+          <t>Karşılıksız Çek Elden Ödeme</t>
+        </is>
+      </c>
+      <c r="B292" s="12" t="inlineStr">
+        <is>
+          <t>390.48TL</t>
+        </is>
+      </c>
+      <c r="C292" s="12" t="inlineStr"/>
+      <c r="D292" s="12" t="inlineStr"/>
+      <c r="E292" s="12" t="inlineStr"/>
+      <c r="F292" s="12" t="inlineStr"/>
+      <c r="G292" s="12" t="inlineStr"/>
+      <c r="H292" s="12" t="inlineStr"/>
+      <c r="I292" s="12" t="inlineStr"/>
+    </row>
+    <row r="294" ht="16" customHeight="1">
+      <c r="A294" s="10" t="inlineStr">
+        <is>
+          <t>Senet İade Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="20" customHeight="1">
+      <c r="A295" s="11" t="inlineStr">
+        <is>
+          <t>Senet Tahsili (Muhabir Bankada)</t>
+        </is>
+      </c>
+      <c r="B295" s="12" t="inlineStr"/>
+      <c r="C295" s="12" t="inlineStr"/>
+      <c r="D295" s="12" t="inlineStr"/>
+      <c r="E295" s="12" t="inlineStr"/>
+      <c r="F295" s="12" t="inlineStr"/>
+      <c r="G295" s="12" t="inlineStr"/>
+      <c r="H295" s="12" t="inlineStr">
         <is>
           <t>600 TL</t>
         </is>
       </c>
-      <c r="I98" s="12" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 13.08.2026 17:20</t>
+      <c r="I295" s="12" t="inlineStr"/>
+    </row>
+    <row r="296" ht="20" customHeight="1">
+      <c r="A296" s="11" t="inlineStr">
+        <is>
+          <t>Senet Tahsili (Bankamızda)</t>
+        </is>
+      </c>
+      <c r="B296" s="12" t="inlineStr"/>
+      <c r="C296" s="12" t="inlineStr"/>
+      <c r="D296" s="12" t="inlineStr"/>
+      <c r="E296" s="12" t="inlineStr"/>
+      <c r="F296" s="12" t="inlineStr"/>
+      <c r="G296" s="12" t="inlineStr"/>
+      <c r="H296" s="12" t="inlineStr">
+        <is>
+          <t>600 TL</t>
+        </is>
+      </c>
+      <c r="I296" s="12" t="inlineStr"/>
+    </row>
+    <row r="297" ht="20" customHeight="1">
+      <c r="A297" s="11" t="inlineStr">
+        <is>
+          <t>Senet İade (Protestolu/Protestosuz)</t>
+        </is>
+      </c>
+      <c r="B297" s="12" t="inlineStr"/>
+      <c r="C297" s="12" t="inlineStr"/>
+      <c r="D297" s="12" t="inlineStr"/>
+      <c r="E297" s="12" t="inlineStr"/>
+      <c r="F297" s="12" t="inlineStr"/>
+      <c r="G297" s="12" t="inlineStr"/>
+      <c r="H297" s="12" t="inlineStr">
+        <is>
+          <t>600 TL</t>
+        </is>
+      </c>
+      <c r="I297" s="12" t="inlineStr"/>
+    </row>
+    <row r="298" ht="20" customHeight="1">
+      <c r="A298" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto Kaldırma</t>
+        </is>
+      </c>
+      <c r="B298" s="12" t="inlineStr"/>
+      <c r="C298" s="12" t="inlineStr"/>
+      <c r="D298" s="12" t="inlineStr"/>
+      <c r="E298" s="12" t="inlineStr"/>
+      <c r="F298" s="12" t="inlineStr"/>
+      <c r="G298" s="12" t="inlineStr"/>
+      <c r="H298" s="12" t="inlineStr">
+        <is>
+          <t>551,43 TL</t>
+        </is>
+      </c>
+      <c r="I298" s="12" t="inlineStr"/>
+    </row>
+    <row r="299" ht="20" customHeight="1">
+      <c r="A299" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protestosu</t>
+        </is>
+      </c>
+      <c r="B299" s="12" t="inlineStr"/>
+      <c r="C299" s="12" t="inlineStr"/>
+      <c r="D299" s="12" t="inlineStr"/>
+      <c r="E299" s="12" t="inlineStr"/>
+      <c r="F299" s="12" t="inlineStr"/>
+      <c r="G299" s="12" t="inlineStr"/>
+      <c r="H299" s="12" t="inlineStr">
+        <is>
+          <t>600 TL</t>
+        </is>
+      </c>
+      <c r="I299" s="12" t="inlineStr"/>
+    </row>
+    <row r="301" ht="16" customHeight="1">
+      <c r="A301" s="10" t="inlineStr">
+        <is>
+          <t>Senet Protesto İşlemleri Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="20" customHeight="1">
+      <c r="A302" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto Kaldirimi</t>
+        </is>
+      </c>
+      <c r="B302" s="12" t="inlineStr">
+        <is>
+          <t>533.34TL</t>
+        </is>
+      </c>
+      <c r="C302" s="12" t="inlineStr"/>
+      <c r="D302" s="12" t="inlineStr"/>
+      <c r="E302" s="12" t="inlineStr"/>
+      <c r="F302" s="12" t="inlineStr"/>
+      <c r="G302" s="12" t="inlineStr"/>
+      <c r="H302" s="12" t="inlineStr"/>
+      <c r="I302" s="12" t="inlineStr"/>
+    </row>
+    <row r="303" ht="20" customHeight="1">
+      <c r="A303" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto Ücreti</t>
+        </is>
+      </c>
+      <c r="B303" s="12" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="C303" s="12" t="inlineStr"/>
+      <c r="D303" s="12" t="inlineStr"/>
+      <c r="E303" s="12" t="inlineStr"/>
+      <c r="F303" s="12" t="inlineStr"/>
+      <c r="G303" s="12" t="inlineStr"/>
+      <c r="H303" s="12" t="inlineStr"/>
+      <c r="I303" s="12" t="inlineStr"/>
+    </row>
+    <row r="305" ht="16" customHeight="1">
+      <c r="A305" s="10" t="inlineStr">
+        <is>
+          <t>Senet Tahsile Alma Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="20" customHeight="1">
+      <c r="A306" s="11" t="inlineStr">
+        <is>
+          <t>GB Şubesinden Senet Tahsilatı</t>
+        </is>
+      </c>
+      <c r="B306" s="12" t="inlineStr"/>
+      <c r="C306" s="12" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="D306" s="12" t="inlineStr"/>
+      <c r="E306" s="12" t="inlineStr"/>
+      <c r="F306" s="12" t="inlineStr"/>
+      <c r="G306" s="12" t="inlineStr"/>
+      <c r="H306" s="12" t="inlineStr"/>
+      <c r="I306" s="12" t="inlineStr"/>
+    </row>
+    <row r="307" ht="20" customHeight="1">
+      <c r="A307" s="11" t="inlineStr">
+        <is>
+          <t>Muhabirden (Ziraat bankası şubesi)</t>
+        </is>
+      </c>
+      <c r="B307" s="12" t="inlineStr"/>
+      <c r="C307" s="12" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="D307" s="12" t="inlineStr"/>
+      <c r="E307" s="12" t="inlineStr"/>
+      <c r="F307" s="12" t="inlineStr"/>
+      <c r="G307" s="12" t="inlineStr"/>
+      <c r="H307" s="12" t="inlineStr"/>
+      <c r="I307" s="12" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="13" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 13.08.2026 17:35</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A41:I41"/>
+  <mergeCells count="20">
+    <mergeCell ref="A305:I305"/>
+    <mergeCell ref="A54:I54"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A177:I177"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A89:I89"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A198:I198"/>
+    <mergeCell ref="A294:I294"/>
+    <mergeCell ref="A301:I301"/>
+    <mergeCell ref="A151:I151"/>
+    <mergeCell ref="A141:I141"/>
+    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A290:I290"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A96:I96"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A280:I280"/>
+    <mergeCell ref="A190:I190"/>
+    <mergeCell ref="A170:I170"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A187:I187"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     </font>
     <font>
       <b val="1"/>
+      <i val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
@@ -42,14 +43,27 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFD700"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0000B050"/>
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="0000B050"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000070C0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -58,11 +72,29 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -83,8 +115,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00012169"/>
         <bgColor rgb="00012169"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -95,8 +139,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4B183"/>
+        <bgColor rgb="00F4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00003087"/>
         <bgColor rgb="00003087"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008EA9C1"/>
+        <bgColor rgb="008EA9C1"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -140,40 +196,64 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,18 +619,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -618,7 +699,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
           <t>EFT Gönderimi</t>
@@ -631,18 +712,51 @@
           <t>EFT İsme Gelen</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr"/>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr"/>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="12" t="inlineStr"/>
-      <c r="G4" s="12" t="inlineStr"/>
-      <c r="H4" s="12" t="inlineStr"/>
-      <c r="I4" s="12" t="inlineStr"/>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>Para çekmeyi, para yatırmayı eklemedim</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -655,17 +769,46 @@
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>7,97TL</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="12" t="inlineStr"/>
-      <c r="G5" s="12" t="inlineStr"/>
-      <c r="H5" s="12" t="inlineStr"/>
-      <c r="I5" s="12" t="inlineStr"/>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>Akbank'ta bireysel kotalar var havale/EFT için</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -678,21 +821,46 @@
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>199,41TL</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>199,41 TL</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr"/>
-      <c r="H6" s="12" t="inlineStr"/>
-      <c r="I6" s="12" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>Kredi Risk Raporumuz zamanlanabilir</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -700,26 +868,51 @@
           <t>EFT - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>27,84TL</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr"/>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>Şubeden kıymetli maden teslimi %10'a kadar</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -727,34 +920,46 @@
           <t>EFT - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>199.41TL</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>398,83TL</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>398,83 TL</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>797,68 TL</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -762,26 +967,46 @@
           <t>EFT Gönderimi</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>85.72TL</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>619.047,62 TL</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>39,87 TL</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -789,24 +1014,48 @@
           <t>Düzenli EFT</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>1.00TL / 1.00%</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="12" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>7,97 TL</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Havale Gönderimi</t>
@@ -824,17 +1073,41 @@
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>3,99TL</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr"/>
-      <c r="G13" s="12" t="inlineStr"/>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -847,25 +1120,41 @@
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>99,71TL</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="12" t="inlineStr"/>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -873,30 +1162,42 @@
           <t>Havale - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>19.94TL</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>3,99TL</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="12" t="inlineStr"/>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>13,92 TL / -</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>19,94 TL / -</t>
         </is>
@@ -908,38 +1209,42 @@
           <t>Havale - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>99.71TL</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>398.84TL</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>99,71TL</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>199,42</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>398,84 TL</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>27,62 TL / -</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>398,84 TL / -</t>
         </is>
@@ -951,42 +1256,46 @@
           <t>Havale Gönderimi</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>1900.00TL / 0.70%</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>3676.20TL / 0.70%</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>150TL</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>125TL</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>309.523,81 TL</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>39,88 TL</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>13,33 TL / -</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -994,24 +1303,48 @@
           <t>Düzenli Havale</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr"/>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr"/>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>3,99 TL</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>3,99 TL</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="12" t="inlineStr"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>FAST</t>
@@ -1024,22 +1357,46 @@
           <t>FAST</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>380.95TL / 0.48%</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr"/>
-      <c r="G21" s="12" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>200 TL / 0,4</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr"/>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -1047,22 +1404,46 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr"/>
-      <c r="F22" s="12" t="inlineStr"/>
-      <c r="G22" s="12" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>7,97 TL / -</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr"/>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -1070,24 +1451,48 @@
           <t>FAST - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
-      <c r="G23" s="12" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>15,96 TL / -</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Kiralık Kasa</t>
@@ -1100,26 +1505,46 @@
           <t>Yıllık Kasa Ücreti - büyük</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>30000.00TL</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>4140TL</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr"/>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="12" t="inlineStr"/>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr"/>
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -1127,26 +1552,46 @@
           <t>Yıllık Kasa Ücreti - küçük</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>22000.00TL</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>2610TL</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr"/>
-      <c r="F27" s="12" t="inlineStr"/>
-      <c r="G27" s="12" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr"/>
+      <c r="I27" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -1154,26 +1599,46 @@
           <t>Yıllık Kasa Ücreti - orta</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>25000.00TL</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>3390TL</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr"/>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="12" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr"/>
+      <c r="I28" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -1181,22 +1646,46 @@
           <t>Kasa Depozito - büyük</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="12" t="inlineStr"/>
-      <c r="E29" s="12" t="inlineStr"/>
-      <c r="F29" s="12" t="inlineStr"/>
-      <c r="G29" s="12" t="inlineStr"/>
-      <c r="H29" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr"/>
+      <c r="I29" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -1204,22 +1693,46 @@
           <t>Kasa Depozito - orta</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="12" t="inlineStr"/>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr"/>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -1227,22 +1740,46 @@
           <t>Kasa Depozito - küçük</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr"/>
-      <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="12" t="inlineStr"/>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr"/>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -1255,13 +1792,41 @@
           <t>1469.52TL</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr"/>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
-      <c r="F32" s="12" t="inlineStr"/>
-      <c r="G32" s="12" t="inlineStr"/>
-      <c r="H32" s="12" t="inlineStr"/>
-      <c r="I32" s="12" t="inlineStr"/>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
@@ -1269,20 +1834,48 @@
           <t>Kasa Depozito - genel</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr"/>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>9420TL</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr"/>
-      <c r="F33" s="12" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr"/>
-      <c r="H33" s="12" t="inlineStr"/>
-      <c r="I33" s="12" t="inlineStr"/>
-    </row>
-    <row r="35" ht="16" customHeight="1">
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Kıymetli Maden</t>
@@ -1295,26 +1888,46 @@
           <t>Altın Transfer</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>100.00TL</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>415TL</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr"/>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>0.00018</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr"/>
-      <c r="H36" s="12" t="inlineStr"/>
-      <c r="I36" s="12" t="inlineStr"/>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -1322,22 +1935,46 @@
           <t>Altın Transfer - 1-10gr</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr"/>
-      <c r="C37" s="12" t="inlineStr"/>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>57,5TL</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>60 TL</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr"/>
-      <c r="I37" s="12" t="inlineStr"/>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -1345,24 +1982,48 @@
           <t>Altın Transfer - 11-100gr</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr"/>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>115TL</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr"/>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>120 TL</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr"/>
-      <c r="H38" s="12" t="inlineStr"/>
-      <c r="I38" s="12" t="inlineStr"/>
-    </row>
-    <row r="40" ht="16" customHeight="1">
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
@@ -1375,40 +2036,48 @@
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="21" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr"/>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H41" s="21" t="inlineStr">
         <is>
           <t>339 TL / -</t>
         </is>
       </c>
-      <c r="I41" s="12" t="inlineStr"/>
-    </row>
-    <row r="43" ht="16" customHeight="1">
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri - Kart</t>
@@ -1421,43 +2090,68 @@
           <t>Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="G44" s="13" t="inlineStr">
+      <c r="G44" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
+      <c r="H44" s="21" t="inlineStr">
         <is>
           <t>0,63 TL / -</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr"/>
-    </row>
-    <row r="46" ht="16" customHeight="1">
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>Fatura ödemeleri üst tier için %3,5'a çıkabiliyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>Borcu Yoktur Yazısı almak için ücret alınabiliyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
+        </is>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>Mevduat Araştırma Ücretleri zamlanabilir</t>
         </is>
       </c>
     </row>
@@ -1467,32 +2161,53 @@
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>3.50TL / 3.50%</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr"/>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr"/>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
         <is>
           <t>2 TL / 3,5%</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr"/>
-      <c r="H47" s="12" t="inlineStr"/>
-      <c r="I47" s="12" t="inlineStr">
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
         <is>
           <t>3 TL / -</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>Güvenli Araç Alım Satım YKB 97,53 TRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
@@ -1510,23 +2225,43 @@
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr"/>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="12" t="inlineStr"/>
-    </row>
-    <row r="52" ht="16" customHeight="1">
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
@@ -1539,24 +2274,48 @@
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr"/>
-      <c r="C53" s="12" t="inlineStr"/>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
         <is>
           <t>26TL</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr"/>
-      <c r="F53" s="13" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr"/>
-      <c r="H53" s="12" t="inlineStr"/>
-      <c r="I53" s="12" t="inlineStr"/>
-    </row>
-    <row r="55" ht="16" customHeight="1">
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I53" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
@@ -1569,20 +2328,48 @@
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr"/>
-      <c r="C56" s="12" t="inlineStr"/>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr"/>
-      <c r="F56" s="12" t="inlineStr"/>
-      <c r="G56" s="12" t="inlineStr"/>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="12" t="inlineStr"/>
-    </row>
-    <row r="58" ht="16" customHeight="1">
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I56" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri Aracılık</t>
@@ -1595,18 +2382,46 @@
           <t>Telefon Ödemeleri</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr"/>
-      <c r="C59" s="12" t="inlineStr"/>
-      <c r="D59" s="12" t="inlineStr"/>
-      <c r="E59" s="12" t="inlineStr"/>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>1 %</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr"/>
-      <c r="H59" s="12" t="inlineStr"/>
-      <c r="I59" s="12" t="inlineStr"/>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I59" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -1614,20 +2429,48 @@
           <t>Telefon - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr"/>
-      <c r="C60" s="12" t="inlineStr"/>
-      <c r="D60" s="12" t="inlineStr"/>
-      <c r="E60" s="12" t="inlineStr"/>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr"/>
-      <c r="H60" s="12" t="inlineStr"/>
-      <c r="I60" s="12" t="inlineStr"/>
-    </row>
-    <row r="62" ht="16" customHeight="1">
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Vergi Tahsilat Aracılık</t>
@@ -1641,15 +2484,15 @@
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr"/>
-      <c r="C63" s="12" t="inlineStr"/>
-      <c r="D63" s="12" t="inlineStr"/>
-      <c r="E63" s="12" t="inlineStr"/>
-      <c r="F63" s="12" t="inlineStr"/>
-      <c r="G63" s="12" t="inlineStr"/>
-      <c r="H63" s="12" t="inlineStr"/>
-      <c r="I63" s="12" t="inlineStr"/>
-    </row>
-    <row r="65" ht="16" customHeight="1">
+      <c r="C63" s="13" t="inlineStr"/>
+      <c r="D63" s="14" t="inlineStr"/>
+      <c r="E63" s="15" t="inlineStr"/>
+      <c r="F63" s="16" t="inlineStr"/>
+      <c r="G63" s="17" t="inlineStr"/>
+      <c r="H63" s="18" t="inlineStr"/>
+      <c r="I63" s="19" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
@@ -1667,15 +2510,43 @@
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr"/>
-      <c r="D66" s="12" t="inlineStr"/>
-      <c r="E66" s="12" t="inlineStr"/>
-      <c r="F66" s="12" t="inlineStr"/>
-      <c r="G66" s="12" t="inlineStr"/>
-      <c r="H66" s="12" t="inlineStr"/>
-      <c r="I66" s="12" t="inlineStr"/>
-    </row>
-    <row r="68" ht="16" customHeight="1">
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Mevduat Araştırma</t>
@@ -1688,26 +2559,46 @@
           <t>Referans Mektubu -</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B69" s="21" t="inlineStr">
         <is>
           <t>4000.00TL</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr"/>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
         <is>
           <t>770TL</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr"/>
-      <c r="F69" s="12" t="inlineStr"/>
-      <c r="G69" s="12" t="inlineStr"/>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H69" s="21" t="inlineStr">
         <is>
           <t>50 TL / -</t>
         </is>
       </c>
-      <c r="I69" s="12" t="inlineStr"/>
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
@@ -1715,22 +2606,46 @@
           <t>Hesap Özeti Verilmesi -</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr"/>
-      <c r="C70" s="12" t="inlineStr"/>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
         <is>
           <t>190TL</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr"/>
-      <c r="F70" s="13" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="inlineStr">
         <is>
           <t>12 TL</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr"/>
-      <c r="H70" s="12" t="inlineStr"/>
-      <c r="I70" s="12" t="inlineStr"/>
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
@@ -1738,20 +2653,48 @@
           <t>Borcu Yoktur Yazısı</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr"/>
-      <c r="C71" s="12" t="inlineStr"/>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr"/>
-      <c r="F71" s="12" t="inlineStr"/>
-      <c r="G71" s="12" t="inlineStr"/>
-      <c r="H71" s="12" t="inlineStr"/>
-      <c r="I71" s="12" t="inlineStr"/>
-    </row>
-    <row r="73" ht="16" customHeight="1">
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
@@ -1764,24 +2707,48 @@
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr"/>
-      <c r="C74" s="12" t="inlineStr"/>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
       </c>
-      <c r="E74" s="12" t="inlineStr"/>
-      <c r="F74" s="12" t="inlineStr"/>
-      <c r="G74" s="12" t="inlineStr"/>
-      <c r="H74" s="13" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H74" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I74" s="12" t="inlineStr"/>
-    </row>
-    <row r="76" ht="16" customHeight="1">
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
@@ -1794,24 +2761,48 @@
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr"/>
-      <c r="C77" s="12" t="inlineStr"/>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr"/>
-      <c r="F77" s="13" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="inlineStr">
         <is>
           <t>0.27 TL</t>
         </is>
       </c>
-      <c r="G77" s="12" t="inlineStr"/>
-      <c r="H77" s="12" t="inlineStr"/>
-      <c r="I77" s="12" t="inlineStr"/>
-    </row>
-    <row r="79" ht="16" customHeight="1">
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I77" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
           <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
@@ -1824,30 +2815,46 @@
           <t>Çek Düzenleme -</t>
         </is>
       </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="B80" s="21" t="inlineStr">
         <is>
           <t>9.52TL / 0.10%</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr"/>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D80" s="21" t="inlineStr">
         <is>
           <t>290TL / 1.10%</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr"/>
-      <c r="F80" s="13" t="inlineStr">
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
         <is>
           <t>761,90 TL</t>
         </is>
       </c>
-      <c r="G80" s="12" t="inlineStr"/>
-      <c r="H80" s="13" t="inlineStr">
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" s="21" t="inlineStr">
         <is>
           <t>104,76 TL / -</t>
         </is>
       </c>
-      <c r="I80" s="12" t="inlineStr"/>
+      <c r="I80" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
@@ -1855,20 +2862,48 @@
           <t>Çek Defteri (Yaprak Başı) -</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr"/>
-      <c r="C81" s="12" t="inlineStr"/>
-      <c r="D81" s="12" t="inlineStr"/>
-      <c r="E81" s="12" t="inlineStr"/>
-      <c r="F81" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
         <is>
           <t>2.380,95 TL</t>
         </is>
       </c>
-      <c r="G81" s="12" t="inlineStr"/>
-      <c r="H81" s="12" t="inlineStr"/>
-      <c r="I81" s="12" t="inlineStr"/>
-    </row>
-    <row r="83" ht="16" customHeight="1">
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
@@ -1881,32 +2916,48 @@
           <t>Çek İade Ücreti</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr"/>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr"/>
-      <c r="F84" s="13" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
         <is>
           <t>380,95 TL</t>
         </is>
       </c>
-      <c r="G84" s="12" t="inlineStr"/>
-      <c r="H84" s="13" t="inlineStr">
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="inlineStr">
         <is>
           <t>123,81 TL / -</t>
         </is>
       </c>
-      <c r="I84" s="12" t="inlineStr"/>
-    </row>
-    <row r="86" ht="16" customHeight="1">
+      <c r="I84" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
           <t>Çek Tahsilat Ücreti</t>
@@ -1919,34 +2970,42 @@
           <t>Çek Tahsilat</t>
         </is>
       </c>
-      <c r="B87" s="13" t="inlineStr">
+      <c r="B87" s="21" t="inlineStr">
         <is>
           <t>45USD</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C87" s="21" t="inlineStr">
         <is>
           <t>590.48TL / 0.77%</t>
         </is>
       </c>
-      <c r="D87" s="12" t="inlineStr"/>
-      <c r="E87" s="13" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="inlineStr">
         <is>
           <t>1.70%</t>
         </is>
       </c>
-      <c r="F87" s="13" t="inlineStr">
+      <c r="F87" s="21" t="inlineStr">
         <is>
           <t>714,29 TL</t>
         </is>
       </c>
-      <c r="G87" s="12" t="inlineStr"/>
-      <c r="H87" s="13" t="inlineStr">
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H87" s="21" t="inlineStr">
         <is>
           <t>260 TL / -</t>
         </is>
       </c>
-      <c r="I87" s="13" t="inlineStr">
+      <c r="I87" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
@@ -1958,34 +3017,46 @@
           <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B88" s="21" t="inlineStr">
         <is>
           <t>257.15TL</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr"/>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D88" s="21" t="inlineStr">
         <is>
           <t>2940TL / 1%</t>
         </is>
       </c>
-      <c r="E88" s="13" t="inlineStr">
+      <c r="E88" s="21" t="inlineStr">
         <is>
           <t>390TL / 0.2%</t>
         </is>
       </c>
-      <c r="F88" s="13" t="inlineStr">
+      <c r="F88" s="21" t="inlineStr">
         <is>
           <t>1.666,67 TL</t>
         </is>
       </c>
-      <c r="G88" s="13" t="inlineStr">
+      <c r="G88" s="21" t="inlineStr">
         <is>
           <t>585,71 TL</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr"/>
-      <c r="I88" s="12" t="inlineStr"/>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I88" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
@@ -1993,22 +3064,42 @@
           <t>Diğer Banka Çeki -</t>
         </is>
       </c>
-      <c r="B89" s="13" t="inlineStr">
+      <c r="B89" s="21" t="inlineStr">
         <is>
           <t>390.48TL</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr"/>
-      <c r="D89" s="13" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
         <is>
           <t>350TL</t>
         </is>
       </c>
-      <c r="E89" s="12" t="inlineStr"/>
-      <c r="F89" s="12" t="inlineStr"/>
-      <c r="G89" s="12" t="inlineStr"/>
-      <c r="H89" s="12" t="inlineStr"/>
-      <c r="I89" s="12" t="inlineStr">
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I89" s="19" t="inlineStr">
         <is>
           <t>576,19 TL / 0,6</t>
         </is>
@@ -2020,20 +3111,48 @@
           <t>Aynı Banka Çeki -</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr"/>
-      <c r="C90" s="12" t="inlineStr"/>
-      <c r="D90" s="12" t="inlineStr"/>
-      <c r="E90" s="12" t="inlineStr"/>
-      <c r="F90" s="12" t="inlineStr"/>
-      <c r="G90" s="12" t="inlineStr"/>
-      <c r="H90" s="12" t="inlineStr"/>
-      <c r="I90" s="12" t="inlineStr">
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I90" s="19" t="inlineStr">
         <is>
           <t>427,62 TL / -</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
+    <row r="92" ht="18" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
           <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
@@ -2046,20 +3165,48 @@
           <t>Karşılıksız Çek Belgelendirme -</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr"/>
-      <c r="C93" s="12" t="inlineStr"/>
-      <c r="D93" s="12" t="inlineStr"/>
-      <c r="E93" s="12" t="inlineStr"/>
-      <c r="F93" s="12" t="inlineStr"/>
-      <c r="G93" s="12" t="inlineStr"/>
-      <c r="H93" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
         <is>
           <t>371,43 TL / -</t>
         </is>
       </c>
-      <c r="I93" s="12" t="inlineStr"/>
-    </row>
-    <row r="95" ht="16" customHeight="1">
+      <c r="I93" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
           <t>Senet İade Ücreti</t>
@@ -2072,32 +3219,48 @@
           <t>Senet İade Ücreti</t>
         </is>
       </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="B96" s="21" t="inlineStr">
         <is>
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="C96" s="12" t="inlineStr"/>
-      <c r="D96" s="13" t="inlineStr">
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D96" s="21" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr"/>
-      <c r="F96" s="13" t="inlineStr">
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
         <is>
           <t>571,43 TL</t>
         </is>
       </c>
-      <c r="G96" s="12" t="inlineStr"/>
-      <c r="H96" s="13" t="inlineStr">
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I96" s="12" t="inlineStr"/>
-    </row>
-    <row r="98" ht="16" customHeight="1">
+      <c r="I96" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
           <t>Senet Protesto İşlemleri Ücreti</t>
@@ -2110,30 +3273,46 @@
           <t>Senet Protesto Kaldırma -</t>
         </is>
       </c>
-      <c r="B99" s="13" t="inlineStr">
+      <c r="B99" s="21" t="inlineStr">
         <is>
           <t>533.34TL</t>
         </is>
       </c>
-      <c r="C99" s="12" t="inlineStr"/>
-      <c r="D99" s="13" t="inlineStr">
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D99" s="21" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
-      <c r="E99" s="12" t="inlineStr"/>
-      <c r="F99" s="13" t="inlineStr">
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
         <is>
           <t>619,05 TL</t>
         </is>
       </c>
-      <c r="G99" s="12" t="inlineStr"/>
-      <c r="H99" s="13" t="inlineStr">
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="inlineStr">
         <is>
           <t>551,43 TL / -</t>
         </is>
       </c>
-      <c r="I99" s="12" t="inlineStr"/>
+      <c r="I99" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
@@ -2141,32 +3320,48 @@
           <t>Senet Protesto -</t>
         </is>
       </c>
-      <c r="B100" s="13" t="inlineStr">
+      <c r="B100" s="21" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="C100" s="12" t="inlineStr"/>
-      <c r="D100" s="13" t="inlineStr">
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D100" s="21" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
-      <c r="E100" s="12" t="inlineStr"/>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="inlineStr">
         <is>
           <t>666,67 TL</t>
         </is>
       </c>
-      <c r="G100" s="12" t="inlineStr"/>
-      <c r="H100" s="13" t="inlineStr">
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" s="21" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I100" s="12" t="inlineStr"/>
-    </row>
-    <row r="102" ht="16" customHeight="1">
+      <c r="I100" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
           <t>Senet Tahsile Alma Ücreti</t>
@@ -2179,26 +3374,46 @@
           <t>Muhabir Banka Senet Tahsili -</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr"/>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr"/>
-      <c r="E103" s="12" t="inlineStr"/>
-      <c r="F103" s="13" t="inlineStr">
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
         <is>
           <t>666,67 TL</t>
         </is>
       </c>
-      <c r="G103" s="12" t="inlineStr"/>
-      <c r="H103" s="13" t="inlineStr">
+      <c r="G103" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" s="21" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I103" s="12" t="inlineStr"/>
+      <c r="I103" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
@@ -2206,20 +3421,48 @@
           <t>Aynı Banka Senet Tahsili -</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr"/>
-      <c r="C104" s="12" t="inlineStr"/>
-      <c r="D104" s="12" t="inlineStr"/>
-      <c r="E104" s="12" t="inlineStr"/>
-      <c r="F104" s="12" t="inlineStr"/>
-      <c r="G104" s="12" t="inlineStr"/>
-      <c r="H104" s="12" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I104" s="12" t="inlineStr"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
+      <c r="I104" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
           <t>HGS</t>
@@ -2232,64 +3475,59 @@
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B107" s="13" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C107" s="12" t="inlineStr"/>
-      <c r="D107" s="13" t="inlineStr">
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E107" s="12" t="inlineStr"/>
-      <c r="F107" s="13" t="inlineStr">
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G107" s="12" t="inlineStr"/>
-      <c r="H107" s="12" t="inlineStr"/>
-      <c r="I107" s="12" t="inlineStr"/>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I107" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="14" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 10:30</t>
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 10:46</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A65:I65"/>
+  <mergeCells count="5">
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A46:I46"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A86:I86"/>
-    <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A106:I106"/>
-    <mergeCell ref="A35:I35"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A92:I92"/>
-    <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A79:I79"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -781,7 +781,7 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,97TL</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -813,12 +813,12 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Düzenli EFT - 399000+ TRY</t>
+          <t>Düzenli EFT - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>199.41TL</t>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>199,41TL</t>
+          <t>15,96TL</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>15,96TL</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>199,41 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -865,32 +865,32 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>EFT - 0-8300 TRY</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>7.97TL</t>
+          <t>Düzenli EFT - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>199.41TL</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>39.87TL</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>27,84TL</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>199,41TL</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>199,41TL</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>199,41 TL</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -917,37 +917,37 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>EFT - 399000+ TRY</t>
+          <t>EFT - 0-8300 TRY</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>199.41TL</t>
+          <t>7.97TL</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>797.68TL</t>
+          <t>39.87TL</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>398,83TL</t>
+          <t>27,84TL</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>398,83 TL</t>
+          <t>39,87TL</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>797,68 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
@@ -964,37 +964,37 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>EFT Gönderimi</t>
+          <t>EFT - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>85.72TL</t>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>79.76TL</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>55,69TL</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>619.047,62 TL</t>
+          <t>79,76TL</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>39,87 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
@@ -1011,175 +1011,175 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>EFT - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>199.41TL</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>797.68TL</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>398,83TL</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>797,68TL</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>398,83 TL</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>797,68 TL</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>EFT Gönderimi</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>85.72TL</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>619.047,62 TL</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>39,87 TL</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>Düzenli EFT</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>1.00TL / 1.00%</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>7,97 TL</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Havale Gönderimi</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Düzenli Havale - 0-8300 TRY</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>3.99TL</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>3,99TL</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Düzenli Havale - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>99.71TL</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>99,71TL</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>99,71 TL</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>99,71 TL</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Havale - 0-8300 TRY</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+          <t>Düzenli Havale - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>3.99TL</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>19.94TL</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>3,99TL</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3,99TL</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -1192,103 +1192,103 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t>13,92 TL / -</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>19,94 TL / -</t>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Havale - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>99.71TL</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>398.84TL</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>99,71TL</t>
+          <t>Düzenli Havale - 8300-399000 TRY</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>7.98TL</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>7,98TL</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>199,42</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>398,84 TL</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>27,62 TL / -</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>398,84 TL / -</t>
+          <t>7,98TL</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Havale Gönderimi</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>1900.00TL / 0.70%</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>3676.20TL / 0.70%</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>150TL</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>125TL</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>309.523,81 TL</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>39,88 TL</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>13,33 TL / -</t>
+          <t>Düzenli Havale - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>99.71TL</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>99,71TL</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>99,71TL</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I17" s="19" t="inlineStr">
@@ -1300,96 +1300,183 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Düzenli Havale</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Havale - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>3.99TL</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>19.94TL</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>3,99TL</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>19,94TL</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>3,99 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>3,99 TL</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>FAST</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>13,92 TL / -</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>19,94 TL / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Havale - 8300-399000 TRY</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>7.98TL</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>39.88TL</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>7,98TL</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>39,88TL</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Havale - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>99.71TL</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>398.84TL</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>99,71TL</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>398,84TL</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>199,42</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>398,84 TL</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>27,62 TL / -</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>398,84 TL / -</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>Havale Gönderimi</t>
         </is>
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>380.95TL / 0.48%</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>1900.00TL / 0.70%</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>3676.20TL / 0.70%</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>150TL</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>125TL</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>309.523,81 TL</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>39,88 TL</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>200 TL / 0,4</t>
+          <t>13,33 TL / -</t>
         </is>
       </c>
       <c r="I21" s="19" t="inlineStr">
@@ -1401,12 +1488,12 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>FAST - 0-8300 TRY</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>7.97TL</t>
+          <t>Düzenli Havale</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -1426,17 +1513,17 @@
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3,99 TL</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>7,97 TL / -</t>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -1445,69 +1532,69 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>FAST - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>15.96TL</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>15,96 TL / -</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Kiralık Kasa</t>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>380.95TL / 0.48%</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>200 TL / 0,4</t>
+        </is>
+      </c>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - büyük</t>
+          <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>30000.00TL</t>
+          <t>7.97TL</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -1515,9 +1602,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>4140TL</t>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
@@ -1537,7 +1624,7 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t>- / -</t>
+          <t>7,97 TL / -</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1549,12 +1636,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - küçük</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>22000.00TL</t>
+          <t>FAST - 8300-399000 TRY</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -1562,9 +1649,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>2610TL</t>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -1582,9 +1669,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
@@ -1596,12 +1683,12 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - orta</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>25000.00TL</t>
+          <t>FAST - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -1609,9 +1696,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>3390TL</t>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
@@ -1629,9 +1716,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>15,96 TL / -</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
@@ -1640,109 +1727,22 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Kasa Depozito - büyük</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>28570.00TL</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Kasa Depozito - orta</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>23805.00TL</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - küçük</t>
+          <t>Yıllık Kasa Ücreti - büyük</t>
         </is>
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>20950.00TL</t>
+          <t>30000.00TL</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -1750,9 +1750,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>4140TL</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -1784,12 +1784,12 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - genel</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>1469.52TL</t>
+          <t>Yıllık Kasa Ücreti - küçük</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>22000.00TL</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -1797,9 +1797,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>2610TL</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -1817,9 +1817,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - genel</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Yıllık Kasa Ücreti - orta</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>25000.00TL</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1844,9 +1844,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>9420TL</t>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>3390TL</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -1864,9 +1864,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
       <c r="I33" s="19" t="inlineStr">
@@ -1875,22 +1875,109 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>Kıymetli Maden</t>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Kasa Depozito - büyük</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>28570.00TL</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Kasa Depozito - orta</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>23805.00TL</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer</t>
+          <t>Kasa Depozito - küçük</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>100.00TL</t>
+          <t>20950.00TL</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -1898,9 +1985,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>415TL</t>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -1908,9 +1995,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>0.00018</t>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -1918,9 +2005,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
       <c r="I36" s="19" t="inlineStr">
@@ -1932,12 +2019,12 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 1-10gr</t>
+          <t>Yıllık Kasa Ücreti - genel</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1469.52TL</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -1945,9 +2032,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>57,5TL</t>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -1955,9 +2042,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>60 TL</t>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -1979,7 +2066,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 11-100gr</t>
+          <t>Kasa Depozito - genel</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -1992,9 +2079,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>115TL</t>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>9420TL</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
@@ -2002,9 +2089,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>120 TL</t>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -2026,636 +2113,636 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
+          <t>Kıymetli Maden</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
+          <t>Altın Transfer</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>100.00TL</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>415TL</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>0.00018</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Altın Transfer - 1-10gr</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>57,5TL</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>60 TL</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Altın Transfer - 11-100gr</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>115TL</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>120 TL</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B41" s="21" t="inlineStr">
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D41" s="21" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H41" s="21" t="inlineStr">
+      <c r="H46" s="21" t="inlineStr">
         <is>
           <t>339 TL / -</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="I46" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri - Kart</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C44" s="21" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D44" s="21" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr">
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="H44" s="21" t="inlineStr">
+      <c r="H49" s="21" t="inlineStr">
         <is>
           <t>0,63 TL / -</t>
         </is>
       </c>
-      <c r="I44" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L44" s="20" t="inlineStr">
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
         <is>
           <t>Fatura ödemeleri üst tier için %3,5'a çıkabiliyor</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="L45" s="20" t="inlineStr">
+    <row r="50">
+      <c r="L50" s="20" t="inlineStr">
         <is>
           <t>Borcu Yoktur Yazısı almak için ücret alınabiliyor</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="L46" s="20" t="inlineStr">
+      <c r="L51" s="20" t="inlineStr">
         <is>
           <t>Mevduat Araştırma Ücretleri zamlanabilir</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>3.50TL / 3.50%</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F47" s="21" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
         <is>
           <t>2 TL / 3,5%</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H47" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I47" s="19" t="inlineStr">
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>3 TL / -</t>
         </is>
       </c>
-      <c r="L47" s="20" t="inlineStr">
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>Güvenli Araç Alım Satım YKB 97,53 TRY</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>275TL</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H50" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D53" s="21" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="inlineStr">
         <is>
           <t>26TL</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H53" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I53" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I58" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H56" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I56" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>1 %</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I59" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Telefon - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I60" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I65" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>Vergi Tahsilat Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Vergi Tahsilat</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr"/>
-      <c r="C63" s="13" t="inlineStr"/>
-      <c r="D63" s="14" t="inlineStr"/>
-      <c r="E63" s="15" t="inlineStr"/>
-      <c r="F63" s="16" t="inlineStr"/>
-      <c r="G63" s="17" t="inlineStr"/>
-      <c r="H63" s="18" t="inlineStr"/>
-      <c r="I63" s="19" t="inlineStr"/>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr"/>
+      <c r="C68" s="13" t="inlineStr"/>
+      <c r="D68" s="14" t="inlineStr"/>
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="16" t="inlineStr"/>
+      <c r="G68" s="17" t="inlineStr"/>
+      <c r="H68" s="18" t="inlineStr"/>
+      <c r="I68" s="19" t="inlineStr"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>Arşiv Araştırma Ücreti</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>287.62TL</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H66" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I66" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Mevduat Araştırma</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>Referans Mektubu -</t>
-        </is>
-      </c>
-      <c r="B69" s="21" t="inlineStr">
-        <is>
-          <t>4000.00TL</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D69" s="21" t="inlineStr">
-        <is>
-          <t>770TL</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H69" s="21" t="inlineStr">
-        <is>
-          <t>50 TL / -</t>
-        </is>
-      </c>
-      <c r="I69" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>Hesap Özeti Verilmesi -</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>190TL</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F70" s="21" t="inlineStr">
-        <is>
-          <t>12 TL</t>
-        </is>
-      </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H70" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I70" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>Borcu Yoktur Yazısı</t>
+          <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>287.62TL</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -2665,7 +2752,7 @@
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>390TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
@@ -2697,376 +2784,376 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Bakiye Sorma - Yurtiçi - ATM</t>
+          <t>Mevduat Araştırma</t>
         </is>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
+          <t>Referans Mektubu -</t>
+        </is>
+      </c>
+      <c r="B74" s="21" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>770TL</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H74" s="21" t="inlineStr">
+        <is>
+          <t>50 TL / -</t>
+        </is>
+      </c>
+      <c r="I74" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>Hesap Özeti Verilmesi -</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>190TL</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>12 TL</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>Borcu Yoktur Yazısı</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>390TL</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Bakiye Sorma - Yurtiçi - ATM</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H74" s="21" t="inlineStr">
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H79" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="I79" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D77" s="21" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F77" s="21" t="inlineStr">
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
         <is>
           <t>0.27 TL</t>
         </is>
       </c>
-      <c r="G77" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H77" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I77" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I82" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>Çek Düzenleme -</t>
         </is>
       </c>
-      <c r="B80" s="21" t="inlineStr">
+      <c r="B85" s="21" t="inlineStr">
         <is>
           <t>9.52TL / 0.10%</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
         <is>
           <t>290TL / 1.10%</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
         <is>
           <t>761,90 TL</t>
         </is>
       </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H80" s="21" t="inlineStr">
+      <c r="G85" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H85" s="21" t="inlineStr">
         <is>
           <t>104,76 TL / -</t>
         </is>
       </c>
-      <c r="I80" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="I85" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>Çek Defteri (Yaprak Başı) -</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
         <is>
           <t>2.380,95 TL</t>
         </is>
       </c>
-      <c r="G81" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H81" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I81" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>Çek İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B84" s="21" t="inlineStr">
-        <is>
-          <t>171.43TL</t>
-        </is>
-      </c>
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
-      <c r="E84" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>380,95 TL</t>
-        </is>
-      </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H84" s="21" t="inlineStr">
-        <is>
-          <t>123,81 TL / -</t>
-        </is>
-      </c>
-      <c r="I84" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>Çek Tahsilat Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>Çek Tahsilat</t>
-        </is>
-      </c>
-      <c r="B87" s="21" t="inlineStr">
-        <is>
-          <t>45USD</t>
-        </is>
-      </c>
-      <c r="C87" s="21" t="inlineStr">
-        <is>
-          <t>590.48TL / 0.77%</t>
-        </is>
-      </c>
-      <c r="D87" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E87" s="21" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>714,29 TL</t>
-        </is>
-      </c>
-      <c r="G87" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H87" s="21" t="inlineStr">
-        <is>
-          <t>260 TL / -</t>
-        </is>
-      </c>
-      <c r="I87" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
-        </is>
-      </c>
-      <c r="B88" s="21" t="inlineStr">
-        <is>
-          <t>257.15TL</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D88" s="21" t="inlineStr">
-        <is>
-          <t>2940TL / 1%</t>
-        </is>
-      </c>
-      <c r="E88" s="21" t="inlineStr">
-        <is>
-          <t>390TL / 0.2%</t>
-        </is>
-      </c>
-      <c r="F88" s="21" t="inlineStr">
-        <is>
-          <t>1.666,67 TL</t>
-        </is>
-      </c>
-      <c r="G88" s="21" t="inlineStr">
-        <is>
-          <t>585,71 TL</t>
-        </is>
-      </c>
-      <c r="H88" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I88" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>Diğer Banka Çeki -</t>
+          <t>Çek İade Ücreti</t>
         </is>
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>390.48TL</t>
+          <t>171.43TL</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -3076,7 +3163,7 @@
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>350TL</t>
+          <t>390TL</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
@@ -3084,9 +3171,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F89" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>380,95 TL</t>
         </is>
       </c>
       <c r="G89" s="17" t="inlineStr">
@@ -3094,432 +3181,580 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H89" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>123,81 TL / -</t>
         </is>
       </c>
       <c r="I89" s="19" t="inlineStr">
         <is>
-          <t>576,19 TL / 0,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>Aynı Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D90" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F90" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H90" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I90" s="19" t="inlineStr">
-        <is>
-          <t>427,62 TL / -</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="inlineStr">
+        <is>
+          <t>45USD</t>
+        </is>
+      </c>
+      <c r="C92" s="21" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77%</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="inlineStr">
+        <is>
+          <t>714,29 TL</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" s="21" t="inlineStr">
+        <is>
+          <t>260 TL / -</t>
+        </is>
+      </c>
+      <c r="I92" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
+          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>257.15TL</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
+      <c r="E93" s="21" t="inlineStr">
+        <is>
+          <t>390TL / 0.2%</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>1.666,67 TL</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>585,71 TL</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I93" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>Diğer Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B94" s="21" t="inlineStr">
+        <is>
+          <t>390.48TL</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D94" s="21" t="inlineStr">
+        <is>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I95" s="19" t="inlineStr">
+        <is>
+          <t>427,62 TL / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
           <t>Karşılıksız Çek Belgelendirme -</t>
         </is>
       </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D93" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F93" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H93" s="18" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
         <is>
           <t>371,43 TL / -</t>
         </is>
       </c>
-      <c r="I93" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="I98" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>Senet İade Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>Senet İade Ücreti</t>
         </is>
       </c>
-      <c r="B96" s="21" t="inlineStr">
+      <c r="B101" s="21" t="inlineStr">
         <is>
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D96" s="21" t="inlineStr">
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D101" s="21" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F96" s="21" t="inlineStr">
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
         <is>
           <t>571,43 TL</t>
         </is>
       </c>
-      <c r="G96" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="inlineStr">
+      <c r="G101" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H101" s="21" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I96" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="I101" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>Senet Protesto İşlemleri Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>Senet Protesto Kaldırma -</t>
-        </is>
-      </c>
-      <c r="B99" s="21" t="inlineStr">
-        <is>
-          <t>533.34TL</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F99" s="21" t="inlineStr">
-        <is>
-          <t>619,05 TL</t>
-        </is>
-      </c>
-      <c r="G99" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H99" s="21" t="inlineStr">
-        <is>
-          <t>551,43 TL / -</t>
-        </is>
-      </c>
-      <c r="I99" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>Senet Protesto -</t>
-        </is>
-      </c>
-      <c r="B100" s="21" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="C100" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F100" s="21" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G100" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H100" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I100" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>Senet Tahsile Alma Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>Muhabir Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E103" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F103" s="21" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G103" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H103" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I103" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
+          <t>Senet Protesto Kaldırma -</t>
+        </is>
+      </c>
+      <c r="B104" s="21" t="inlineStr">
+        <is>
+          <t>533.34TL</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D104" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>619,05 TL</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" s="21" t="inlineStr">
+        <is>
+          <t>551,43 TL / -</t>
+        </is>
+      </c>
+      <c r="I104" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto -</t>
+        </is>
+      </c>
+      <c r="B105" s="21" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G105" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" s="21" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I105" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>Senet Tahsile Alma Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>Muhabir Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C108" s="13" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H108" s="21" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I108" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
           <t>Aynı Banka Senet Tahsili -</t>
         </is>
       </c>
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C104" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D104" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F104" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G104" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H104" s="18" t="inlineStr">
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F109" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I104" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="I109" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>HGS</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B112" s="21" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C107" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D107" s="21" t="inlineStr">
+      <c r="C112" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D112" s="21" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E107" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F107" s="21" t="inlineStr">
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>550TL</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G107" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H107" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I107" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="22" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 10:46</t>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I112" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 11:11</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,97 TL</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>15,96 TL</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -940,14 +940,14 @@
           <t>39,87TL</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>309.523,82 TL</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>39,87 TL</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
@@ -987,14 +987,14 @@
           <t>79,76TL</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>619.047,62 TL</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>79,76 TL</t>
         </is>
       </c>
       <c r="H9" s="18" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>619.047,62 TL</t>
+          <t>4.25 %</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>39,87 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" s="18" t="inlineStr">
@@ -1108,7 +1108,7 @@
           <t>Düzenli EFT</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>1.00TL / 1.00%</t>
         </is>
@@ -1128,9 +1128,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>7,97 TL</t>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3,99 TL</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3,99 TL</t>
         </is>
       </c>
       <c r="H15" s="18" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,98 TL</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7,98 TL</t>
         </is>
       </c>
       <c r="H16" s="18" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>3.99TL</t>
+          <t>1050.00TL</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>19.94TL</t>
+          <t>2485.72TL</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -1323,19 +1323,19 @@
           <t>19,94TL</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>152.380,96 TL</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>19,94 TL</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t>13,92 TL / -</t>
+          <t>13,33 TL / -</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -1350,44 +1350,44 @@
           <t>Havale - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>7.98TL</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>39.88TL</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>1500.00TL</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>2923.81TL</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>7,98TL</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>39,88TL</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>309.523,81 TL</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>39,88 TL</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>27,62 TL / -</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>39,88 TL / -</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>99.71TL</t>
+          <t>1900.00TL / 0.70%</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>398.84TL</t>
+          <t>3676.20TL / 0.70%</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>27,62 TL / -</t>
+          <t>199,05 TL / -</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -1444,14 +1444,14 @@
           <t>Havale Gönderimi</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>1900.00TL / 0.70%</t>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>3676.20TL / 0.70%</t>
+          <t>1038.10TL / 0.58%</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>309.523,81 TL</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>39,88 TL</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>13,33 TL / -</t>
+          <t>1.300 TL / 0,6 %</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I21" s="19" t="inlineStr">
@@ -1485,67 +1485,67 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Düzenli Havale</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>3,99 TL</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>3,99 TL</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>FAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>FAST - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>7.97TL</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>7,97 TL / -</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
+          <t>FAST - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>380.95TL / 0.48%</t>
         </is>
@@ -1575,9 +1575,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>200 TL / 0,4</t>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>FAST - 0-8300 TRY</t>
+          <t>FAST - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>7.97TL</t>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="H26" s="21" t="inlineStr">
         <is>
-          <t>7,97 TL / -</t>
+          <t>15,96 TL / -</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>FAST - 8300-399000 TRY</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>15.96TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>200 TL / 0,4</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
@@ -1680,69 +1680,69 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>FAST - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>15,96 TL / -</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Kiralık Kasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Yıllık Kasa Ücreti - büyük</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>30000.00TL</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>4140TL</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - büyük</t>
+          <t>Yıllık Kasa Ücreti - küçük</t>
         </is>
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>30000.00TL</t>
+          <t>22000.00TL</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>4140TL</t>
+          <t>2610TL</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -1784,12 +1784,12 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - küçük</t>
+          <t>Yıllık Kasa Ücreti - orta</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>22000.00TL</t>
+          <t>25000.00TL</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>2610TL</t>
+          <t>3390TL</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - orta</t>
+          <t>Kasa Depozito - büyük</t>
         </is>
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>25000.00TL</t>
+          <t>28570.00TL</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1844,9 +1844,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>3390TL</t>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - büyük</t>
+          <t>Kasa Depozito - orta</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>28570.00TL</t>
+          <t>23805.00TL</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - orta</t>
+          <t>Kasa Depozito - küçük</t>
         </is>
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>23805.00TL</t>
+          <t>20950.00TL</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - küçük</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>20950.00TL</t>
+          <t>Yıllık Kasa Ücreti - genel</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>1469.52TL</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -2005,9 +2005,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I36" s="19" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - genel</t>
+          <t>Kasa Depozito - genel</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>1469.52TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9420TL</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -2063,64 +2063,64 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Kasa Depozito - genel</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>9420TL</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Kıymetli Maden</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Altın Transfer - 0-8300</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>50.00TL</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer</t>
+          <t>Altın Transfer - 8300-399000</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>415TL</t>
+          <t>170TL</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
@@ -2143,9 +2143,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>0.00018</t>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
@@ -2167,7 +2167,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 1-10gr</t>
+          <t>Altın Transfer</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -2182,17 +2182,17 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>57,5TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
         <is>
-          <t>60 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
@@ -2214,636 +2214,723 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
+          <t>Altın Transfer - 1-10gr</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>57,5TL</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>60 TL</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
           <t>Altın Transfer - 11-100gr</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>115TL</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>120 TL</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H43" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Altın Transfer - 399000+</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>415TL</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>0.00018</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H46" s="21" t="inlineStr">
+      <c r="H48" s="21" t="inlineStr">
         <is>
           <t>339 TL / -</t>
         </is>
       </c>
-      <c r="I46" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri - Kart</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C49" s="21" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D49" s="21" t="inlineStr">
+      <c r="D51" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E49" s="21" t="inlineStr">
+      <c r="E51" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="F49" s="21" t="inlineStr">
+      <c r="F51" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="H49" s="21" t="inlineStr">
+      <c r="H51" s="21" t="inlineStr">
         <is>
           <t>0,63 TL / -</t>
         </is>
       </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L49" s="20" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
         <is>
           <t>Fatura ödemeleri üst tier için %3,5'a çıkabiliyor</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="L50" s="20" t="inlineStr">
+    <row r="52">
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>Borcu Yoktur Yazısı almak için ücret alınabiliyor</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="L51" s="20" t="inlineStr">
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>Mevduat Araştırma Ücretleri zamlanabilir</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="B52" s="21" t="inlineStr">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>3.50TL / 3.50%</t>
         </is>
       </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D52" s="21" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F52" s="21" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
         <is>
           <t>2 TL / 3,5%</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>3 TL / -</t>
         </is>
       </c>
-      <c r="L52" s="20" t="inlineStr">
+      <c r="L54" s="20" t="inlineStr">
         <is>
           <t>Güvenli Araç Alım Satım YKB 97,53 TRY</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H55" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I55" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D58" s="21" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>26TL</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F58" s="21" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H58" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I58" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H61" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I61" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>Telefon Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>1 %</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H64" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>Telefon - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>99,71 TL</t>
-        </is>
-      </c>
-      <c r="G65" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H65" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I65" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>Vergi Tahsilat Aracılık</t>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Telefon - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>Telefon - 8300-399000 TRY</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>7,98 TL</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I67" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
+          <t>Telefon - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I68" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>Telefon Ödemeleri</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>1 %</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Vergi Tahsilat Aracılık</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
           <t>Vergi Tahsilat</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr"/>
-      <c r="C68" s="13" t="inlineStr"/>
-      <c r="D68" s="14" t="inlineStr"/>
-      <c r="E68" s="15" t="inlineStr"/>
-      <c r="F68" s="16" t="inlineStr"/>
-      <c r="G68" s="17" t="inlineStr"/>
-      <c r="H68" s="18" t="inlineStr"/>
-      <c r="I68" s="19" t="inlineStr"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr"/>
+      <c r="C72" s="13" t="inlineStr"/>
+      <c r="D72" s="14" t="inlineStr"/>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="16" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr"/>
+      <c r="H72" s="18" t="inlineStr"/>
+      <c r="I72" s="19" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>Arşiv Araştırma Ücreti</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>287.62TL</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H71" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I71" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>Mevduat Araştırma</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>Referans Mektubu -</t>
-        </is>
-      </c>
-      <c r="B74" s="21" t="inlineStr">
-        <is>
-          <t>4000.00TL</t>
-        </is>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>770TL</t>
-        </is>
-      </c>
-      <c r="E74" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H74" s="21" t="inlineStr">
-        <is>
-          <t>50 TL / -</t>
-        </is>
-      </c>
-      <c r="I74" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>Hesap Özeti Verilmesi -</t>
+          <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>287.62TL</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -2851,9 +2938,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D75" s="21" t="inlineStr">
-        <is>
-          <t>190TL</t>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
@@ -2861,9 +2948,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F75" s="21" t="inlineStr">
-        <is>
-          <t>12 TL</t>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G75" s="17" t="inlineStr">
@@ -2882,219 +2969,219 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>Borcu Yoktur Yazısı</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G76" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H76" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I76" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Bakiye Sorma - Yurtiçi - ATM</t>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Mevduat Araştırma</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>Referans Mektubu -</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>770TL</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H78" s="21" t="inlineStr">
+        <is>
+          <t>50 TL / -</t>
+        </is>
+      </c>
+      <c r="I78" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
+          <t>Hesap Özeti Verilmesi -</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>190TL</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F79" s="21" t="inlineStr">
+        <is>
+          <t>12 TL</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I79" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>Borcu Yoktur Yazısı</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>390TL</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I80" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D79" s="21" t="inlineStr">
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>Bakiye Sorma - Yurtiçi - ATM</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
       </c>
-      <c r="E79" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F79" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G79" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H79" s="21" t="inlineStr">
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="inlineStr">
         <is>
           <t>- / -</t>
         </is>
       </c>
-      <c r="I79" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="I83" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>Bakiye Sorma - Yurtdışı - ATM</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>0.45EUR</t>
-        </is>
-      </c>
-      <c r="E82" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>0.27 TL</t>
-        </is>
-      </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H82" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I82" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>Çek Düzenleme -</t>
-        </is>
-      </c>
-      <c r="B85" s="21" t="inlineStr">
-        <is>
-          <t>9.52TL / 0.10%</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>290TL / 1.10%</t>
-        </is>
-      </c>
-      <c r="E85" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
-        <is>
-          <t>761,90 TL</t>
-        </is>
-      </c>
-      <c r="G85" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H85" s="21" t="inlineStr">
-        <is>
-          <t>104,76 TL / -</t>
-        </is>
-      </c>
-      <c r="I85" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>Çek Defteri (Yaprak Başı) -</t>
+          <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
       <c r="B86" s="12" t="inlineStr">
@@ -3107,9 +3194,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D86" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>0.45EUR</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
@@ -3117,9 +3204,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F86" s="16" t="inlineStr">
-        <is>
-          <t>2.380,95 TL</t>
+      <c r="F86" s="21" t="inlineStr">
+        <is>
+          <t>0.27 TL</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -3141,423 +3228,423 @@
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Çek İade Ücreti</t>
+          <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
         </is>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
+          <t>Çek Düzenleme -</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>9.52TL / 0.10%</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>290TL / 1.10%</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>761,90 TL</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>104,76 TL / -</t>
+        </is>
+      </c>
+      <c r="I89" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>Çek Defteri (Yaprak Başı) -</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>2.380,95 TL</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I90" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
           <t>Çek İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B89" s="21" t="inlineStr">
-        <is>
-          <t>171.43TL</t>
-        </is>
-      </c>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
-      <c r="E89" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F89" s="21" t="inlineStr">
-        <is>
-          <t>380,95 TL</t>
-        </is>
-      </c>
-      <c r="G89" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H89" s="21" t="inlineStr">
-        <is>
-          <t>123,81 TL / -</t>
-        </is>
-      </c>
-      <c r="I89" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>Çek Tahsilat Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>Çek Tahsilat</t>
-        </is>
-      </c>
-      <c r="B92" s="21" t="inlineStr">
-        <is>
-          <t>45USD</t>
-        </is>
-      </c>
-      <c r="C92" s="21" t="inlineStr">
-        <is>
-          <t>590.48TL / 0.77%</t>
-        </is>
-      </c>
-      <c r="D92" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E92" s="21" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="F92" s="21" t="inlineStr">
-        <is>
-          <t>714,29 TL</t>
-        </is>
-      </c>
-      <c r="G92" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H92" s="21" t="inlineStr">
-        <is>
-          <t>260 TL / -</t>
-        </is>
-      </c>
-      <c r="I92" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
         </is>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
+          <t>Çek İade Ücreti</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>171.43TL</t>
+        </is>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>390TL</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>380,95 TL</t>
+        </is>
+      </c>
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>123,81 TL / -</t>
+        </is>
+      </c>
+      <c r="I93" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>45USD</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77%</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E96" s="21" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>714,29 TL</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>260 TL / -</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
           <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
         </is>
       </c>
-      <c r="B93" s="21" t="inlineStr">
+      <c r="B97" s="21" t="inlineStr">
         <is>
           <t>257.15TL</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
         <is>
           <t>2940TL / 1%</t>
         </is>
       </c>
-      <c r="E93" s="21" t="inlineStr">
+      <c r="E97" s="21" t="inlineStr">
         <is>
           <t>390TL / 0.2%</t>
         </is>
       </c>
-      <c r="F93" s="21" t="inlineStr">
+      <c r="F97" s="21" t="inlineStr">
         <is>
           <t>1.666,67 TL</t>
         </is>
       </c>
-      <c r="G93" s="21" t="inlineStr">
+      <c r="G97" s="21" t="inlineStr">
         <is>
           <t>585,71 TL</t>
         </is>
       </c>
-      <c r="H93" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I93" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>Diğer Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B94" s="21" t="inlineStr">
-        <is>
-          <t>390.48TL</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>350TL</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F94" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H94" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I94" s="19" t="inlineStr">
-        <is>
-          <t>576,19 TL / 0,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>Aynı Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D95" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F95" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G95" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H95" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I95" s="19" t="inlineStr">
-        <is>
-          <t>427,62 TL / -</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I97" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
+          <t>Diğer Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B98" s="21" t="inlineStr">
+        <is>
+          <t>390.48TL</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" s="21" t="inlineStr">
+        <is>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I98" s="19" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I99" s="19" t="inlineStr">
+        <is>
+          <t>427,62 TL / -</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
           <t>Karşılıksız Çek Belgelendirme -</t>
         </is>
       </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D98" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F98" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G98" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H98" s="18" t="inlineStr">
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr">
         <is>
           <t>371,43 TL / -</t>
         </is>
       </c>
-      <c r="I98" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="I102" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>Senet İade Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t>Senet İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B101" s="21" t="inlineStr">
-        <is>
-          <t>495.24TL</t>
-        </is>
-      </c>
-      <c r="C101" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F101" s="21" t="inlineStr">
-        <is>
-          <t>571,43 TL</t>
-        </is>
-      </c>
-      <c r="G101" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H101" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I101" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>Senet Protesto İşlemleri Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>Senet Protesto Kaldırma -</t>
-        </is>
-      </c>
-      <c r="B104" s="21" t="inlineStr">
-        <is>
-          <t>533.34TL</t>
-        </is>
-      </c>
-      <c r="C104" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D104" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>619,05 TL</t>
-        </is>
-      </c>
-      <c r="G104" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H104" s="21" t="inlineStr">
-        <is>
-          <t>551,43 TL / -</t>
-        </is>
-      </c>
-      <c r="I104" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>Senet Protesto -</t>
+          <t>Senet İade Ücreti</t>
         </is>
       </c>
       <c r="B105" s="21" t="inlineStr">
         <is>
-          <t>600.00TL</t>
+          <t>495.24TL</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -3577,7 +3664,7 @@
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>666,67 TL</t>
+          <t>571,43 TL</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr">
@@ -3599,29 +3686,29 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Senet Tahsile Alma Ücreti</t>
+          <t>Senet Protesto İşlemleri Ücreti</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Muhabir Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Senet Protesto Kaldırma -</t>
+        </is>
+      </c>
+      <c r="B108" s="21" t="inlineStr">
+        <is>
+          <t>533.34TL</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="D108" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
@@ -3631,7 +3718,7 @@
       </c>
       <c r="F108" s="21" t="inlineStr">
         <is>
-          <t>666,67 TL</t>
+          <t>619,05 TL</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr">
@@ -3641,7 +3728,7 @@
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>600 TL / -</t>
+          <t>551,43 TL / -</t>
         </is>
       </c>
       <c r="I108" s="19" t="inlineStr">
@@ -3653,12 +3740,12 @@
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>Aynı Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Senet Protesto -</t>
+        </is>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -3666,9 +3753,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
         </is>
       </c>
       <c r="E109" s="15" t="inlineStr">
@@ -3676,9 +3763,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F109" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
         </is>
       </c>
       <c r="G109" s="17" t="inlineStr">
@@ -3686,7 +3773,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H109" s="18" t="inlineStr">
+      <c r="H109" s="21" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
@@ -3700,61 +3787,162 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>HGS</t>
+          <t>Senet Tahsile Alma Ücreti</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
+          <t>Muhabir Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="13" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" s="21" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I112" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" s="18" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I113" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>HGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B112" s="21" t="inlineStr">
+      <c r="B116" s="21" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C112" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D112" s="21" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E112" s="15" t="inlineStr">
+      <c r="E116" s="15" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="F112" s="21" t="inlineStr">
+      <c r="F116" s="21" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H112" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I112" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="22" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 11:11</t>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I116" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 11:28</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -3942,7 +3942,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>Son güncelleme: 14.08.2026 11:28</t>
+          <t>Son güncelleme: 14.08.2026 11:53</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -3942,7 +3942,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>Son güncelleme: 14.08.2026 11:53</t>
+          <t>Son güncelleme: 14.08.2026 12:09</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -3942,7 +3942,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>Son güncelleme: 14.08.2026 12:09</t>
+          <t>Son güncelleme: 14.08.2026 14:17</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -3942,7 +3942,7 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>Son güncelleme: 14.08.2026 14:17</t>
+          <t>Son güncelleme: 14.08.2026 14:56</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1333,14 +1333,14 @@
           <t>19,94 TL</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>13,33 TL / -</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>19,94 TL / -</t>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1380,14 +1380,14 @@
           <t>39,88 TL</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>27,62 TL / -</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>39,88 TL / -</t>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1427,14 +1427,14 @@
           <t>398,84 TL</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>199,05 TL / -</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>398,84 TL / -</t>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -1528,9 +1528,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>7,97 TL / -</t>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -1592,7 +1592,7 @@
           <t>FAST - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -1622,9 +1622,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>15,96 TL / -</t>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1633,69 +1633,69 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>200 TL / 0,4</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Kiralık Kasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Yıllık Kasa Ücreti - büyük</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>30000.00TL</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>4140TL</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I29" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - büyük</t>
+          <t>Yıllık Kasa Ücreti - küçük</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>30000.00TL</t>
+          <t>22000.00TL</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>4140TL</t>
+          <t>2610TL</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -1737,12 +1737,12 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - küçük</t>
+          <t>Yıllık Kasa Ücreti - orta</t>
         </is>
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>22000.00TL</t>
+          <t>25000.00TL</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>2610TL</t>
+          <t>3390TL</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -1784,12 +1784,12 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - orta</t>
+          <t>Kasa Depozito - büyük</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>25000.00TL</t>
+          <t>28570.00TL</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -1797,9 +1797,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>3390TL</t>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - büyük</t>
+          <t>Kasa Depozito - orta</t>
         </is>
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>28570.00TL</t>
+          <t>23805.00TL</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - orta</t>
+          <t>Kasa Depozito - küçük</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>23805.00TL</t>
+          <t>20950.00TL</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - küçük</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>20950.00TL</t>
+          <t>Yıllık Kasa Ücreti - genel</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>1469.52TL</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - genel</t>
+          <t>Kasa Depozito - genel</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>1469.52TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9420TL</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - genel</t>
+          <t>Kasa Depozito - 0-8300</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>9420TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>- / -</t>
         </is>
       </c>
       <c r="I37" s="19" t="inlineStr">
@@ -2063,69 +2063,69 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Yıllık Kasa Ücreti - 0-8300</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Kıymetli Maden</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Altın Transfer - 0-8300</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>50.00TL</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>3.25%</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 8300-399000</t>
+          <t>Altın Transfer - 0-8300</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>100.00TL</t>
+          <t>50.00TL</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>170TL</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Altın Transfer - 8300-399000</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>100.00TL</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -2180,9 +2180,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>10%</t>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>170TL</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 1-10gr</t>
+          <t>Altın Transfer</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>57,5TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>60 TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 11-100gr</t>
+          <t>Altın Transfer - 1-10gr</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>115TL</t>
+          <t>57,5TL</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>120 TL</t>
+          <t>60 TL</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
@@ -2308,454 +2308,454 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
+          <t>Altın Transfer - 11-100gr</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>115TL</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>120 TL</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
           <t>Altın Transfer - 399000+</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
         <is>
           <t>415TL</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F45" s="21" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
         <is>
           <t>0.00018</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H45" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I45" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D48" s="21" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="G49" s="17" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>339 TL / -</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri - Kart</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
+      <c r="C52" s="21" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D51" s="21" t="inlineStr">
+      <c r="D52" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E51" s="21" t="inlineStr">
+      <c r="E52" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="F51" s="21" t="inlineStr">
+      <c r="F52" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
+      <c r="G52" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="H51" s="21" t="inlineStr">
-        <is>
-          <t>0,63 TL / -</t>
-        </is>
-      </c>
-      <c r="I51" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L51" s="20" t="inlineStr">
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I52" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
         <is>
           <t>Fatura ödemeleri üst tier için %3,5'a çıkabiliyor</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="L52" s="20" t="inlineStr">
+    <row r="53">
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>Borcu Yoktur Yazısı almak için ücret alınabiliyor</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="L53" s="20" t="inlineStr">
+      <c r="L54" s="20" t="inlineStr">
         <is>
           <t>Mevduat Araştırma Ücretleri zamlanabilir</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>3.50TL / 3.50%</t>
         </is>
       </c>
-      <c r="C54" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D54" s="21" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F54" s="21" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
         <is>
           <t>2 TL / 3,5%</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H54" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>3 TL / -</t>
-        </is>
-      </c>
-      <c r="L54" s="20" t="inlineStr">
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
         <is>
           <t>Güvenli Araç Alım Satım YKB 97,53 TRY</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="E57" s="15" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="F57" s="16" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H57" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I57" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I58" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D60" s="21" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
         <is>
           <t>26TL</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F60" s="21" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I60" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H63" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I64" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri Aracılık</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>Telefon - 0-8300 TRY</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>3,99 TL</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H66" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I66" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>Telefon - 8300-399000 TRY</t>
+          <t>Telefon - 0-8300 TRY</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>7,98 TL</t>
+          <t>3,99 TL</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>Telefon - 399000+ TRY</t>
+          <t>Telefon - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>99,71 TL</t>
+          <t>7,98 TL</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -2849,189 +2849,189 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
+          <t>Telefon - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>99,71 TL</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
           <t>Telefon Ödemeleri</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F69" s="16" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
         <is>
           <t>1 %</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I69" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="G70" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I70" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>Vergi Tahsilat Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>Vergi Tahsilat</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr"/>
-      <c r="C72" s="13" t="inlineStr"/>
-      <c r="D72" s="14" t="inlineStr"/>
-      <c r="E72" s="15" t="inlineStr"/>
-      <c r="F72" s="16" t="inlineStr"/>
-      <c r="G72" s="17" t="inlineStr"/>
-      <c r="H72" s="18" t="inlineStr"/>
-      <c r="I72" s="19" t="inlineStr"/>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="10" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr"/>
+      <c r="C73" s="13" t="inlineStr"/>
+      <c r="D73" s="14" t="inlineStr"/>
+      <c r="E73" s="15" t="inlineStr"/>
+      <c r="F73" s="16" t="inlineStr"/>
+      <c r="G73" s="17" t="inlineStr"/>
+      <c r="H73" s="18" t="inlineStr"/>
+      <c r="I73" s="19" t="inlineStr"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E75" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G75" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H75" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I75" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Mevduat Araştırma</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>Referans Mektubu -</t>
-        </is>
-      </c>
-      <c r="B78" s="21" t="inlineStr">
-        <is>
-          <t>4000.00TL</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>770TL</t>
-        </is>
-      </c>
-      <c r="E78" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F78" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G78" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H78" s="21" t="inlineStr">
-        <is>
-          <t>50 TL / -</t>
-        </is>
-      </c>
-      <c r="I78" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>Hesap Özeti Verilmesi -</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Referans Mektubu -</t>
+        </is>
+      </c>
+      <c r="B79" s="21" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>190TL</t>
+          <t>770TL</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
@@ -3049,9 +3049,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F79" s="21" t="inlineStr">
-        <is>
-          <t>12 TL</t>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr">
@@ -3073,401 +3073,401 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
+          <t>Hesap Özeti Verilmesi -</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D80" s="21" t="inlineStr">
+        <is>
+          <t>190TL</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>12 TL</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I80" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
           <t>Borcu Yoktur Yazısı</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E80" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F80" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G80" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H80" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I80" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I81" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D83" s="21" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F83" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G83" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H83" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
-      <c r="I83" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I84" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D86" s="21" t="inlineStr">
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="inlineStr">
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
         <is>
           <t>0.27 TL</t>
         </is>
       </c>
-      <c r="G86" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H86" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I86" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="G87" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I87" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>Çek Düzenleme -</t>
-        </is>
-      </c>
-      <c r="B89" s="21" t="inlineStr">
-        <is>
-          <t>9.52TL / 0.10%</t>
-        </is>
-      </c>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>290TL / 1.10%</t>
-        </is>
-      </c>
-      <c r="E89" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F89" s="21" t="inlineStr">
-        <is>
-          <t>761,90 TL</t>
-        </is>
-      </c>
-      <c r="G89" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H89" s="21" t="inlineStr">
-        <is>
-          <t>104,76 TL / -</t>
-        </is>
-      </c>
-      <c r="I89" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
+          <t>Çek Düzenleme -</t>
+        </is>
+      </c>
+      <c r="B90" s="21" t="inlineStr">
+        <is>
+          <t>9.52TL / 0.10%</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>290TL / 1.10%</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F90" s="21" t="inlineStr">
+        <is>
+          <t>761,90 TL</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I90" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
           <t>Çek Defteri (Yaprak Başı) -</t>
         </is>
       </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D90" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F90" s="16" t="inlineStr">
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
         <is>
           <t>2.380,95 TL</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H90" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I90" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="G91" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I91" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
         </is>
       </c>
-      <c r="B93" s="21" t="inlineStr">
+      <c r="B94" s="21" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D94" s="21" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F93" s="21" t="inlineStr">
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F94" s="21" t="inlineStr">
         <is>
           <t>380,95 TL</t>
         </is>
       </c>
-      <c r="G93" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H93" s="21" t="inlineStr">
-        <is>
-          <t>123,81 TL / -</t>
-        </is>
-      </c>
-      <c r="I93" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>Çek Tahsilat Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>Çek Tahsilat</t>
-        </is>
-      </c>
-      <c r="B96" s="21" t="inlineStr">
-        <is>
-          <t>45USD</t>
-        </is>
-      </c>
-      <c r="C96" s="21" t="inlineStr">
-        <is>
-          <t>590.48TL / 0.77%</t>
-        </is>
-      </c>
-      <c r="D96" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E96" s="21" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
-      <c r="F96" s="21" t="inlineStr">
-        <is>
-          <t>714,29 TL</t>
-        </is>
-      </c>
-      <c r="G96" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>260 TL / -</t>
-        </is>
-      </c>
-      <c r="I96" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
+          <t>Çek Tahsilat</t>
         </is>
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>257.15TL</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D97" s="21" t="inlineStr">
-        <is>
-          <t>2940TL / 1%</t>
+          <t>45USD</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77%</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>390TL / 0.2%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>1.666,67 TL</t>
-        </is>
-      </c>
-      <c r="G97" s="21" t="inlineStr">
-        <is>
-          <t>585,71 TL</t>
+          <t>714,29 TL</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H97" s="18" t="inlineStr">
@@ -3484,12 +3484,12 @@
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Diğer Banka Çeki -</t>
+          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>390.48TL</t>
+          <t>257.15TL</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="D98" s="21" t="inlineStr">
         <is>
-          <t>350TL</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F98" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G98" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>2940TL / 1%</t>
+        </is>
+      </c>
+      <c r="E98" s="21" t="inlineStr">
+        <is>
+          <t>390TL / 0.2%</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>1.666,67 TL</t>
+        </is>
+      </c>
+      <c r="G98" s="21" t="inlineStr">
+        <is>
+          <t>585,71 TL</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="I98" s="19" t="inlineStr">
         <is>
-          <t>576,19 TL / 0,6</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Aynı Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Diğer Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
+        <is>
+          <t>390.48TL</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -3544,9 +3544,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>350TL</t>
         </is>
       </c>
       <c r="E99" s="15" t="inlineStr">
@@ -3571,26 +3571,26 @@
       </c>
       <c r="I99" s="19" t="inlineStr">
         <is>
-          <t>427,62 TL / -</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
+          <t>Senet İade Ücreti</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>Karşılıksız Çek Belgelendirme -</t>
-        </is>
-      </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>Senet İade Ücreti</t>
+        </is>
+      </c>
+      <c r="B102" s="21" t="inlineStr">
+        <is>
+          <t>495.24TL</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -3598,9 +3598,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D102" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
@@ -3608,9 +3608,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F102" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t>571,43 TL</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr">
@@ -3618,9 +3618,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H102" s="18" t="inlineStr">
-        <is>
-          <t>371,43 TL / -</t>
+      <c r="H102" s="21" t="inlineStr">
+        <is>
+          <t>123,81 TL / -</t>
         </is>
       </c>
       <c r="I102" s="19" t="inlineStr">
@@ -3632,19 +3632,19 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Senet İade Ücreti</t>
+          <t>Senet Protesto İşlemleri Ücreti</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>Senet İade Ücreti</t>
+          <t>Senet Protesto Kaldırma -</t>
         </is>
       </c>
       <c r="B105" s="21" t="inlineStr">
         <is>
-          <t>495.24TL</t>
+          <t>533.34TL</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>571,43 TL</t>
+          <t>619,05 TL</t>
         </is>
       </c>
       <c r="G105" s="17" t="inlineStr">
@@ -3674,88 +3674,88 @@
       </c>
       <c r="H105" s="21" t="inlineStr">
         <is>
+          <t>551,43 TL / -</t>
+        </is>
+      </c>
+      <c r="I105" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto -</t>
+        </is>
+      </c>
+      <c r="B106" s="21" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D106" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" s="21" t="inlineStr">
+        <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I105" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>Senet Protesto İşlemleri Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>Senet Protesto Kaldırma -</t>
-        </is>
-      </c>
-      <c r="B108" s="21" t="inlineStr">
-        <is>
-          <t>533.34TL</t>
-        </is>
-      </c>
-      <c r="C108" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D108" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F108" s="21" t="inlineStr">
-        <is>
-          <t>619,05 TL</t>
-        </is>
-      </c>
-      <c r="G108" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H108" s="21" t="inlineStr">
-        <is>
-          <t>551,43 TL / -</t>
-        </is>
-      </c>
-      <c r="I108" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="I106" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>Senet Tahsile Alma Ücreti</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>Senet Protesto -</t>
-        </is>
-      </c>
-      <c r="B109" s="21" t="inlineStr">
+          <t>Muhabir Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="C109" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E109" s="15" t="inlineStr">
@@ -3775,78 +3775,78 @@
       </c>
       <c r="H109" s="21" t="inlineStr">
         <is>
+          <t>104,76 TL / -</t>
+        </is>
+      </c>
+      <c r="I109" s="21" t="inlineStr">
+        <is>
+          <t>576,19 TL / 0,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Aynı Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C110" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="inlineStr">
+        <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I109" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>Senet Tahsile Alma Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>Muhabir Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" s="13" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="D112" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F112" s="21" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H112" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I112" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="I110" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>HGS</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>Aynı Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>HGS Kart Ücreti</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>550.00TL</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
@@ -3854,19 +3854,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D113" s="21" t="inlineStr">
+        <is>
+          <t>550TL</t>
         </is>
       </c>
       <c r="E113" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F113" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>550TL</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>500 TL</t>
         </is>
       </c>
       <c r="G113" s="17" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H113" s="18" t="inlineStr">
         <is>
-          <t>600 TL / -</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I113" s="19" t="inlineStr">
@@ -3885,64 +3885,10 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>HGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t>HGS Kart Ücreti</t>
-        </is>
-      </c>
-      <c r="B116" s="21" t="inlineStr">
-        <is>
-          <t>550.00TL</t>
-        </is>
-      </c>
-      <c r="C116" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D116" s="21" t="inlineStr">
-        <is>
-          <t>550TL</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>550TL</t>
-        </is>
-      </c>
-      <c r="F116" s="21" t="inlineStr">
-        <is>
-          <t>500 TL</t>
-        </is>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H116" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I116" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="22" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 14:56</t>
+    <row r="115">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 15:13</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1333,14 +1333,14 @@
           <t>19,94 TL</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>13,33 TL / -</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>19,94 TL / -</t>
         </is>
       </c>
     </row>
@@ -1380,14 +1380,14 @@
           <t>39,88 TL</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>27,62 TL / -</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>39,88 TL / -</t>
         </is>
       </c>
     </row>
@@ -1427,14 +1427,14 @@
           <t>398,84 TL</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>199,05 TL / -</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>398,84 TL / -</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -1528,9 +1528,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>7,97 TL / -</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -1592,7 +1592,7 @@
           <t>FAST - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -1622,9 +1622,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>15,96 TL / -</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1633,69 +1633,69 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>200 TL / 0,4</t>
+        </is>
+      </c>
+      <c r="I27" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Kiralık Kasa</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Yıllık Kasa Ücreti - büyük</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>30000.00TL</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>4140TL</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - küçük</t>
+          <t>Yıllık Kasa Ücreti - büyük</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>22000.00TL</t>
+          <t>30000.00TL</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>2610TL</t>
+          <t>4140TL</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -1737,12 +1737,12 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - orta</t>
+          <t>Yıllık Kasa Ücreti - küçük</t>
         </is>
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>25000.00TL</t>
+          <t>22000.00TL</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>3390TL</t>
+          <t>2610TL</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -1784,12 +1784,12 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - büyük</t>
+          <t>Yıllık Kasa Ücreti - orta</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>28570.00TL</t>
+          <t>25000.00TL</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -1797,9 +1797,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>3390TL</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - orta</t>
+          <t>Kasa Depozito - büyük</t>
         </is>
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>23805.00TL</t>
+          <t>28570.00TL</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - küçük</t>
+          <t>Kasa Depozito - orta</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>20950.00TL</t>
+          <t>23805.00TL</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - genel</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>1469.52TL</t>
+          <t>Kasa Depozito - küçük</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>20950.00TL</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -1958,9 +1958,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - genel</t>
+          <t>Yıllık Kasa Ücreti - genel</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1469.52TL</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>9420TL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Kasa Depozito - 0-8300</t>
+          <t>Kasa Depozito - genel</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9420TL</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>- / -</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I37" s="19" t="inlineStr">
@@ -2063,69 +2063,69 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Yıllık Kasa Ücreti - 0-8300</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>- / -</t>
-        </is>
-      </c>
-      <c r="I38" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Kıymetli Maden</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Altın Transfer - 0-8300</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>50.00TL</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 0-8300</t>
+          <t>Altın Transfer - 8300-399000</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>50.00TL</t>
+          <t>100.00TL</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>170TL</t>
         </is>
       </c>
       <c r="E41" s="15" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 8300-399000</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>100.00TL</t>
+          <t>Altın Transfer</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -2180,9 +2180,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>170TL</t>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>10%</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer</t>
+          <t>Altın Transfer - 1-10gr</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>57,5TL</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>60 TL</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
@@ -2261,7 +2261,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 1-10gr</t>
+          <t>Altın Transfer - 11-100gr</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>57,5TL</t>
+          <t>115TL</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>60 TL</t>
+          <t>120 TL</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>Altın Transfer - 11-100gr</t>
+          <t>Altın Transfer - 399000+</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
@@ -2321,19 +2321,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>415TL</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>115TL</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>120 TL</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>0.00018</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
@@ -2352,410 +2352,410 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Altın Transfer - 399000+</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>415TL</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>0.00018</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H46" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I46" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Üçüncü Kişi ve Kuruluşlardan Temin Edilecek Rapor Ücretleri - Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D49" s="21" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F49" s="21" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr">
+      <c r="G48" s="17" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H49" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I49" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="H48" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I48" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri - Kart</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Fatura Ödemeleri</t>
         </is>
       </c>
-      <c r="B52" s="21" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D52" s="21" t="inlineStr">
+      <c r="D51" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="E51" s="21" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="F52" s="21" t="inlineStr">
+      <c r="F51" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="G52" s="21" t="inlineStr">
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H51" s="21" t="inlineStr">
+        <is>
+          <t>0,63 TL / -</t>
+        </is>
+      </c>
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>Fatura ödemeleri üst tier için %3,5'a çıkabiliyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
       <c r="L52" s="20" t="inlineStr">
         <is>
-          <t>Fatura ödemeleri üst tier için %3,5'a çıkabiliyor</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
+          <t>Borcu Yoktur Yazısı almak için ücret alınabiliyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>SGK Prim Ödemeleri</t>
+        </is>
+      </c>
       <c r="L53" s="20" t="inlineStr">
         <is>
-          <t>Borcu Yoktur Yazısı almak için ücret alınabiliyor</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+          <t>Mevduat Araştırma Ücretleri zamlanabilir</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>SGK Prim Ödemeleri</t>
         </is>
       </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>3.50TL / 3.50%</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>2 TL / 3,5%</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I54" s="19" t="inlineStr">
+        <is>
+          <t>3 TL / -</t>
+        </is>
+      </c>
       <c r="L54" s="20" t="inlineStr">
         <is>
-          <t>Mevduat Araştırma Ücretleri zamlanabilir</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>SGK Prim Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="inlineStr">
-        <is>
-          <t>3.50TL / 3.50%</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D55" s="21" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>2 TL / 3,5%</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H55" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I55" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
           <t>Güvenli Araç Alım Satım YKB 97,53 TRY</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>275TL</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H58" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I58" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I57" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Şans Oyunu Ödemeleri Aracılık</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
         <is>
           <t>26TL</t>
         </is>
       </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F61" s="21" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H61" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I61" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H64" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Telefon Ödemeleri Aracılık</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Telefon - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>Telefon - 0-8300 TRY</t>
+          <t>Telefon - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>3,99 TL</t>
+          <t>7,98 TL</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
@@ -2802,7 +2802,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>Telefon - 8300-399000 TRY</t>
+          <t>Telefon - 399000+ TRY</t>
         </is>
       </c>
       <c r="B68" s="12" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>7,98 TL</t>
+          <t>99,71 TL</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>Telefon - 399000+ TRY</t>
+          <t>Telefon Ödemeleri</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
-          <t>99,71 TL</t>
+          <t>1 %</t>
         </is>
       </c>
       <c r="G69" s="17" t="inlineStr">
@@ -2893,145 +2893,145 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>Telefon Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>1 %</t>
-        </is>
-      </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H70" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I70" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>Vergi Tahsilat Aracılık</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>Vergi Tahsilat</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr"/>
-      <c r="C73" s="13" t="inlineStr"/>
-      <c r="D73" s="14" t="inlineStr"/>
-      <c r="E73" s="15" t="inlineStr"/>
-      <c r="F73" s="16" t="inlineStr"/>
-      <c r="G73" s="17" t="inlineStr"/>
-      <c r="H73" s="18" t="inlineStr"/>
-      <c r="I73" s="19" t="inlineStr"/>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr"/>
+      <c r="C72" s="13" t="inlineStr"/>
+      <c r="D72" s="14" t="inlineStr"/>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="16" t="inlineStr"/>
+      <c r="G72" s="17" t="inlineStr"/>
+      <c r="H72" s="18" t="inlineStr"/>
+      <c r="I72" s="19" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>Arşiv Araştırma Ücreti</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>287.62TL</t>
         </is>
       </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G76" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H76" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I76" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>Mevduat Araştırma</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>Referans Mektubu -</t>
+        </is>
+      </c>
+      <c r="B78" s="21" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>770TL</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H78" s="21" t="inlineStr">
+        <is>
+          <t>50 TL / -</t>
+        </is>
+      </c>
+      <c r="I78" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>Referans Mektubu -</t>
-        </is>
-      </c>
-      <c r="B79" s="21" t="inlineStr">
-        <is>
-          <t>4000.00TL</t>
+          <t>Hesap Özeti Verilmesi -</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>770TL</t>
+          <t>190TL</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
@@ -3049,9 +3049,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F79" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="F79" s="21" t="inlineStr">
+        <is>
+          <t>12 TL</t>
         </is>
       </c>
       <c r="G79" s="17" t="inlineStr">
@@ -3073,7 +3073,7 @@
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>Hesap Özeti Verilmesi -</t>
+          <t>Borcu Yoktur Yazısı</t>
         </is>
       </c>
       <c r="B80" s="12" t="inlineStr">
@@ -3086,9 +3086,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>190TL</t>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>390TL</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
@@ -3096,9 +3096,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>12 TL</t>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
@@ -3117,177 +3117,177 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>Borcu Yoktur Yazısı</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
-      <c r="E81" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F81" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G81" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H81" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I81" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
       </c>
-      <c r="E84" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F84" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G84" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H84" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I84" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
+        </is>
+      </c>
+      <c r="I83" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D87" s="21" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D86" s="21" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
-      <c r="E87" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F86" s="21" t="inlineStr">
         <is>
           <t>0.27 TL</t>
         </is>
       </c>
-      <c r="G87" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H87" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I87" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>Çek Düzenleme -</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>9.52TL / 0.10%</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>290TL / 1.10%</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>761,90 TL</t>
+        </is>
+      </c>
+      <c r="G89" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>104,76 TL / -</t>
+        </is>
+      </c>
+      <c r="I89" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>Çek Düzenleme -</t>
-        </is>
-      </c>
-      <c r="B90" s="21" t="inlineStr">
-        <is>
-          <t>9.52TL / 0.10%</t>
+          <t>Çek Defteri (Yaprak Başı) -</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -3295,9 +3295,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D90" s="21" t="inlineStr">
-        <is>
-          <t>290TL / 1.10%</t>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
@@ -3305,9 +3305,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F90" s="21" t="inlineStr">
-        <is>
-          <t>761,90 TL</t>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>2.380,95 TL</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -3326,148 +3326,148 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>Çek Defteri (Yaprak Başı) -</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E91" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F91" s="16" t="inlineStr">
-        <is>
-          <t>2.380,95 TL</t>
-        </is>
-      </c>
-      <c r="G91" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H91" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I91" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>Çek İade Ücreti</t>
         </is>
       </c>
-      <c r="B94" s="21" t="inlineStr">
+      <c r="B93" s="21" t="inlineStr">
         <is>
           <t>171.43TL</t>
         </is>
       </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D94" s="21" t="inlineStr">
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
-      <c r="E94" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F94" s="21" t="inlineStr">
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
         <is>
           <t>380,95 TL</t>
         </is>
       </c>
-      <c r="G94" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H94" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I94" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
+      <c r="G93" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>123,81 TL / -</t>
+        </is>
+      </c>
+      <c r="I93" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>Çek Tahsilat Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>45USD</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77%</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E96" s="21" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>714,29 TL</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>260 TL / -</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="inlineStr">
+        <is>
+          <t>- / -</t>
         </is>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Çek Tahsilat</t>
+          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
         </is>
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>45USD</t>
-        </is>
-      </c>
-      <c r="C97" s="21" t="inlineStr">
-        <is>
-          <t>590.48TL / 0.77%</t>
-        </is>
-      </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>257.15TL</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>2940TL / 1%</t>
         </is>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>390TL / 0.2%</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>714,29 TL</t>
-        </is>
-      </c>
-      <c r="G97" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>1.666,67 TL</t>
+        </is>
+      </c>
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>585,71 TL</t>
         </is>
       </c>
       <c r="H97" s="18" t="inlineStr">
@@ -3484,12 +3484,12 @@
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Döviz Çekleri Tahsilatı (Diğer Banka) -</t>
+          <t>Diğer Banka Çeki -</t>
         </is>
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>257.15TL</t>
+          <t>390.48TL</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="D98" s="21" t="inlineStr">
         <is>
-          <t>2940TL / 1%</t>
-        </is>
-      </c>
-      <c r="E98" s="21" t="inlineStr">
-        <is>
-          <t>390TL / 0.2%</t>
-        </is>
-      </c>
-      <c r="F98" s="21" t="inlineStr">
-        <is>
-          <t>1.666,67 TL</t>
-        </is>
-      </c>
-      <c r="G98" s="21" t="inlineStr">
-        <is>
-          <t>585,71 TL</t>
+          <t>350TL</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="I98" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>576,19 TL / 0,6</t>
         </is>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Diğer Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B99" s="21" t="inlineStr">
-        <is>
-          <t>390.48TL</t>
+          <t>Aynı Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -3544,9 +3544,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>350TL</t>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E99" s="15" t="inlineStr">
@@ -3571,26 +3571,26 @@
       </c>
       <c r="I99" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>427,62 TL / -</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Senet İade Ücreti</t>
+          <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
         </is>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>Senet İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B102" s="21" t="inlineStr">
-        <is>
-          <t>495.24TL</t>
+          <t>Karşılıksız Çek Belgelendirme -</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -3598,9 +3598,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D102" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
@@ -3608,9 +3608,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F102" s="21" t="inlineStr">
-        <is>
-          <t>571,43 TL</t>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr">
@@ -3618,9 +3618,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H102" s="21" t="inlineStr">
-        <is>
-          <t>123,81 TL / -</t>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>371,43 TL / -</t>
         </is>
       </c>
       <c r="I102" s="19" t="inlineStr">
@@ -3632,263 +3632,317 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Senet Protesto İşlemleri Ücreti</t>
+          <t>Senet İade Ücreti</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
+          <t>Senet İade Ücreti</t>
+        </is>
+      </c>
+      <c r="B105" s="21" t="inlineStr">
+        <is>
+          <t>495.24TL</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D105" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>571,43 TL</t>
+        </is>
+      </c>
+      <c r="G105" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" s="21" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I105" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>Senet Protesto İşlemleri Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
           <t>Senet Protesto Kaldırma -</t>
         </is>
       </c>
-      <c r="B105" s="21" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>533.34TL</t>
         </is>
       </c>
-      <c r="C105" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D105" s="21" t="inlineStr">
+      <c r="C108" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D108" s="21" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="inlineStr">
         <is>
           <t>619,05 TL</t>
         </is>
       </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H105" s="21" t="inlineStr">
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H108" s="21" t="inlineStr">
         <is>
           <t>551,43 TL / -</t>
         </is>
       </c>
-      <c r="I105" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t>Senet Protesto -</t>
-        </is>
-      </c>
-      <c r="B106" s="21" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="C106" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D106" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G106" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H106" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I106" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>Senet Tahsile Alma Ücreti</t>
+      <c r="I108" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
+          <t>Senet Protesto -</t>
+        </is>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D109" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G109" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" s="21" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I109" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Senet Tahsile Alma Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
           <t>Muhabir Banka Senet Tahsili -</t>
         </is>
       </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C109" s="21" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="13" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E109" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
         <is>
           <t>666,67 TL</t>
         </is>
       </c>
-      <c r="G109" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H109" s="21" t="inlineStr">
-        <is>
-          <t>104,76 TL / -</t>
-        </is>
-      </c>
-      <c r="I109" s="21" t="inlineStr">
-        <is>
-          <t>576,19 TL / 0,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t>Aynı Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B110" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C110" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D110" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F110" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H110" s="18" t="inlineStr">
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" s="21" t="inlineStr">
         <is>
           <t>600 TL / -</t>
         </is>
       </c>
-      <c r="I110" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>HGS</t>
+      <c r="I112" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
+          <t>Aynı Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G113" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" s="18" t="inlineStr">
+        <is>
+          <t>600 TL / -</t>
+        </is>
+      </c>
+      <c r="I113" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>HGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B113" s="21" t="inlineStr">
+      <c r="B116" s="21" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C113" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D113" s="21" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D116" s="21" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E113" s="15" t="inlineStr">
+      <c r="E116" s="15" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="F113" s="21" t="inlineStr">
+      <c r="F116" s="21" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G113" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H113" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I113" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="22" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 15:13</t>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I116" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 15:31</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1333,14 +1333,14 @@
           <t>19,94 TL</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>13,33 TL / -</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>19,94 TL / -</t>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1380,14 +1380,14 @@
           <t>39,88 TL</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>27,62 TL / -</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>39,88 TL / -</t>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1427,14 +1427,14 @@
           <t>398,84 TL</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>199,05 TL / -</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>398,84 TL / -</t>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -1528,9 +1528,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>7,97 TL / -</t>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -1592,7 +1592,7 @@
           <t>FAST - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -1622,9 +1622,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>15,96 TL / -</t>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1639,46 +1639,14 @@
           <t>FAST</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>200 TL / 0,4</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="B27" s="12" t="inlineStr"/>
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr"/>
+      <c r="F27" s="16" t="inlineStr"/>
+      <c r="G27" s="17" t="inlineStr"/>
+      <c r="H27" s="18" t="inlineStr"/>
+      <c r="I27" s="19" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
@@ -1723,9 +1691,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
@@ -1770,9 +1738,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I31" s="19" t="inlineStr">
@@ -1817,9 +1785,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" s="19" t="inlineStr">
@@ -1834,7 +1802,7 @@
           <t>Kasa Depozito - büyük</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
@@ -1864,9 +1832,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I33" s="19" t="inlineStr">
@@ -1881,7 +1849,7 @@
           <t>Kasa Depozito - orta</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
@@ -1911,9 +1879,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I34" s="19" t="inlineStr">
@@ -1928,7 +1896,7 @@
           <t>Kasa Depozito - küçük</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
@@ -1958,9 +1926,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I35" s="19" t="inlineStr">
@@ -2395,9 +2363,9 @@
           <t>95,24 TL</t>
         </is>
       </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I48" s="19" t="inlineStr">
@@ -2449,9 +2417,9 @@
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="H51" s="21" t="inlineStr">
-        <is>
-          <t>0,63 TL / -</t>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I51" s="19" t="inlineStr">
@@ -2527,7 +2495,7 @@
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>3 TL / -</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L54" s="20" t="inlineStr">
@@ -3012,9 +2980,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H78" s="21" t="inlineStr">
-        <is>
-          <t>50 TL / -</t>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I78" s="19" t="inlineStr">
@@ -3140,7 +3108,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D83" s="21" t="inlineStr">
+      <c r="D83" s="14" t="inlineStr">
         <is>
           <t>0.41TL</t>
         </is>
@@ -3160,9 +3128,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H83" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I83" s="19" t="inlineStr">
@@ -3268,9 +3236,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H89" s="21" t="inlineStr">
-        <is>
-          <t>104,76 TL / -</t>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I89" s="19" t="inlineStr">
@@ -3369,9 +3337,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H93" s="21" t="inlineStr">
-        <is>
-          <t>123,81 TL / -</t>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I93" s="19" t="inlineStr">
@@ -3423,14 +3391,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H96" s="21" t="inlineStr">
-        <is>
-          <t>260 TL / -</t>
-        </is>
-      </c>
-      <c r="I96" s="21" t="inlineStr">
-        <is>
-          <t>- / -</t>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I96" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3524,181 +3492,149 @@
       </c>
       <c r="I98" s="19" t="inlineStr">
         <is>
-          <t>576,19 TL / 0,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>Aynı Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D99" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F99" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G99" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H99" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I99" s="19" t="inlineStr">
-        <is>
-          <t>427,62 TL / -</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="10" t="inlineStr">
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>Çek Belgelendirme ve Düzeltme Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>Karşılıksız Çek Belgelendirme -</t>
         </is>
       </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F102" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G102" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H102" s="18" t="inlineStr">
-        <is>
-          <t>371,43 TL / -</t>
-        </is>
-      </c>
-      <c r="I102" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="10" t="inlineStr">
+      <c r="B101" s="12" t="inlineStr"/>
+      <c r="C101" s="13" t="inlineStr"/>
+      <c r="D101" s="14" t="inlineStr"/>
+      <c r="E101" s="15" t="inlineStr"/>
+      <c r="F101" s="16" t="inlineStr"/>
+      <c r="G101" s="17" t="inlineStr"/>
+      <c r="H101" s="18" t="inlineStr"/>
+      <c r="I101" s="19" t="inlineStr"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>Senet İade Ücreti</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>Senet İade Ücreti</t>
         </is>
       </c>
-      <c r="B105" s="21" t="inlineStr">
+      <c r="B104" s="21" t="inlineStr">
         <is>
           <t>495.24TL</t>
         </is>
       </c>
-      <c r="C105" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D105" s="21" t="inlineStr">
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D104" s="21" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
-      <c r="E105" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
         <is>
           <t>571,43 TL</t>
         </is>
       </c>
-      <c r="G105" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H105" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I105" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I104" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>Senet Protesto İşlemleri Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>Senet Protesto Kaldırma -</t>
+        </is>
+      </c>
+      <c r="B107" s="21" t="inlineStr">
+        <is>
+          <t>533.34TL</t>
+        </is>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D107" s="21" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>619,05 TL</t>
+        </is>
+      </c>
+      <c r="G107" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I107" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Senet Protesto Kaldırma -</t>
+          <t>Senet Protesto -</t>
         </is>
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>533.34TL</t>
+          <t>600.00TL</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -3718,7 +3654,7 @@
       </c>
       <c r="F108" s="21" t="inlineStr">
         <is>
-          <t>619,05 TL</t>
+          <t>666,67 TL</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr">
@@ -3726,9 +3662,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="H108" s="21" t="inlineStr">
-        <is>
-          <t>551,43 TL / -</t>
+      <c r="H108" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I108" s="19" t="inlineStr">
@@ -3737,212 +3673,133 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>Senet Protesto -</t>
-        </is>
-      </c>
-      <c r="B109" s="21" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>Senet Tahsile Alma Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>Muhabir Banka Senet Tahsili -</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
         <is>
           <t>600.00TL</t>
         </is>
       </c>
-      <c r="C109" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E109" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F111" s="16" t="inlineStr">
         <is>
           <t>666,67 TL</t>
         </is>
       </c>
-      <c r="G109" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H109" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I109" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>Senet Tahsile Alma Ücreti</t>
+      <c r="G111" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I111" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>Muhabir Banka Senet Tahsili -</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" s="13" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="D112" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F112" s="21" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H112" s="21" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I112" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
           <t>Aynı Banka Senet Tahsili -</t>
         </is>
       </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E113" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F113" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G113" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H113" s="18" t="inlineStr">
-        <is>
-          <t>600 TL / -</t>
-        </is>
-      </c>
-      <c r="I113" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="10" t="inlineStr">
+      <c r="B112" s="12" t="inlineStr"/>
+      <c r="C112" s="13" t="inlineStr"/>
+      <c r="D112" s="14" t="inlineStr"/>
+      <c r="E112" s="15" t="inlineStr"/>
+      <c r="F112" s="16" t="inlineStr"/>
+      <c r="G112" s="17" t="inlineStr"/>
+      <c r="H112" s="18" t="inlineStr"/>
+      <c r="I112" s="19" t="inlineStr"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>HGS</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
         <is>
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B116" s="21" t="inlineStr">
+      <c r="B115" s="21" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D116" s="21" t="inlineStr">
+      <c r="C115" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D115" s="21" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E116" s="15" t="inlineStr">
+      <c r="E115" s="15" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="F116" s="21" t="inlineStr">
+      <c r="F115" s="21" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H116" s="18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I116" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="22" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 15:31</t>
+      <c r="G115" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H115" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I115" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 15:52</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -45,7 +45,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="0000B050"/>
       <sz val="10"/>
     </font>
     <font>
@@ -62,12 +62,12 @@
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
       <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="0000B050"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -75,7 +75,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -124,12 +124,6 @@
         <bgColor rgb="00F4B183"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -157,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,7 +180,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,9 +196,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -660,12 +651,12 @@
       </c>
       <c r="D4" s="12" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>4.25 %</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr"/>
+      <c r="G4" s="15" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -673,7 +664,7 @@
           <t>Düzenli EFT - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -689,12 +680,12 @@
           <t>7,97TL</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>7,97 TL</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr"/>
+      <c r="G5" s="15" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -702,7 +693,7 @@
           <t>Düzenli EFT - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -718,12 +709,12 @@
           <t>15,96TL</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>15,96 TL</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr"/>
+      <c r="G6" s="15" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -731,7 +722,7 @@
           <t>Düzenli EFT - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>199.41TL</t>
         </is>
@@ -747,12 +738,12 @@
           <t>199,41TL</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>199,41 TL</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr"/>
+      <c r="G7" s="15" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -770,7 +761,7 @@
           <t>39.87TL</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>27,84TL</t>
         </is>
@@ -780,12 +771,12 @@
           <t>39,87TL</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>309.523,82 TL</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>39,87 TL</t>
         </is>
@@ -807,7 +798,7 @@
           <t>79.76TL</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>55,69TL</t>
         </is>
@@ -817,12 +808,12 @@
           <t>79,76TL</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>619.047,62 TL</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>79,76 TL</t>
         </is>
@@ -844,7 +835,7 @@
           <t>797.68TL</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>398,83TL</t>
         </is>
@@ -854,12 +845,12 @@
           <t>797,68TL</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>398,83 TL</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>797,68 TL</t>
         </is>
@@ -871,7 +862,7 @@
           <t>Düzenli EFT</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>1.00TL / 1.00%</t>
         </is>
@@ -879,8 +870,8 @@
       <c r="C11" s="11" t="inlineStr"/>
       <c r="D11" s="12" t="inlineStr"/>
       <c r="E11" s="13" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -895,7 +886,7 @@
           <t>Düzenli Havale - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>3.99TL</t>
         </is>
@@ -911,12 +902,12 @@
           <t>3,99TL</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>3,99 TL</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>3,99 TL</t>
         </is>
@@ -928,7 +919,7 @@
           <t>Düzenli Havale - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>7.98TL</t>
         </is>
@@ -944,12 +935,12 @@
           <t>7,98TL</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>7,98 TL</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>7,98 TL</t>
         </is>
@@ -961,7 +952,7 @@
           <t>Düzenli Havale - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>99.71TL</t>
         </is>
@@ -977,12 +968,12 @@
           <t>99,71TL</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>99,71 TL</t>
         </is>
@@ -999,27 +990,27 @@
           <t>1050.00TL</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>2485.72TL</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>3,99TL</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>19,94TL</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>152.380,96 TL</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>19,94 TL</t>
         </is>
@@ -1036,27 +1027,27 @@
           <t>1500.00TL</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>2923.81TL</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>7,98TL</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>39,88TL</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>309.523,81 TL</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>39,88 TL</t>
         </is>
@@ -1073,27 +1064,27 @@
           <t>1900.00TL / 0.70%</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>3676.20TL / 0.70%</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>99,71TL</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>398,84TL</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>199,42</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>398,84 TL</t>
         </is>
@@ -1105,28 +1096,28 @@
           <t>Havale Gönderimi</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr"/>
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>1038.10TL / 0.58%</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>150TL</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>125TL</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>1.300 TL / 0,6 %</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr"/>
+      <c r="G20" s="15" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -1141,7 +1132,7 @@
           <t>FAST - 0-8300 TRY</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>7.97TL</t>
         </is>
@@ -1149,8 +1140,8 @@
       <c r="C23" s="11" t="inlineStr"/>
       <c r="D23" s="12" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -1158,7 +1149,7 @@
           <t>FAST - 399000+ TRY</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>380.95TL / 0.48%</t>
         </is>
@@ -1166,8 +1157,8 @@
       <c r="C24" s="11" t="inlineStr"/>
       <c r="D24" s="12" t="inlineStr"/>
       <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr"/>
-      <c r="G24" s="14" t="inlineStr"/>
+      <c r="F24" s="14" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -1175,7 +1166,7 @@
           <t>FAST - 8300-399000 TRY</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>15.96TL</t>
         </is>
@@ -1183,8 +1174,8 @@
       <c r="C25" s="11" t="inlineStr"/>
       <c r="D25" s="12" t="inlineStr"/>
       <c r="E25" s="13" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr"/>
-      <c r="G25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -1205,7 +1196,7 @@
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>2355TL</t>
         </is>
@@ -1215,8 +1206,8 @@
           <t>3270TL / 0,7%</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="14" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr"/>
+      <c r="G28" s="15" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -1224,16 +1215,16 @@
           <t>Uluslararası Transfer - 0-8300</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr"/>
+      <c r="B29" s="10" t="inlineStr"/>
       <c r="C29" s="11" t="inlineStr"/>
       <c r="D29" s="12" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>919.047,62 TL</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
@@ -1254,14 +1245,14 @@
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr"/>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>3.25%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr"/>
-      <c r="F32" s="16" t="inlineStr"/>
-      <c r="G32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr"/>
+      <c r="G32" s="15" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
@@ -1275,14 +1266,14 @@
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr"/>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>170TL</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="16" t="inlineStr"/>
-      <c r="G33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="15" t="inlineStr"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
@@ -1290,7 +1281,7 @@
           <t>Altın Transfer</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr"/>
       <c r="C34" s="11" t="inlineStr"/>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1298,8 +1289,8 @@
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr"/>
-      <c r="F34" s="16" t="inlineStr"/>
-      <c r="G34" s="14" t="inlineStr"/>
+      <c r="F34" s="14" t="inlineStr"/>
+      <c r="G34" s="15" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
@@ -1307,7 +1298,7 @@
           <t>Altın Transfer - 1-10gr</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr"/>
       <c r="C35" s="11" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr"/>
       <c r="E35" s="13" t="inlineStr">
@@ -1315,12 +1306,12 @@
           <t>57,5TL</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>60 TL</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr"/>
+      <c r="G35" s="15" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
@@ -1328,7 +1319,7 @@
           <t>Altın Transfer - 11-100gr</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr"/>
+      <c r="B36" s="10" t="inlineStr"/>
       <c r="C36" s="11" t="inlineStr"/>
       <c r="D36" s="12" t="inlineStr"/>
       <c r="E36" s="13" t="inlineStr">
@@ -1336,12 +1327,12 @@
           <t>115TL</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>120 TL</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr"/>
+      <c r="G36" s="15" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
@@ -1349,20 +1340,20 @@
           <t>Altın Transfer - 399000+</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr"/>
       <c r="C37" s="11" t="inlineStr"/>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>415TL</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>0.00018</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr"/>
+      <c r="G37" s="15" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -1383,14 +1374,14 @@
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr"/>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>4140TL</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr"/>
-      <c r="F40" s="16" t="inlineStr"/>
-      <c r="G40" s="14" t="inlineStr"/>
+      <c r="F40" s="14" t="inlineStr"/>
+      <c r="G40" s="15" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
@@ -1404,14 +1395,14 @@
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr"/>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>2610TL</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr"/>
-      <c r="F41" s="16" t="inlineStr"/>
-      <c r="G41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="15" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
@@ -1425,14 +1416,14 @@
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr"/>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>3390TL</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr"/>
-      <c r="F42" s="16" t="inlineStr"/>
-      <c r="G42" s="14" t="inlineStr"/>
+      <c r="F42" s="14" t="inlineStr"/>
+      <c r="G42" s="15" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
@@ -1440,7 +1431,7 @@
           <t>Kasa Depozito - büyük</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>28570.00TL</t>
         </is>
@@ -1448,8 +1439,8 @@
       <c r="C43" s="11" t="inlineStr"/>
       <c r="D43" s="12" t="inlineStr"/>
       <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="16" t="inlineStr"/>
-      <c r="G43" s="14" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="15" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
@@ -1457,7 +1448,7 @@
           <t>Kasa Depozito - orta</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>23805.00TL</t>
         </is>
@@ -1465,8 +1456,8 @@
       <c r="C44" s="11" t="inlineStr"/>
       <c r="D44" s="12" t="inlineStr"/>
       <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="16" t="inlineStr"/>
-      <c r="G44" s="14" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="15" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
@@ -1474,7 +1465,7 @@
           <t>Kasa Depozito - küçük</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>20950.00TL</t>
         </is>
@@ -1482,8 +1473,8 @@
       <c r="C45" s="11" t="inlineStr"/>
       <c r="D45" s="12" t="inlineStr"/>
       <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="16" t="inlineStr"/>
-      <c r="G45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="15" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
@@ -1491,7 +1482,7 @@
           <t>Yıllık Kasa Ücreti - genel</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>1469.52TL</t>
         </is>
@@ -1499,8 +1490,8 @@
       <c r="C46" s="11" t="inlineStr"/>
       <c r="D46" s="12" t="inlineStr"/>
       <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="16" t="inlineStr"/>
-      <c r="G46" s="14" t="inlineStr"/>
+      <c r="F46" s="14" t="inlineStr"/>
+      <c r="G46" s="15" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
@@ -1508,7 +1499,7 @@
           <t>Kasa Depozito - genel</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr"/>
+      <c r="B47" s="10" t="inlineStr"/>
       <c r="C47" s="11" t="inlineStr"/>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -1516,8 +1507,8 @@
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr"/>
-      <c r="F47" s="16" t="inlineStr"/>
-      <c r="G47" s="14" t="inlineStr"/>
+      <c r="F47" s="14" t="inlineStr"/>
+      <c r="G47" s="15" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
@@ -1532,7 +1523,7 @@
           <t>HGS Etiket Bedeli</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>275.00TL</t>
         </is>
@@ -1548,12 +1539,12 @@
           <t>275TL</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>275 TL</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr"/>
+      <c r="G50" s="15" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
@@ -1574,18 +1565,18 @@
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr"/>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>290TL / 1.10%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr"/>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>761,90 TL</t>
         </is>
       </c>
-      <c r="G53" s="14" t="inlineStr"/>
+      <c r="G53" s="15" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
@@ -1593,16 +1584,16 @@
           <t>Çek Defteri (Yaprak Başı) -</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr"/>
+      <c r="B54" s="10" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr"/>
       <c r="D54" s="12" t="inlineStr"/>
       <c r="E54" s="13" t="inlineStr"/>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>2.380,95 TL</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr"/>
+      <c r="G54" s="15" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
@@ -1623,18 +1614,18 @@
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr"/>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>390TL</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr"/>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="14" t="inlineStr">
         <is>
           <t>380,95 TL</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr"/>
+      <c r="G57" s="15" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
@@ -1654,27 +1645,27 @@
           <t>11.99%</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>95.24TL</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>780TL / 0.6%</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>41.904,77 TL</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G60" s="15" t="inlineStr">
         <is>
           <t>95,24 TL</t>
         </is>
@@ -1686,20 +1677,20 @@
           <t>Aynı Banka Çeki -</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr"/>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr"/>
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>438.10TL</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr"/>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>390TL / 0.2%</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr"/>
-      <c r="G61" s="14" t="inlineStr"/>
+      <c r="F61" s="14" t="inlineStr"/>
+      <c r="G61" s="15" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
@@ -1717,14 +1708,14 @@
           <t>590.48TL / 0.77%</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>350TL</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr"/>
-      <c r="F62" s="16" t="inlineStr"/>
-      <c r="G62" s="14" t="inlineStr"/>
+      <c r="F62" s="14" t="inlineStr"/>
+      <c r="G62" s="15" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
@@ -1745,18 +1736,18 @@
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr"/>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr"/>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>55.333,33 TL</t>
         </is>
       </c>
-      <c r="G65" s="14" t="inlineStr"/>
+      <c r="G65" s="15" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
@@ -1777,18 +1768,18 @@
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr"/>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr"/>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="14" t="inlineStr">
         <is>
           <t>619,05 TL</t>
         </is>
       </c>
-      <c r="G68" s="14" t="inlineStr"/>
+      <c r="G68" s="15" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
@@ -1802,18 +1793,18 @@
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr"/>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>780TL</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr"/>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>666,67 TL</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr"/>
+      <c r="G69" s="15" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
@@ -1828,7 +1819,7 @@
           <t>Senet Tahsile Alma -</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr"/>
+      <c r="B72" s="10" t="inlineStr"/>
       <c r="C72" s="11" t="inlineStr">
         <is>
           <t>600.00TL</t>
@@ -1836,12 +1827,12 @@
       </c>
       <c r="D72" s="12" t="inlineStr"/>
       <c r="E72" s="13" t="inlineStr"/>
-      <c r="F72" s="16" t="inlineStr">
+      <c r="F72" s="14" t="inlineStr">
         <is>
           <t>666,67 TL</t>
         </is>
       </c>
-      <c r="G72" s="14" t="inlineStr"/>
+      <c r="G72" s="15" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
@@ -1861,27 +1852,27 @@
           <t>5.00TL / 3.50%</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>0.00TL</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="14" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G75" s="15" t="inlineStr">
         <is>
           <t>0.5 TL</t>
         </is>
@@ -1906,18 +1897,18 @@
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr"/>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>0TL</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr"/>
-      <c r="F78" s="10" t="inlineStr">
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>2 TL / 3,5%</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr"/>
+      <c r="G78" s="15" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
@@ -1932,12 +1923,12 @@
           <t>Vergi Tahsilat</t>
         </is>
       </c>
-      <c r="B81" s="15" t="inlineStr"/>
+      <c r="B81" s="10" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr"/>
       <c r="D81" s="12" t="inlineStr"/>
       <c r="E81" s="13" t="inlineStr"/>
-      <c r="F81" s="16" t="inlineStr"/>
-      <c r="G81" s="14" t="inlineStr"/>
+      <c r="F81" s="14" t="inlineStr"/>
+      <c r="G81" s="15" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
@@ -1952,20 +1943,20 @@
           <t>Şans Oyunu Ödemeleri</t>
         </is>
       </c>
-      <c r="B84" s="15" t="inlineStr"/>
+      <c r="B84" s="10" t="inlineStr"/>
       <c r="C84" s="11" t="inlineStr"/>
-      <c r="D84" s="10" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>26TL</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr"/>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F84" s="14" t="inlineStr">
         <is>
           <t>38,10 TL</t>
         </is>
       </c>
-      <c r="G84" s="14" t="inlineStr"/>
+      <c r="G84" s="15" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
@@ -1980,16 +1971,16 @@
           <t>Telefon Ödemeleri</t>
         </is>
       </c>
-      <c r="B87" s="15" t="inlineStr"/>
+      <c r="B87" s="10" t="inlineStr"/>
       <c r="C87" s="11" t="inlineStr"/>
       <c r="D87" s="12" t="inlineStr"/>
       <c r="E87" s="13" t="inlineStr"/>
-      <c r="F87" s="16" t="inlineStr">
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>1 %</t>
         </is>
       </c>
-      <c r="G87" s="14" t="inlineStr"/>
+      <c r="G87" s="15" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
@@ -2004,7 +1995,7 @@
           <t>Özel Okul Ödeme</t>
         </is>
       </c>
-      <c r="B90" s="15" t="inlineStr"/>
+      <c r="B90" s="10" t="inlineStr"/>
       <c r="C90" s="11" t="inlineStr"/>
       <c r="D90" s="12" t="inlineStr">
         <is>
@@ -2012,8 +2003,8 @@
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr"/>
-      <c r="F90" s="16" t="inlineStr"/>
-      <c r="G90" s="14" t="inlineStr"/>
+      <c r="F90" s="14" t="inlineStr"/>
+      <c r="G90" s="15" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
@@ -2028,7 +2019,7 @@
           <t>Bakiye Sorma - Yurtiçi - ATM</t>
         </is>
       </c>
-      <c r="B93" s="15" t="inlineStr"/>
+      <c r="B93" s="10" t="inlineStr"/>
       <c r="C93" s="11" t="inlineStr"/>
       <c r="D93" s="12" t="inlineStr">
         <is>
@@ -2036,8 +2027,8 @@
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr"/>
-      <c r="F93" s="16" t="inlineStr"/>
-      <c r="G93" s="14" t="inlineStr"/>
+      <c r="F93" s="14" t="inlineStr"/>
+      <c r="G93" s="15" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
@@ -2052,20 +2043,20 @@
           <t>Bakiye Sorma - Yurtdışı - ATM</t>
         </is>
       </c>
-      <c r="B96" s="15" t="inlineStr"/>
+      <c r="B96" s="10" t="inlineStr"/>
       <c r="C96" s="11" t="inlineStr"/>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>0.45EUR</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr"/>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="14" t="inlineStr">
         <is>
           <t>0.27 TL</t>
         </is>
       </c>
-      <c r="G96" s="14" t="inlineStr"/>
+      <c r="G96" s="15" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
@@ -2080,20 +2071,20 @@
           <t>Kredi Risk Raporu</t>
         </is>
       </c>
-      <c r="B99" s="15" t="inlineStr"/>
+      <c r="B99" s="10" t="inlineStr"/>
       <c r="C99" s="11" t="inlineStr"/>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D99" s="12" t="inlineStr">
         <is>
           <t>95TL</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr"/>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="14" t="inlineStr">
         <is>
           <t>65 TL</t>
         </is>
       </c>
-      <c r="G99" s="14" t="inlineStr"/>
+      <c r="G99" s="15" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
@@ -2114,14 +2105,14 @@
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr"/>
-      <c r="D102" s="10" t="inlineStr">
+      <c r="D102" s="12" t="inlineStr">
         <is>
           <t>770TL</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr"/>
-      <c r="F102" s="16" t="inlineStr"/>
-      <c r="G102" s="14" t="inlineStr"/>
+      <c r="F102" s="14" t="inlineStr"/>
+      <c r="G102" s="15" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
@@ -2136,7 +2127,7 @@
           <t>Arşiv Araştırma</t>
         </is>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>287.62TL</t>
         </is>
@@ -2144,8 +2135,8 @@
       <c r="C105" s="11" t="inlineStr"/>
       <c r="D105" s="12" t="inlineStr"/>
       <c r="E105" s="13" t="inlineStr"/>
-      <c r="F105" s="16" t="inlineStr"/>
-      <c r="G105" s="14" t="inlineStr"/>
+      <c r="F105" s="14" t="inlineStr"/>
+      <c r="G105" s="15" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
@@ -2160,20 +2151,20 @@
           <t>Hesap Özeti</t>
         </is>
       </c>
-      <c r="B108" s="15" t="inlineStr"/>
+      <c r="B108" s="10" t="inlineStr"/>
       <c r="C108" s="11" t="inlineStr"/>
-      <c r="D108" s="10" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr">
         <is>
           <t>190TL</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr"/>
-      <c r="F108" s="10" t="inlineStr">
+      <c r="F108" s="14" t="inlineStr">
         <is>
           <t>12 TL</t>
         </is>
       </c>
-      <c r="G108" s="14" t="inlineStr"/>
+      <c r="G108" s="15" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
@@ -2194,7 +2185,7 @@
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr"/>
-      <c r="D111" s="10" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
@@ -2204,17 +2195,17 @@
           <t>550TL</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F111" s="14" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G111" s="14" t="inlineStr"/>
+      <c r="G111" s="15" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="17" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 16:24</t>
+      <c r="A113" s="16" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 17:03</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -653,7 +653,7 @@
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>4.25 %</t>
+          <t xml:space="preserve">4.25 </t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>1.00TL / 1.00%</t>
+          <t>1.00TL / 1.00</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr"/>
@@ -873,268 +873,302 @@
       <c r="F11" s="14" t="inlineStr"/>
       <c r="G11" s="15" t="inlineStr"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Havale Gönderimi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Düzenli Havale - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>3.99TL</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr"/>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>3,99TL</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>3,99TL</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>3,99 TL</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Düzenli Havale - 0-8300 TRY</t>
+          <t>Düzenli Havale - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>3.99TL</t>
+          <t>7.98TL</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr"/>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3,99TL</t>
+          <t>7,98TL</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>3,99TL</t>
+          <t>7,98TL</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>3,99 TL</t>
+          <t>7,98 TL</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>3,99 TL</t>
+          <t>7,98 TL</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Düzenli Havale - 8300-399000 TRY</t>
+          <t>Düzenli Havale - 399000+ TRY</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>7.98TL</t>
+          <t>99.71TL</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr"/>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>7,98TL</t>
+          <t>99,71TL</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>7,98TL</t>
+          <t>99,71TL</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>7,98 TL</t>
+          <t>99,71 TL</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>7,98 TL</t>
+          <t>99,71 TL</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Düzenli Havale - 399000+ TRY</t>
+          <t>Havale - 0-8300 TRY</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>99.71TL</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr"/>
+          <t>1050.00TL</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>2485.72TL</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>99,71TL</t>
+          <t>3,99TL</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>99,71TL</t>
+          <t>19,94TL</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>99,71 TL</t>
+          <t>152.380,96 TL</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>99,71 TL</t>
+          <t>19,94 TL</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Havale - 0-8300 TRY</t>
+          <t>Havale - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>1050.00TL</t>
+          <t>1500.00TL</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>2485.72TL</t>
+          <t>2923.81TL</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>3,99TL</t>
+          <t>7,98TL</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>19,94TL</t>
+          <t>39,88TL</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>152.380,96 TL</t>
+          <t>309.523,81 TL</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>19,94 TL</t>
+          <t>39,88 TL</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Havale - 8300-399000 TRY</t>
+          <t>Havale - 399000+ TRY</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>1500.00TL</t>
+          <t>1900.00TL / 0.70</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>2923.81TL</t>
+          <t>3676.20TL / 0.70</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>7,98TL</t>
+          <t>99,71TL</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>39,88TL</t>
+          <t>398,84TL</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>309.523,81 TL</t>
+          <t>199,42</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>39,88 TL</t>
+          <t>398,84 TL</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Havale - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>1900.00TL / 0.70%</t>
-        </is>
-      </c>
+          <t>Havale Gönderimi</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>3676.20TL / 0.70%</t>
+          <t>1038.10TL / 0.58</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>99,71TL</t>
+          <t>150TL</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>398,84TL</t>
+          <t>125TL</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>199,42</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>398,84 TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Havale Gönderimi</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>1038.10TL / 0.58%</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>150TL</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>125TL</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>1.300 TL / 0,6 %</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+          <t xml:space="preserve">1.300 TL / 0,6 </t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>FAST - 0-8300 TRY</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>7.97TL</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr"/>
+      <c r="D21" s="12" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>FAST - 399000+ TRY</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>380.95TL / 0.48</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr"/>
+      <c r="D22" s="12" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr"/>
+      <c r="G22" s="15" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>FAST - 0-8300 TRY</t>
+          <t>FAST - 8300-399000 TRY</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>7.97TL</t>
+          <t>15.96TL</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr"/>
@@ -1143,242 +1177,301 @@
       <c r="F23" s="14" t="inlineStr"/>
       <c r="G23" s="15" t="inlineStr"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>FAST - 399000+ TRY</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>380.95TL / 0.48%</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr"/>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="13" t="inlineStr"/>
-      <c r="F24" s="14" t="inlineStr"/>
-      <c r="G24" s="15" t="inlineStr"/>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Uluslararası Transfer</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>FAST - 8300-399000 TRY</t>
+          <t>Uluslararası Transfer</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>15.96TL</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr"/>
-      <c r="D25" s="12" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr"/>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2355TL</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>3270TL / 0,7</t>
+        </is>
+      </c>
       <c r="F25" s="14" t="inlineStr"/>
       <c r="G25" s="15" t="inlineStr"/>
     </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Uluslararası Transfer - 0-8300</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr"/>
+      <c r="D26" s="12" t="inlineStr"/>
+      <c r="E26" s="13" t="inlineStr"/>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>919.047,62 TL</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr"/>
+    </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Uluslararası Transfer</t>
+          <t>Kıymetli Maden</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Uluslararası Transfer</t>
+          <t>Altın Transfer - 0-8300</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>50.00TL</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>2355TL</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>3270TL / 0,7%</t>
-        </is>
-      </c>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="15" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Uluslararası Transfer - 0-8300</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
+          <t>Altın Transfer - 8300-399000</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>100.00TL</t>
+        </is>
+      </c>
       <c r="C29" s="11" t="inlineStr"/>
-      <c r="D29" s="12" t="inlineStr"/>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>170TL</t>
+        </is>
+      </c>
       <c r="E29" s="13" t="inlineStr"/>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>919.047,62 TL</t>
-        </is>
-      </c>
+      <c r="F29" s="14" t="inlineStr"/>
       <c r="G29" s="15" t="inlineStr"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Kıymetli Maden</t>
-        </is>
-      </c>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Altın Transfer</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr"/>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr"/>
+      <c r="G30" s="15" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Altın Transfer - 1-10gr</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr"/>
+      <c r="C31" s="11" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr"/>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>57,5TL</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>60 TL</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Altın Transfer - 0-8300</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>50.00TL</t>
-        </is>
-      </c>
+          <t>Altın Transfer - 11-100gr</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr"/>
       <c r="C32" s="11" t="inlineStr"/>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>3.25%</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr"/>
-      <c r="F32" s="14" t="inlineStr"/>
+      <c r="D32" s="12" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>115TL</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>120 TL</t>
+        </is>
+      </c>
       <c r="G32" s="15" t="inlineStr"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Altın Transfer - 8300-399000</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>100.00TL</t>
-        </is>
-      </c>
+          <t>Altın Transfer - 399000+</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr"/>
       <c r="C33" s="11" t="inlineStr"/>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>170TL</t>
+          <t>415TL</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>0.00018</t>
+        </is>
+      </c>
       <c r="G33" s="15" t="inlineStr"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Altın Transfer</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr"/>
-      <c r="C34" s="11" t="inlineStr"/>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr"/>
-      <c r="F34" s="14" t="inlineStr"/>
-      <c r="G34" s="15" t="inlineStr"/>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Kiralık Kasa</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Altın Transfer - 1-10gr</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr"/>
+          <t>Yıllık Kasa Ücreti - büyük</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>30000.00TL</t>
+        </is>
+      </c>
       <c r="C35" s="11" t="inlineStr"/>
-      <c r="D35" s="12" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>57,5TL</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>60 TL</t>
-        </is>
-      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>4140TL</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="15" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Altın Transfer - 11-100gr</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr"/>
+          <t>Yıllık Kasa Ücreti - küçük</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>22000.00TL</t>
+        </is>
+      </c>
       <c r="C36" s="11" t="inlineStr"/>
-      <c r="D36" s="12" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>115TL</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>120 TL</t>
-        </is>
-      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>2610TL</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr"/>
+      <c r="F36" s="14" t="inlineStr"/>
       <c r="G36" s="15" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Altın Transfer - 399000+</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr"/>
+          <t>Yıllık Kasa Ücreti - orta</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>25000.00TL</t>
+        </is>
+      </c>
       <c r="C37" s="11" t="inlineStr"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>415TL</t>
+          <t>3390TL</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr"/>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>0.00018</t>
-        </is>
-      </c>
+      <c r="F37" s="14" t="inlineStr"/>
       <c r="G37" s="15" t="inlineStr"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Kiralık Kasa</t>
-        </is>
-      </c>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Kasa Depozito - büyük</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>28570.00TL</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr"/>
+      <c r="D38" s="12" t="inlineStr"/>
+      <c r="E38" s="13" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
+      <c r="G38" s="15" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Kasa Depozito - orta</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>23805.00TL</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr"/>
+      <c r="E39" s="13" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="15" t="inlineStr"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - büyük</t>
+          <t>Kasa Depozito - küçük</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>30000.00TL</t>
+          <t>20950.00TL</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr"/>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>4140TL</t>
-        </is>
-      </c>
+      <c r="D40" s="12" t="inlineStr"/>
       <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr"/>
       <c r="G40" s="15" t="inlineStr"/>
@@ -1386,20 +1479,16 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - küçük</t>
+          <t>Yıllık Kasa Ücreti - genel</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>22000.00TL</t>
+          <t>1469.52TL</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr"/>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2610TL</t>
-        </is>
-      </c>
+      <c r="D41" s="12" t="inlineStr"/>
       <c r="E41" s="13" t="inlineStr"/>
       <c r="F41" s="14" t="inlineStr"/>
       <c r="G41" s="15" t="inlineStr"/>
@@ -1407,805 +1496,716 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - orta</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>25000.00TL</t>
-        </is>
-      </c>
+          <t>Kasa Depozito - genel</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr"/>
       <c r="C42" s="11" t="inlineStr"/>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>3390TL</t>
+          <t>9420TL</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr"/>
       <c r="G42" s="15" t="inlineStr"/>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Kasa Depozito - büyük</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>28570.00TL</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="15" t="inlineStr"/>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>HGS Etiket Bedeli</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Kasa Depozito - orta</t>
+          <t>HGS Etiket Bedeli</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>23805.00TL</t>
+          <t>275.00TL</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr"/>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>275TL</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>275TL</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>275 TL</t>
+        </is>
+      </c>
       <c r="G44" s="15" t="inlineStr"/>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Kasa Depozito - küçük</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>20950.00TL</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="14" t="inlineStr"/>
-      <c r="G45" s="15" t="inlineStr"/>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Yıllık Kasa Ücreti - genel</t>
+          <t>Çek Düzenleme -</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>1469.52TL</t>
+          <t>9.52TL / 0.10</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr"/>
-      <c r="D46" s="12" t="inlineStr"/>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>290TL / 1.10</t>
+        </is>
+      </c>
       <c r="E46" s="13" t="inlineStr"/>
-      <c r="F46" s="14" t="inlineStr"/>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>761,90 TL</t>
+        </is>
+      </c>
       <c r="G46" s="15" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Kasa Depozito - genel</t>
+          <t>Çek Defteri (Yaprak Başı) -</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr"/>
       <c r="C47" s="11" t="inlineStr"/>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>9420TL</t>
-        </is>
-      </c>
+      <c r="D47" s="12" t="inlineStr"/>
       <c r="E47" s="13" t="inlineStr"/>
-      <c r="F47" s="14" t="inlineStr"/>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>2.380,95 TL</t>
+        </is>
+      </c>
       <c r="G47" s="15" t="inlineStr"/>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>HGS Etiket Bedeli</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>HGS Etiket Bedeli</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>275.00TL</t>
-        </is>
-      </c>
-      <c r="C50" s="11" t="inlineStr"/>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>275TL</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>275TL</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>275 TL</t>
-        </is>
-      </c>
-      <c r="G50" s="15" t="inlineStr"/>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Çek Defteri ve Çek Düzenleme Ücreti</t>
-        </is>
-      </c>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Çek İade Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Çek İade Ücreti</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>171.43TL</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr"/>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>390TL</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>380,95 TL</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Çek Tahsilat</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>11.99</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>95.24TL</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>780TL / 0.6</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>41.904,77 TL</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>95,24 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Aynı Banka Çeki -</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr"/>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>438.10TL</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>390TL / 0.2</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr"/>
+      <c r="G52" s="15" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Çek Düzenleme -</t>
+          <t>Diğer Banka Çeki -</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>9.52TL / 0.10%</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="inlineStr"/>
+          <t>390.48TL</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>590.48TL / 0.77</t>
+        </is>
+      </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>290TL / 1.10%</t>
+          <t>350TL</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr"/>
-      <c r="F53" s="14" t="inlineStr">
-        <is>
-          <t>761,90 TL</t>
-        </is>
-      </c>
+      <c r="F53" s="14" t="inlineStr"/>
       <c r="G53" s="15" t="inlineStr"/>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>Çek Defteri (Yaprak Başı) -</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr"/>
-      <c r="C54" s="11" t="inlineStr"/>
-      <c r="D54" s="12" t="inlineStr"/>
-      <c r="E54" s="13" t="inlineStr"/>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>2.380,95 TL</t>
-        </is>
-      </c>
-      <c r="G54" s="15" t="inlineStr"/>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Senet İade Ücreti</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Senet İade Ücreti</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>495.24TL</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr"/>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr"/>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>55.333,33 TL</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>Çek İade Ücreti</t>
+          <t>Senet Protesto İşlemleri Ücreti</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>Çek İade Ücreti</t>
+          <t>Senet Protesto Kaldırma -</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>171.43TL</t>
+          <t>533.34TL</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr"/>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>390TL</t>
+          <t>780TL</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr"/>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>380,95 TL</t>
+          <t>619,05 TL</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Senet Protesto -</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr"/>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>780TL</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr"/>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Çek Tahsilat Ücreti</t>
+          <t>Senet Tahsile Alma Ücreti</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>Çek Tahsilat</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>11.99%</t>
-        </is>
-      </c>
+          <t>Senet Tahsile Alma -</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr"/>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>95.24TL</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>780TL / 0.6%</t>
-        </is>
-      </c>
+          <t>600.00TL</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>41.904,77 TL</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>95,24 TL</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>Aynı Banka Çeki -</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr"/>
-      <c r="C61" s="11" t="inlineStr">
-        <is>
-          <t>438.10TL</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr"/>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>390TL / 0.2%</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr"/>
-      <c r="G61" s="15" t="inlineStr"/>
+          <t>666,67 TL</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Fatura Ödemeleri</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>Diğer Banka Çeki -</t>
+          <t>Fatura Ödemeleri</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>390.48TL</t>
+          <t>5.00TL / 3.50</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>590.48TL / 0.77%</t>
+          <t>0.00TL</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>350TL</t>
-        </is>
-      </c>
-      <c r="E62" s="13" t="inlineStr"/>
-      <c r="F62" s="14" t="inlineStr"/>
-      <c r="G62" s="15" t="inlineStr"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>Senet İade Ücreti</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>Senet İade Ücreti</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>495.24TL</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="inlineStr"/>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr"/>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>55.333,33 TL</t>
-        </is>
-      </c>
-      <c r="G65" s="15" t="inlineStr"/>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>0.5 TL</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>0.5 TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>SGK Prim Ödemeleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>SGK Prim Ödemeleri</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>3.50TL / 3.50</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr"/>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>0TL</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr"/>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>2 TL / 3,5</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Vergi Tahsilat</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Vergi Tahsilat</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr"/>
+      <c r="C66" s="11" t="inlineStr"/>
+      <c r="D66" s="12" t="inlineStr"/>
+      <c r="E66" s="13" t="inlineStr"/>
+      <c r="F66" s="14" t="inlineStr"/>
+      <c r="G66" s="15" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>Senet Protesto İşlemleri Ücreti</t>
+          <t>Şans Oyunu Ödemeleri</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>Senet Protesto Kaldırma -</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>533.34TL</t>
-        </is>
-      </c>
+          <t>Şans Oyunu Ödemeleri</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr"/>
       <c r="C68" s="11" t="inlineStr"/>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>780TL</t>
+          <t>26TL</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>619,05 TL</t>
+          <t>38,10 TL</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr"/>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>Senet Protesto -</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr"/>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>780TL</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr"/>
-      <c r="F69" s="14" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
-      <c r="G69" s="15" t="inlineStr"/>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Telefon Ödemeleri</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Telefon Ödemeleri</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr"/>
+      <c r="C70" s="11" t="inlineStr"/>
+      <c r="D70" s="12" t="inlineStr"/>
+      <c r="E70" s="13" t="inlineStr"/>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Senet Tahsile Alma Ücreti</t>
+          <t>Özel Okul Ödeme</t>
         </is>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>Senet Tahsile Alma -</t>
+          <t>Özel Okul Ödeme</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr"/>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>600.00TL</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr"/>
+      <c r="C72" s="11" t="inlineStr"/>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>390TL</t>
+        </is>
+      </c>
       <c r="E72" s="13" t="inlineStr"/>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>666,67 TL</t>
-        </is>
-      </c>
+      <c r="F72" s="14" t="inlineStr"/>
       <c r="G72" s="15" t="inlineStr"/>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Fatura Ödemeleri</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>Fatura Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>5.00TL / 3.50%</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>0.00TL</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="inlineStr">
-        <is>
-          <t>0TL</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="inlineStr">
-        <is>
-          <t>0.5 TL</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>0.5 TL</t>
-        </is>
-      </c>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Bakiye Sorma - Yurtiçi - ATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Bakiye Sorma - Yurtiçi - ATM</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr"/>
+      <c r="C74" s="11" t="inlineStr"/>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>0.41TL</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr"/>
+      <c r="F74" s="14" t="inlineStr"/>
+      <c r="G74" s="15" t="inlineStr"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Bakiye Sorma - Yurtdışı - ATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Bakiye Sorma - Yurtdışı - ATM</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr"/>
+      <c r="C76" s="11" t="inlineStr"/>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>0.45EUR</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr"/>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>0.27 TL</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>SGK Prim Ödemeleri</t>
+          <t>Kredi Risk Raporu</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>SGK Prim Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>3.50TL / 3.50%</t>
-        </is>
-      </c>
+          <t>Kredi Risk Raporu</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr"/>
       <c r="C78" s="11" t="inlineStr"/>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>0TL</t>
+          <t>95TL</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>2 TL / 3,5%</t>
+          <t>65 TL</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr"/>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Vergi Tahsilat</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>Vergi Tahsilat</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr"/>
-      <c r="C81" s="11" t="inlineStr"/>
-      <c r="D81" s="12" t="inlineStr"/>
-      <c r="E81" s="13" t="inlineStr"/>
-      <c r="F81" s="14" t="inlineStr"/>
-      <c r="G81" s="15" t="inlineStr"/>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Referans Mektubu</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>Referans Mektubu</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>4000.00TL</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr"/>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>770TL</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr"/>
+      <c r="F80" s="14" t="inlineStr"/>
+      <c r="G80" s="15" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Arşiv Araştırma</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Arşiv Araştırma</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>287.62TL</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr"/>
+      <c r="D82" s="12" t="inlineStr"/>
+      <c r="E82" s="13" t="inlineStr"/>
+      <c r="F82" s="14" t="inlineStr"/>
+      <c r="G82" s="15" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>Şans Oyunu Ödemeleri</t>
+          <t>Hesap Özeti</t>
         </is>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>Şans Oyunu Ödemeleri</t>
+          <t>Hesap Özeti</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr"/>
       <c r="C84" s="11" t="inlineStr"/>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>26TL</t>
+          <t>190TL</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>38,10 TL</t>
+          <t>12 TL</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr"/>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Telefon Ödemeleri</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>Telefon Ödemeleri</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr"/>
-      <c r="C87" s="11" t="inlineStr"/>
-      <c r="D87" s="12" t="inlineStr"/>
-      <c r="E87" s="13" t="inlineStr"/>
-      <c r="F87" s="14" t="inlineStr">
-        <is>
-          <t>1 %</t>
-        </is>
-      </c>
-      <c r="G87" s="15" t="inlineStr"/>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>Özel Okul Ödeme</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="9" t="inlineStr">
-        <is>
-          <t>Özel Okul Ödeme</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="inlineStr"/>
-      <c r="C90" s="11" t="inlineStr"/>
-      <c r="D90" s="12" t="inlineStr">
-        <is>
-          <t>390TL</t>
-        </is>
-      </c>
-      <c r="E90" s="13" t="inlineStr"/>
-      <c r="F90" s="14" t="inlineStr"/>
-      <c r="G90" s="15" t="inlineStr"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>Bakiye Sorma - Yurtiçi - ATM</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>Bakiye Sorma - Yurtiçi - ATM</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="inlineStr"/>
-      <c r="C93" s="11" t="inlineStr"/>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>0.41TL</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr"/>
-      <c r="F93" s="14" t="inlineStr"/>
-      <c r="G93" s="15" t="inlineStr"/>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>Bakiye Sorma - Yurtdışı - ATM</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>Bakiye Sorma - Yurtdışı - ATM</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="inlineStr"/>
-      <c r="C96" s="11" t="inlineStr"/>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>0.45EUR</t>
-        </is>
-      </c>
-      <c r="E96" s="13" t="inlineStr"/>
-      <c r="F96" s="14" t="inlineStr">
-        <is>
-          <t>0.27 TL</t>
-        </is>
-      </c>
-      <c r="G96" s="15" t="inlineStr"/>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Kredi Risk Raporu</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>Kredi Risk Raporu</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr"/>
-      <c r="C99" s="11" t="inlineStr"/>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>95TL</t>
-        </is>
-      </c>
-      <c r="E99" s="13" t="inlineStr"/>
-      <c r="F99" s="14" t="inlineStr">
-        <is>
-          <t>65 TL</t>
-        </is>
-      </c>
-      <c r="G99" s="15" t="inlineStr"/>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>Referans Mektubu</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>Referans Mektubu</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t>4000.00TL</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr"/>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>770TL</t>
-        </is>
-      </c>
-      <c r="E102" s="13" t="inlineStr"/>
-      <c r="F102" s="14" t="inlineStr"/>
-      <c r="G102" s="15" t="inlineStr"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t>Arşiv Araştırma</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>Arşiv Araştırma</t>
-        </is>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>287.62TL</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr"/>
-      <c r="D105" s="12" t="inlineStr"/>
-      <c r="E105" s="13" t="inlineStr"/>
-      <c r="F105" s="14" t="inlineStr"/>
-      <c r="G105" s="15" t="inlineStr"/>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>Hesap Özeti</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>Hesap Özeti</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="inlineStr"/>
-      <c r="C108" s="11" t="inlineStr"/>
-      <c r="D108" s="12" t="inlineStr">
-        <is>
-          <t>190TL</t>
-        </is>
-      </c>
-      <c r="E108" s="13" t="inlineStr"/>
-      <c r="F108" s="14" t="inlineStr">
-        <is>
-          <t>12 TL</t>
-        </is>
-      </c>
-      <c r="G108" s="15" t="inlineStr"/>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>HGS</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>HGS Kart Ücreti</t>
         </is>
       </c>
-      <c r="B111" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>550.00TL</t>
         </is>
       </c>
-      <c r="C111" s="11" t="inlineStr"/>
-      <c r="D111" s="12" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr"/>
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="E111" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>550TL</t>
         </is>
       </c>
-      <c r="F111" s="14" t="inlineStr">
+      <c r="F86" s="14" t="inlineStr">
         <is>
           <t>500 TL</t>
         </is>
       </c>
-      <c r="G111" s="15" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="16" t="inlineStr">
-        <is>
-          <t>Son güncelleme: 14.08.2026 17:03</t>
+      <c r="G86" s="15" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>Son güncelleme: 14.08.2026 17:20</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -653,7 +653,7 @@
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.25 </t>
+          <t>3,99 TL</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr"/>
@@ -864,7 +864,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>1.00TL / 1.00</t>
+          <t>1.00TL</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>1900.00TL / 0.70</t>
+          <t>1900.00TL</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>3676.20TL / 0.70</t>
+          <t>3676.20TL</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1099,7 +1099,7 @@
       <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>1038.10TL / 0.58</t>
+          <t>1038.10TL</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.300 TL / 0,6 </t>
+          <t>1.300 TL</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>380.95TL / 0.48</t>
+          <t>380.95TL</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>15.00TL</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>3270TL / 0,7</t>
+          <t>3270TL</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr"/>
@@ -1245,11 +1245,7 @@
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+      <c r="D28" s="12" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="15" t="inlineStr"/>
@@ -1285,7 +1281,7 @@
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0TL</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
@@ -1348,11 +1344,7 @@
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>0.00018</t>
-        </is>
-      </c>
+      <c r="F33" s="14" t="inlineStr"/>
       <c r="G33" s="15" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1561,13 +1553,13 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>9.52TL / 0.10</t>
+          <t>9.52TL</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr"/>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>290TL / 1.10</t>
+          <t>290TL</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr"/>
@@ -1642,7 +1634,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>0.45EUR</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -1657,7 +1649,7 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>780TL / 0.6</t>
+          <t>780TL</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
@@ -1686,7 +1678,7 @@
       <c r="D52" s="12" t="inlineStr"/>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>390TL / 0.2</t>
+          <t>390TL</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr"/>
@@ -1705,7 +1697,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>590.48TL / 0.77</t>
+          <t>590.48TL</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -1849,7 +1841,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>5.00TL / 3.50</t>
+          <t>5.00TL</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -1893,7 +1885,7 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>3.50TL / 3.50</t>
+          <t>3.50TL</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr"/>
@@ -1905,7 +1897,7 @@
       <c r="E64" s="13" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>2 TL / 3,5</t>
+          <t>2 TL</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr"/>
@@ -1977,7 +1969,7 @@
       <c r="E70" s="13" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 </t>
+          <t>99,71 TL</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr"/>
@@ -2205,7 +2197,7 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Son güncelleme: 14.08.2026 17:20</t>
+          <t>Son güncelleme: 14.08.2026 17:38</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -2197,7 +2197,7 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Son güncelleme: 14.08.2026 17:38</t>
+          <t>Son güncelleme: 15.08.2026 09:08</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -2197,7 +2197,7 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Son güncelleme: 15.08.2026 09:08</t>
+          <t>Son güncelleme: 16.08.2026 09:11</t>
         </is>
       </c>
     </row>

--- a/komisyon_karsilastirma.xlsx
+++ b/komisyon_karsilastirma.xlsx
@@ -653,7 +653,7 @@
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>3,99 TL</t>
+          <t>4.25 %</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>15.00TL</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr"/>
@@ -1245,7 +1245,11 @@
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr"/>
-      <c r="D28" s="12" t="inlineStr"/>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="15" t="inlineStr"/>
@@ -1281,7 +1285,7 @@
       <c r="C30" s="11" t="inlineStr"/>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>0TL</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr"/>
@@ -1344,7 +1348,11 @@
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr"/>
-      <c r="F33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>0.00018</t>
+        </is>
+      </c>
       <c r="G33" s="15" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1634,7 +1642,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>0.45EUR</t>
+          <t>11.99%</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -1969,7 +1977,7 @@
       <c r="E70" s="13" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>99,71 TL</t>
+          <t>1 %</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr"/>
@@ -2197,7 +2205,7 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Son güncelleme: 16.08.2026 09:11</t>
+          <t>Son güncelleme: 17.08.2026 09:20</t>
         </is>
       </c>
     </row>
